--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Matches" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Historico" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Bajo umbral" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matches" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bajo umbral" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +68,38 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A32626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B7791F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +109,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F6EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF2E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,6 +169,39 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -511,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-08-25 16:50 · UF 40,864.55 · 0 licitaciones activas barridas</t>
+          <t>Corrida 2026-08-25 13:28 · UF 40,865.87 · 4,504 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -534,7 +609,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA(Matches!P2:P1)</f>
+        <f>COUNTA(Matches!P2:P11)</f>
         <v/>
       </c>
     </row>
@@ -545,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Matches!A2:A1,"SI")</f>
+        <f>COUNTIF(Matches!A2:A11,"SI")</f>
         <v/>
       </c>
     </row>
@@ -556,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Matches!B2:B1,"CAMBIO*")</f>
+        <f>COUNTIF(Matches!B2:B11,"CAMBIO*")</f>
         <v/>
       </c>
     </row>
@@ -567,7 +642,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Matches!C2:C1,"ALTA")</f>
+        <f>COUNTIF(Matches!C2:C11,"ALTA")</f>
         <v/>
       </c>
     </row>
@@ -578,7 +653,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Matches!E2:E1,"Mandato de SERVICIO")</f>
+        <f>COUNTIF(Matches!E2:E11,"Mandato de SERVICIO")</f>
         <v/>
       </c>
     </row>
@@ -589,7 +664,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Matches!E2:E1,"Estado BUSCA inmueble")</f>
+        <f>COUNTIF(Matches!E2:E11,"Estado BUSCA inmueble")</f>
         <v/>
       </c>
     </row>
@@ -600,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Matches!E2:E1,"Estado OFRECE inmueble")</f>
+        <f>COUNTIF(Matches!E2:E11,"Estado OFRECE inmueble")</f>
         <v/>
       </c>
     </row>
@@ -611,7 +686,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Matches!G2:G1,"Gamma")</f>
+        <f>COUNTIF(Matches!G2:G11,"Gamma")</f>
         <v/>
       </c>
     </row>
@@ -622,7 +697,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Matches!G2:G1,"Realsa Brokers")</f>
+        <f>COUNTIF(Matches!G2:G11,"Realsa Brokers")</f>
         <v/>
       </c>
     </row>
@@ -633,7 +708,7 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS(Matches!N2:N1,"&lt;=7",Matches!N2:N1,"&gt;=0")</f>
+        <f>COUNTIFS(Matches!N2:N11,"&lt;=7",Matches!N2:N11,"&gt;=0")</f>
         <v/>
       </c>
     </row>
@@ -644,7 +719,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>SUM(Matches!M2:M1)</f>
+        <f>SUM(Matches!M2:M11)</f>
         <v/>
       </c>
     </row>
@@ -669,7 +744,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Umbrales aplicados: Region Metropolitana desde UF 500.0 · resto del pais desde UF 2000.0 · minimo 1 dias al cierre. Las licitaciones sin monto publicado NO se descartan: pasan marcadas como "no publicado" (Mercado Publico permite ocultar el monto estimado). Fuente: API oficial api.mercadopublico.cl. Valor UF: mindicador.cl.</t>
+          <t>Umbrales aplicados: Region Metropolitana desde UF 500 · resto del pais desde UF 2000 · minimo 1 dias al cierre. Las licitaciones sin monto publicado NO se descartan: pasan marcadas como "no publicado" (Mercado Publico permite ocultar el monto estimado). Fuente: API oficial api.mercadopublico.cl. Valor UF: mindicador.cl.</t>
         </is>
       </c>
     </row>
@@ -691,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -830,8 +905,1026 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Mandato de SERVICIO</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TASACION COMERCIAL DE INMUEBLE</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:00</t>
+        </is>
+      </c>
+      <c r="P2" s="13" t="inlineStr">
+        <is>
+          <t>3994-21-L126</t>
+        </is>
+      </c>
+      <c r="Q2" s="14" t="inlineStr">
+        <is>
+          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14) | UNSPSC 80131800 (+40)</t>
+        </is>
+      </c>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S2" s="14" t="inlineStr">
+        <is>
+          <t>SE REQUIERE TASACION COMERCIAL DE INMUEBLE UBICADA EN EMILIO REDARD OLIVAR ALTO CORRESPONDIENTE AL LOTE A-4</t>
+        </is>
+      </c>
+      <c r="T2" s="13" t="inlineStr">
+        <is>
+          <t>FABIAN ENCINA TAPIA</t>
+        </is>
+      </c>
+      <c r="U2" s="13" t="inlineStr"/>
+      <c r="V2" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA BODEGA Y ARCHIVOS INMEDIATOS DE DISTINTAS DIRECCIONES MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Región del Biobío</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:00</t>
+        </is>
+      </c>
+      <c r="P3" s="13" t="inlineStr">
+        <is>
+          <t>2760-98-LE26</t>
+        </is>
+      </c>
+      <c r="Q3" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R3" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S3" s="14" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA BODEGA Y ARCHIVOS INMEDIATOS DE DISTINTAS DIRECCIONES MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="T3" s="13" t="inlineStr">
+        <is>
+          <t>Javier Valencia Labarca</t>
+        </is>
+      </c>
+      <c r="U3" s="13" t="inlineStr"/>
+      <c r="V3" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO INMUEBLES PARA OFICINAS</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:00</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>1743-64-LE26</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R4" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S4" s="14" t="inlineStr">
+        <is>
+          <t>La necesidad de contratar el servicio de arriendo de uno o más inmuebles que cuenten con las características descritas en las presentes Bases.</t>
+        </is>
+      </c>
+      <c r="T4" s="13" t="inlineStr">
+        <is>
+          <t>Sergio Gajardo Donoso</t>
+        </is>
+      </c>
+      <c r="U4" s="13" t="inlineStr"/>
+      <c r="V4" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA OFICINA Y RESIDENCIA</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:00</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t>2495-16-CO26</t>
+        </is>
+      </c>
+      <c r="Q5" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S5" s="14" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA OFICINAS ADMINISTRATIVAS DEL CENTRO RAYEN Y UN ESPACIO RESIDENCIAL, PARA LA RESIDENCIA TRANSITORIA, SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS.</t>
+        </is>
+      </c>
+      <c r="T5" s="13" t="inlineStr">
+        <is>
+          <t>GABRIELA OSORIO AGUILAR</t>
+        </is>
+      </c>
+      <c r="U5" s="13" t="inlineStr"/>
+      <c r="V5" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>Región del Biobío</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:30</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t>2359-13-LP26</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R6" s="14" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S6" s="14" t="inlineStr">
+        <is>
+          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
+        </is>
+      </c>
+      <c r="T6" s="13" t="inlineStr">
+        <is>
+          <t>Victor Sandoval Arias</t>
+        </is>
+      </c>
+      <c r="U6" s="13" t="inlineStr"/>
+      <c r="V6" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo - Folio 852 - DIDECO</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>CLP 144,000,000</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>3524</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>2713-157-LP26</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>objeto/desc: inmueble (+7) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R7" s="14" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S7" s="14" t="inlineStr">
+        <is>
+          <t>La Municipalidad de Aysén –en adelante Municipalidad - llama a presentar ofertas para el arrendamiento de un bien inmueble destinado al funcionamiento del Centro de las Mujeres y demás programas en convenio con SERNAMEG para el Departamento de Desarrollo Comunitario DIDECO de la Municipalidad de Aysén por un periodo de tres años</t>
+        </is>
+      </c>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t>Victor Godoy Tapia</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="inlineStr"/>
+      <c r="V7" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>CONCESIÓN DE LOCALES COMERCIALES PASEO SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>Región del Maule</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:00</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>552578-38-L126</t>
+        </is>
+      </c>
+      <c r="Q8" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: locales comerciales (+10) | transaccion/desc: arriendo (+6) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R8" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S8" s="14" t="inlineStr">
+        <is>
+          <t>Con la intención de fomentar el desarrollo productivo y la participación local de los emprendedores de la comuna de San Rafael, se abre la convocatoria para entregar en arriendo 8 locales comerciales del espacio llamado ‘‘Paseo San Rafael’’, con la finalidad de que dicha comercialización sea de productos de interés para la comunidad. Según Bases Administrativas.</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="inlineStr">
+        <is>
+          <t>Héctor Ramírez Calderón</t>
+        </is>
+      </c>
+      <c r="U8" s="13" t="inlineStr"/>
+      <c r="V8" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Región de Coquimbo</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>4295-54-LR26</t>
+        </is>
+      </c>
+      <c r="Q9" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
+        </is>
+      </c>
+      <c r="R9" s="14" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t>Dirección de Administración y Finanzas</t>
+        </is>
+      </c>
+      <c r="U9" s="13" t="inlineStr"/>
+      <c r="V9" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Región de Tarapacá</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>CLP 5,000,000,000</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>122351</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>5358-9-LR26</t>
+        </is>
+      </c>
+      <c r="Q10" s="14" t="inlineStr">
+        <is>
+          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
+        </is>
+      </c>
+      <c r="R10" s="14" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
+          <t>Jorge Bernal Peralta</t>
+        </is>
+      </c>
+      <c r="U10" s="13" t="inlineStr"/>
+      <c r="V10" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Mandato de SERVICIO</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>CLP 45,000,000</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>1101</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:00</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>867990-62-LE26</t>
+        </is>
+      </c>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14)</t>
+        </is>
+      </c>
+      <c r="R11" s="14" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>El objeto de la presente licitación es la contratación del servicio de tasación de bienes inmuebles institucionales de la Universidad de Santiago de Chile, con el propósito de actualizar la información patrimonial de la Institución mediante la determinación del valor razonable de sus activos inmobiliarios, de conformidad con las Normas Internacionales de Información Financiera IFRS, las Normas Internacionales de Valoración IVS vigentes y demás normativa técnica aplicable, de acuerdo con las condiciones que se detallan en el Título II de las presentes bases de licitación.</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>meliza cabello</t>
+        </is>
+      </c>
+      <c r="U11" s="13" t="inlineStr"/>
+      <c r="V11" s="15" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:V11"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -842,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -909,7 +2002,452 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>3994-21-L126</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TASACION COMERCIAL DE INMUEBLE</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:00</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>2760-98-LE26</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA BODEGA Y ARCHIVOS INMEDIATOS DE DISTINTAS DIRECCIONES MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:00</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>1743-64-LE26</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO INMUEBLES PARA OFICINAS</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:00</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>2495-16-CO26</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA OFICINA Y RESIDENCIA</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:00</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>2359-13-LP26</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:30</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>2713-157-LP26</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo - Folio 852 - DIDECO</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>59</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>3524</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>552578-38-L126</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>CONCESIÓN DE LOCALES COMERCIALES PASEO SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:00</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>4295-54-LR26</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>5358-9-LR26</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>122351</v>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>867990-62-LE26</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:00</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>1101</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -921,7 +2459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1000,15 +2538,193 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="18" t="n">
+        <v>62</v>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE OFICINA CORPORATIVA EN MATO GROSSO DO SUL BRASIL PARA LA CORPORACIÓN REGIONAL DE DESARROLLO DE LA REGIÓN DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>CORPORACION REGIONAL DE DESARROLLO DE LA REGION DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Región de Tarapacá</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>CLP 26,000,000</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>636</v>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>obras 100-1.000 UTM</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:00</t>
+        </is>
+      </c>
+      <c r="J2" s="19" t="inlineStr">
+        <is>
+          <t>bajo umbral de monto (Nacional, UF 636 (umbral UF 2.000))</t>
+        </is>
+      </c>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>1422259-9-CO26</t>
+        </is>
+      </c>
+      <c r="L2" s="20" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TASACION COMERCIAL INMUEBLE CALLE DOCTOR LAGARRIGUE S/N, COQUIMBO</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Región de Coquimbo</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>CLP 3,000,000</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>&lt; 100 UTM (~&lt; UF 170)</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:00</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>bajo umbral de monto (Nacional, UF 73 (umbral UF 2.000))</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>894863-37-L126</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO STAND PDI</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>CLP 20,000,000</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>489</v>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>obras 100-1.000 UTM</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:10</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>bajo umbral de monto (RM, UF 489 (umbral UF 500))</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>2981-239-CO26</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Estas licitaciones SI calzan con el servicio, pero quedan fuera por monto o plazo. Ojo: Mercado Publico publica el valor del CONTRATO (honorario), no el valor del activo — una tasacion de un edificio grande puede aparecer como UF 73. Revisar antes de descartar.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1019,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1050,7 +2766,6446 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>1012975-14-L126</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO PARA TRASLADOS DE PROFESIONALES DE SERNAMEG CONVENIO DE TRANSFERENCIA DE RECURSOS Y EJECUCION PROYECTO MULTAS VIF.VER DETALLE ANEXO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>1039-8-LP26</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE TRANSPORTE TERRESTRE</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>1057049-273-LR26</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>1057049-285-LR26</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>1057049-293-LE26</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>JCD CRIOSONDA FLEXIBLE FUS 4062026 CON COMODATO</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>1057049-296-LR26</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>1057055-68-LP26</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>1057404-82-LE26</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>1057417-183-LP26</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>1057429-28-LP26</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACTIVOS HORMONALES CON EQUIPO EN COMODATO </t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>1057429-52-LP26</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>REACTIVOS HEMATOLOGICOS VHS Y EQUIPOS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>1057429-53-LP26</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>REACTIVOS GASES EN SANGRE CON EQUIPOS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>1057472-92-LP26</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>1057480-46-LR26</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1057490-50-LR26</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Arriendo Lavado y Administración de Ropa.</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>1057490-57-LP26</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>1057490-65-LE26</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>1057492-111-LP26</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>1057501-396-LP26</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Convenio reactivos para paneles de biología con procesamiento directo desde muestra con equipo en comodato por 24 meses</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>1057501-435-LR26</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>1057501-477-LP26</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>1057503-117-LP26</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo de equipos de monitoreo</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>1057539-118-LP26</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>1057547-347-LP26</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>CONV. ARRIENDO SERV. CIRUGIA ENDOSCOPICA LUMBAR 2-</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>score 6 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>1057547-348-LE26</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION BRONCOSCOPIOS DESECHABLES CON COMODATO DE MONITOR</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>1057547-350-LR26</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>1057547-354-LP26</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>1057736-6-L126</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>1057922-23-LE26</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN EQUIPAMIENTO GENERAL PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>1057977-12-LE26</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>cierro terreno futuro H. Rio Negro Hornopiren</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>1071775-12-LE26</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>TRASLADO DE ESTUDIANTES ULAGOS SEDE CHILOÉ -PIDPID</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>score 12 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>1075963-309-LP26</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>1075963-315-LP26</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>1075963-324-LE26</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN FÁRMACOS DE PRODUCTOS OFICINALES Y MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>1078177-45-LE26</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SERVICIO DE CAMBIO DE VENTANAS PARA LA ZONA DE CARABINEROS ARAUCANÍA.</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>1080936-43-LE26</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN DEL SISTEMA DE DETECCIÓN ALARMA Y CONTROL DE INCENDIO DEL EDIFICIO DE LA ESCUELA DE INVESTIGACIONES POLICIALES</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>1110404-155-L126</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>1126920-29-LE26</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE RELOJ CONTROL P02-P01-JJ</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>1126922-33-LP26</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>1134432-67-LE26</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>1155683-16-L126</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE ARRIENDO DE 2 AIRES ACONDICIONADO INVERTER CON INSTALACIÓN POR UN PERIODO DE 12 MESES EN OFICINA CONAF ÑUBLE”</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>score 22 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>1160-14-LE26</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>score 17 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>1160-15-LE26</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>1180830-16-LR26</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>1191688-57-LP26</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>Mat. y Arriendo Bomba para Estanque Lo Blanco</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>1202333-74-LE26</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN DE INFRAESTRUCTURA STAND DE VENTA SECTOR VIP Y OBRAS CIVILES PARA FIESTA COSTUMBRISTA 2026”.</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>1202333-75-LE26</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS QUIMICOS</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>1208985-7-LP26</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN RESIDENCIA FAMILIAR ADOLESCENTE P.ARE</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>1227-3-LP26</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>SERV DE TRASLADO ESTIBA Y DESESTIBA DE MERCANCIAS</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>1261-19-LR26</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>1280-40-LE26</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DOS RODILLOS LISOS</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>1293138-13-LP26</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>1305527-3-LP26</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>1320138-2-LP26</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>PROYECTO FNDR HABILITACIÓN BODEGA EDIFICIO EX MOL</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>1336-18-LP26</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>1350-7-LE26</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>1360-8-LE26</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DEL SERVICIO DE MONITOREO DE ALARMAS PARA LAS OFICINAS DE LA DIRECCIÓN REGIÓN METROPOLITANA DEL SERVICIO DE REGISTRO CIVIL E IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>1395865-13-LE26</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO MANTENCIÓN PREVENTIVA  ÁREA ELÉCTRICA - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>1415863-2-LE26</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>1422824-1-LR26</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>1422832-9-LR26</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>1426037-25-LE26</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>RETIRO TRASLADO E INSTALACIÓN DE GALPÓN</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>1426098-12-LP26</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>1448821-14-LP26</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>1460278-46-L126</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>1469-166-L126</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>score 13 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>1499-164-LP26</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DGM MANGA COMPRESIVA DESTINADA A TERAPIA DE COMPRESIÓN NEUMÁTICA INTERMITENTE PARA PREVENCIÓN DE TROMBOSIS VENOSA PROFUNDA EN PACIENTES HOSPITALIZADOS O CON MOVILIDAD REDUCIDA CON EQUIPO EN COMODATOS </t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>1499-170-LE26</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>SAM MONITOR DESFIBRILADOR CAMILLA DE TRASLADO DE PACIENTES Y OXÍMETRO DE PULSO</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>1499-174-LE26</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>SAM SERVICIO DE DESARMADO TRASLADO Y ARMADO DE KARDEX VERTICAL MARCA GRIFOLS MODELO SYS 12012</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>1501-5-O126</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN PISCINA INFILTRACIÓN PTAS SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>1515304-164-LE26</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>ADQ DE EN ARRIENDO DE 02 VAN Y 01 SUV</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>1532-47-L126</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SISTEMAS SECTORIALES VENTANILLA UNICA</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>1549-67-LE26</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE 02 DERMATOMOS PARA PABELLÓN AMBULATORI</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>1549-70-LR26</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>1554-55-LR26</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>1605-41-LP26</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>LP-4872 Servicios de mantención general edificios</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>1605-45-LP26</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>1638-81-LE26</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>1641-219-LR26</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>1655-23-LP26</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>1658-147-LE26</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>1658-189-LP26</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>1671-30-LE26</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>1696-11-LE26</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>1697-40-LR26</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>1736-89-LE26</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO E INSTALCION DE JUEGOS</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>1851-26-LE26</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>1867-39-LP26</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de traslado terrestre de SLCs</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>1905-2-LE26</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>score 4 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>1947-130-LP26</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>1949-1-LP26</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>1979-182-LE26</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>2078-39-LE26</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>2080-248-LP26</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>SUM. KITS DIAGNOSTICO MOLECULAR CON EQ. COMODATO</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>2080-261-LP26</t>
+        </is>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>2101-136-L126</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>“ADQUISICIÓN DE MATERIALES Y ARTÍCULOS DE ESCRITORIO PARA BODEGA DE ECONOMATO Y VACUNATORIO”</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>2102-25-LE26</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION DE CONSERVACION UNIDAD DE URGENCIAS HSIL</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>2107-130-LE26</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>2107-136-LE26</t>
+        </is>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>2173-27-LE26</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>2178-17-LE26</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRANSPORTE PARA TRASLADO NOTIFICADORES</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>2184-11-LE26</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>Serv mant cubiertas edificios Jurisdicción CAPJ SM</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>2189-6-LE26</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN EQUIPOS PARA CASA DEL DONANTE SSM</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>2251-11-LE26</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo de plataforma Adobe Connect</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>2258-133-LR26</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>2258-37-LR26</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>2258-72-LE26</t>
+        </is>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>2271-65-LE26</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>2275-29-LE26</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>2282-96-LE26</t>
+        </is>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>2282-97-LR26</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>2308-72-LE26</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>2320-26-LE26</t>
+        </is>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>2322-72-LE26</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>Regularización del Activo Fijo  Inventario Munici</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>2332-98-L126</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MONTAJE DE LENTES ÓPTICOS PARA LA UNIDAD DE ATENCIÓN PRIMARIA OFTALMOLÓGICA DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>2360-67-LE26</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE RECARGA Y ARRIENDO DE CILINDROS DE OXIGENO Y AIRE MEDICINAL PARA CESFAM DE LA COMUNA</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>2366-54-LE26</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>2366-64-LE26</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>8HABILITACION DE LAVAMANOS PSR SAN MIGUEL M.147</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>2369-64-LP26</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>PP 69 Implementación bodegas resguardo de fichas</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>2385-51-LE26</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO Y MONTAJE DE GRADERÍAS FIESTA DE AYQUINA 2026</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>2402-72-CO26</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>2402-74-L126</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>2405-108-LR26</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t>score 6 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>2408-177-LE26</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE BAÑOS QUÍMICOS FIESTAS PATRIAS EN LOS ÁNGELES 2026.</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>2409-86-L126</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>2410-35-LP26</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>2410-46-LE26</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE ARTÍCULOS Y EQUIPAMIENTO PARA EL DEPARTAMENTO DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t>2410-83-LE26</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>2410-84-LE26</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>2416-22-LE26</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>2430-57-LP26</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>“HABILITACIÓN ALUMBRADO PÚBLICO ACCESO LA PORTADA COMUNA DE ANTOFAGASTA”</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>2430-69-LP26</t>
+        </is>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>2430-71-LP26</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D134" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>2445-102-LP26</t>
+        </is>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION SALAS DE ESPERA SP787</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>2452-19-L126</t>
+        </is>
+      </c>
+      <c r="B136" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D136" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>2455-46-LP26</t>
+        </is>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>2460-99-LE26</t>
+        </is>
+      </c>
+      <c r="B138" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>2483-231-LP26</t>
+        </is>
+      </c>
+      <c r="B139" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>2490-71-LR26</t>
+        </is>
+      </c>
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>“SERVICIO HABILITACIÓN Y ARRIENDO DE EQUIPAMIENTO TELEFÓNICO PARA LA MUNICIPALIDAD DE PROVIDENCIA”</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>2494-79-LP26</t>
+        </is>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>score 13 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>2546-49-LP26</t>
+        </is>
+      </c>
+      <c r="B142" s="19" t="inlineStr">
+        <is>
+          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D142" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>2548-71-LE26</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D143" s="19" t="inlineStr">
+        <is>
+          <t>score 6 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>2548-73-LE26</t>
+        </is>
+      </c>
+      <c r="B144" s="19" t="inlineStr">
+        <is>
+          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D144" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>2555-10-LP26</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>2565-14-LP26</t>
+        </is>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>2565-15-LR26</t>
+        </is>
+      </c>
+      <c r="B147" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>2581-37-LP26</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>2582-53-LR26</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
+        <is>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>2591-156-B226</t>
+        </is>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D150" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>2600-23-LE26</t>
+        </is>
+      </c>
+      <c r="B151" s="19" t="inlineStr">
+        <is>
+          <t>Const. Accesibilidad Universal Edificio Municipal</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>2600-26-LR26</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>2627-15-LE26</t>
+        </is>
+      </c>
+      <c r="B153" s="19" t="inlineStr">
+        <is>
+          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D153" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>2664-38-L126</t>
+        </is>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>2667-39-LR26</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D155" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>2697-23-LP26</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>2697-25-LR26</t>
+        </is>
+      </c>
+      <c r="B157" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>2699-32-LR26</t>
+        </is>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de Arriendo de Flota Vehicular</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="18" t="inlineStr">
+        <is>
+          <t>2702-62-LE26</t>
+        </is>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>2755-29-LE26</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>PROYECTO TRASLADO CENTRAL DE CAMARAS DE TELEVIGILA</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="18" t="inlineStr">
+        <is>
+          <t>2755-34-LE26</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D161" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>2770-109-LR26</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D162" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>2784-42-LP26</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>2788-43-LE26</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="inlineStr">
+        <is>
+          <t>2788-44-LE26</t>
+        </is>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>2793-100-CO26</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="18" t="inlineStr">
+        <is>
+          <t>2793-91-LE26</t>
+        </is>
+      </c>
+      <c r="B167" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>2793-97-LE26</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>2825-49-L126</t>
+        </is>
+      </c>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>2905-40-LP26</t>
+        </is>
+      </c>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D170" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="18" t="inlineStr">
+        <is>
+          <t>2910-23-LE26</t>
+        </is>
+      </c>
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>Suministro y comodato de equipo point of care -POC</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>2963-26-LR26</t>
+        </is>
+      </c>
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D172" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>29-64-LP26</t>
+        </is>
+      </c>
+      <c r="B173" s="19" t="inlineStr">
+        <is>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D173" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>2981-235-LP26</t>
+        </is>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D174" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>2981-236-LR26</t>
+        </is>
+      </c>
+      <c r="B175" s="19" t="inlineStr">
+        <is>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>3017-64-LE26</t>
+        </is>
+      </c>
+      <c r="B176" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE HERRAMIENTAS PARA 24 PROYECTOS PMU-E LOTA</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>3117-85-LE26</t>
+        </is>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>CAMBIO DE CUBIERTA EDIFICIO CENTRAL BIENVALP</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D177" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr">
+        <is>
+          <t>3172-46-LR26</t>
+        </is>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D178" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>3172-53-LE26</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>ESTUDIOS TERRENOS REPOSICIÓN 6°COMISARÍA COLCHANE.</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D179" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>3172-63-LE26</t>
+        </is>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D180" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>3179-33-LE26</t>
+        </is>
+      </c>
+      <c r="B181" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D181" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
+        <is>
+          <t>3210-7-L126</t>
+        </is>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D182" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>324-48-LP26</t>
+        </is>
+      </c>
+      <c r="B183" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>3263-1-LE26</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO EQUIPO CONE BEAM</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
+        <is>
+          <t>3290-7-LE26</t>
+        </is>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D185" s="19" t="inlineStr">
+        <is>
+          <t>score 6 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>3378-46-LP26</t>
+        </is>
+      </c>
+      <c r="B186" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE 02 TORRES DE LAPAROSCOPIA PARA EL DEPARTAMENTO DE PABELLONES QUIRÚRGICOS DEL HOSPITAL MILITAR DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D186" s="19" t="inlineStr">
+        <is>
+          <t>score 17 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="18" t="inlineStr">
+        <is>
+          <t>3420-5-LE26</t>
+        </is>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de Mant. y Reparación de 01 Inmueble</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D187" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>3428-16-LE26</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>Compra Materiales para reparaciones de inmuebles</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D188" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="18" t="inlineStr">
+        <is>
+          <t>3453-78-LE26</t>
+        </is>
+      </c>
+      <c r="B189" s="19" t="inlineStr">
+        <is>
+          <t>ADQ SERV. REP. Y MANT DE OFICINAS PASILLOS Y BAÑOS</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D189" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>3477-76-LE26</t>
+        </is>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D190" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
+        <is>
+          <t>3479-84-LE26</t>
+        </is>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de Arriendo  Equipo Alza Hombre</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
+        <is>
+          <t>3542-22-LE26</t>
+        </is>
+      </c>
+      <c r="B192" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D192" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>3565-58-LE26</t>
+        </is>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D193" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>3587-17-LE26</t>
+        </is>
+      </c>
+      <c r="B194" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE AGUA PURIFICADA DEPENDENCIAS DSM</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D194" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>3588-36-LP26</t>
+        </is>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO SISTEMA GESTIÓN MUNICIPALIDAD YUNGAY</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D195" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>3595-25-LE26</t>
+        </is>
+      </c>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>Cambio de pavimento edificio consistorial</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D196" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>359-98-LE26</t>
+        </is>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPO EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>359-99-CO26</t>
+        </is>
+      </c>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>ADQ ROCURONIO BROMURO CON COMODATO EQUIPO</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>3656-148-LP26</t>
+        </is>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D199" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>3668-14-LP26</t>
+        </is>
+      </c>
+      <c r="B200" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D200" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>3756-41-LE26</t>
+        </is>
+      </c>
+      <c r="B201" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN ESTACIONAMIENTO VILLA DEPARTAMENTAL PELARCO</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D201" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>3775-28-LP26</t>
+        </is>
+      </c>
+      <c r="B202" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D202" s="19" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>3798-13-LP26</t>
+        </is>
+      </c>
+      <c r="B203" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D203" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>3798-15-LP26</t>
+        </is>
+      </c>
+      <c r="B204" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>3836-32-LE26</t>
+        </is>
+      </c>
+      <c r="B205" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN MÓDULO PREFABRICADO PARA OFICINA CON WC</t>
+        </is>
+      </c>
+      <c r="C205" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D205" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="18" t="inlineStr">
+        <is>
+          <t>3843-30-LE26</t>
+        </is>
+      </c>
+      <c r="B206" s="19" t="inlineStr">
+        <is>
+          <t>PROYECTO INTEGRAL HABILITACION E IMPLEMENTACION DE PATIOS</t>
+        </is>
+      </c>
+      <c r="C206" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="18" t="inlineStr">
+        <is>
+          <t>3882-72-LP26</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="C207" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D207" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="18" t="inlineStr">
+        <is>
+          <t>3887-39-LP26</t>
+        </is>
+      </c>
+      <c r="B208" s="19" t="inlineStr">
+        <is>
+          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+        </is>
+      </c>
+      <c r="C208" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D208" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="18" t="inlineStr">
+        <is>
+          <t>3890-162-E226</t>
+        </is>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE MATERIALES DE OFICINA PARA LOS PROGRAMAS DE DISCAPACIDAD Y PSD</t>
+        </is>
+      </c>
+      <c r="C209" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
+        <is>
+          <t>3890-167-L126</t>
+        </is>
+      </c>
+      <c r="B210" s="19" t="inlineStr">
+        <is>
+          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="C210" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D210" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="18" t="inlineStr">
+        <is>
+          <t>3890-171-L126</t>
+        </is>
+      </c>
+      <c r="B211" s="19" t="inlineStr">
+        <is>
+          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
+        </is>
+      </c>
+      <c r="C211" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D211" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="18" t="inlineStr">
+        <is>
+          <t>3934-29-L126</t>
+        </is>
+      </c>
+      <c r="B212" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICION DE FARMACOS PARA USO EN ESTABLECIMIENTOS DE SALUD DEL DEPARTAMENTO DE SALUD MUNICIPAL FREIRE </t>
+        </is>
+      </c>
+      <c r="C212" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D212" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="18" t="inlineStr">
+        <is>
+          <t>3935-83-LP26</t>
+        </is>
+      </c>
+      <c r="B213" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+        </is>
+      </c>
+      <c r="C213" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="18" t="inlineStr">
+        <is>
+          <t>3948-37-LE26</t>
+        </is>
+      </c>
+      <c r="B214" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE TRANSPORTE PREESCOLAR</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="18" t="inlineStr">
+        <is>
+          <t>3981-23-LE26</t>
+        </is>
+      </c>
+      <c r="B215" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN E IMPLEMENTACIÓN DE SALA DE RESGUARDO FAMILIAR MUNICIPAL SALA CUNA</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D215" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="18" t="inlineStr">
+        <is>
+          <t>4031-14-LE26</t>
+        </is>
+      </c>
+      <c r="B216" s="19" t="inlineStr">
+        <is>
+          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D216" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="18" t="inlineStr">
+        <is>
+          <t>407-113-LP26</t>
+        </is>
+      </c>
+      <c r="B217" s="19" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+        </is>
+      </c>
+      <c r="C217" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D217" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="18" t="inlineStr">
+        <is>
+          <t>4099-22-LP26</t>
+        </is>
+      </c>
+      <c r="B218" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+        </is>
+      </c>
+      <c r="C218" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D218" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="18" t="inlineStr">
+        <is>
+          <t>4121-23-LE26</t>
+        </is>
+      </c>
+      <c r="B219" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+        </is>
+      </c>
+      <c r="C219" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="18" t="inlineStr">
+        <is>
+          <t>4168-81-LE26</t>
+        </is>
+      </c>
+      <c r="B220" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE GRADERÍAS MECANO</t>
+        </is>
+      </c>
+      <c r="C220" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="18" t="inlineStr">
+        <is>
+          <t>418-51-LP26</t>
+        </is>
+      </c>
+      <c r="B221" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="18" t="inlineStr">
+        <is>
+          <t>4202-38-LE26</t>
+        </is>
+      </c>
+      <c r="B222" s="19" t="inlineStr">
+        <is>
+          <t>Arriendo de recinto actividad Pasamos Agosto</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D222" s="19" t="inlineStr">
+        <is>
+          <t>score 17 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="18" t="inlineStr">
+        <is>
+          <t>4237-12-LR26</t>
+        </is>
+      </c>
+      <c r="B223" s="19" t="inlineStr">
+        <is>
+          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+        </is>
+      </c>
+      <c r="C223" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D223" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="18" t="inlineStr">
+        <is>
+          <t>4238-66-B226</t>
+        </is>
+      </c>
+      <c r="B224" s="19" t="inlineStr">
+        <is>
+          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="18" t="inlineStr">
+        <is>
+          <t>4284-141-L126</t>
+        </is>
+      </c>
+      <c r="B225" s="19" t="inlineStr">
+        <is>
+          <t>Contrato suministro leña para calefacción dependencias ELEAM Ayen Ruca según NUMERAL 5 B.A.G Bases administrativas Generales</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D225" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="18" t="inlineStr">
+        <is>
+          <t>4295-41-LP26</t>
+        </is>
+      </c>
+      <c r="B226" s="19" t="inlineStr">
+        <is>
+          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D226" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="18" t="inlineStr">
+        <is>
+          <t>4309-215-LP26</t>
+        </is>
+      </c>
+      <c r="B227" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="18" t="inlineStr">
+        <is>
+          <t>4328-31-B226</t>
+        </is>
+      </c>
+      <c r="B228" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
+        </is>
+      </c>
+      <c r="C228" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D228" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="18" t="inlineStr">
+        <is>
+          <t>4362-15-LP26</t>
+        </is>
+      </c>
+      <c r="B229" s="19" t="inlineStr">
+        <is>
+          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D229" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="18" t="inlineStr">
+        <is>
+          <t>4362-20-LE26</t>
+        </is>
+      </c>
+      <c r="B230" s="19" t="inlineStr">
+        <is>
+          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+        </is>
+      </c>
+      <c r="C230" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D230" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="18" t="inlineStr">
+        <is>
+          <t>438-49-LE26</t>
+        </is>
+      </c>
+      <c r="B231" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="18" t="inlineStr">
+        <is>
+          <t>4414-61-LE26</t>
+        </is>
+      </c>
+      <c r="B232" s="19" t="inlineStr">
+        <is>
+          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
+        </is>
+      </c>
+      <c r="C232" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D232" s="19" t="inlineStr">
+        <is>
+          <t>score 15 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="18" t="inlineStr">
+        <is>
+          <t>45-44-LE26</t>
+        </is>
+      </c>
+      <c r="B233" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
+        </is>
+      </c>
+      <c r="C233" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D233" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="18" t="inlineStr">
+        <is>
+          <t>4594-25-LE26</t>
+        </is>
+      </c>
+      <c r="B234" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D234" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="18" t="inlineStr">
+        <is>
+          <t>4642-91-LP26</t>
+        </is>
+      </c>
+      <c r="B235" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="18" t="inlineStr">
+        <is>
+          <t>4642-92-LP26</t>
+        </is>
+      </c>
+      <c r="B236" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
+        </is>
+      </c>
+      <c r="C236" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="18" t="inlineStr">
+        <is>
+          <t>4642-93-LP26</t>
+        </is>
+      </c>
+      <c r="B237" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
+        </is>
+      </c>
+      <c r="C237" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="18" t="inlineStr">
+        <is>
+          <t>4644-5-LP26</t>
+        </is>
+      </c>
+      <c r="B238" s="19" t="inlineStr">
+        <is>
+          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
+        </is>
+      </c>
+      <c r="C238" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="18" t="inlineStr">
+        <is>
+          <t>4778-18-LE26</t>
+        </is>
+      </c>
+      <c r="B239" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
+        </is>
+      </c>
+      <c r="C239" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D239" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="18" t="inlineStr">
+        <is>
+          <t>4829-43-L126</t>
+        </is>
+      </c>
+      <c r="B240" s="19" t="inlineStr">
+        <is>
+          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
+        </is>
+      </c>
+      <c r="C240" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D240" s="19" t="inlineStr">
+        <is>
+          <t>score 13 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="18" t="inlineStr">
+        <is>
+          <t>4850-3-LE26</t>
+        </is>
+      </c>
+      <c r="B241" s="19" t="inlineStr">
+        <is>
+          <t>Servicio para reparación edificio</t>
+        </is>
+      </c>
+      <c r="C241" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D241" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="18" t="inlineStr">
+        <is>
+          <t>4887-22-L126</t>
+        </is>
+      </c>
+      <c r="B242" s="19" t="inlineStr">
+        <is>
+          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
+        </is>
+      </c>
+      <c r="C242" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D242" s="19" t="inlineStr">
+        <is>
+          <t>score 8 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="18" t="inlineStr">
+        <is>
+          <t>4928-21-LP26</t>
+        </is>
+      </c>
+      <c r="B243" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
+        </is>
+      </c>
+      <c r="C243" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="18" t="inlineStr">
+        <is>
+          <t>4956-63-LP26</t>
+        </is>
+      </c>
+      <c r="B244" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
+        </is>
+      </c>
+      <c r="C244" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D244" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="18" t="inlineStr">
+        <is>
+          <t>4956-68-LP26</t>
+        </is>
+      </c>
+      <c r="B245" s="19" t="inlineStr">
+        <is>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+        </is>
+      </c>
+      <c r="C245" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="18" t="inlineStr">
+        <is>
+          <t>4956-71-LE26</t>
+        </is>
+      </c>
+      <c r="B246" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE SERVICIOS HIGIENICOS PARA FONDAS</t>
+        </is>
+      </c>
+      <c r="C246" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="18" t="inlineStr">
+        <is>
+          <t>4967-7-LR26</t>
+        </is>
+      </c>
+      <c r="B247" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+        </is>
+      </c>
+      <c r="C247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="18" t="inlineStr">
+        <is>
+          <t>4993-69-L126</t>
+        </is>
+      </c>
+      <c r="B248" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MOVILIZACIÓN PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE VIVIENDA CHOLCHOL 2026</t>
+        </is>
+      </c>
+      <c r="C248" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="18" t="inlineStr">
+        <is>
+          <t>5048-13-O126</t>
+        </is>
+      </c>
+      <c r="B249" s="19" t="inlineStr">
+        <is>
+          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="C249" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="18" t="inlineStr">
+        <is>
+          <t>5056-102-LP26</t>
+        </is>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+        </is>
+      </c>
+      <c r="C250" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="18" t="inlineStr">
+        <is>
+          <t>5056-98-LP26</t>
+        </is>
+      </c>
+      <c r="B251" s="19" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE CAMAS DE ATENCIÓN INTEGRAL DE PARTO</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="18" t="inlineStr">
+        <is>
+          <t>507428-94-LE26</t>
+        </is>
+      </c>
+      <c r="B252" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+        </is>
+      </c>
+      <c r="C252" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="18" t="inlineStr">
+        <is>
+          <t>5194-4-LE26</t>
+        </is>
+      </c>
+      <c r="B253" s="19" t="inlineStr">
+        <is>
+          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+        </is>
+      </c>
+      <c r="C253" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="18" t="inlineStr">
+        <is>
+          <t>5240-90-LR26</t>
+        </is>
+      </c>
+      <c r="B254" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="C254" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="18" t="inlineStr">
+        <is>
+          <t>5240-91-LE26</t>
+        </is>
+      </c>
+      <c r="B255" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
+        </is>
+      </c>
+      <c r="C255" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D255" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="18" t="inlineStr">
+        <is>
+          <t>528208-35-LP26</t>
+        </is>
+      </c>
+      <c r="B256" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+        </is>
+      </c>
+      <c r="C256" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="18" t="inlineStr">
+        <is>
+          <t>528208-38-LE26</t>
+        </is>
+      </c>
+      <c r="B257" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE PROVISIÓN CON INSTALACIÓN DE VENTANAS PARA FACHADA Y REVESTIMIENTO DE ESCALA PARA GALERÍA DE EXPOSICIÓN MEMORIAS CHILE VIETNAM CERRO NAVIA</t>
+        </is>
+      </c>
+      <c r="C257" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="18" t="inlineStr">
+        <is>
+          <t>5300-50-LP26</t>
+        </is>
+      </c>
+      <c r="B258" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
+        </is>
+      </c>
+      <c r="C258" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D258" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="18" t="inlineStr">
+        <is>
+          <t>5300-54-LP26</t>
+        </is>
+      </c>
+      <c r="B259" s="19" t="inlineStr">
+        <is>
+          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D259" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="18" t="inlineStr">
+        <is>
+          <t>5349-90-LR26</t>
+        </is>
+      </c>
+      <c r="B260" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+        </is>
+      </c>
+      <c r="C260" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="18" t="inlineStr">
+        <is>
+          <t>539119-82-CO26</t>
+        </is>
+      </c>
+      <c r="B261" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA LA REPARACIÓN DE LAS FACHADAS DEL CONJUNTO HABITACIONAL PAJARITOS ADMINISTRADO POR EL DEPARTAMENTO GESTIÓN DE VIVIENDAS Y POBLACIONES B.4 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS.</t>
+        </is>
+      </c>
+      <c r="C261" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D261" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="18" t="inlineStr">
+        <is>
+          <t>539119-85-LP26</t>
+        </is>
+      </c>
+      <c r="B262" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+        </is>
+      </c>
+      <c r="C262" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D262" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="18" t="inlineStr">
+        <is>
+          <t>539119-86-LE26</t>
+        </is>
+      </c>
+      <c r="B263" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="C263" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D263" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="18" t="inlineStr">
+        <is>
+          <t>5413-65-LE26</t>
+        </is>
+      </c>
+      <c r="B264" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="C264" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="18" t="inlineStr">
+        <is>
+          <t>5420-20-LE26</t>
+        </is>
+      </c>
+      <c r="B265" s="19" t="inlineStr">
+        <is>
+          <t>Diseño eléctrico para normalización de edificios</t>
+        </is>
+      </c>
+      <c r="C265" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D265" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="18" t="inlineStr">
+        <is>
+          <t>548874-70-LR26</t>
+        </is>
+      </c>
+      <c r="B266" s="19" t="inlineStr">
+        <is>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+        </is>
+      </c>
+      <c r="C266" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D266" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="18" t="inlineStr">
+        <is>
+          <t>5520-75-LP26</t>
+        </is>
+      </c>
+      <c r="B267" s="19" t="inlineStr">
+        <is>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
+        </is>
+      </c>
+      <c r="C267" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="18" t="inlineStr">
+        <is>
+          <t>5586-126-LE26</t>
+        </is>
+      </c>
+      <c r="B268" s="19" t="inlineStr">
+        <is>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+        </is>
+      </c>
+      <c r="C268" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D268" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="18" t="inlineStr">
+        <is>
+          <t>5626-9-LP26</t>
+        </is>
+      </c>
+      <c r="B269" s="19" t="inlineStr">
+        <is>
+          <t>EQUIPOS PARA HABILITACIÓN DE AUDITORIO Y SALAS</t>
+        </is>
+      </c>
+      <c r="C269" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="18" t="inlineStr">
+        <is>
+          <t>564953-61-LP26</t>
+        </is>
+      </c>
+      <c r="B270" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de traslado de estudiantes</t>
+        </is>
+      </c>
+      <c r="C270" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="18" t="inlineStr">
+        <is>
+          <t>5722-4-L126</t>
+        </is>
+      </c>
+      <c r="B271" s="19" t="inlineStr">
+        <is>
+          <t>Traslado Materiales a Lugar De Acopio, Obra Restauración Y Ampliación Del Museo De Arte Contemporáneo Valdivia</t>
+        </is>
+      </c>
+      <c r="C271" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D271" s="19" t="inlineStr">
+        <is>
+          <t>score 6 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="18" t="inlineStr">
+        <is>
+          <t>575924-9-E226</t>
+        </is>
+      </c>
+      <c r="B272" s="19" t="inlineStr">
+        <is>
+          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
+        </is>
+      </c>
+      <c r="C272" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="18" t="inlineStr">
+        <is>
+          <t>607-60-LE26</t>
+        </is>
+      </c>
+      <c r="B273" s="19" t="inlineStr">
+        <is>
+          <t>MEJOR. DEPENDENCIAS SERVICIO SOCIAL Y OIRS</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D273" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="18" t="inlineStr">
+        <is>
+          <t>607-67-O126</t>
+        </is>
+      </c>
+      <c r="B274" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+        </is>
+      </c>
+      <c r="C274" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="18" t="inlineStr">
+        <is>
+          <t>608-126-LR26</t>
+        </is>
+      </c>
+      <c r="B275" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C275" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="18" t="inlineStr">
+        <is>
+          <t>613-6-LE26</t>
+        </is>
+      </c>
+      <c r="B276" s="19" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO DE OFICINAS SECTOR ZÓCALO EDIFICIO SE</t>
+        </is>
+      </c>
+      <c r="C276" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D276" s="19" t="inlineStr">
+        <is>
+          <t>score 19 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="18" t="inlineStr">
+        <is>
+          <t>622-55-LE26</t>
+        </is>
+      </c>
+      <c r="B277" s="19" t="inlineStr">
+        <is>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="18" t="inlineStr">
+        <is>
+          <t>627786-14-LE26</t>
+        </is>
+      </c>
+      <c r="B278" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
+        </is>
+      </c>
+      <c r="C278" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D278" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="18" t="inlineStr">
+        <is>
+          <t>633-48-LR26</t>
+        </is>
+      </c>
+      <c r="B279" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+        </is>
+      </c>
+      <c r="C279" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="18" t="inlineStr">
+        <is>
+          <t>638-14-O126</t>
+        </is>
+      </c>
+      <c r="B280" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="C280" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D280" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="18" t="inlineStr">
+        <is>
+          <t>640-2-LP26</t>
+        </is>
+      </c>
+      <c r="B281" s="19" t="inlineStr">
+        <is>
+          <t>MANTENCIÓN Y REPARACIONES OBRAS MENORES OFICINAS</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D281" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="18" t="inlineStr">
+        <is>
+          <t>653-15-O126</t>
+        </is>
+      </c>
+      <c r="B282" s="19" t="inlineStr">
+        <is>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+        </is>
+      </c>
+      <c r="C282" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D282" s="19" t="inlineStr">
+        <is>
+          <t>score 15 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="18" t="inlineStr">
+        <is>
+          <t>673-3-LE26</t>
+        </is>
+      </c>
+      <c r="B283" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D283" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="18" t="inlineStr">
+        <is>
+          <t>673663-20-LP26</t>
+        </is>
+      </c>
+      <c r="B284" s="19" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+        </is>
+      </c>
+      <c r="C284" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D284" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="18" t="inlineStr">
+        <is>
+          <t>677-6-LP26</t>
+        </is>
+      </c>
+      <c r="B285" s="19" t="inlineStr">
+        <is>
+          <t>Elab. Diag. Plan Maestro y Plan de Gestión. Lonco</t>
+        </is>
+      </c>
+      <c r="C285" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="D285" s="19" t="inlineStr">
+        <is>
+          <t>score 23 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="18" t="inlineStr">
+        <is>
+          <t>682-3-LE26</t>
+        </is>
+      </c>
+      <c r="B286" s="19" t="inlineStr">
+        <is>
+          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
+        </is>
+      </c>
+      <c r="C286" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D286" s="19" t="inlineStr">
+        <is>
+          <t>score 10 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="18" t="inlineStr">
+        <is>
+          <t>697057-30-LE26</t>
+        </is>
+      </c>
+      <c r="B287" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="C287" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="18" t="inlineStr">
+        <is>
+          <t>707420-20-LE26</t>
+        </is>
+      </c>
+      <c r="B288" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+        </is>
+      </c>
+      <c r="C288" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D288" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="18" t="inlineStr">
+        <is>
+          <t>712307-58-O126</t>
+        </is>
+      </c>
+      <c r="B289" s="19" t="inlineStr">
+        <is>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C289" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D289" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="18" t="inlineStr">
+        <is>
+          <t>730377-1-L126</t>
+        </is>
+      </c>
+      <c r="B290" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo de dispensadores de agua purificada para 2°Juzgado de Familia de San Miguel</t>
+        </is>
+      </c>
+      <c r="C290" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="18" t="inlineStr">
+        <is>
+          <t>731159-2-L126</t>
+        </is>
+      </c>
+      <c r="B291" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
+        </is>
+      </c>
+      <c r="C291" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="18" t="inlineStr">
+        <is>
+          <t>732434-19-LE26</t>
+        </is>
+      </c>
+      <c r="B292" s="19" t="inlineStr">
+        <is>
+          <t>REPARACIÓN CUBIERTAS VARIOS RECINTOS CSC</t>
+        </is>
+      </c>
+      <c r="C292" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D292" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="18" t="inlineStr">
+        <is>
+          <t>732868-3-L126</t>
+        </is>
+      </c>
+      <c r="B293" s="19" t="inlineStr">
+        <is>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+        </is>
+      </c>
+      <c r="C293" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="18" t="inlineStr">
+        <is>
+          <t>734-47-L126</t>
+        </is>
+      </c>
+      <c r="B294" s="19" t="inlineStr">
+        <is>
+          <t>ASESORÍA TECNICA ADMINISTRATIVA DE LA SECCIÓN DE EQUIPAMIENTO PARA EL SUBDEPARTAMENTO DE RECURSOS FISICOS E INVERSIONES DEL SERVICIO DE SALUD AYSÉN</t>
+        </is>
+      </c>
+      <c r="C294" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D294" s="19" t="inlineStr">
+        <is>
+          <t>score 3 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="18" t="inlineStr">
+        <is>
+          <t>735949-1-LE26</t>
+        </is>
+      </c>
+      <c r="B295" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIOS PARA EL DEPARTAMENTO DE DESARROLLO RURAL</t>
+        </is>
+      </c>
+      <c r="C295" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D295" s="19" t="inlineStr">
+        <is>
+          <t>score 7 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="18" t="inlineStr">
+        <is>
+          <t>739231-17-LP26</t>
+        </is>
+      </c>
+      <c r="B296" s="19" t="inlineStr">
+        <is>
+          <t>Habilitación Area de Juegos en Sector Costanera de Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C296" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="18" t="inlineStr">
+        <is>
+          <t>742-7-L126</t>
+        </is>
+      </c>
+      <c r="B297" s="19" t="inlineStr">
+        <is>
+          <t>Mantención Oficina ubicada en Las Lengas N°1450 de la ciudad de Coyhaique de INDAP, región de Aysén</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D297" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="18" t="inlineStr">
+        <is>
+          <t>748201-10-LE26</t>
+        </is>
+      </c>
+      <c r="B298" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+        </is>
+      </c>
+      <c r="C298" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="18" t="inlineStr">
+        <is>
+          <t>748201-9-LP26</t>
+        </is>
+      </c>
+      <c r="B299" s="19" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+        </is>
+      </c>
+      <c r="C299" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="18" t="inlineStr">
+        <is>
+          <t>750998-56-LE26</t>
+        </is>
+      </c>
+      <c r="B300" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACIÓN SALAS CINU</t>
+        </is>
+      </c>
+      <c r="C300" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D300" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="18" t="inlineStr">
+        <is>
+          <t>761391-126-LE26</t>
+        </is>
+      </c>
+      <c r="B301" s="19" t="inlineStr">
+        <is>
+          <t>BAEBGUBECG148SVC TRASLADO DE PERSONAL PARADA MILITAR 2026.</t>
+        </is>
+      </c>
+      <c r="C301" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="18" t="inlineStr">
+        <is>
+          <t>768-19-LR26</t>
+        </is>
+      </c>
+      <c r="B302" s="19" t="inlineStr">
+        <is>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+        </is>
+      </c>
+      <c r="C302" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D302" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="18" t="inlineStr">
+        <is>
+          <t>824-3-LE26</t>
+        </is>
+      </c>
+      <c r="B303" s="19" t="inlineStr">
+        <is>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+        </is>
+      </c>
+      <c r="C303" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D303" s="19" t="inlineStr">
+        <is>
+          <t>score 19 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="18" t="inlineStr">
+        <is>
+          <t>829-2-O126</t>
+        </is>
+      </c>
+      <c r="B304" s="19" t="inlineStr">
+        <is>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+        </is>
+      </c>
+      <c r="C304" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D304" s="19" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="18" t="inlineStr">
+        <is>
+          <t>837-88-LP26</t>
+        </is>
+      </c>
+      <c r="B305" s="19" t="inlineStr">
+        <is>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D305" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="18" t="inlineStr">
+        <is>
+          <t>838100-6-L126</t>
+        </is>
+      </c>
+      <c r="B306" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+        </is>
+      </c>
+      <c r="C306" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="18" t="inlineStr">
+        <is>
+          <t>845-17-LR26</t>
+        </is>
+      </c>
+      <c r="B307" s="19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+        </is>
+      </c>
+      <c r="C307" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D307" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="18" t="inlineStr">
+        <is>
+          <t>886954-222-LR26</t>
+        </is>
+      </c>
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+        </is>
+      </c>
+      <c r="C308" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="18" t="inlineStr">
+        <is>
+          <t>886954-230-LP26</t>
+        </is>
+      </c>
+      <c r="B309" s="19" t="inlineStr">
+        <is>
+          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
+        </is>
+      </c>
+      <c r="C309" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="18" t="inlineStr">
+        <is>
+          <t>886954-262-LP26</t>
+        </is>
+      </c>
+      <c r="B310" s="19" t="inlineStr">
+        <is>
+          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+        </is>
+      </c>
+      <c r="C310" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="18" t="inlineStr">
+        <is>
+          <t>886954-297-LP26</t>
+        </is>
+      </c>
+      <c r="B311" s="19" t="inlineStr">
+        <is>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+        </is>
+      </c>
+      <c r="C311" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="18" t="inlineStr">
+        <is>
+          <t>899-31-L126</t>
+        </is>
+      </c>
+      <c r="B312" s="19" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de argollas de anclaje para la techumbre del Hospital San José de Casablanca</t>
+        </is>
+      </c>
+      <c r="C312" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D312" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="18" t="inlineStr">
+        <is>
+          <t>930-20-LE26</t>
+        </is>
+      </c>
+      <c r="B313" s="19" t="inlineStr">
+        <is>
+          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
+        </is>
+      </c>
+      <c r="C313" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D313" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="18" t="inlineStr">
+        <is>
+          <t>932-24-LE26</t>
+        </is>
+      </c>
+      <c r="B314" s="19" t="inlineStr">
+        <is>
+          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
+        </is>
+      </c>
+      <c r="C314" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D314" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="18" t="inlineStr">
+        <is>
+          <t>956-57-L126</t>
+        </is>
+      </c>
+      <c r="B315" s="19" t="inlineStr">
+        <is>
+          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+        </is>
+      </c>
+      <c r="C315" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D315" s="19" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="18" t="inlineStr">
+        <is>
+          <t>956-58-LE26</t>
+        </is>
+      </c>
+      <c r="B316" s="19" t="inlineStr">
+        <is>
+          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+        </is>
+      </c>
+      <c r="C316" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D316" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="18" t="inlineStr">
+        <is>
+          <t>957865-6-LE26</t>
+        </is>
+      </c>
+      <c r="B317" s="19" t="inlineStr">
+        <is>
+          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+        </is>
+      </c>
+      <c r="C317" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="18" t="inlineStr">
+        <is>
+          <t>975-12-O126</t>
+        </is>
+      </c>
+      <c r="B318" s="19" t="inlineStr">
+        <is>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+        </is>
+      </c>
+      <c r="C318" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D318" s="19" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="18" t="inlineStr">
+        <is>
+          <t>976-14-LP26</t>
+        </is>
+      </c>
+      <c r="B319" s="19" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+        </is>
+      </c>
+      <c r="C319" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="18" t="inlineStr">
+        <is>
+          <t>979-49-L126</t>
+        </is>
+      </c>
+      <c r="B320" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+        </is>
+      </c>
+      <c r="C320" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D320" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="18" t="inlineStr">
+        <is>
+          <t>986278-16-LE26</t>
+        </is>
+      </c>
+      <c r="B321" s="19" t="inlineStr">
+        <is>
+          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
+        </is>
+      </c>
+      <c r="C321" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D321" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="18" t="inlineStr">
+        <is>
+          <t>993-42-LE26</t>
+        </is>
+      </c>
+      <c r="B322" s="19" t="inlineStr">
+        <is>
+          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+        </is>
+      </c>
+      <c r="C322" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D322" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="18" t="inlineStr">
+        <is>
+          <t>997-32-LP26</t>
+        </is>
+      </c>
+      <c r="B323" s="19" t="inlineStr">
+        <is>
+          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" s="19" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matches" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bajo umbral" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matches" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Historico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bajo umbral" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$11</definedName>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-08-25 13:28 · UF 40,865.87 · 4,504 licitaciones activas barridas</t>
+          <t>Corrida 2026-08-25 17:38 · UF 40,865.87 · 4,508 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Umbrales aplicados: Region Metropolitana desde UF 500 · resto del pais desde UF 2000 · minimo 1 dias al cierre. Las licitaciones sin monto publicado NO se descartan: pasan marcadas como "no publicado" (Mercado Publico permite ocultar el monto estimado). Fuente: API oficial api.mercadopublico.cl. Valor UF: mindicador.cl.</t>
+          <t>Umbrales aplicados: Region Metropolitana desde UF 500.0 · resto del pais desde UF 2000.0 · minimo 1 dias al cierre. Las licitaciones sin monto publicado NO se descartan: pasan marcadas como "no publicado" (Mercado Publico permite ocultar el monto estimado). Fuente: API oficial api.mercadopublico.cl. Valor UF: mindicador.cl.</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D323"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3489,72 +3489,72 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>1110404-155-L126</t>
+          <t>1109692-8-LE26</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
+          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>1126920-29-LE26</t>
+          <t>1110404-155-L126</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE RELOJ CONTROL P02-P01-JJ</t>
+          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>1126922-33-LP26</t>
+          <t>1126920-29-LE26</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO DE ARRIENDO DE RELOJ CONTROL P02-P01-JJ</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>1134432-67-LE26</t>
+          <t>1126922-33-LP26</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
+          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
@@ -3569,76 +3569,76 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>1155683-16-L126</t>
+          <t>1134432-67-LE26</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>“SERVICIO DE ARRIENDO DE 2 AIRES ACONDICIONADO INVERTER CON INSTALACIÓN POR UN PERIODO DE 12 MESES EN OFICINA CONAF ÑUBLE”</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>1160-14-LE26</t>
+          <t>1155683-16-L126</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
+          <t>“SERVICIO DE ARRIENDO DE 2 AIRES ACONDICIONADO INVERTER CON INSTALACIÓN POR UN PERIODO DE 12 MESES EN OFICINA CONAF ÑUBLE”</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>1160-15-LE26</t>
+          <t>1160-14-LE26</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
+          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>1180830-16-LR26</t>
+          <t>1160-15-LE26</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D45" s="19" t="inlineStr">
         <is>
@@ -3649,72 +3649,72 @@
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>1191688-57-LP26</t>
+          <t>1180830-16-LR26</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>Mat. y Arriendo Bomba para Estanque Lo Blanco</t>
+          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>1202333-74-LE26</t>
+          <t>1191688-57-LP26</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE INFRAESTRUCTURA STAND DE VENTA SECTOR VIP Y OBRAS CIVILES PARA FIESTA COSTUMBRISTA 2026”.</t>
+          <t>Mat. y Arriendo Bomba para Estanque Lo Blanco</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>1202333-75-LE26</t>
+          <t>1202333-74-LE26</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS QUIMICOS</t>
+          <t>HABILITACIÓN DE INFRAESTRUCTURA STAND DE VENTA SECTOR VIP Y OBRAS CIVILES PARA FIESTA COSTUMBRISTA 2026”.</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>1208985-7-LP26</t>
+          <t>1202333-75-LE26</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN RESIDENCIA FAMILIAR ADOLESCENTE P.ARE</t>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
@@ -3729,52 +3729,52 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>1227-3-LP26</t>
+          <t>1208985-7-LP26</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>SERV DE TRASLADO ESTIBA Y DESESTIBA DE MERCANCIAS</t>
+          <t>HABILITACIÓN RESIDENCIA FAMILIAR ADOLESCENTE P.ARE</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1227-3-LP26</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t>SERV DE TRASLADO ESTIBA Y DESESTIBA DE MERCANCIAS</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>1280-40-LE26</t>
+          <t>1261-19-LR26</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS RODILLOS LISOS</t>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
@@ -3789,112 +3789,112 @@
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1280-40-LE26</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t>ARRIENDO DOS RODILLOS LISOS</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1293138-13-LP26</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>1320138-2-LP26</t>
+          <t>1305527-3-LP26</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>PROYECTO FNDR HABILITACIÓN BODEGA EDIFICIO EX MOL</t>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>1336-18-LP26</t>
+          <t>1320138-2-LP26</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
+          <t>PROYECTO FNDR HABILITACIÓN BODEGA EDIFICIO EX MOL</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>1350-7-LE26</t>
+          <t>1336-18-LP26</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
+          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>1360-8-LE26</t>
+          <t>1350-7-LE26</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MONITOREO DE ALARMAS PARA LAS OFICINAS DE LA DIRECCIÓN REGIÓN METROPOLITANA DEL SERVICIO DE REGISTRO CIVIL E IDENTIFICACIÓN</t>
+          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
@@ -3909,12 +3909,12 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>1395865-13-LE26</t>
+          <t>1360-8-LE26</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN PREVENTIVA  ÁREA ELÉCTRICA - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MONITOREO DE ALARMAS PARA LAS OFICINAS DE LA DIRECCIÓN REGIÓN METROPOLITANA DEL SERVICIO DE REGISTRO CIVIL E IDENTIFICACIÓN</t>
         </is>
       </c>
       <c r="C59" s="18" t="n">
@@ -3929,16 +3929,16 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>1415863-2-LE26</t>
+          <t>1395865-13-LE26</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO MANTENCIÓN PREVENTIVA  ÁREA ELÉCTRICA - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
@@ -3949,32 +3949,32 @@
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1415863-2-LE26</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C62" s="18" t="n">
@@ -3989,132 +3989,132 @@
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>1426037-25-LE26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>RETIRO TRASLADO E INSTALACIÓN DE GALPÓN</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>1426098-12-LP26</t>
+          <t>1426037-25-LE26</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
+          <t>RETIRO TRASLADO E INSTALACIÓN DE GALPÓN</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1426098-12-LP26</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>1460278-46-L126</t>
+          <t>1448821-14-LP26</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>1469-166-L126</t>
+          <t>1460278-46-L126</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
+          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>1499-164-LP26</t>
+          <t>1469-166-L126</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DGM MANGA COMPRESIVA DESTINADA A TERAPIA DE COMPRESIÓN NEUMÁTICA INTERMITENTE PARA PREVENCIÓN DE TROMBOSIS VENOSA PROFUNDA EN PACIENTES HOSPITALIZADOS O CON MOVILIDAD REDUCIDA CON EQUIPO EN COMODATOS </t>
+          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>1499-170-LE26</t>
+          <t>1499-164-LP26</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>SAM MONITOR DESFIBRILADOR CAMILLA DE TRASLADO DE PACIENTES Y OXÍMETRO DE PULSO</t>
+          <t xml:space="preserve">DGM MANGA COMPRESIVA DESTINADA A TERAPIA DE COMPRESIÓN NEUMÁTICA INTERMITENTE PARA PREVENCIÓN DE TROMBOSIS VENOSA PROFUNDA EN PACIENTES HOSPITALIZADOS O CON MOVILIDAD REDUCIDA CON EQUIPO EN COMODATOS </t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
@@ -4129,12 +4129,12 @@
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>1499-174-LE26</t>
+          <t>1499-170-LE26</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>SAM SERVICIO DE DESARMADO TRASLADO Y ARMADO DE KARDEX VERTICAL MARCA GRIFOLS MODELO SYS 12012</t>
+          <t>SAM MONITOR DESFIBRILADOR CAMILLA DE TRASLADO DE PACIENTES Y OXÍMETRO DE PULSO</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
@@ -4149,12 +4149,12 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>1501-5-O126</t>
+          <t>1499-174-LE26</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PISCINA INFILTRACIÓN PTAS SAN PEDRO DE ATACAMA</t>
+          <t>SAM SERVICIO DE DESARMADO TRASLADO Y ARMADO DE KARDEX VERTICAL MARCA GRIFOLS MODELO SYS 12012</t>
         </is>
       </c>
       <c r="C71" s="18" t="n">
@@ -4169,52 +4169,52 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>1515304-164-LE26</t>
+          <t>1501-5-O126</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>ADQ DE EN ARRIENDO DE 02 VAN Y 01 SUV</t>
+          <t>HABILITACIÓN PISCINA INFILTRACIÓN PTAS SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>1532-47-L126</t>
+          <t>1515304-164-LE26</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SISTEMAS SECTORIALES VENTANILLA UNICA</t>
+          <t>ADQ DE EN ARRIENDO DE 02 VAN Y 01 SUV</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>1549-67-LE26</t>
+          <t>1532-47-L126</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 02 DERMATOMOS PARA PABELLÓN AMBULATORI</t>
+          <t>SERVICIO DE SISTEMAS SECTORIALES VENTANILLA UNICA</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
@@ -4229,12 +4229,12 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1549-67-LE26</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>ARRIENDO DE 02 DERMATOMOS PARA PABELLÓN AMBULATORI</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
@@ -4249,12 +4249,12 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
@@ -4269,92 +4269,92 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1554-55-LR26</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>1605-45-LP26</t>
+          <t>1605-41-LP26</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+          <t>LP-4872 Servicios de mantención general edificios</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D78" s="19" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>1638-81-LE26</t>
+          <t>1605-45-LP26</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
+          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>1641-219-LR26</t>
+          <t>1638-81-LE26</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>1655-23-LP26</t>
+          <t>1641-219-LR26</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C81" s="18" t="n">
@@ -4369,36 +4369,36 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>1658-147-LE26</t>
+          <t>1655-23-LP26</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
+          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D82" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>1658-147-LE26</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
@@ -4409,16 +4409,16 @@
     <row r="84">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>1671-30-LE26</t>
+          <t>1658-189-LP26</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D84" s="19" t="inlineStr">
         <is>
@@ -4429,32 +4429,32 @@
     <row r="85">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>1696-11-LE26</t>
+          <t>1671-30-LE26</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
+          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1696-11-LE26</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
@@ -4469,12 +4469,12 @@
     <row r="87">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>1736-89-LE26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO E INSTALCION DE JUEGOS</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C87" s="18" t="n">
@@ -4489,12 +4489,12 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>1851-26-LE26</t>
+          <t>1736-89-LE26</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
+          <t>SERVICIO DE ARRIENDO E INSTALCION DE JUEGOS</t>
         </is>
       </c>
       <c r="C88" s="18" t="n">
@@ -4509,12 +4509,12 @@
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>1867-39-LP26</t>
+          <t>1851-26-LE26</t>
         </is>
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>Servicio de traslado terrestre de SLCs</t>
+          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
         </is>
       </c>
       <c r="C89" s="18" t="n">
@@ -4529,92 +4529,92 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>1905-2-LE26</t>
+          <t>1867-39-LP26</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
+          <t>Servicio de traslado terrestre de SLCs</t>
         </is>
       </c>
       <c r="C90" s="18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D90" s="19" t="inlineStr">
         <is>
-          <t>score 4 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>1947-130-LP26</t>
+          <t>1905-2-LE26</t>
         </is>
       </c>
       <c r="B91" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
         </is>
       </c>
       <c r="C91" s="18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 4 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>1949-1-LP26</t>
+          <t>1947-130-LP26</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
         </is>
       </c>
       <c r="C92" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D92" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>1979-182-LE26</t>
+          <t>1949-1-LP26</t>
         </is>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
-          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
         </is>
       </c>
       <c r="C93" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>2078-39-LE26</t>
+          <t>1979-182-LE26</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
+          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
         </is>
       </c>
       <c r="C94" s="18" t="n">
@@ -4629,12 +4629,12 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>2080-248-LP26</t>
+          <t>2078-39-LE26</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>SUM. KITS DIAGNOSTICO MOLECULAR CON EQ. COMODATO</t>
+          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
         </is>
       </c>
       <c r="C95" s="18" t="n">
@@ -4649,12 +4649,12 @@
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>2080-261-LP26</t>
+          <t>2080-248-LP26</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
+          <t>SUM. KITS DIAGNOSTICO MOLECULAR CON EQ. COMODATO</t>
         </is>
       </c>
       <c r="C96" s="18" t="n">
@@ -4669,52 +4669,52 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>2101-136-L126</t>
+          <t>2080-261-LP26</t>
         </is>
       </c>
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES Y ARTÍCULOS DE ESCRITORIO PARA BODEGA DE ECONOMATO Y VACUNATORIO”</t>
+          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C97" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>2102-25-LE26</t>
+          <t>2101-136-L126</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION DE CONSERVACION UNIDAD DE URGENCIAS HSIL</t>
+          <t>“ADQUISICIÓN DE MATERIALES Y ARTÍCULOS DE ESCRITORIO PARA BODEGA DE ECONOMATO Y VACUNATORIO”</t>
         </is>
       </c>
       <c r="C98" s="18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D98" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>2107-130-LE26</t>
+          <t>2102-25-LE26</t>
         </is>
       </c>
       <c r="B99" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>HABILITACION DE CONSERVACION UNIDAD DE URGENCIAS HSIL</t>
         </is>
       </c>
       <c r="C99" s="18" t="n">
@@ -4729,12 +4729,12 @@
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>2107-136-LE26</t>
+          <t>2107-130-LE26</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="C100" s="18" t="n">
@@ -4749,76 +4749,76 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>2173-27-LE26</t>
+          <t>2107-136-LE26</t>
         </is>
       </c>
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="C101" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>2178-17-LE26</t>
+          <t>2173-27-LE26</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE PARA TRASLADO NOTIFICADORES</t>
+          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
         </is>
       </c>
       <c r="C102" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D102" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>2184-11-LE26</t>
+          <t>2178-17-LE26</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
         <is>
-          <t>Serv mant cubiertas edificios Jurisdicción CAPJ SM</t>
+          <t>SERVICIO DE TRANSPORTE PARA TRASLADO NOTIFICADORES</t>
         </is>
       </c>
       <c r="C103" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>2189-6-LE26</t>
+          <t>2184-11-LE26</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPOS PARA CASA DEL DONANTE SSM</t>
+          <t>Serv mant cubiertas edificios Jurisdicción CAPJ SM</t>
         </is>
       </c>
       <c r="C104" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D104" s="19" t="inlineStr">
         <is>
@@ -4829,32 +4829,32 @@
     <row r="105">
       <c r="A105" s="18" t="inlineStr">
         <is>
-          <t>2251-11-LE26</t>
+          <t>2189-6-LE26</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
         <is>
-          <t>Servicio de arriendo de plataforma Adobe Connect</t>
+          <t>ADQUISICIÓN EQUIPOS PARA CASA DEL DONANTE SSM</t>
         </is>
       </c>
       <c r="C105" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="inlineStr">
         <is>
-          <t>2258-133-LR26</t>
+          <t>2251-11-LE26</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>Servicio de arriendo de plataforma Adobe Connect</t>
         </is>
       </c>
       <c r="C106" s="18" t="n">
@@ -4869,12 +4869,12 @@
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2258-133-LR26</t>
         </is>
       </c>
       <c r="B107" s="19" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C107" s="18" t="n">
@@ -4889,12 +4889,12 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>2258-72-LE26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C108" s="18" t="n">
@@ -4909,12 +4909,12 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>2271-65-LE26</t>
+          <t>2258-72-LE26</t>
         </is>
       </c>
       <c r="B109" s="19" t="inlineStr">
         <is>
-          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C109" s="18" t="n">
@@ -4929,52 +4929,52 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2271-65-LE26</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
         </is>
       </c>
       <c r="C110" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D110" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>2282-96-LE26</t>
+          <t>2275-29-LE26</t>
         </is>
       </c>
       <c r="B111" s="19" t="inlineStr">
         <is>
-          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
         </is>
       </c>
       <c r="C111" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2282-96-LE26</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
         </is>
       </c>
       <c r="C112" s="18" t="n">
@@ -4989,52 +4989,52 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>2308-72-LE26</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B113" s="19" t="inlineStr">
         <is>
-          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C113" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>2320-26-LE26</t>
+          <t>2308-72-LE26</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
+          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
         </is>
       </c>
       <c r="C114" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D114" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>2322-72-LE26</t>
+          <t>2320-26-LE26</t>
         </is>
       </c>
       <c r="B115" s="19" t="inlineStr">
         <is>
-          <t>Regularización del Activo Fijo  Inventario Munici</t>
+          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
         </is>
       </c>
       <c r="C115" s="18" t="n">
@@ -5049,52 +5049,52 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>2332-98-L126</t>
+          <t>2322-72-LE26</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MONTAJE DE LENTES ÓPTICOS PARA LA UNIDAD DE ATENCIÓN PRIMARIA OFTALMOLÓGICA DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>Regularización del Activo Fijo  Inventario Munici</t>
         </is>
       </c>
       <c r="C116" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D116" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>2360-67-LE26</t>
+          <t>2332-98-L126</t>
         </is>
       </c>
       <c r="B117" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE RECARGA Y ARRIENDO DE CILINDROS DE OXIGENO Y AIRE MEDICINAL PARA CESFAM DE LA COMUNA</t>
+          <t>SERVICIO DE MONTAJE DE LENTES ÓPTICOS PARA LA UNIDAD DE ATENCIÓN PRIMARIA OFTALMOLÓGICA DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C117" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>2366-54-LE26</t>
+          <t>2360-67-LE26</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+          <t>SERVICIO DE RECARGA Y ARRIENDO DE CILINDROS DE OXIGENO Y AIRE MEDICINAL PARA CESFAM DE LA COMUNA</t>
         </is>
       </c>
       <c r="C118" s="18" t="n">
@@ -5109,12 +5109,12 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>2366-64-LE26</t>
+          <t>2366-54-LE26</t>
         </is>
       </c>
       <c r="B119" s="19" t="inlineStr">
         <is>
-          <t>8HABILITACION DE LAVAMANOS PSR SAN MIGUEL M.147</t>
+          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
         </is>
       </c>
       <c r="C119" s="18" t="n">
@@ -5129,132 +5129,132 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>2369-64-LP26</t>
+          <t>2366-64-LE26</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
         <is>
-          <t>PP 69 Implementación bodegas resguardo de fichas</t>
+          <t>8HABILITACION DE LAVAMANOS PSR SAN MIGUEL M.147</t>
         </is>
       </c>
       <c r="C120" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D120" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>2385-51-LE26</t>
+          <t>2369-64-LP26</t>
         </is>
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO Y MONTAJE DE GRADERÍAS FIESTA DE AYQUINA 2026</t>
+          <t>PP 69 Implementación bodegas resguardo de fichas</t>
         </is>
       </c>
       <c r="C121" s="18" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>2402-72-CO26</t>
+          <t>2385-51-LE26</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
         <is>
-          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
+          <t>SERVICIO DE ARRIENDO Y MONTAJE DE GRADERÍAS FIESTA DE AYQUINA 2026</t>
         </is>
       </c>
       <c r="C122" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D122" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>2402-74-L126</t>
+          <t>2402-72-CO26</t>
         </is>
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
+          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
         </is>
       </c>
       <c r="C123" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D123" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2402-74-L126</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
         </is>
       </c>
       <c r="C124" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D124" s="19" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>2408-177-LE26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B125" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE BAÑOS QUÍMICOS FIESTAS PATRIAS EN LOS ÁNGELES 2026.</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C125" s="18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>2409-86-L126</t>
+          <t>2408-177-LE26</t>
         </is>
       </c>
       <c r="B126" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
+          <t>ARRIENDO DE BAÑOS QUÍMICOS FIESTAS PATRIAS EN LOS ÁNGELES 2026.</t>
         </is>
       </c>
       <c r="C126" s="18" t="n">
@@ -5269,36 +5269,36 @@
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>2410-35-LP26</t>
+          <t>2409-86-L126</t>
         </is>
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
+          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
         </is>
       </c>
       <c r="C127" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>2410-46-LE26</t>
+          <t>2410-35-LP26</t>
         </is>
       </c>
       <c r="B128" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS Y EQUIPAMIENTO PARA EL DEPARTAMENTO DE SEGURIDAD</t>
+          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
         </is>
       </c>
       <c r="C128" s="18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D128" s="19" t="inlineStr">
         <is>
@@ -5309,16 +5309,16 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>2410-83-LE26</t>
+          <t>2410-46-LE26</t>
         </is>
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS Y EQUIPAMIENTO PARA EL DEPARTAMENTO DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C129" s="18" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D129" s="19" t="inlineStr">
         <is>
@@ -5329,196 +5329,196 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>2410-84-LE26</t>
+          <t>2410-83-LE26</t>
         </is>
       </c>
       <c r="B130" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
         </is>
       </c>
       <c r="C130" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D130" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="18" t="inlineStr">
         <is>
-          <t>2416-22-LE26</t>
+          <t>2410-84-LE26</t>
         </is>
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C131" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="18" t="inlineStr">
         <is>
-          <t>2430-57-LP26</t>
+          <t>2416-22-LE26</t>
         </is>
       </c>
       <c r="B132" s="19" t="inlineStr">
         <is>
-          <t>“HABILITACIÓN ALUMBRADO PÚBLICO ACCESO LA PORTADA COMUNA DE ANTOFAGASTA”</t>
+          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
         </is>
       </c>
       <c r="C132" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D132" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>2430-69-LP26</t>
+          <t>2430-57-LP26</t>
         </is>
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
+          <t>“HABILITACIÓN ALUMBRADO PÚBLICO ACCESO LA PORTADA COMUNA DE ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C133" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>2430-71-LP26</t>
+          <t>2430-69-LP26</t>
         </is>
       </c>
       <c r="B134" s="19" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
         </is>
       </c>
       <c r="C134" s="18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D134" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>2445-102-LP26</t>
+          <t>2430-71-LP26</t>
         </is>
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION SALAS DE ESPERA SP787</t>
+          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
         </is>
       </c>
       <c r="C135" s="18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>2452-19-L126</t>
+          <t>2445-102-LP26</t>
         </is>
       </c>
       <c r="B136" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
+          <t>HABILITACION SALAS DE ESPERA SP787</t>
         </is>
       </c>
       <c r="C136" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D136" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2452-19-L126</t>
         </is>
       </c>
       <c r="B137" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
         </is>
       </c>
       <c r="C137" s="18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D137" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>2460-99-LE26</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C138" s="18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D138" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>2483-231-LP26</t>
+          <t>2460-99-LE26</t>
         </is>
       </c>
       <c r="B139" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
+          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
         </is>
       </c>
       <c r="C139" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D139" s="19" t="inlineStr">
         <is>
@@ -5529,132 +5529,132 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>2490-71-LR26</t>
+          <t>2483-231-LP26</t>
         </is>
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>“SERVICIO HABILITACIÓN Y ARRIENDO DE EQUIPAMIENTO TELEFÓNICO PARA LA MUNICIPALIDAD DE PROVIDENCIA”</t>
+          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C140" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D140" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="18" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2490-71-LR26</t>
         </is>
       </c>
       <c r="B141" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>“SERVICIO HABILITACIÓN Y ARRIENDO DE EQUIPAMIENTO TELEFÓNICO PARA LA MUNICIPALIDAD DE PROVIDENCIA”</t>
         </is>
       </c>
       <c r="C141" s="18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D141" s="19" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>2546-49-LP26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C142" s="18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D142" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>2548-71-LE26</t>
+          <t>2546-49-LP26</t>
         </is>
       </c>
       <c r="B143" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
+          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
         </is>
       </c>
       <c r="C143" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D143" s="19" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>2548-73-LE26</t>
+          <t>2548-71-LE26</t>
         </is>
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
+          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
         </is>
       </c>
       <c r="C144" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D144" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>2555-10-LP26</t>
+          <t>2548-73-LE26</t>
         </is>
       </c>
       <c r="B145" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="C145" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D145" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>2565-14-LP26</t>
+          <t>2555-10-LP26</t>
         </is>
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
         </is>
       </c>
       <c r="C146" s="18" t="n">
@@ -5669,12 +5669,12 @@
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2565-14-LP26</t>
         </is>
       </c>
       <c r="B147" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C147" s="18" t="n">
@@ -5689,72 +5689,72 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C148" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D148" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2581-37-LP26</t>
         </is>
       </c>
       <c r="B149" s="19" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
         </is>
       </c>
       <c r="C149" s="18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D149" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C150" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D150" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>2600-23-LE26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B151" s="19" t="inlineStr">
         <is>
-          <t>Const. Accesibilidad Universal Edificio Municipal</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C151" s="18" t="n">
@@ -5769,16 +5769,16 @@
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2600-23-LE26</t>
         </is>
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>Const. Accesibilidad Universal Edificio Municipal</t>
         </is>
       </c>
       <c r="C152" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D152" s="19" t="inlineStr">
         <is>
@@ -5789,16 +5789,16 @@
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>2627-15-LE26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B153" s="19" t="inlineStr">
         <is>
-          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C153" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D153" s="19" t="inlineStr">
         <is>
@@ -5809,112 +5809,112 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>2664-38-L126</t>
+          <t>2627-15-LE26</t>
         </is>
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
+          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C154" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D154" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2664-38-L126</t>
         </is>
       </c>
       <c r="B155" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
         </is>
       </c>
       <c r="C155" s="18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D155" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>2697-23-LP26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C156" s="18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2697-23-LP26</t>
         </is>
       </c>
       <c r="B157" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="C157" s="18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D157" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>2699-32-LR26</t>
+          <t>2697-25-LR26</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Flota Vehicular</t>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
         </is>
       </c>
       <c r="C158" s="18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D158" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>2702-62-LE26</t>
+          <t>2699-32-LR26</t>
         </is>
       </c>
       <c r="B159" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
+          <t>Servicio de Arriendo de Flota Vehicular</t>
         </is>
       </c>
       <c r="C159" s="18" t="n">
@@ -5929,12 +5929,12 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>2755-29-LE26</t>
+          <t>2702-62-LE26</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>PROYECTO TRASLADO CENTRAL DE CAMARAS DE TELEVIGILA</t>
+          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
         </is>
       </c>
       <c r="C160" s="18" t="n">
@@ -5949,92 +5949,92 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>2755-29-LE26</t>
         </is>
       </c>
       <c r="B161" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t>PROYECTO TRASLADO CENTRAL DE CAMARAS DE TELEVIGILA</t>
         </is>
       </c>
       <c r="C161" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D161" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>2770-109-LR26</t>
+          <t>2755-34-LE26</t>
         </is>
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
         </is>
       </c>
       <c r="C162" s="18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D162" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>2770-109-LR26</t>
         </is>
       </c>
       <c r="B163" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C163" s="18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>2788-43-LE26</t>
+          <t>2784-42-LP26</t>
         </is>
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
         </is>
       </c>
       <c r="C164" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D164" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>2788-44-LE26</t>
+          <t>2788-43-LE26</t>
         </is>
       </c>
       <c r="B165" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
         </is>
       </c>
       <c r="C165" s="18" t="n">
@@ -6049,72 +6049,72 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>2793-100-CO26</t>
+          <t>2788-44-LE26</t>
         </is>
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
+          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
         </is>
       </c>
       <c r="C166" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D166" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>2793-91-LE26</t>
+          <t>2793-100-CO26</t>
         </is>
       </c>
       <c r="B167" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
+          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
         </is>
       </c>
       <c r="C167" s="18" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D167" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>2793-97-LE26</t>
+          <t>2793-91-LE26</t>
         </is>
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
+          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
         </is>
       </c>
       <c r="C168" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D168" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>2825-49-L126</t>
+          <t>2793-97-LE26</t>
         </is>
       </c>
       <c r="B169" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
+          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
         </is>
       </c>
       <c r="C169" s="18" t="n">
@@ -6129,92 +6129,92 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>2905-40-LP26</t>
+          <t>2825-49-L126</t>
         </is>
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
         </is>
       </c>
       <c r="C170" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D170" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>2910-23-LE26</t>
+          <t>2905-40-LP26</t>
         </is>
       </c>
       <c r="B171" s="19" t="inlineStr">
         <is>
-          <t>Suministro y comodato de equipo point of care -POC</t>
+          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
         </is>
       </c>
       <c r="C171" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D171" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>2963-26-LR26</t>
+          <t>2910-23-LE26</t>
         </is>
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+          <t>Suministro y comodato de equipo point of care -POC</t>
         </is>
       </c>
       <c r="C172" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D172" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2963-26-LR26</t>
         </is>
       </c>
       <c r="B173" s="19" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
         </is>
       </c>
       <c r="C173" s="18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D173" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C174" s="18" t="n">
@@ -6229,32 +6229,32 @@
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B175" s="19" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C175" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D175" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>3017-64-LE26</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE HERRAMIENTAS PARA 24 PROYECTOS PMU-E LOTA</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C176" s="18" t="n">
@@ -6269,32 +6269,32 @@
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>3117-85-LE26</t>
+          <t>3017-64-LE26</t>
         </is>
       </c>
       <c r="B177" s="19" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA EDIFICIO CENTRAL BIENVALP</t>
+          <t>SERVICIO DE ARRIENDO DE HERRAMIENTAS PARA 24 PROYECTOS PMU-E LOTA</t>
         </is>
       </c>
       <c r="C177" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D177" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>3172-46-LR26</t>
+          <t>3117-85-LE26</t>
         </is>
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+          <t>CAMBIO DE CUBIERTA EDIFICIO CENTRAL BIENVALP</t>
         </is>
       </c>
       <c r="C178" s="18" t="n">
@@ -6309,16 +6309,16 @@
     <row r="179">
       <c r="A179" s="18" t="inlineStr">
         <is>
-          <t>3172-53-LE26</t>
+          <t>3172-46-LR26</t>
         </is>
       </c>
       <c r="B179" s="19" t="inlineStr">
         <is>
-          <t>ESTUDIOS TERRENOS REPOSICIÓN 6°COMISARÍA COLCHANE.</t>
+          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C179" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D179" s="19" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>3172-63-LE26</t>
+          <t>3172-53-LE26</t>
         </is>
       </c>
       <c r="B180" s="19" t="inlineStr">
         <is>
-          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
+          <t>ESTUDIOS TERRENOS REPOSICIÓN 6°COMISARÍA COLCHANE.</t>
         </is>
       </c>
       <c r="C180" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D180" s="19" t="inlineStr">
         <is>
@@ -6349,16 +6349,16 @@
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>3179-33-LE26</t>
+          <t>3172-63-LE26</t>
         </is>
       </c>
       <c r="B181" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
+          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
         </is>
       </c>
       <c r="C181" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D181" s="19" t="inlineStr">
         <is>
@@ -6369,132 +6369,132 @@
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>3210-7-L126</t>
+          <t>3179-33-LE26</t>
         </is>
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
+          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
         </is>
       </c>
       <c r="C182" s="18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D182" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>3210-7-L126</t>
         </is>
       </c>
       <c r="B183" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="C183" s="18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D183" s="19" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>3263-1-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B184" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIPO CONE BEAM</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C184" s="18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D184" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>3290-7-LE26</t>
+          <t>3263-1-LE26</t>
         </is>
       </c>
       <c r="B185" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>ARRIENDO EQUIPO CONE BEAM</t>
         </is>
       </c>
       <c r="C185" s="18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D185" s="19" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>3378-46-LP26</t>
+          <t>3290-7-LE26</t>
         </is>
       </c>
       <c r="B186" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE 02 TORRES DE LAPAROSCOPIA PARA EL DEPARTAMENTO DE PABELLONES QUIRÚRGICOS DEL HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
         </is>
       </c>
       <c r="C186" s="18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D186" s="19" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>3420-5-LE26</t>
+          <t>3378-46-LP26</t>
         </is>
       </c>
       <c r="B187" s="19" t="inlineStr">
         <is>
-          <t>Servicio de Mant. y Reparación de 01 Inmueble</t>
+          <t>SERVICIO DE ARRIENDO DE 02 TORRES DE LAPAROSCOPIA PARA EL DEPARTAMENTO DE PABELLONES QUIRÚRGICOS DEL HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="C187" s="18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D187" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>3428-16-LE26</t>
+          <t>3420-5-LE26</t>
         </is>
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>Compra Materiales para reparaciones de inmuebles</t>
+          <t>Servicio de Mant. y Reparación de 01 Inmueble</t>
         </is>
       </c>
       <c r="C188" s="18" t="n">
@@ -6509,16 +6509,16 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>3453-78-LE26</t>
+          <t>3428-16-LE26</t>
         </is>
       </c>
       <c r="B189" s="19" t="inlineStr">
         <is>
-          <t>ADQ SERV. REP. Y MANT DE OFICINAS PASILLOS Y BAÑOS</t>
+          <t>Compra Materiales para reparaciones de inmuebles</t>
         </is>
       </c>
       <c r="C189" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D189" s="19" t="inlineStr">
         <is>
@@ -6529,16 +6529,16 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>3477-76-LE26</t>
+          <t>3453-78-LE26</t>
         </is>
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
-          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
+          <t>ADQ SERV. REP. Y MANT DE OFICINAS PASILLOS Y BAÑOS</t>
         </is>
       </c>
       <c r="C190" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D190" s="19" t="inlineStr">
         <is>
@@ -6549,72 +6549,72 @@
     <row r="191">
       <c r="A191" s="18" t="inlineStr">
         <is>
-          <t>3479-84-LE26</t>
+          <t>3477-76-LE26</t>
         </is>
       </c>
       <c r="B191" s="19" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo  Equipo Alza Hombre</t>
+          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
         </is>
       </c>
       <c r="C191" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D191" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>3542-22-LE26</t>
+          <t>3479-84-LE26</t>
         </is>
       </c>
       <c r="B192" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>Servicio de Arriendo  Equipo Alza Hombre</t>
         </is>
       </c>
       <c r="C192" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D192" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>3565-58-LE26</t>
+          <t>3542-22-LE26</t>
         </is>
       </c>
       <c r="B193" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C193" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D193" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>3587-17-LE26</t>
+          <t>3565-58-LE26</t>
         </is>
       </c>
       <c r="B194" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE AGUA PURIFICADA DEPENDENCIAS DSM</t>
+          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
         </is>
       </c>
       <c r="C194" s="18" t="n">
@@ -6622,79 +6622,79 @@
       </c>
       <c r="D194" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
-          <t>3588-36-LP26</t>
+          <t>3587-17-LE26</t>
         </is>
       </c>
       <c r="B195" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO SISTEMA GESTIÓN MUNICIPALIDAD YUNGAY</t>
+          <t>SUMINISTRO DE AGUA PURIFICADA DEPENDENCIAS DSM</t>
         </is>
       </c>
       <c r="C195" s="18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D195" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>3595-25-LE26</t>
+          <t>3588-36-LP26</t>
         </is>
       </c>
       <c r="B196" s="19" t="inlineStr">
         <is>
-          <t>Cambio de pavimento edificio consistorial</t>
+          <t>ARRIENDO SISTEMA GESTIÓN MUNICIPALIDAD YUNGAY</t>
         </is>
       </c>
       <c r="C196" s="18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D196" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>359-98-LE26</t>
+          <t>3595-25-LE26</t>
         </is>
       </c>
       <c r="B197" s="19" t="inlineStr">
         <is>
-          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPO EN COMODATO</t>
+          <t>Cambio de pavimento edificio consistorial</t>
         </is>
       </c>
       <c r="C197" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D197" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>359-99-CO26</t>
+          <t>359-98-LE26</t>
         </is>
       </c>
       <c r="B198" s="19" t="inlineStr">
         <is>
-          <t>ADQ ROCURONIO BROMURO CON COMODATO EQUIPO</t>
+          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C198" s="18" t="n">
@@ -6709,32 +6709,32 @@
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>3656-148-LP26</t>
+          <t>359-99-CO26</t>
         </is>
       </c>
       <c r="B199" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+          <t>ADQ ROCURONIO BROMURO CON COMODATO EQUIPO</t>
         </is>
       </c>
       <c r="C199" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D199" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>3668-14-LP26</t>
+          <t>3656-148-LP26</t>
         </is>
       </c>
       <c r="B200" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
         </is>
       </c>
       <c r="C200" s="18" t="n">
@@ -6749,152 +6749,152 @@
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>3756-41-LE26</t>
+          <t>3668-14-LP26</t>
         </is>
       </c>
       <c r="B201" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN ESTACIONAMIENTO VILLA DEPARTAMENTAL PELARCO</t>
+          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
         </is>
       </c>
       <c r="C201" s="18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D201" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>3775-28-LP26</t>
+          <t>3756-41-LE26</t>
         </is>
       </c>
       <c r="B202" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+          <t>CONSTRUCCIÓN ESTACIONAMIENTO VILLA DEPARTAMENTAL PELARCO</t>
         </is>
       </c>
       <c r="C202" s="18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D202" s="19" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>3798-13-LP26</t>
+          <t>3775-28-LP26</t>
         </is>
       </c>
       <c r="B203" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
         </is>
       </c>
       <c r="C203" s="18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D203" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>3798-15-LP26</t>
+          <t>3798-13-LP26</t>
         </is>
       </c>
       <c r="B204" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
+          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
         </is>
       </c>
       <c r="C204" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D204" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="18" t="inlineStr">
         <is>
-          <t>3836-32-LE26</t>
+          <t>3798-15-LP26</t>
         </is>
       </c>
       <c r="B205" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN MÓDULO PREFABRICADO PARA OFICINA CON WC</t>
+          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
         </is>
       </c>
       <c r="C205" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D205" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>3843-30-LE26</t>
+          <t>3836-32-LE26</t>
         </is>
       </c>
       <c r="B206" s="19" t="inlineStr">
         <is>
-          <t>PROYECTO INTEGRAL HABILITACION E IMPLEMENTACION DE PATIOS</t>
+          <t>ADQUISICIÓN MÓDULO PREFABRICADO PARA OFICINA CON WC</t>
         </is>
       </c>
       <c r="C206" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D206" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="18" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>3843-30-LE26</t>
         </is>
       </c>
       <c r="B207" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>PROYECTO INTEGRAL HABILITACION E IMPLEMENTACION DE PATIOS</t>
         </is>
       </c>
       <c r="C207" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D207" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>3887-39-LP26</t>
+          <t>3882-72-LP26</t>
         </is>
       </c>
       <c r="B208" s="19" t="inlineStr">
         <is>
-          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C208" s="18" t="n">
@@ -6909,16 +6909,16 @@
     <row r="209">
       <c r="A209" s="18" t="inlineStr">
         <is>
-          <t>3890-162-E226</t>
+          <t>3887-39-LP26</t>
         </is>
       </c>
       <c r="B209" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MATERIALES DE OFICINA PARA LOS PROGRAMAS DE DISCAPACIDAD Y PSD</t>
+          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
         </is>
       </c>
       <c r="C209" s="18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D209" s="19" t="inlineStr">
         <is>
@@ -6929,12 +6929,12 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>3890-167-L126</t>
+          <t>3890-162-E226</t>
         </is>
       </c>
       <c r="B210" s="19" t="inlineStr">
         <is>
-          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
+          <t>ADQUISICION DE MATERIALES DE OFICINA PARA LOS PROGRAMAS DE DISCAPACIDAD Y PSD</t>
         </is>
       </c>
       <c r="C210" s="18" t="n">
@@ -6949,12 +6949,12 @@
     <row r="211">
       <c r="A211" s="18" t="inlineStr">
         <is>
-          <t>3890-171-L126</t>
+          <t>3890-167-L126</t>
         </is>
       </c>
       <c r="B211" s="19" t="inlineStr">
         <is>
-          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
+          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="C211" s="18" t="n">
@@ -6969,16 +6969,16 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>3934-29-L126</t>
+          <t>3890-171-L126</t>
         </is>
       </c>
       <c r="B212" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE FARMACOS PARA USO EN ESTABLECIMIENTOS DE SALUD DEL DEPARTAMENTO DE SALUD MUNICIPAL FREIRE </t>
+          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
         </is>
       </c>
       <c r="C212" s="18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D212" s="19" t="inlineStr">
         <is>
@@ -6989,32 +6989,32 @@
     <row r="213">
       <c r="A213" s="18" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>3934-29-L126</t>
         </is>
       </c>
       <c r="B213" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t xml:space="preserve">ADQUISICION DE FARMACOS PARA USO EN ESTABLECIMIENTOS DE SALUD DEL DEPARTAMENTO DE SALUD MUNICIPAL FREIRE </t>
         </is>
       </c>
       <c r="C213" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D213" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="18" t="inlineStr">
         <is>
-          <t>3948-37-LE26</t>
+          <t>3935-83-LP26</t>
         </is>
       </c>
       <c r="B214" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE TRANSPORTE PREESCOLAR</t>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
         </is>
       </c>
       <c r="C214" s="18" t="n">
@@ -7029,52 +7029,52 @@
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>3981-23-LE26</t>
+          <t>3948-37-LE26</t>
         </is>
       </c>
       <c r="B215" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN E IMPLEMENTACIÓN DE SALA DE RESGUARDO FAMILIAR MUNICIPAL SALA CUNA</t>
+          <t>SERVICIO DE ARRIENDO DE TRANSPORTE PREESCOLAR</t>
         </is>
       </c>
       <c r="C215" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D215" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="18" t="inlineStr">
         <is>
-          <t>4031-14-LE26</t>
+          <t>3981-23-LE26</t>
         </is>
       </c>
       <c r="B216" s="19" t="inlineStr">
         <is>
-          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
+          <t>HABILITACIÓN E IMPLEMENTACIÓN DE SALA DE RESGUARDO FAMILIAR MUNICIPAL SALA CUNA</t>
         </is>
       </c>
       <c r="C216" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D216" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>4031-14-LE26</t>
         </is>
       </c>
       <c r="B217" s="19" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
         </is>
       </c>
       <c r="C217" s="18" t="n">
@@ -7089,12 +7089,12 @@
     <row r="218">
       <c r="A218" s="18" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B218" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C218" s="18" t="n">
@@ -7109,32 +7109,32 @@
     <row r="219">
       <c r="A219" s="18" t="inlineStr">
         <is>
-          <t>4121-23-LE26</t>
+          <t>4099-22-LP26</t>
         </is>
       </c>
       <c r="B219" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
         </is>
       </c>
       <c r="C219" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D219" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
         <is>
-          <t>4168-81-LE26</t>
+          <t>4121-23-LE26</t>
         </is>
       </c>
       <c r="B220" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE GRADERÍAS MECANO</t>
+          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
         </is>
       </c>
       <c r="C220" s="18" t="n">
@@ -7149,12 +7149,12 @@
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>418-51-LP26</t>
+          <t>4168-81-LE26</t>
         </is>
       </c>
       <c r="B221" s="19" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+          <t>ARRIENDO DE GRADERÍAS MECANO</t>
         </is>
       </c>
       <c r="C221" s="18" t="n">
@@ -7169,92 +7169,92 @@
     <row r="222">
       <c r="A222" s="18" t="inlineStr">
         <is>
-          <t>4202-38-LE26</t>
+          <t>418-51-LP26</t>
         </is>
       </c>
       <c r="B222" s="19" t="inlineStr">
         <is>
-          <t>Arriendo de recinto actividad Pasamos Agosto</t>
+          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
         </is>
       </c>
       <c r="C222" s="18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D222" s="19" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="18" t="inlineStr">
         <is>
-          <t>4237-12-LR26</t>
+          <t>4202-38-LE26</t>
         </is>
       </c>
       <c r="B223" s="19" t="inlineStr">
         <is>
-          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+          <t>Arriendo de recinto actividad Pasamos Agosto</t>
         </is>
       </c>
       <c r="C223" s="18" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D223" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="18" t="inlineStr">
         <is>
-          <t>4238-66-B226</t>
+          <t>4237-12-LR26</t>
         </is>
       </c>
       <c r="B224" s="19" t="inlineStr">
         <is>
-          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
         </is>
       </c>
       <c r="C224" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D224" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
-          <t>4284-141-L126</t>
+          <t>4238-66-B226</t>
         </is>
       </c>
       <c r="B225" s="19" t="inlineStr">
         <is>
-          <t>Contrato suministro leña para calefacción dependencias ELEAM Ayen Ruca según NUMERAL 5 B.A.G Bases administrativas Generales</t>
+          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
         </is>
       </c>
       <c r="C225" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D225" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>4295-41-LP26</t>
+          <t>4284-141-L126</t>
         </is>
       </c>
       <c r="B226" s="19" t="inlineStr">
         <is>
-          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+          <t>Contrato suministro leña para calefacción dependencias ELEAM Ayen Ruca según NUMERAL 5 B.A.G Bases administrativas Generales</t>
         </is>
       </c>
       <c r="C226" s="18" t="n">
@@ -7269,56 +7269,56 @@
     <row r="227">
       <c r="A227" s="18" t="inlineStr">
         <is>
-          <t>4309-215-LP26</t>
+          <t>4295-41-LP26</t>
         </is>
       </c>
       <c r="B227" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
+          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
         </is>
       </c>
       <c r="C227" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D227" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="18" t="inlineStr">
         <is>
-          <t>4328-31-B226</t>
+          <t>4309-215-LP26</t>
         </is>
       </c>
       <c r="B228" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
+          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
         </is>
       </c>
       <c r="C228" s="18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D228" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="18" t="inlineStr">
         <is>
-          <t>4362-15-LP26</t>
+          <t>4328-31-B226</t>
         </is>
       </c>
       <c r="B229" s="19" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
         </is>
       </c>
       <c r="C229" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D229" s="19" t="inlineStr">
         <is>
@@ -7329,12 +7329,12 @@
     <row r="230">
       <c r="A230" s="18" t="inlineStr">
         <is>
-          <t>4362-20-LE26</t>
+          <t>4362-15-LP26</t>
         </is>
       </c>
       <c r="B230" s="19" t="inlineStr">
         <is>
-          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
         </is>
       </c>
       <c r="C230" s="18" t="n">
@@ -7349,76 +7349,76 @@
     <row r="231">
       <c r="A231" s="18" t="inlineStr">
         <is>
-          <t>438-49-LE26</t>
+          <t>4362-20-LE26</t>
         </is>
       </c>
       <c r="B231" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
+          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
         </is>
       </c>
       <c r="C231" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D231" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="18" t="inlineStr">
         <is>
-          <t>4414-61-LE26</t>
+          <t>438-49-LE26</t>
         </is>
       </c>
       <c r="B232" s="19" t="inlineStr">
         <is>
-          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
+          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
         </is>
       </c>
       <c r="C232" s="18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D232" s="19" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="18" t="inlineStr">
         <is>
-          <t>45-44-LE26</t>
+          <t>4414-61-LE26</t>
         </is>
       </c>
       <c r="B233" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
+          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
         </is>
       </c>
       <c r="C233" s="18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D233" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="18" t="inlineStr">
         <is>
-          <t>4594-25-LE26</t>
+          <t>45-44-LE26</t>
         </is>
       </c>
       <c r="B234" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
+          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
         </is>
       </c>
       <c r="C234" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D234" s="19" t="inlineStr">
         <is>
@@ -7429,32 +7429,32 @@
     <row r="235">
       <c r="A235" s="18" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>4594-25-LE26</t>
         </is>
       </c>
       <c r="B235" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
         </is>
       </c>
       <c r="C235" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D235" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>4642-92-LP26</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B236" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C236" s="18" t="n">
@@ -7469,12 +7469,12 @@
     <row r="237">
       <c r="A237" s="18" t="inlineStr">
         <is>
-          <t>4642-93-LP26</t>
+          <t>4642-92-LP26</t>
         </is>
       </c>
       <c r="B237" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
+          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
         </is>
       </c>
       <c r="C237" s="18" t="n">
@@ -7489,12 +7489,12 @@
     <row r="238">
       <c r="A238" s="18" t="inlineStr">
         <is>
-          <t>4644-5-LP26</t>
+          <t>4642-93-LP26</t>
         </is>
       </c>
       <c r="B238" s="19" t="inlineStr">
         <is>
-          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
+          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C238" s="18" t="n">
@@ -7509,72 +7509,72 @@
     <row r="239">
       <c r="A239" s="18" t="inlineStr">
         <is>
-          <t>4778-18-LE26</t>
+          <t>4644-5-LP26</t>
         </is>
       </c>
       <c r="B239" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
+          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
         </is>
       </c>
       <c r="C239" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D239" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="18" t="inlineStr">
         <is>
-          <t>4829-43-L126</t>
+          <t>4778-18-LE26</t>
         </is>
       </c>
       <c r="B240" s="19" t="inlineStr">
         <is>
-          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
+          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
         </is>
       </c>
       <c r="C240" s="18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D240" s="19" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="18" t="inlineStr">
         <is>
-          <t>4850-3-LE26</t>
+          <t>4829-43-L126</t>
         </is>
       </c>
       <c r="B241" s="19" t="inlineStr">
         <is>
-          <t>Servicio para reparación edificio</t>
+          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
         </is>
       </c>
       <c r="C241" s="18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D241" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="18" t="inlineStr">
         <is>
-          <t>4887-22-L126</t>
+          <t>4850-3-LE26</t>
         </is>
       </c>
       <c r="B242" s="19" t="inlineStr">
         <is>
-          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
+          <t>Servicio para reparación edificio</t>
         </is>
       </c>
       <c r="C242" s="18" t="n">
@@ -7582,79 +7582,79 @@
       </c>
       <c r="D242" s="19" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="18" t="inlineStr">
         <is>
-          <t>4928-21-LP26</t>
+          <t>4887-22-L126</t>
         </is>
       </c>
       <c r="B243" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
+          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
         </is>
       </c>
       <c r="C243" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D243" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="18" t="inlineStr">
         <is>
-          <t>4956-63-LP26</t>
+          <t>4928-21-LP26</t>
         </is>
       </c>
       <c r="B244" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
+          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
         </is>
       </c>
       <c r="C244" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D244" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="18" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>4956-63-LP26</t>
         </is>
       </c>
       <c r="B245" s="19" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
         </is>
       </c>
       <c r="C245" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D245" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="18" t="inlineStr">
         <is>
-          <t>4956-71-LE26</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B246" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SERVICIOS HIGIENICOS PARA FONDAS</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C246" s="18" t="n">
@@ -7669,12 +7669,12 @@
     <row r="247">
       <c r="A247" s="18" t="inlineStr">
         <is>
-          <t>4967-7-LR26</t>
+          <t>4956-71-LE26</t>
         </is>
       </c>
       <c r="B247" s="19" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+          <t>ARRIENDO DE SERVICIOS HIGIENICOS PARA FONDAS</t>
         </is>
       </c>
       <c r="C247" s="18" t="n">
@@ -7689,12 +7689,12 @@
     <row r="248">
       <c r="A248" s="18" t="inlineStr">
         <is>
-          <t>4993-69-L126</t>
+          <t>4967-7-LR26</t>
         </is>
       </c>
       <c r="B248" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MOVILIZACIÓN PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE VIVIENDA CHOLCHOL 2026</t>
+          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
         </is>
       </c>
       <c r="C248" s="18" t="n">
@@ -7709,12 +7709,12 @@
     <row r="249">
       <c r="A249" s="18" t="inlineStr">
         <is>
-          <t>5048-13-O126</t>
+          <t>4993-69-L126</t>
         </is>
       </c>
       <c r="B249" s="19" t="inlineStr">
         <is>
-          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
+          <t>SERVICIO DE MOVILIZACIÓN PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE VIVIENDA CHOLCHOL 2026</t>
         </is>
       </c>
       <c r="C249" s="18" t="n">
@@ -7729,12 +7729,12 @@
     <row r="250">
       <c r="A250" s="18" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>5048-13-O126</t>
         </is>
       </c>
       <c r="B250" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="C250" s="18" t="n">
@@ -7749,12 +7749,12 @@
     <row r="251">
       <c r="A251" s="18" t="inlineStr">
         <is>
-          <t>5056-98-LP26</t>
+          <t>5056-102-LP26</t>
         </is>
       </c>
       <c r="B251" s="19" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CAMAS DE ATENCIÓN INTEGRAL DE PARTO</t>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
         </is>
       </c>
       <c r="C251" s="18" t="n">
@@ -7769,12 +7769,12 @@
     <row r="252">
       <c r="A252" s="18" t="inlineStr">
         <is>
-          <t>507428-94-LE26</t>
+          <t>5056-98-LP26</t>
         </is>
       </c>
       <c r="B252" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+          <t>ARRIENDO DE CAMAS DE ATENCIÓN INTEGRAL DE PARTO</t>
         </is>
       </c>
       <c r="C252" s="18" t="n">
@@ -7789,12 +7789,12 @@
     <row r="253">
       <c r="A253" s="18" t="inlineStr">
         <is>
-          <t>5194-4-LE26</t>
+          <t>507428-94-LE26</t>
         </is>
       </c>
       <c r="B253" s="19" t="inlineStr">
         <is>
-          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
         </is>
       </c>
       <c r="C253" s="18" t="n">
@@ -7809,12 +7809,12 @@
     <row r="254">
       <c r="A254" s="18" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>5194-4-LE26</t>
         </is>
       </c>
       <c r="B254" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
         </is>
       </c>
       <c r="C254" s="18" t="n">
@@ -7829,52 +7829,52 @@
     <row r="255">
       <c r="A255" s="18" t="inlineStr">
         <is>
-          <t>5240-91-LE26</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B255" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C255" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D255" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="18" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>5240-91-LE26</t>
         </is>
       </c>
       <c r="B256" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
         </is>
       </c>
       <c r="C256" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D256" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="18" t="inlineStr">
         <is>
-          <t>528208-38-LE26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B257" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE PROVISIÓN CON INSTALACIÓN DE VENTANAS PARA FACHADA Y REVESTIMIENTO DE ESCALA PARA GALERÍA DE EXPOSICIÓN MEMORIAS CHILE VIETNAM CERRO NAVIA</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C257" s="18" t="n">
@@ -7889,36 +7889,36 @@
     <row r="258">
       <c r="A258" s="18" t="inlineStr">
         <is>
-          <t>5300-50-LP26</t>
+          <t>528208-38-LE26</t>
         </is>
       </c>
       <c r="B258" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
+          <t>SERVICIO DE PROVISIÓN CON INSTALACIÓN DE VENTANAS PARA FACHADA Y REVESTIMIENTO DE ESCALA PARA GALERÍA DE EXPOSICIÓN MEMORIAS CHILE VIETNAM CERRO NAVIA</t>
         </is>
       </c>
       <c r="C258" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D258" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="18" t="inlineStr">
         <is>
-          <t>5300-54-LP26</t>
+          <t>5300-50-LP26</t>
         </is>
       </c>
       <c r="B259" s="19" t="inlineStr">
         <is>
-          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
+          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
         </is>
       </c>
       <c r="C259" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D259" s="19" t="inlineStr">
         <is>
@@ -7929,52 +7929,52 @@
     <row r="260">
       <c r="A260" s="18" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>5300-54-LP26</t>
         </is>
       </c>
       <c r="B260" s="19" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
         </is>
       </c>
       <c r="C260" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D260" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="18" t="inlineStr">
         <is>
-          <t>539119-82-CO26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B261" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA LA REPARACIÓN DE LAS FACHADAS DEL CONJUNTO HABITACIONAL PAJARITOS ADMINISTRADO POR EL DEPARTAMENTO GESTIÓN DE VIVIENDAS Y POBLACIONES B.4 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS.</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C261" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D261" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="18" t="inlineStr">
         <is>
-          <t>539119-85-LP26</t>
+          <t>539119-82-CO26</t>
         </is>
       </c>
       <c r="B262" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+          <t>SUMINISTRO DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA LA REPARACIÓN DE LAS FACHADAS DEL CONJUNTO HABITACIONAL PAJARITOS ADMINISTRADO POR EL DEPARTAMENTO GESTIÓN DE VIVIENDAS Y POBLACIONES B.4 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C262" s="18" t="n">
@@ -7989,12 +7989,12 @@
     <row r="263">
       <c r="A263" s="18" t="inlineStr">
         <is>
-          <t>539119-86-LE26</t>
+          <t>539119-85-LP26</t>
         </is>
       </c>
       <c r="B263" s="19" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
         </is>
       </c>
       <c r="C263" s="18" t="n">
@@ -8009,56 +8009,56 @@
     <row r="264">
       <c r="A264" s="18" t="inlineStr">
         <is>
-          <t>5413-65-LE26</t>
+          <t>539119-86-LE26</t>
         </is>
       </c>
       <c r="B264" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
+          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C264" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D264" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="18" t="inlineStr">
         <is>
-          <t>5420-20-LE26</t>
+          <t>5413-65-LE26</t>
         </is>
       </c>
       <c r="B265" s="19" t="inlineStr">
         <is>
-          <t>Diseño eléctrico para normalización de edificios</t>
+          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
         </is>
       </c>
       <c r="C265" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D265" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="18" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>5420-20-LE26</t>
         </is>
       </c>
       <c r="B266" s="19" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>Diseño eléctrico para normalización de edificios</t>
         </is>
       </c>
       <c r="C266" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D266" s="19" t="inlineStr">
         <is>
@@ -8069,72 +8069,72 @@
     <row r="267">
       <c r="A267" s="18" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B267" s="19" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C267" s="18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D267" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="18" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B268" s="19" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C268" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D268" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="18" t="inlineStr">
         <is>
-          <t>5626-9-LP26</t>
+          <t>5586-126-LE26</t>
         </is>
       </c>
       <c r="B269" s="19" t="inlineStr">
         <is>
-          <t>EQUIPOS PARA HABILITACIÓN DE AUDITORIO Y SALAS</t>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
         </is>
       </c>
       <c r="C269" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D269" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="18" t="inlineStr">
         <is>
-          <t>564953-61-LP26</t>
+          <t>5626-9-LP26</t>
         </is>
       </c>
       <c r="B270" s="19" t="inlineStr">
         <is>
-          <t>Servicio de traslado de estudiantes</t>
+          <t>EQUIPOS PARA HABILITACIÓN DE AUDITORIO Y SALAS</t>
         </is>
       </c>
       <c r="C270" s="18" t="n">
@@ -8149,92 +8149,92 @@
     <row r="271">
       <c r="A271" s="18" t="inlineStr">
         <is>
-          <t>5722-4-L126</t>
+          <t>564953-61-LP26</t>
         </is>
       </c>
       <c r="B271" s="19" t="inlineStr">
         <is>
-          <t>Traslado Materiales a Lugar De Acopio, Obra Restauración Y Ampliación Del Museo De Arte Contemporáneo Valdivia</t>
+          <t>Servicio de traslado de estudiantes</t>
         </is>
       </c>
       <c r="C271" s="18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D271" s="19" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="18" t="inlineStr">
         <is>
-          <t>575924-9-E226</t>
+          <t>5722-4-L126</t>
         </is>
       </c>
       <c r="B272" s="19" t="inlineStr">
         <is>
-          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
+          <t>Traslado Materiales a Lugar De Acopio, Obra Restauración Y Ampliación Del Museo De Arte Contemporáneo Valdivia</t>
         </is>
       </c>
       <c r="C272" s="18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D272" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="18" t="inlineStr">
         <is>
-          <t>607-60-LE26</t>
+          <t>575924-9-E226</t>
         </is>
       </c>
       <c r="B273" s="19" t="inlineStr">
         <is>
-          <t>MEJOR. DEPENDENCIAS SERVICIO SOCIAL Y OIRS</t>
+          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
         </is>
       </c>
       <c r="C273" s="18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D273" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="18" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>607-60-LE26</t>
         </is>
       </c>
       <c r="B274" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>MEJOR. DEPENDENCIAS SERVICIO SOCIAL Y OIRS</t>
         </is>
       </c>
       <c r="C274" s="18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D274" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="18" t="inlineStr">
         <is>
-          <t>608-126-LR26</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B275" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C275" s="18" t="n">
@@ -8249,116 +8249,116 @@
     <row r="276">
       <c r="A276" s="18" t="inlineStr">
         <is>
-          <t>613-6-LE26</t>
+          <t>608-126-LR26</t>
         </is>
       </c>
       <c r="B276" s="19" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE OFICINAS SECTOR ZÓCALO EDIFICIO SE</t>
+          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
         </is>
       </c>
       <c r="C276" s="18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D276" s="19" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="18" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>613-6-LE26</t>
         </is>
       </c>
       <c r="B277" s="19" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>MEJORAMIENTO DE OFICINAS SECTOR ZÓCALO EDIFICIO SE</t>
         </is>
       </c>
       <c r="C277" s="18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D277" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="18" t="inlineStr">
         <is>
-          <t>627786-14-LE26</t>
+          <t>622-55-LE26</t>
         </is>
       </c>
       <c r="B278" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
         </is>
       </c>
       <c r="C278" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D278" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="18" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>627786-14-LE26</t>
         </is>
       </c>
       <c r="B279" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
         </is>
       </c>
       <c r="C279" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D279" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="18" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>633-48-LR26</t>
         </is>
       </c>
       <c r="B280" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
         </is>
       </c>
       <c r="C280" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D280" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="18" t="inlineStr">
         <is>
-          <t>640-2-LP26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B281" s="19" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REPARACIONES OBRAS MENORES OFICINAS</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C281" s="18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D281" s="19" t="inlineStr">
         <is>
@@ -8369,52 +8369,52 @@
     <row r="282">
       <c r="A282" s="18" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>640-2-LP26</t>
         </is>
       </c>
       <c r="B282" s="19" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>MANTENCIÓN Y REPARACIONES OBRAS MENORES OFICINAS</t>
         </is>
       </c>
       <c r="C282" s="18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D282" s="19" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="18" t="inlineStr">
         <is>
-          <t>673-3-LE26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B283" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C283" s="18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D283" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="18" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>673-3-LE26</t>
         </is>
       </c>
       <c r="B284" s="19" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
         </is>
       </c>
       <c r="C284" s="18" t="n">
@@ -8429,96 +8429,96 @@
     <row r="285">
       <c r="A285" s="18" t="inlineStr">
         <is>
-          <t>677-6-LP26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B285" s="19" t="inlineStr">
         <is>
-          <t>Elab. Diag. Plan Maestro y Plan de Gestión. Lonco</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C285" s="18" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D285" s="19" t="inlineStr">
         <is>
-          <t>score 23 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="18" t="inlineStr">
         <is>
-          <t>682-3-LE26</t>
+          <t>677-6-LP26</t>
         </is>
       </c>
       <c r="B286" s="19" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
+          <t>Elab. Diag. Plan Maestro y Plan de Gestión. Lonco</t>
         </is>
       </c>
       <c r="C286" s="18" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D286" s="19" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 23 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="18" t="inlineStr">
         <is>
-          <t>697057-30-LE26</t>
+          <t>682-3-LE26</t>
         </is>
       </c>
       <c r="B287" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
         </is>
       </c>
       <c r="C287" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D287" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="18" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>697057-30-LE26</t>
         </is>
       </c>
       <c r="B288" s="19" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
         </is>
       </c>
       <c r="C288" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D288" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="18" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>707420-20-LE26</t>
         </is>
       </c>
       <c r="B289" s="19" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
         </is>
       </c>
       <c r="C289" s="18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D289" s="19" t="inlineStr">
         <is>
@@ -8529,32 +8529,32 @@
     <row r="290">
       <c r="A290" s="18" t="inlineStr">
         <is>
-          <t>730377-1-L126</t>
+          <t>712307-58-O126</t>
         </is>
       </c>
       <c r="B290" s="19" t="inlineStr">
         <is>
-          <t>Servicio de arriendo de dispensadores de agua purificada para 2°Juzgado de Familia de San Miguel</t>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
         </is>
       </c>
       <c r="C290" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D290" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="18" t="inlineStr">
         <is>
-          <t>731159-2-L126</t>
+          <t>730377-1-L126</t>
         </is>
       </c>
       <c r="B291" s="19" t="inlineStr">
         <is>
-          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
+          <t>Servicio de arriendo de dispensadores de agua purificada para 2°Juzgado de Familia de San Miguel</t>
         </is>
       </c>
       <c r="C291" s="18" t="n">
@@ -8569,152 +8569,152 @@
     <row r="292">
       <c r="A292" s="18" t="inlineStr">
         <is>
-          <t>732434-19-LE26</t>
+          <t>731159-2-L126</t>
         </is>
       </c>
       <c r="B292" s="19" t="inlineStr">
         <is>
-          <t>REPARACIÓN CUBIERTAS VARIOS RECINTOS CSC</t>
+          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
         </is>
       </c>
       <c r="C292" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D292" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="18" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>732434-19-LE26</t>
         </is>
       </c>
       <c r="B293" s="19" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>REPARACIÓN CUBIERTAS VARIOS RECINTOS CSC</t>
         </is>
       </c>
       <c r="C293" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D293" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="18" t="inlineStr">
         <is>
-          <t>734-47-L126</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B294" s="19" t="inlineStr">
         <is>
-          <t>ASESORÍA TECNICA ADMINISTRATIVA DE LA SECCIÓN DE EQUIPAMIENTO PARA EL SUBDEPARTAMENTO DE RECURSOS FISICOS E INVERSIONES DEL SERVICIO DE SALUD AYSÉN</t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C294" s="18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D294" s="19" t="inlineStr">
         <is>
-          <t>score 3 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="18" t="inlineStr">
         <is>
-          <t>735949-1-LE26</t>
+          <t>734-47-L126</t>
         </is>
       </c>
       <c r="B295" s="19" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA EL DEPARTAMENTO DE DESARROLLO RURAL</t>
+          <t>ASESORÍA TECNICA ADMINISTRATIVA DE LA SECCIÓN DE EQUIPAMIENTO PARA EL SUBDEPARTAMENTO DE RECURSOS FISICOS E INVERSIONES DEL SERVICIO DE SALUD AYSÉN</t>
         </is>
       </c>
       <c r="C295" s="18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D295" s="19" t="inlineStr">
         <is>
-          <t>score 7 &lt; 30</t>
+          <t>score 3 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="18" t="inlineStr">
         <is>
-          <t>739231-17-LP26</t>
+          <t>735949-1-LE26</t>
         </is>
       </c>
       <c r="B296" s="19" t="inlineStr">
         <is>
-          <t>Habilitación Area de Juegos en Sector Costanera de Puerto Octay</t>
+          <t>SERVICIOS PARA EL DEPARTAMENTO DE DESARROLLO RURAL</t>
         </is>
       </c>
       <c r="C296" s="18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D296" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 7 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="18" t="inlineStr">
         <is>
-          <t>742-7-L126</t>
+          <t>739231-17-LP26</t>
         </is>
       </c>
       <c r="B297" s="19" t="inlineStr">
         <is>
-          <t>Mantención Oficina ubicada en Las Lengas N°1450 de la ciudad de Coyhaique de INDAP, región de Aysén</t>
+          <t>Habilitación Area de Juegos en Sector Costanera de Puerto Octay</t>
         </is>
       </c>
       <c r="C297" s="18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D297" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="18" t="inlineStr">
         <is>
-          <t>748201-10-LE26</t>
+          <t>742-7-L126</t>
         </is>
       </c>
       <c r="B298" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+          <t>Mantención Oficina ubicada en Las Lengas N°1450 de la ciudad de Coyhaique de INDAP, región de Aysén</t>
         </is>
       </c>
       <c r="C298" s="18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D298" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="18" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>748201-10-LE26</t>
         </is>
       </c>
       <c r="B299" s="19" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C299" s="18" t="n">
@@ -8729,12 +8729,12 @@
     <row r="300">
       <c r="A300" s="18" t="inlineStr">
         <is>
-          <t>750998-56-LE26</t>
+          <t>748201-9-LP26</t>
         </is>
       </c>
       <c r="B300" s="19" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALAS CINU</t>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C300" s="18" t="n">
@@ -8749,12 +8749,12 @@
     <row r="301">
       <c r="A301" s="18" t="inlineStr">
         <is>
-          <t>761391-126-LE26</t>
+          <t>750998-56-LE26</t>
         </is>
       </c>
       <c r="B301" s="19" t="inlineStr">
         <is>
-          <t>BAEBGUBECG148SVC TRASLADO DE PERSONAL PARADA MILITAR 2026.</t>
+          <t>HABILITACIÓN SALAS CINU</t>
         </is>
       </c>
       <c r="C301" s="18" t="n">
@@ -8769,152 +8769,152 @@
     <row r="302">
       <c r="A302" s="18" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>761391-126-LE26</t>
         </is>
       </c>
       <c r="B302" s="19" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>BAEBGUBECG148SVC TRASLADO DE PERSONAL PARADA MILITAR 2026.</t>
         </is>
       </c>
       <c r="C302" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D302" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="18" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B303" s="19" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C303" s="18" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D303" s="19" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="18" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>824-3-LE26</t>
         </is>
       </c>
       <c r="B304" s="19" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
         </is>
       </c>
       <c r="C304" s="18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D304" s="19" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="18" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B305" s="19" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C305" s="18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D305" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="18" t="inlineStr">
         <is>
-          <t>838100-6-L126</t>
+          <t>837-88-LP26</t>
         </is>
       </c>
       <c r="B306" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
         </is>
       </c>
       <c r="C306" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D306" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="18" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>838100-6-L126</t>
         </is>
       </c>
       <c r="B307" s="19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
         </is>
       </c>
       <c r="C307" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D307" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="18" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>845-17-LR26</t>
         </is>
       </c>
       <c r="B308" s="19" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
         </is>
       </c>
       <c r="C308" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D308" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="18" t="inlineStr">
         <is>
-          <t>886954-230-LP26</t>
+          <t>886954-222-LR26</t>
         </is>
       </c>
       <c r="B309" s="19" t="inlineStr">
         <is>
-          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
         </is>
       </c>
       <c r="C309" s="18" t="n">
@@ -8929,12 +8929,12 @@
     <row r="310">
       <c r="A310" s="18" t="inlineStr">
         <is>
-          <t>886954-262-LP26</t>
+          <t>886954-230-LP26</t>
         </is>
       </c>
       <c r="B310" s="19" t="inlineStr">
         <is>
-          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
         </is>
       </c>
       <c r="C310" s="18" t="n">
@@ -8949,12 +8949,12 @@
     <row r="311">
       <c r="A311" s="18" t="inlineStr">
         <is>
-          <t>886954-297-LP26</t>
+          <t>886954-262-LP26</t>
         </is>
       </c>
       <c r="B311" s="19" t="inlineStr">
         <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
         </is>
       </c>
       <c r="C311" s="18" t="n">
@@ -8969,32 +8969,32 @@
     <row r="312">
       <c r="A312" s="18" t="inlineStr">
         <is>
-          <t>899-31-L126</t>
+          <t>886954-297-LP26</t>
         </is>
       </c>
       <c r="B312" s="19" t="inlineStr">
         <is>
-          <t>Suministro e instalación de argollas de anclaje para la techumbre del Hospital San José de Casablanca</t>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
         </is>
       </c>
       <c r="C312" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D312" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="18" t="inlineStr">
         <is>
-          <t>930-20-LE26</t>
+          <t>899-31-L126</t>
         </is>
       </c>
       <c r="B313" s="19" t="inlineStr">
         <is>
-          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
+          <t>Suministro e instalación de argollas de anclaje para la techumbre del Hospital San José de Casablanca</t>
         </is>
       </c>
       <c r="C313" s="18" t="n">
@@ -9009,12 +9009,12 @@
     <row r="314">
       <c r="A314" s="18" t="inlineStr">
         <is>
-          <t>932-24-LE26</t>
+          <t>930-20-LE26</t>
         </is>
       </c>
       <c r="B314" s="19" t="inlineStr">
         <is>
-          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
+          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
         </is>
       </c>
       <c r="C314" s="18" t="n">
@@ -9029,136 +9029,136 @@
     <row r="315">
       <c r="A315" s="18" t="inlineStr">
         <is>
-          <t>956-57-L126</t>
+          <t>932-24-LE26</t>
         </is>
       </c>
       <c r="B315" s="19" t="inlineStr">
         <is>
-          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
         </is>
       </c>
       <c r="C315" s="18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D315" s="19" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="18" t="inlineStr">
         <is>
-          <t>956-58-LE26</t>
+          <t>956-57-L126</t>
         </is>
       </c>
       <c r="B316" s="19" t="inlineStr">
         <is>
-          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
         </is>
       </c>
       <c r="C316" s="18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D316" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="18" t="inlineStr">
         <is>
-          <t>957865-6-LE26</t>
+          <t>956-58-LE26</t>
         </is>
       </c>
       <c r="B317" s="19" t="inlineStr">
         <is>
-          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
         </is>
       </c>
       <c r="C317" s="18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D317" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="18" t="inlineStr">
         <is>
-          <t>975-12-O126</t>
+          <t>957865-6-LE26</t>
         </is>
       </c>
       <c r="B318" s="19" t="inlineStr">
         <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
         </is>
       </c>
       <c r="C318" s="18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D318" s="19" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="18" t="inlineStr">
         <is>
-          <t>976-14-LP26</t>
+          <t>975-12-O126</t>
         </is>
       </c>
       <c r="B319" s="19" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
         </is>
       </c>
       <c r="C319" s="18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D319" s="19" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="18" t="inlineStr">
         <is>
-          <t>979-49-L126</t>
+          <t>976-14-LP26</t>
         </is>
       </c>
       <c r="B320" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
         </is>
       </c>
       <c r="C320" s="18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D320" s="19" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="18" t="inlineStr">
         <is>
-          <t>986278-16-LE26</t>
+          <t>979-49-L126</t>
         </is>
       </c>
       <c r="B321" s="19" t="inlineStr">
         <is>
-          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
+          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
         </is>
       </c>
       <c r="C321" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D321" s="19" t="inlineStr">
         <is>
@@ -9169,16 +9169,16 @@
     <row r="322">
       <c r="A322" s="18" t="inlineStr">
         <is>
-          <t>993-42-LE26</t>
+          <t>986278-16-LE26</t>
         </is>
       </c>
       <c r="B322" s="19" t="inlineStr">
         <is>
-          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C322" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D322" s="19" t="inlineStr">
         <is>
@@ -9189,18 +9189,38 @@
     <row r="323">
       <c r="A323" s="18" t="inlineStr">
         <is>
+          <t>993-42-LE26</t>
+        </is>
+      </c>
+      <c r="B323" s="19" t="inlineStr">
+        <is>
+          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D323" s="19" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="18" t="inlineStr">
+        <is>
           <t>997-32-LP26</t>
         </is>
       </c>
-      <c r="B323" s="19" t="inlineStr">
+      <c r="B324" s="19" t="inlineStr">
         <is>
           <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
         </is>
       </c>
-      <c r="C323" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D323" s="19" t="inlineStr">
+      <c r="C324" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" s="19" t="inlineStr">
         <is>
           <t>score 0 &lt; 30</t>
         </is>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +92,20 @@
       <color rgb="00B7791F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +115,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F6EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF2E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,10 +201,52 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -558,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-08-25 17:49 · UF 40,865.87 · 4,511 licitaciones activas barridas</t>
+          <t>Corrida 2026-08-29 19:34 · UF 40,871.14 · 4,717 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -581,7 +655,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA(Matches!P2:P11)</f>
+        <f>COUNTA(Matches!P2:P9)</f>
         <v/>
       </c>
     </row>
@@ -592,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Matches!A2:A11,"SI")</f>
+        <f>COUNTIF(Matches!A2:A9,"SI")</f>
         <v/>
       </c>
     </row>
@@ -603,7 +677,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Matches!B2:B11,"CAMBIO*")</f>
+        <f>COUNTIF(Matches!B2:B9,"CAMBIO*")</f>
         <v/>
       </c>
     </row>
@@ -614,7 +688,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Matches!C2:C11,"ALTA")</f>
+        <f>COUNTIF(Matches!C2:C9,"ALTA")</f>
         <v/>
       </c>
     </row>
@@ -625,7 +699,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Matches!E2:E11,"Mandato de SERVICIO")</f>
+        <f>COUNTIF(Matches!E2:E9,"Mandato de SERVICIO")</f>
         <v/>
       </c>
     </row>
@@ -636,7 +710,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Matches!E2:E11,"Estado BUSCA inmueble")</f>
+        <f>COUNTIF(Matches!E2:E9,"Estado BUSCA inmueble")</f>
         <v/>
       </c>
     </row>
@@ -647,7 +721,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Matches!E2:E11,"Estado OFRECE inmueble")</f>
+        <f>COUNTIF(Matches!E2:E9,"Estado OFRECE inmueble")</f>
         <v/>
       </c>
     </row>
@@ -658,7 +732,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Matches!G2:G11,"Gamma")</f>
+        <f>COUNTIF(Matches!G2:G9,"Gamma")</f>
         <v/>
       </c>
     </row>
@@ -669,7 +743,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Matches!G2:G11,"Realsa Brokers")</f>
+        <f>COUNTIF(Matches!G2:G9,"Realsa Brokers")</f>
         <v/>
       </c>
     </row>
@@ -680,7 +754,7 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS(Matches!N2:N11,"&lt;=7",Matches!N2:N11,"&gt;=0")</f>
+        <f>COUNTIFS(Matches!N2:N9,"&lt;=7",Matches!N2:N9,"&gt;=0")</f>
         <v/>
       </c>
     </row>
@@ -691,7 +765,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>SUM(Matches!M2:M11)</f>
+        <f>SUM(Matches!M2:M9)</f>
         <v/>
       </c>
     </row>
@@ -738,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -894,16 +968,16 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Mandato de SERVICIO</t>
+          <t>Estado BUSCA inmueble</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -913,12 +987,12 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TASACION COMERCIAL DE INMUEBLE</t>
+          <t>SERVICIO DE ARRIENDO INMUEBLES PARA OFICINAS</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
@@ -928,7 +1002,7 @@
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -938,21 +1012,21 @@
       </c>
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:00</t>
+          <t>2026-08-31 16:00</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>3994-21-L126</t>
+          <t>1743-64-LE26</t>
         </is>
       </c>
       <c r="Q2" s="13" t="inlineStr">
         <is>
-          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14) | UNSPSC 80131800 (+40)</t>
+          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
         </is>
       </c>
       <c r="R2" s="13" t="inlineStr">
@@ -962,12 +1036,12 @@
       </c>
       <c r="S2" s="13" t="inlineStr">
         <is>
-          <t>SE REQUIERE TASACION COMERCIAL DE INMUEBLE UBICADA EN EMILIO REDARD OLIVAR ALTO CORRESPONDIENTE AL LOTE A-4</t>
+          <t>La necesidad de contratar el servicio de arriendo de uno o más inmuebles que cuenten con las características descritas en las presentes Bases.</t>
         </is>
       </c>
       <c r="T2" s="11" t="inlineStr">
         <is>
-          <t>FABIAN ENCINA TAPIA</t>
+          <t>Sergio Gajardo Donoso</t>
         </is>
       </c>
       <c r="U2" s="11" t="inlineStr"/>
@@ -1013,22 +1087,22 @@
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLE PARA BODEGA Y ARCHIVOS INMEDIATOS DE DISTINTAS DIRECCIONES MUNICIPALES</t>
+          <t>ARRIENDO DE INMUEBLE PARA OFICINA Y RESIDENCIA</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Región del Biobío</t>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -1038,16 +1112,16 @@
       </c>
       <c r="M3" s="11" t="n"/>
       <c r="N3" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:00</t>
+          <t>2026-08-31 16:00</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>2760-98-LE26</t>
+          <t>2495-16-CO26</t>
         </is>
       </c>
       <c r="Q3" s="13" t="inlineStr">
@@ -1062,12 +1136,12 @@
       </c>
       <c r="S3" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLE PARA BODEGA Y ARCHIVOS INMEDIATOS DE DISTINTAS DIRECCIONES MUNICIPALES</t>
+          <t>ARRIENDO DE INMUEBLE PARA OFICINAS ADMINISTRATIVAS DEL CENTRO RAYEN Y UN ESPACIO RESIDENCIAL, PARA LA RESIDENCIA TRANSITORIA, SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS.</t>
         </is>
       </c>
       <c r="T3" s="11" t="inlineStr">
         <is>
-          <t>Javier Valencia Labarca</t>
+          <t>GABRIELA OSORIO AGUILAR</t>
         </is>
       </c>
       <c r="U3" s="11" t="inlineStr"/>
@@ -1108,27 +1182,27 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Realsa Brokers</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO INMUEBLES PARA OFICINAS</t>
+          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región del Biobío</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -1138,16 +1212,16 @@
       </c>
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00</t>
+          <t>2026-09-08 15:30</t>
         </is>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t>1743-64-LE26</t>
+          <t>2359-13-LP26</t>
         </is>
       </c>
       <c r="Q4" s="13" t="inlineStr">
@@ -1157,17 +1231,17 @@
       </c>
       <c r="R4" s="13" t="inlineStr">
         <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
         </is>
       </c>
       <c r="S4" s="13" t="inlineStr">
         <is>
-          <t>La necesidad de contratar el servicio de arriendo de uno o más inmuebles que cuenten con las características descritas en las presentes Bases.</t>
+          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
         </is>
       </c>
       <c r="T4" s="11" t="inlineStr">
         <is>
-          <t>Sergio Gajardo Donoso</t>
+          <t>Victor Sandoval Arias</t>
         </is>
       </c>
       <c r="U4" s="11" t="inlineStr"/>
@@ -1178,100 +1252,102 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: monto UF 3524.0-&gt;3523.0</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D5" s="18" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Estado BUSCA inmueble</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Realsa Brokers</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>ARRIENDO DE INMUEBLE PARA OFICINA Y RESIDENCIA</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo - Folio 852 - DIDECO</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>no publicado</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-31 16:00</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>2495-16-CO26</t>
-        </is>
-      </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R5" s="13" t="inlineStr">
-        <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
-        </is>
-      </c>
-      <c r="S5" s="13" t="inlineStr">
-        <is>
-          <t>ARRIENDO DE INMUEBLE PARA OFICINAS ADMINISTRATIVAS DEL CENTRO RAYEN Y UN ESPACIO RESIDENCIAL, PARA LA RESIDENCIA TRANSITORIA, SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS.</t>
-        </is>
-      </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>GABRIELA OSORIO AGUILAR</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="14" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>CLP 144,000,000</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>3523</v>
+      </c>
+      <c r="N5" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>2713-157-LP26</t>
+        </is>
+      </c>
+      <c r="Q5" s="19" t="inlineStr">
+        <is>
+          <t>objeto/desc: inmueble (+7) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R5" s="19" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S5" s="19" t="inlineStr">
+        <is>
+          <t>La Municipalidad de Aysén –en adelante Municipalidad - llama a presentar ofertas para el arrendamiento de un bien inmueble destinado al funcionamiento del Centro de las Mujeres y demás programas en convenio con SERNAMEG para el Departamento de Desarrollo Comunitario DIDECO de la Municipalidad de Aysén por un periodo de tres años</t>
+        </is>
+      </c>
+      <c r="T5" s="18" t="inlineStr">
+        <is>
+          <t>Victor Godoy Tapia</t>
+        </is>
+      </c>
+      <c r="U5" s="18" t="inlineStr"/>
+      <c r="V5" s="21" t="inlineStr">
         <is>
           <t>Ver ficha</t>
         </is>
@@ -1294,16 +1370,16 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Estado BUSCA inmueble</t>
+          <t>Estado OFRECE inmueble</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1313,22 +1389,22 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
+          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Región del Biobío</t>
+          <t>Región de Coquimbo</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
@@ -1338,21 +1414,21 @@
       </c>
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>2026-09-08 15:30</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>2359-13-LP26</t>
+          <t>4295-54-LR26</t>
         </is>
       </c>
       <c r="Q6" s="13" t="inlineStr">
         <is>
-          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
         </is>
       </c>
       <c r="R6" s="13" t="inlineStr">
@@ -1362,12 +1438,12 @@
       </c>
       <c r="S6" s="13" t="inlineStr">
         <is>
-          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
+          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>Victor Sandoval Arias</t>
+          <t>Dirección de Administración y Finanzas</t>
         </is>
       </c>
       <c r="U6" s="11" t="inlineStr"/>
@@ -1378,202 +1454,202 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: monto UF 122351.0-&gt;122336.0</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>Región de Tarapacá</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>CLP 5,000,000,000</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>122336</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>5358-9-LR26</t>
+        </is>
+      </c>
+      <c r="Q7" s="19" t="inlineStr">
+        <is>
+          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
+        </is>
+      </c>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S7" s="19" t="inlineStr">
+        <is>
+          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
+        </is>
+      </c>
+      <c r="T7" s="18" t="inlineStr">
+        <is>
+          <t>Jorge Bernal Peralta</t>
+        </is>
+      </c>
+      <c r="U7" s="18" t="inlineStr"/>
+      <c r="V7" s="21" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Estado BUSCA inmueble</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>Servicio de arriendo - Folio 852 - DIDECO</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>CLP 144,000,000</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>3524</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:30</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>2713-157-LP26</t>
-        </is>
-      </c>
-      <c r="Q7" s="13" t="inlineStr">
-        <is>
-          <t>objeto/desc: inmueble (+7) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R7" s="13" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S7" s="13" t="inlineStr">
-        <is>
-          <t>La Municipalidad de Aysén –en adelante Municipalidad - llama a presentar ofertas para el arrendamiento de un bien inmueble destinado al funcionamiento del Centro de las Mujeres y demás programas en convenio con SERNAMEG para el Departamento de Desarrollo Comunitario DIDECO de la Municipalidad de Aysén por un periodo de tres años</t>
-        </is>
-      </c>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>Victor Godoy Tapia</t>
-        </is>
-      </c>
-      <c r="U7" s="11" t="inlineStr"/>
-      <c r="V7" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>Realsa Brokers</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>CONCESIÓN DE LOCALES COMERCIALES PASEO SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Región del Maule</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>Región de los Lagos</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>no publicado</t>
         </is>
       </c>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-27 18:00</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>552578-38-L126</t>
-        </is>
-      </c>
-      <c r="Q8" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: locales comerciales (+10) | transaccion/desc: arriendo (+6) | UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="P8" s="26" t="inlineStr">
+        <is>
+          <t>1063538-206-I226</t>
+        </is>
+      </c>
+      <c r="Q8" s="27" t="inlineStr">
+        <is>
+          <t>UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R8" s="27" t="inlineStr">
         <is>
           <t>proceso menor o sin ponderacion fuerte de experiencia</t>
         </is>
       </c>
-      <c r="S8" s="13" t="inlineStr">
-        <is>
-          <t>Con la intención de fomentar el desarrollo productivo y la participación local de los emprendedores de la comuna de San Rafael, se abre la convocatoria para entregar en arriendo 8 locales comerciales del espacio llamado ‘‘Paseo San Rafael’’, con la finalidad de que dicha comercialización sea de productos de interés para la comunidad. Según Bases Administrativas.</t>
-        </is>
-      </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>Héctor Ramírez Calderón</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="inlineStr"/>
-      <c r="V8" s="14" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
+        <is>
+          <t>El Hospital Base San José de Osorno, en adelante también “el Hospital”, llama a propuesta privada para generar un convenio de Arriendo de celdas de media tensión MT del Hospital Base San Jose Osorno. La forma de la presente licitación pública corresponde a aquella adquisición mayor o igual a 5.000 UTM y menor a 10.000 UTM.</t>
+        </is>
+      </c>
+      <c r="T8" s="26" t="inlineStr">
+        <is>
+          <t>Yasna Albarran</t>
+        </is>
+      </c>
+      <c r="U8" s="26" t="inlineStr"/>
+      <c r="V8" s="28" t="inlineStr">
         <is>
           <t>Ver ficha</t>
         </is>
@@ -1590,86 +1666,88 @@
           <t>VIGENTE</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Estado OFRECE inmueble</t>
+          <t>Mandato de SERVICIO</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Realsa Brokers</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
+          <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Región de Coquimbo</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>no publicado</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="n"/>
+          <t>CLP 45,000,000</t>
+        </is>
+      </c>
+      <c r="M9" s="30" t="n">
+        <v>1101</v>
+      </c>
       <c r="N9" s="11" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00</t>
+          <t>2026-08-31 15:00</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>4295-54-LR26</t>
+          <t>867990-62-LE26</t>
         </is>
       </c>
       <c r="Q9" s="13" t="inlineStr">
         <is>
-          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
+          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14)</t>
         </is>
       </c>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
         </is>
       </c>
       <c r="S9" s="13" t="inlineStr">
         <is>
-          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
+          <t>El objeto de la presente licitación es la contratación del servicio de tasación de bienes inmuebles institucionales de la Universidad de Santiago de Chile, con el propósito de actualizar la información patrimonial de la Institución mediante la determinación del valor razonable de sus activos inmobiliarios, de conformidad con las Normas Internacionales de Información Financiera IFRS, las Normas Internacionales de Valoración IVS vigentes y demás normativa técnica aplicable, de acuerdo con las condiciones que se detallan en el Título II de las presentes bases de licitación.</t>
         </is>
       </c>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>Dirección de Administración y Finanzas</t>
+          <t>meliza cabello</t>
         </is>
       </c>
       <c r="U9" s="11" t="inlineStr"/>
@@ -1679,212 +1757,8 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>Región de Tarapacá</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>CLP 5,000,000,000</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>122351</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:01</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>5358-9-LR26</t>
-        </is>
-      </c>
-      <c r="Q10" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
-        </is>
-      </c>
-      <c r="R10" s="13" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S10" s="13" t="inlineStr">
-        <is>
-          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>Jorge Bernal Peralta</t>
-        </is>
-      </c>
-      <c r="U10" s="11" t="inlineStr"/>
-      <c r="V10" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Mandato de SERVICIO</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Realsa Brokers</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>CLP 45,000,000</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>1101</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:00</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>867990-62-LE26</t>
-        </is>
-      </c>
-      <c r="Q11" s="13" t="inlineStr">
-        <is>
-          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14)</t>
-        </is>
-      </c>
-      <c r="R11" s="13" t="inlineStr">
-        <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
-        </is>
-      </c>
-      <c r="S11" s="13" t="inlineStr">
-        <is>
-          <t>El objeto de la presente licitación es la contratación del servicio de tasación de bienes inmuebles institucionales de la Universidad de Santiago de Chile, con el propósito de actualizar la información patrimonial de la Institución mediante la determinación del valor razonable de sus activos inmobiliarios, de conformidad con las Normas Internacionales de Información Financiera IFRS, las Normas Internacionales de Valoración IVS vigentes y demás normativa técnica aplicable, de acuerdo con las condiciones que se detallan en el Título II de las presentes bases de licitación.</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>meliza cabello</t>
-        </is>
-      </c>
-      <c r="U11" s="11" t="inlineStr"/>
-      <c r="V11" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V11"/>
+  <autoFilter ref="A1:V9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId2"/>
@@ -1894,8 +1768,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1907,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2099,7 +1971,7 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J4" s="11" t="n">
@@ -2143,7 +2015,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
@@ -2187,7 +2059,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J6" s="11" t="n">
@@ -2224,7 +2096,7 @@
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
@@ -2233,7 +2105,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
@@ -2321,7 +2193,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
@@ -2358,7 +2230,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122351</v>
+        <v>122336</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2367,7 +2239,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
@@ -2377,46 +2249,90 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>1063538-206-I226</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>867990-62-LE26</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Realsa Brokers</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Publicada</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>2026-08-31 15:00</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>1101</v>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n">
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2431,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2568,124 +2484,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIO DE TASACION COMERCIAL INMUEBLE CALLE DOCTOR LAGARRIGUE S/N, COQUIMBO</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Región de Coquimbo</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>CLP 3,000,000</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>&lt; 100 UTM (~&lt; UF 170)</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:00</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>bajo umbral de monto (Nacional, UF 73 (umbral UF 2.000))</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>894863-37-L126</t>
-        </is>
-      </c>
-      <c r="L3" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIO DE ARRIENDO STAND PDI</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>CLP 20,000,000</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>489</v>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>obras 100-1.000 UTM</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-27 15:10</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>bajo umbral de monto (RM, UF 489 (umbral UF 500))</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>2981-239-CO26</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Estas licitaciones SI calzan con el servicio, pero quedan fuera por monto o plazo. Ojo: Mercado Publico publica el valor del CONTRATO (honorario), no el valor del activo — una tasacion de un edificio grande puede aparecer como UF 73. Revisar antes de descartar.</t>
         </is>
@@ -2694,8 +2494,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2707,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2741,12 +2539,12 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>1012975-14-L126</t>
+          <t>1002772-88-LR26</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO PARA TRASLADOS DE PROFESIONALES DE SERNAMEG CONVENIO DE TRANSFERENCIA DE RECURSOS Y EJECUCION PROYECTO MULTAS VIF.VER DETALLE ANEXO ECONOMICO</t>
+          <t>PRÓTESIS DE RODILLA EN CONSIGNACIÓN CON COMODATO</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
@@ -2781,12 +2579,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1057049-273-LR26</t>
+          <t>1052836-6-LE26</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
+          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
@@ -2801,12 +2599,12 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1057049-285-LR26</t>
+          <t>1057049-273-LR26</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
@@ -2821,12 +2619,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1057049-293-LE26</t>
+          <t>1057049-285-LR26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JCD CRIOSONDA FLEXIBLE FUS 4062026 CON COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
@@ -2861,12 +2659,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1057055-68-LP26</t>
+          <t>1057049-321-LE26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
@@ -2881,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1057404-82-LE26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2901,12 +2699,12 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1057417-183-LP26</t>
+          <t>1057055-68-LP26</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
@@ -2921,32 +2719,32 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1057429-28-LP26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACTIVOS HORMONALES CON EQUIPO EN COMODATO </t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057429-52-LP26</t>
+          <t>1057404-82-LE26</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS HEMATOLOGICOS VHS Y EQUIPOS EN COMODATO</t>
+          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -2961,12 +2759,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057429-53-LP26</t>
+          <t>1057417-183-LP26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS GASES EN SANGRE CON EQUIPOS EN COMODATO</t>
+          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -2981,12 +2779,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057472-92-LP26</t>
+          <t>1057417-51-LP26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
+          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
@@ -3001,32 +2799,32 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057420-37-LP26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057490-50-LR26</t>
+          <t>1057429-28-LP26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Lavado y Administración de Ropa.</t>
+          <t xml:space="preserve">REACTIVOS HORMONALES CON EQUIPO EN COMODATO </t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
@@ -3041,12 +2839,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057490-57-LP26</t>
+          <t>1057429-53-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
+          <t>REACTIVOS GASES EN SANGRE CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -3061,12 +2859,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057490-65-LE26</t>
+          <t>1057472-92-LP26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
+          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
@@ -3081,12 +2879,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057492-111-LP26</t>
+          <t>1057480-46-LR26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -3101,32 +2899,32 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057501-396-LP26</t>
+          <t>1057489-255-LE26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para paneles de biología con procesamiento directo desde muestra con equipo en comodato por 24 meses</t>
+          <t>Funcionamiento y Habilitación de nueva Bodega</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057490-50-LR26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>Arriendo Lavado y Administración de Ropa.</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -3141,12 +2939,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057490-57-LP26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -3161,12 +2959,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057503-117-LP26</t>
+          <t>1057490-65-LE26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Servicio de arriendo de equipos de monitoreo</t>
+          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -3181,12 +2979,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057539-118-LP26</t>
+          <t>1057492-111-LP26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
+          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -3201,32 +2999,32 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057547-347-LP26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>CONV. ARRIENDO SERV. CIRUGIA ENDOSCOPICA LUMBAR 2-</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057547-348-LE26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION BRONCOSCOPIOS DESECHABLES CON COMODATO DE MONITOR</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
@@ -3241,32 +3039,32 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057501-488-LE26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057547-354-LP26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
@@ -3281,12 +3079,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057736-6-L126</t>
+          <t>1057503-125-LE26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
+          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -3301,72 +3099,72 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057922-23-LE26</t>
+          <t>1057509-253-LE26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPAMIENTO GENERAL PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
+          <t>CONVENIO COMPRA SERVICIOS PROFESIONALES DE TERAPEUTA OCUPACIONAL PARA PROYECTO DE NEUROREHABILITACIÓN PARA USUARIOS SECUELADOS DE ATAQUE CEREBROVASCULAR mjv</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057977-12-LE26</t>
+          <t>1057539-118-LP26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>cierro terreno futuro H. Rio Negro Hornopiren</t>
+          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1071775-12-LE26</t>
+          <t>1057547-348-LE26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>TRASLADO DE ESTUDIANTES ULAGOS SEDE CHILOÉ -PIDPID</t>
+          <t>ADQUISICION BRONCOSCOPIOS DESECHABLES CON COMODATO DE MONITOR</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1075963-309-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -3381,12 +3179,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1075963-315-LP26</t>
+          <t>1057547-354-LP26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
+          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -3401,56 +3199,56 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1075963-324-LE26</t>
+          <t>1057736-6-L126</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN FÁRMACOS DE PRODUCTOS OFICINALES Y MATERIA PRIMA</t>
+          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1078177-45-LE26</t>
+          <t>1057922-22-LP26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE SERVICIO DE CAMBIO DE VENTANAS PARA LA ZONA DE CARABINEROS ARAUCANÍA.</t>
+          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1080936-43-LE26</t>
+          <t>1057977-12-LE26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DEL SISTEMA DE DETECCIÓN ALARMA Y CONTROL DE INCENDIO DEL EDIFICIO DE LA ESCUELA DE INVESTIGACIONES POLICIALES</t>
+          <t>cierro terreno futuro H. Rio Negro Hornopiren</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
@@ -3461,92 +3259,92 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1109692-8-LE26</t>
+          <t>1070620-86-LP26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
+          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1110404-155-L126</t>
+          <t>1071775-12-LE26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
+          <t>TRASLADO DE ESTUDIANTES ULAGOS SEDE CHILOÉ -PIDPID</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1126920-29-LE26</t>
+          <t>1075963-309-LP26</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE RELOJ CONTROL P02-P01-JJ</t>
+          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1126922-33-LP26</t>
+          <t>1075963-315-LP26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1134432-67-LE26</t>
+          <t>1078177-45-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
+          <t>ADQUISICION DE SERVICIO DE CAMBIO DE VENTANAS PARA LA ZONA DE CARABINEROS ARAUCANÍA.</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
@@ -3554,83 +3352,83 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1155683-16-L126</t>
+          <t>1079969-19-LP26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE ARRIENDO DE 2 AIRES ACONDICIONADO INVERTER CON INSTALACIÓN POR UN PERIODO DE 12 MESES EN OFICINA CONAF ÑUBLE”</t>
+          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1160-14-LE26</t>
+          <t>1080936-43-LE26</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
+          <t>SERVICIO DE MANTENCIÓN DEL SISTEMA DE DETECCIÓN ALARMA Y CONTROL DE INCENDIO DEL EDIFICIO DE LA ESCUELA DE INVESTIGACIONES POLICIALES</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1160-15-LE26</t>
+          <t>1099402-21-L126</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
+          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1180830-16-LR26</t>
+          <t>1109692-8-LE26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
@@ -3641,12 +3439,12 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1191688-57-LP26</t>
+          <t>1110404-155-L126</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Mat. y Arriendo Bomba para Estanque Lo Blanco</t>
+          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
@@ -3661,192 +3459,192 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1202333-74-LE26</t>
+          <t>1110404-165-L126</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE INFRAESTRUCTURA STAND DE VENTA SECTOR VIP Y OBRAS CIVILES PARA FIESTA COSTUMBRISTA 2026”.</t>
+          <t>ADQUISICIÓN DE MATERIALES DE OFICINA Y APOYO PEDAGÓGICO PARA ESTABLECIMIENTOS EDUCACIONALES DEL SLEP CHINCHORRO</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1202333-75-LE26</t>
+          <t>1126922-33-LP26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS QUIMICOS</t>
+          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1208985-7-LP26</t>
+          <t>1134432-67-LE26</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN RESIDENCIA FAMILIAR ADOLESCENTE P.ARE</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1227-3-LP26</t>
+          <t>1160-14-LE26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>SERV DE TRASLADO ESTIBA Y DESESTIBA DE MERCANCIAS</t>
+          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1160-15-LE26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1280-40-LE26</t>
+          <t>1165648-6-L126</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS RODILLOS LISOS</t>
+          <t>SERVICIO INTEGRAL DE MANTENIMIENTO PREVENTIVO, ASISTENCIA TÉCNICA, DIAGNÓSTICO, ATENCIÓN CORRECTIVA Y SOPORTE CONTINUO PARA SILLONES DENTALES Y COMPRESOR DEL DEPARTAMENTO DE SALUD MUNICIPAL DE LIMACHE</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1180730-37-LP26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1180830-16-LR26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1320138-2-LP26</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO FNDR HABILITACIÓN BODEGA EDIFICIO EX MOL</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1336-18-LP26</t>
+          <t>1232565-33-LE26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
+          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
@@ -3861,92 +3659,92 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1350-7-LE26</t>
+          <t>1233615-56-LE26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
+          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1360-8-LE26</t>
+          <t>1261-19-LR26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MONITOREO DE ALARMAS PARA LAS OFICINAS DE LA DIRECCIÓN REGIÓN METROPOLITANA DEL SERVICIO DE REGISTRO CIVIL E IDENTIFICACIÓN</t>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1395865-13-LE26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN PREVENTIVA  ÁREA ELÉCTRICA - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1415863-2-LE26</t>
+          <t>1280-41-LE26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1280-42-LE26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
@@ -3961,92 +3759,92 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1293138-13-LP26</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1426037-25-LE26</t>
+          <t>1305527-3-LP26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>RETIRO TRASLADO E INSTALACIÓN DE GALPÓN</t>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1426098-12-LP26</t>
+          <t>1336-18-LP26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
+          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1350-7-LE26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1460278-46-L126</t>
+          <t>1395865-16-LE26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
+          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
@@ -4054,39 +3852,39 @@
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1469-166-L126</t>
+          <t>1415863-2-LE26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
+          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1499-164-LP26</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DGM MANGA COMPRESIVA DESTINADA A TERAPIA DE COMPRESIÓN NEUMÁTICA INTERMITENTE PARA PREVENCIÓN DE TROMBOSIS VENOSA PROFUNDA EN PACIENTES HOSPITALIZADOS O CON MOVILIDAD REDUCIDA CON EQUIPO EN COMODATOS </t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
@@ -4101,12 +3899,12 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1499-170-LE26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>SAM MONITOR DESFIBRILADOR CAMILLA DE TRASLADO DE PACIENTES Y OXÍMETRO DE PULSO</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
@@ -4121,92 +3919,92 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1499-174-LE26</t>
+          <t>1426098-12-LP26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>SAM SERVICIO DE DESARMADO TRASLADO Y ARMADO DE KARDEX VERTICAL MARCA GRIFOLS MODELO SYS 12012</t>
+          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1501-5-O126</t>
+          <t>1443-1-LE26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PISCINA INFILTRACIÓN PTAS SAN PEDRO DE ATACAMA</t>
+          <t>Servicio de bodegaje y almacenamiento</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1515304-164-LE26</t>
+          <t>1448821-14-LP26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>ADQ DE EN ARRIENDO DE 02 VAN Y 01 SUV</t>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1532-47-L126</t>
+          <t>1460278-46-L126</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SISTEMAS SECTORIALES VENTANILLA UNICA</t>
+          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1549-67-LE26</t>
+          <t>1464-58-L126</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 02 DERMATOMOS PARA PABELLÓN AMBULATORI</t>
+          <t>TELE ELECTROCARDIOGRAFIA: ARRIENDO DE EQUIPO E INF</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
@@ -4221,32 +4019,32 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1469-166-L126</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
@@ -4261,72 +4059,72 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1554-55-LR26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1605-45-LP26</t>
+          <t>1605-41-LP26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+          <t>LP-4872 Servicios de mantención general edificios</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1638-81-LE26</t>
+          <t>1605-45-LP26</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
+          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1641-219-LR26</t>
+          <t>162-26-LE26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>Servicio traslado de muestras a los Laboratorios</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
@@ -4341,12 +4139,12 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1655-23-LP26</t>
+          <t>1624-21-L126</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+          <t>Convenio de suministros de Oxígeno Médico, Recarga y Arriendo de cilindros para servicios Urgencias y Hospitalizados</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
@@ -4361,16 +4159,16 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1658-147-LE26</t>
+          <t>1638-81-LE26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
+          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
@@ -4381,112 +4179,112 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>1641-219-LR26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1671-30-LE26</t>
+          <t>1655-23-LP26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
+          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1696-11-LE26</t>
+          <t>1658-147-LE26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
+          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1658-189-LP26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1736-89-LE26</t>
+          <t>1671-30-LE26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO E INSTALCION DE JUEGOS</t>
+          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1851-26-LE26</t>
+          <t>1696-11-LE26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
+          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
@@ -4501,12 +4299,12 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1867-39-LP26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>Servicio de traslado terrestre de SLCs</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
@@ -4521,112 +4319,112 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1905-2-LE26</t>
+          <t>1851-26-LE26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
+          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>score 4 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1947-130-LP26</t>
+          <t>1905-2-LE26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 4 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>1949-1-LP26</t>
+          <t>1947-130-LP26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1979-182-LE26</t>
+          <t>1949-1-LP26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>2078-39-LE26</t>
+          <t>1978-100-L126</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
+          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>2080-248-LP26</t>
+          <t>1979-182-LE26</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>SUM. KITS DIAGNOSTICO MOLECULAR CON EQ. COMODATO</t>
+          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
@@ -4641,12 +4439,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>2080-261-LP26</t>
+          <t>2078-39-LE26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
+          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
@@ -4661,96 +4459,96 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>2101-136-L126</t>
+          <t>2080-261-LP26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES Y ARTÍCULOS DE ESCRITORIO PARA BODEGA DE ECONOMATO Y VACUNATORIO”</t>
+          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>2102-25-LE26</t>
+          <t>2098-124-LE26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CONSERVACION UNIDAD DE URGENCIAS HSIL</t>
+          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>2107-130-LE26</t>
+          <t>2098-127-LE26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>2107-136-LE26</t>
+          <t>2098-133-LP26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>2173-27-LE26</t>
+          <t>2098-134-LP26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
@@ -4761,12 +4559,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>2178-17-LE26</t>
+          <t>2107-130-LE26</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE PARA TRASLADO NOTIFICADORES</t>
+          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
@@ -4781,52 +4579,52 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>2184-11-LE26</t>
+          <t>2107-136-LE26</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>Serv mant cubiertas edificios Jurisdicción CAPJ SM</t>
+          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>2189-6-LE26</t>
+          <t>2109-10-LP26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPOS PARA CASA DEL DONANTE SSM</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>2251-11-LE26</t>
+          <t>2126-128-LE26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>Servicio de arriendo de plataforma Adobe Connect</t>
+          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
@@ -4841,32 +4639,32 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>2258-133-LR26</t>
+          <t>2173-27-LE26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2258-133-LR26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
@@ -4881,12 +4679,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>2258-72-LE26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
@@ -4901,12 +4699,12 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>2271-65-LE26</t>
+          <t>2258-72-LE26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
@@ -4921,32 +4719,32 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2271-65-LE26</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>2282-96-LE26</t>
+          <t>2273-55-LE26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
+          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
@@ -4961,52 +4759,52 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2275-29-LE26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>2308-72-LE26</t>
+          <t>2282-96-LE26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>2320-26-LE26</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -5021,12 +4819,12 @@
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2322-72-LE26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>Regularización del Activo Fijo  Inventario Munici</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
@@ -5041,32 +4839,32 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2332-98-L126</t>
+          <t>2308-72-LE26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MONTAJE DE LENTES ÓPTICOS PARA LA UNIDAD DE ATENCIÓN PRIMARIA OFTALMOLÓGICA DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2360-67-LE26</t>
+          <t>2320-26-LE26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE RECARGA Y ARRIENDO DE CILINDROS DE OXIGENO Y AIRE MEDICINAL PARA CESFAM DE LA COMUNA</t>
+          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
@@ -5081,12 +4879,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2366-54-LE26</t>
+          <t>2322-72-LE26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+          <t>Regularización del Activo Fijo  Inventario Munici</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
@@ -5101,12 +4899,12 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2366-64-LE26</t>
+          <t>2324-107-L126</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>8HABILITACION DE LAVAMANOS PSR SAN MIGUEL M.147</t>
+          <t>LICITACIÓN PÚBLICA N° 1032026 “SERVICIO DE ARRIENDO DE AMPLIFICACIÓN Y BAÑOS QUÍMICOS PARA ACTIVIDADES DEL MES DE LA PATRIA 2026 - DIRECCIÓN DE DESARROLLO COMUNITARIO - MUNICIPALIDAD DE PUERTO MONTT”</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
@@ -5121,16 +4919,16 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>2369-64-LP26</t>
+          <t>2332-101-L126</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>PP 69 Implementación bodegas resguardo de fichas</t>
+          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
@@ -5141,32 +4939,32 @@
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>2385-51-LE26</t>
+          <t>2332-102-L126</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO Y MONTAJE DE GRADERÍAS FIESTA DE AYQUINA 2026</t>
+          <t>MALLA MOSQUITERA E INSTALACIÓN DE ACRÍLICOS PARA SEGREGACIÓN ÁREA SUCIA SAPU Y CESFAM PADRE HURTADO Y CECOSF PUERTA SUR DEL DEPARTAMENTO DE SALUD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2402-72-CO26</t>
+          <t>2366-54-LE26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
+          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
@@ -5181,72 +4979,72 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2402-74-L126</t>
+          <t>2369-64-LP26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
+          <t>PP 69 Implementación bodegas resguardo de fichas</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2408-177-LE26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE BAÑOS QUÍMICOS FIESTAS PATRIAS EN LOS ÁNGELES 2026.</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2409-86-L126</t>
+          <t>2402-72-CO26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
+          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
@@ -5261,56 +5059,56 @@
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2410-35-LP26</t>
+          <t>2402-74-L126</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
+          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2410-46-LE26</t>
+          <t>2402-75-LE26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS Y EQUIPAMIENTO PARA EL DEPARTAMENTO DE SEGURIDAD</t>
+          <t>ARRIENDO E INST. TEMPORAL CAMARAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2410-83-LE26</t>
+          <t>2402-76-LE26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
+          <t>SEGURIDAD RECINTO CELEBRACION FIESTAS PATRIAS 2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -5321,36 +5119,36 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2410-84-LE26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2416-22-LE26</t>
+          <t>2408-160-LP26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
+          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
@@ -5361,92 +5159,92 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2430-57-LP26</t>
+          <t>2408-210-L126</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>“HABILITACIÓN ALUMBRADO PÚBLICO ACCESO LA PORTADA COMUNA DE ANTOFAGASTA”</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS VARIOS PARA CABAÑAS RECINTO CHACAY.</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2430-69-LP26</t>
+          <t>2409-86-L126</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
+          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2430-71-LP26</t>
+          <t>2409-91-L126</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+          <t>SERVICIO TRASLADO ALUMNOS TALLER  EXTRAESCOLAR Y JORNADAS REFLEXION, ESCUELA D-870</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2445-102-LP26</t>
+          <t>2410-35-LP26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION SALAS DE ESPERA SP787</t>
+          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2452-19-L126</t>
+          <t>2410-83-LE26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
+          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
@@ -5461,36 +5259,36 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2410-84-LE26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2460-99-LE26</t>
+          <t>2416-22-LE26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
@@ -5501,12 +5299,12 @@
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2483-231-LP26</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
@@ -5521,96 +5319,96 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2490-71-LR26</t>
+          <t>2430-69-LP26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO HABILITACIÓN Y ARRIENDO DE EQUIPAMIENTO TELEFÓNICO PARA LA MUNICIPALIDAD DE PROVIDENCIA”</t>
+          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2430-71-LP26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2546-49-LP26</t>
+          <t>2445-110-LE26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
+          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2548-71-LE26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2548-73-LE26</t>
+          <t>2452-19-L126</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
+          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
@@ -5621,136 +5419,136 @@
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2555-10-LP26</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2565-14-LP26</t>
+          <t>2460-99-LE26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2483-231-LP26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2546-49-LP26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2548-71-LE26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2600-23-LE26</t>
+          <t>2548-73-LE26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>Const. Accesibilidad Universal Edificio Municipal</t>
+          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
@@ -5761,52 +5559,52 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2555-10-LP26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2627-15-LE26</t>
+          <t>2565-14-LP26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
+          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2664-38-L126</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
@@ -5821,272 +5619,272 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2581-37-LP26</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2697-23-LP26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2585-87-LE26</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>ADQ. VEH. ACUATICO Y TODOTERRENO ORD N°167-TURISMO</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2699-32-LR26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Flota Vehicular</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2702-62-LE26</t>
+          <t>2600-23-LE26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
+          <t>Const. Accesibilidad Universal Edificio Municipal</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2755-29-LE26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO TRASLADO CENTRAL DE CAMARAS DE TELEVIGILA</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>2626-8-LE26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2770-109-LR26</t>
+          <t>2627-15-LE26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
+          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>2664-38-L126</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2788-43-LE26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2788-44-LE26</t>
+          <t>2686-120-CO26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
+          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2793-100-CO26</t>
+          <t>2697-23-LP26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
+          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2793-91-LE26</t>
+          <t>2697-25-LR26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2793-97-LE26</t>
+          <t>2699-32-LR26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
+          <t>Servicio de Arriendo de Flota Vehicular</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
@@ -6101,12 +5899,12 @@
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2825-49-L126</t>
+          <t>2702-62-LE26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
+          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
@@ -6121,72 +5919,72 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2905-40-LP26</t>
+          <t>2703-175-L126</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+          <t>SC 12493 Servicio REAS retiro traslado y eliminación de Residuos</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2910-23-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Suministro y comodato de equipo point of care -POC</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2963-26-LR26</t>
+          <t>2730-113-LE26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2736-32-LE26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>Materiales de Oficina</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
@@ -6194,83 +5992,83 @@
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>2744-30-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>2755-34-LE26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>3017-64-LE26</t>
+          <t>2770-109-LR26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE HERRAMIENTAS PARA 24 PROYECTOS PMU-E LOTA</t>
+          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>3117-85-LE26</t>
+          <t>2784-42-LP26</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA EDIFICIO CENTRAL BIENVALP</t>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
@@ -6281,56 +6079,56 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>3172-46-LR26</t>
+          <t>2788-43-LE26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>3172-53-LE26</t>
+          <t>2788-44-LE26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>ESTUDIOS TERRENOS REPOSICIÓN 6°COMISARÍA COLCHANE.</t>
+          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>3172-63-LE26</t>
+          <t>2793-100-CO26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
+          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
@@ -6341,192 +6139,192 @@
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>3179-33-LE26</t>
+          <t>2793-91-LE26</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
+          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>3210-7-L126</t>
+          <t>2793-97-LE26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
+          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>2825-49-L126</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>3263-1-LE26</t>
+          <t>2905-40-LP26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIPO CONE BEAM</t>
+          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>3290-7-LE26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>3378-46-LP26</t>
+          <t>2963-26-LR26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE 02 TORRES DE LAPAROSCOPIA PARA EL DEPARTAMENTO DE PABELLONES QUIRÚRGICOS DEL HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>3420-5-LE26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Mant. y Reparación de 01 Inmueble</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>3428-16-LE26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>Compra Materiales para reparaciones de inmuebles</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>3453-78-LE26</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>ADQ SERV. REP. Y MANT DE OFICINAS PASILLOS Y BAÑOS</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>3477-76-LE26</t>
+          <t>3017-68-LE26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
+          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
@@ -6541,112 +6339,112 @@
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>3479-84-LE26</t>
+          <t>3069-3-LE26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo  Equipo Alza Hombre</t>
+          <t>Traslado de Pasajeros</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>3542-22-LE26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>3565-58-LE26</t>
+          <t>3092-16-L126</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
+          <t>SERVICIOS DE IMPRESION DE CARNET INTEGRAL  DE SALUD  ( ECICEP) PARA  PACIENTES DE LAS POSTAS DE SALUD RURALES  POR EL PROGRAMA MODELO DE ATENCION INTEGRAL DE SALUD FAMILIAR Y COMUNITARIA EN APS DE LA DIRECCION DE SALUD DE LA I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>3587-17-LE26</t>
+          <t>3159-18-LE26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE AGUA PURIFICADA DEPENDENCIAS DSM</t>
+          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>3588-36-LP26</t>
+          <t>3172-46-LR26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO SISTEMA GESTIÓN MUNICIPALIDAD YUNGAY</t>
+          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>3595-25-LE26</t>
+          <t>3172-63-LE26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>Cambio de pavimento edificio consistorial</t>
+          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
@@ -6661,132 +6459,132 @@
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>359-98-LE26</t>
+          <t>3179-44-LE26</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPO EN COMODATO</t>
+          <t>ADQUISICIÓN DE CASACA OPERATIVA CON POLAR</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>359-99-CO26</t>
+          <t>3210-7-L126</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>ADQ ROCURONIO BROMURO CON COMODATO EQUIPO</t>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>3656-148-LP26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>3668-14-LP26</t>
+          <t>3290-7-LE26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3756-41-LE26</t>
+          <t>3333-32-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN ESTACIONAMIENTO VILLA DEPARTAMENTAL PELARCO</t>
+          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3775-28-LP26</t>
+          <t>3384-20-LP26</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3798-13-LP26</t>
+          <t>3436-97-LE26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+          <t>Servicio mantenimiento de dependencias SIC 351978</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
@@ -6801,32 +6599,32 @@
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>3798-15-LP26</t>
+          <t>3477-76-LE26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
+          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>3836-32-LE26</t>
+          <t>3542-22-LE26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN MÓDULO PREFABRICADO PARA OFICINA CON WC</t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
@@ -6841,36 +6639,36 @@
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>3843-30-LE26</t>
+          <t>3565-58-LE26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO INTEGRAL HABILITACION E IMPLEMENTACION DE PATIOS</t>
+          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>3595-25-LE26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>Cambio de pavimento edificio consistorial</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
@@ -6881,36 +6679,36 @@
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>3887-39-LP26</t>
+          <t>3611-11-LE26</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+          <t>Servicio de retiro traslado y eliminación de material cortopunzante residuos médicos y otros del Departamento de Salud Municipal Puerto Saavedra y su CSR de Dominguez</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>3890-162-E226</t>
+          <t>3656-148-LP26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MATERIALES DE OFICINA PARA LOS PROGRAMAS DE DISCAPACIDAD Y PSD</t>
+          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
@@ -6921,16 +6719,16 @@
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>3890-167-L126</t>
+          <t>3668-14-LP26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
+          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
@@ -6941,72 +6739,72 @@
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>3890-171-L126</t>
+          <t>3671-58-LE26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>3934-29-L126</t>
+          <t>3775-28-LP26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE FARMACOS PARA USO EN ESTABLECIMIENTOS DE SALUD DEL DEPARTAMENTO DE SALUD MUNICIPAL FREIRE </t>
+          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>3798-13-LP26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>3948-37-LE26</t>
+          <t>3798-15-LP26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE TRANSPORTE PREESCOLAR</t>
+          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
@@ -7021,36 +6819,36 @@
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>3981-23-LE26</t>
+          <t>3880-61-LE26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN E IMPLEMENTACIÓN DE SALA DE RESGUARDO FAMILIAR MUNICIPAL SALA CUNA</t>
+          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>4031-14-LE26</t>
+          <t>3882-72-LP26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
@@ -7061,16 +6859,16 @@
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>3887-39-LP26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
@@ -7081,36 +6879,36 @@
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>4086-43-LE26</t>
+          <t>3889-41-LP26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO DE EXCAVADORA</t>
+          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>3890-167-L126</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
@@ -7121,32 +6919,32 @@
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>4121-23-LE26</t>
+          <t>3890-171-L126</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>4168-81-LE26</t>
+          <t>3935-83-LP26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE GRADERÍAS MECANO</t>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
@@ -7161,92 +6959,92 @@
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>418-51-LP26</t>
+          <t>3938-25-LE26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>4202-38-LE26</t>
+          <t>3997-59-B226</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de recinto actividad Pasamos Agosto</t>
+          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>4237-12-LR26</t>
+          <t>4006-21-LE26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+          <t>Mejoramiento Area Deportiva Ventanas</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>4238-66-B226</t>
+          <t>4031-14-LE26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>4284-141-L126</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>Contrato suministro leña para calefacción dependencias ELEAM Ayen Ruca según NUMERAL 5 B.A.G Bases administrativas Generales</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
@@ -7261,112 +7059,112 @@
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>4295-41-LP26</t>
+          <t>4086-43-LE26</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+          <t>SERVICIO ARRIENDO DE EXCAVADORA</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>4309-215-LP26</t>
+          <t>4099-22-LP26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>4328-31-B226</t>
+          <t>4121-23-LE26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
+          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>4362-15-LP26</t>
+          <t>4152-28-LE26</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>4362-20-LE26</t>
+          <t>4168-81-LE26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+          <t>ARRIENDO DE GRADERÍAS MECANO</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>438-49-LE26</t>
+          <t>418-51-LP26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
+          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
@@ -7381,52 +7179,52 @@
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>4414-61-LE26</t>
+          <t>4202-39-LE26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
+          <t>Segundo llamado Arriendo recinto Pasamos Agosto</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>45-44-LE26</t>
+          <t>4236-22-L126</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
+          <t>INSTALACIÓN DE VENTANA Y MAMPARA EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>4594-25-LE26</t>
+          <t>4237-12-LR26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
+          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
@@ -7441,12 +7239,12 @@
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>4238-66-B226</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
@@ -7461,32 +7259,32 @@
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>4642-92-LP26</t>
+          <t>4295-41-LP26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
+          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>4642-93-LP26</t>
+          <t>4309-215-LP26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
+          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
@@ -7501,72 +7299,72 @@
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>4644-5-LP26</t>
+          <t>4328-31-B226</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
+          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>4778-18-LE26</t>
+          <t>4342-2-LP26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
+          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>4829-43-L126</t>
+          <t>4362-15-LP26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
+          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>4850-3-LE26</t>
+          <t>4362-20-LE26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>Servicio para reparación edificio</t>
+          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
@@ -7581,32 +7379,32 @@
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>4887-22-L126</t>
+          <t>438-49-LE26</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
+          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>4928-21-LP26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
@@ -7621,52 +7419,52 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>4956-63-LP26</t>
+          <t>4414-61-LE26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
+          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>45-44-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>4956-71-LE26</t>
+          <t>4591-20-LP26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SERVICIOS HIGIENICOS PARA FONDAS</t>
+          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
@@ -7681,32 +7479,32 @@
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>4967-7-LR26</t>
+          <t>4594-25-LE26</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>4993-69-L126</t>
+          <t>4629-26-LE26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MOVILIZACIÓN PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE VIVIENDA CHOLCHOL 2026</t>
+          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
@@ -7721,12 +7519,12 @@
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>5048-13-O126</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
@@ -7741,12 +7539,12 @@
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>4642-92-LP26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
@@ -7761,12 +7559,12 @@
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>5056-98-LP26</t>
+          <t>4642-93-LP26</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CAMAS DE ATENCIÓN INTEGRAL DE PARTO</t>
+          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
@@ -7781,32 +7579,32 @@
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>507428-94-LE26</t>
+          <t>4642-99-LE26</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>5194-4-LE26</t>
+          <t>4644-5-LP26</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
@@ -7821,92 +7619,92 @@
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>4778-18-LE26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>5240-91-LE26</t>
+          <t>4829-43-L126</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
+          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>4850-3-LE26</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>Servicio para reparación edificio</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>528208-38-LE26</t>
+          <t>4887-22-L126</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PROVISIÓN CON INSTALACIÓN DE VENTANAS PARA FACHADA Y REVESTIMIENTO DE ESCALA PARA GALERÍA DE EXPOSICIÓN MEMORIAS CHILE VIETNAM CERRO NAVIA</t>
+          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>5300-50-LP26</t>
+          <t>4920-12-LE26</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
+          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
@@ -7921,112 +7719,112 @@
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>5300-54-LP26</t>
+          <t>4928-21-LP26</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
-          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
+          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>4956-63-LP26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>539119-82-CO26</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA LA REPARACIÓN DE LAS FACHADAS DEL CONJUNTO HABITACIONAL PAJARITOS ADMINISTRADO POR EL DEPARTAMENTO GESTIÓN DE VIVIENDAS Y POBLACIONES B.4 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS.</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>539119-85-LP26</t>
+          <t>4967-7-LR26</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>539119-86-LE26</t>
+          <t>5048-13-O126</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D265" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>5413-65-LE26</t>
+          <t>5056-102-LP26</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
@@ -8041,52 +7839,52 @@
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>5420-20-LE26</t>
+          <t>507428-94-LE26</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t>Diseño eléctrico para normalización de edificios</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>5194-4-LE26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
@@ -8101,12 +7899,12 @@
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>5240-91-LE26</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
@@ -8121,32 +7919,32 @@
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>5626-9-LP26</t>
+          <t>525512-33-LE26</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS PARA HABILITACIÓN DE AUDITORIO Y SALAS</t>
+          <t>Diseño proyecto construcción sede social JJVV</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>564953-61-LP26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t>Servicio de traslado de estudiantes</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
@@ -8161,192 +7959,192 @@
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>5722-4-L126</t>
+          <t>5300-50-LP26</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t>Traslado Materiales a Lugar De Acopio, Obra Restauración Y Ampliación Del Museo De Arte Contemporáneo Valdivia</t>
+          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>575924-9-E226</t>
+          <t>5300-54-LP26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
+          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>607-60-LE26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t>MEJOR. DEPENDENCIAS SERVICIO SOCIAL Y OIRS</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>608-126-LR26</t>
+          <t>539119-81-LE26</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>613-6-LE26</t>
+          <t>539119-85-LP26</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE OFICINAS SECTOR ZÓCALO EDIFICIO SE</t>
+          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>539119-86-LE26</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D279" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>627786-14-LE26</t>
+          <t>5413-65-LE26</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
+          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>5413-67-LE26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>5420-20-LE26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>Diseño eléctrico para normalización de edificios</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
@@ -8361,16 +8159,16 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>640-2-LP26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REPARACIONES OBRAS MENORES OFICINAS</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
@@ -8381,32 +8179,32 @@
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>673-3-LE26</t>
+          <t>5558-5-L126</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
+          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
@@ -8421,16 +8219,16 @@
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>557639-74-LE26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
@@ -8441,52 +8239,52 @@
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>677-6-LP26</t>
+          <t>5586-126-LE26</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>Elab. Diag. Plan Maestro y Plan de Gestión. Lonco</t>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D287" s="13" t="inlineStr">
         <is>
-          <t>score 23 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>682-3-LE26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>697057-30-LE26</t>
+          <t>575924-9-E226</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
@@ -8501,52 +8299,52 @@
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>608-126-LR26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>730377-1-L126</t>
+          <t>622-55-LE26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>Servicio de arriendo de dispensadores de agua purificada para 2°Juzgado de Familia de San Miguel</t>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
@@ -8561,136 +8359,136 @@
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>731159-2-L126</t>
+          <t>627786-14-LE26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
+          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>732434-19-LE26</t>
+          <t>633-48-LR26</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN CUBIERTAS VARIOS RECINTOS CSC</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>734-47-L126</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>ASESORÍA TECNICA ADMINISTRATIVA DE LA SECCIÓN DE EQUIPAMIENTO PARA EL SUBDEPARTAMENTO DE RECURSOS FISICOS E INVERSIONES DEL SERVICIO DE SALUD AYSÉN</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>score 3 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>735949-1-LE26</t>
+          <t>649-8-LE26</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA EL DEPARTAMENTO DE DESARROLLO RURAL</t>
+          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>score 7 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>739231-17-LP26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Area de Juegos en Sector Costanera de Puerto Octay</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>742-7-L126</t>
+          <t>673-3-LE26</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>Mantención Oficina ubicada en Las Lengas N°1450 de la ciudad de Coyhaique de INDAP, región de Aysén</t>
+          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D299" s="13" t="inlineStr">
         <is>
@@ -8701,52 +8499,52 @@
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>748201-10-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>680-10-LE26</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>750998-56-LE26</t>
+          <t>681016-3-L126</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALAS CINU</t>
+          <t>ADQUISICIÓN DE BIDONES DE AGUA PURIFICADA Y DISPENSADORES EN COMODATO</t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
@@ -8761,112 +8559,112 @@
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>761391-126-LE26</t>
+          <t>682-3-LE26</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>BAEBGUBECG148SVC TRASLADO DE PERSONAL PARADA MILITAR 2026.</t>
+          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>697057-30-LE26</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>707420-20-LE26</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>712307-58-O126</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>731159-2-L126</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>838100-6-L126</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
@@ -8881,16 +8679,16 @@
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>742475-4-LE26</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
@@ -8901,32 +8699,32 @@
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>742-8-L126</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>886954-230-LP26</t>
+          <t>748201-10-LE26</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
+          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
@@ -8941,12 +8739,12 @@
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>886954-262-LP26</t>
+          <t>748201-9-LP26</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
@@ -8961,12 +8759,12 @@
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>886954-297-LP26</t>
+          <t>750998-56-LE26</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+          <t>HABILITACIÓN SALAS CINU</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
@@ -8981,16 +8779,16 @@
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>899-31-L126</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>Suministro e instalación de argollas de anclaje para la techumbre del Hospital San José de Casablanca</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
@@ -9001,156 +8799,156 @@
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>930-20-LE26</t>
+          <t>769-84-LP26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>932-24-LE26</t>
+          <t>813685-9-LE26</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>956-57-L126</t>
+          <t>824-3-LE26</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>956-58-LE26</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>957865-6-LE26</t>
+          <t>837-88-LP26</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>975-12-O126</t>
+          <t>838100-6-L126</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>976-14-LP26</t>
+          <t>840405-12-LE26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+          <t xml:space="preserve">ADQUISICION DE MATERIALES PARA MEJORAMIENTO EDIFICIO ANEXO MUNICIPAL COMUNA DE RÍO CLARO </t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D321" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>979-49-L126</t>
+          <t>845-17-LR26</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
@@ -9161,36 +8959,36 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>986278-16-LE26</t>
+          <t>854-28-LE26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>993-42-LE26</t>
+          <t>867990-59-L126</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+          <t>cc 102 - sol 91975 servicio de mantenimiento del sistema de calefacción central con visita a terreno</t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
@@ -9201,18 +8999,378 @@
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
+          <t>867990-84-L126</t>
+        </is>
+      </c>
+      <c r="B325" s="13" t="inlineStr">
+        <is>
+          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
+        </is>
+      </c>
+      <c r="C325" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D325" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="11" t="inlineStr">
+        <is>
+          <t>875646-67-LE26</t>
+        </is>
+      </c>
+      <c r="B326" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
+        </is>
+      </c>
+      <c r="C326" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="11" t="inlineStr">
+        <is>
+          <t>886954-222-LR26</t>
+        </is>
+      </c>
+      <c r="B327" s="13" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+        </is>
+      </c>
+      <c r="C327" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="11" t="inlineStr">
+        <is>
+          <t>886954-230-LP26</t>
+        </is>
+      </c>
+      <c r="B328" s="13" t="inlineStr">
+        <is>
+          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="11" t="inlineStr">
+        <is>
+          <t>886954-262-LP26</t>
+        </is>
+      </c>
+      <c r="B329" s="13" t="inlineStr">
+        <is>
+          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+        </is>
+      </c>
+      <c r="C329" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="11" t="inlineStr">
+        <is>
+          <t>886954-297-LP26</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="inlineStr">
+        <is>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="11" t="inlineStr">
+        <is>
+          <t>929-23-L126</t>
+        </is>
+      </c>
+      <c r="B331" s="13" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Instalaciones y Equipos Eléctricos, Oficinas DRM</t>
+        </is>
+      </c>
+      <c r="C331" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D331" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="11" t="inlineStr">
+        <is>
+          <t>930-20-LE26</t>
+        </is>
+      </c>
+      <c r="B332" s="13" t="inlineStr">
+        <is>
+          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
+        </is>
+      </c>
+      <c r="C332" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D332" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="11" t="inlineStr">
+        <is>
+          <t>931-25-LE26</t>
+        </is>
+      </c>
+      <c r="B333" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE REPARACIÓN DE TECHUMBRE Y SISTEMA DE AGUAS LLUVIAS – CASA DEL DEPORTISTA VICUÑA</t>
+        </is>
+      </c>
+      <c r="C333" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D333" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="11" t="inlineStr">
+        <is>
+          <t>932-24-LE26</t>
+        </is>
+      </c>
+      <c r="B334" s="13" t="inlineStr">
+        <is>
+          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D334" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="11" t="inlineStr">
+        <is>
+          <t>956-57-L126</t>
+        </is>
+      </c>
+      <c r="B335" s="13" t="inlineStr">
+        <is>
+          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+        </is>
+      </c>
+      <c r="C335" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D335" s="13" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="11" t="inlineStr">
+        <is>
+          <t>956-58-LE26</t>
+        </is>
+      </c>
+      <c r="B336" s="13" t="inlineStr">
+        <is>
+          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D336" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="11" t="inlineStr">
+        <is>
+          <t>957865-6-LE26</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="inlineStr">
+        <is>
+          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+        </is>
+      </c>
+      <c r="C337" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="11" t="inlineStr">
+        <is>
+          <t>975-12-O126</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="inlineStr">
+        <is>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D338" s="13" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="11" t="inlineStr">
+        <is>
+          <t>976-14-LP26</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+        </is>
+      </c>
+      <c r="C339" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="11" t="inlineStr">
+        <is>
+          <t>979-49-L126</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D340" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>986278-16-LE26</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="inlineStr">
+        <is>
+          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
+        </is>
+      </c>
+      <c r="C341" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D341" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="11" t="inlineStr">
+        <is>
+          <t>993-42-LE26</t>
+        </is>
+      </c>
+      <c r="B342" s="13" t="inlineStr">
+        <is>
+          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+        </is>
+      </c>
+      <c r="C342" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D342" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="11" t="inlineStr">
+        <is>
           <t>997-32-LP26</t>
         </is>
       </c>
-      <c r="B325" s="13" t="inlineStr">
+      <c r="B343" s="13" t="inlineStr">
         <is>
           <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
         </is>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D325" s="13" t="inlineStr">
+      <c r="C343" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" s="13" t="inlineStr">
         <is>
           <t>score 0 &lt; 30</t>
         </is>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,20 +92,8 @@
       <color rgb="00B7791F"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7A4B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7A4B"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -125,16 +113,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F6EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF2E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,7 +185,7 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,31 +200,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -632,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-08-29 19:34 · UF 40,871.14 · 4,717 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-02 19:32 · UF 40,876.41 · 4,526 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -655,7 +609,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA(Matches!P2:P9)</f>
+        <f>COUNTA(Matches!P2:P5)</f>
         <v/>
       </c>
     </row>
@@ -666,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Matches!A2:A9,"SI")</f>
+        <f>COUNTIF(Matches!A2:A5,"SI")</f>
         <v/>
       </c>
     </row>
@@ -677,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Matches!B2:B9,"CAMBIO*")</f>
+        <f>COUNTIF(Matches!B2:B5,"CAMBIO*")</f>
         <v/>
       </c>
     </row>
@@ -688,7 +642,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Matches!C2:C9,"ALTA")</f>
+        <f>COUNTIF(Matches!C2:C5,"ALTA")</f>
         <v/>
       </c>
     </row>
@@ -699,7 +653,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Matches!E2:E9,"Mandato de SERVICIO")</f>
+        <f>COUNTIF(Matches!E2:E5,"Mandato de SERVICIO")</f>
         <v/>
       </c>
     </row>
@@ -710,7 +664,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Matches!E2:E9,"Estado BUSCA inmueble")</f>
+        <f>COUNTIF(Matches!E2:E5,"Estado BUSCA inmueble")</f>
         <v/>
       </c>
     </row>
@@ -721,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Matches!E2:E9,"Estado OFRECE inmueble")</f>
+        <f>COUNTIF(Matches!E2:E5,"Estado OFRECE inmueble")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +686,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Matches!G2:G9,"Gamma")</f>
+        <f>COUNTIF(Matches!G2:G5,"Gamma")</f>
         <v/>
       </c>
     </row>
@@ -743,7 +697,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Matches!G2:G9,"Realsa Brokers")</f>
+        <f>COUNTIF(Matches!G2:G5,"Realsa Brokers")</f>
         <v/>
       </c>
     </row>
@@ -754,7 +708,7 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS(Matches!N2:N9,"&lt;=7",Matches!N2:N9,"&gt;=0")</f>
+        <f>COUNTIFS(Matches!N2:N5,"&lt;=7",Matches!N2:N5,"&gt;=0")</f>
         <v/>
       </c>
     </row>
@@ -765,7 +719,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>SUM(Matches!M2:M9)</f>
+        <f>SUM(Matches!M2:M5)</f>
         <v/>
       </c>
     </row>
@@ -812,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -982,27 +936,27 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>Realsa Brokers</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO INMUEBLES PARA OFICINAS</t>
+          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región del Biobío</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -1012,16 +966,16 @@
       </c>
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00</t>
+          <t>2026-09-08 15:30</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>1743-64-LE26</t>
+          <t>2359-13-LP26</t>
         </is>
       </c>
       <c r="Q2" s="13" t="inlineStr">
@@ -1031,17 +985,17 @@
       </c>
       <c r="R2" s="13" t="inlineStr">
         <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
         </is>
       </c>
       <c r="S2" s="13" t="inlineStr">
         <is>
-          <t>La necesidad de contratar el servicio de arriendo de uno o más inmuebles que cuenten con las características descritas en las presentes Bases.</t>
+          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
         </is>
       </c>
       <c r="T2" s="11" t="inlineStr">
         <is>
-          <t>Sergio Gajardo Donoso</t>
+          <t>Victor Sandoval Arias</t>
         </is>
       </c>
       <c r="U2" s="11" t="inlineStr"/>
@@ -1068,41 +1022,41 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Estado BUSCA inmueble</t>
+          <t>Estado OFRECE inmueble</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>Realsa Brokers</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLE PARA OFICINA Y RESIDENCIA</t>
+          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Región de Coquimbo</t>
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -1112,36 +1066,36 @@
       </c>
       <c r="M3" s="11" t="n"/>
       <c r="N3" s="11" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>2495-16-CO26</t>
+          <t>4295-54-LR26</t>
         </is>
       </c>
       <c r="Q3" s="13" t="inlineStr">
         <is>
-          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
         </is>
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLE PARA OFICINAS ADMINISTRATIVAS DEL CENTRO RAYEN Y UN ESPACIO RESIDENCIAL, PARA LA RESIDENCIA TRANSITORIA, SEGÚN BASES ADMINISTRATIVAS Y TÉCNICAS.</t>
+          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
         </is>
       </c>
       <c r="T3" s="11" t="inlineStr">
         <is>
-          <t>GABRIELA OSORIO AGUILAR</t>
+          <t>Dirección de Administración y Finanzas</t>
         </is>
       </c>
       <c r="U3" s="11" t="inlineStr"/>
@@ -1152,622 +1106,214 @@
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: monto UF 122336.0-&gt;122320.0</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Región de Tarapacá</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>CLP 5,000,000,000</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="n">
+        <v>122320</v>
+      </c>
+      <c r="N4" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>5358-9-LR26</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
+        </is>
+      </c>
+      <c r="T4" s="18" t="inlineStr">
+        <is>
+          <t>Jorge Bernal Peralta</t>
+        </is>
+      </c>
+      <c r="U4" s="18" t="inlineStr"/>
+      <c r="V4" s="21" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>VIGENTE</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Estado BUSCA inmueble</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Región del Biobío</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Región de los Lagos</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>no publicado</t>
         </is>
       </c>
-      <c r="M4" s="11" t="n"/>
-      <c r="N4" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-08 15:30</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>2359-13-LP26</t>
-        </is>
-      </c>
-      <c r="Q4" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R4" s="13" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S4" s="13" t="inlineStr">
-        <is>
-          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>Victor Sandoval Arias</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="14" t="inlineStr">
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>1063538-206-I226</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S5" s="13" t="inlineStr">
+        <is>
+          <t>El Hospital Base San José de Osorno, en adelante también “el Hospital”, llama a propuesta privada para generar un convenio de Arriendo de celdas de media tensión MT del Hospital Base San Jose Osorno. La forma de la presente licitación pública corresponde a aquella adquisición mayor o igual a 5.000 UTM y menor a 10.000 UTM.</t>
+        </is>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>Yasna Albarran</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="inlineStr"/>
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>Ver ficha</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>CAMBIO: monto UF 3524.0-&gt;3523.0</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>59</v>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>Estado BUSCA inmueble</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>Servicio de arriendo - Folio 852 - DIDECO</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
-        </is>
-      </c>
-      <c r="K5" s="18" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="inlineStr">
-        <is>
-          <t>CLP 144,000,000</t>
-        </is>
-      </c>
-      <c r="M5" s="20" t="n">
-        <v>3523</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:30</t>
-        </is>
-      </c>
-      <c r="P5" s="18" t="inlineStr">
-        <is>
-          <t>2713-157-LP26</t>
-        </is>
-      </c>
-      <c r="Q5" s="19" t="inlineStr">
-        <is>
-          <t>objeto/desc: inmueble (+7) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R5" s="19" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S5" s="19" t="inlineStr">
-        <is>
-          <t>La Municipalidad de Aysén –en adelante Municipalidad - llama a presentar ofertas para el arrendamiento de un bien inmueble destinado al funcionamiento del Centro de las Mujeres y demás programas en convenio con SERNAMEG para el Departamento de Desarrollo Comunitario DIDECO de la Municipalidad de Aysén por un periodo de tres años</t>
-        </is>
-      </c>
-      <c r="T5" s="18" t="inlineStr">
-        <is>
-          <t>Victor Godoy Tapia</t>
-        </is>
-      </c>
-      <c r="U5" s="18" t="inlineStr"/>
-      <c r="V5" s="21" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Región de Coquimbo</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>no publicado</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-14 15:00</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>4295-54-LR26</t>
-        </is>
-      </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
-        </is>
-      </c>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S6" s="13" t="inlineStr">
-        <is>
-          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
-        </is>
-      </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>Dirección de Administración y Finanzas</t>
-        </is>
-      </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>CAMBIO: monto UF 122351.0-&gt;122336.0</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>Región de Tarapacá</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>CLP 5,000,000,000</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="n">
-        <v>122336</v>
-      </c>
-      <c r="N7" s="18" t="n">
-        <v>53</v>
-      </c>
-      <c r="O7" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:01</t>
-        </is>
-      </c>
-      <c r="P7" s="18" t="inlineStr">
-        <is>
-          <t>5358-9-LR26</t>
-        </is>
-      </c>
-      <c r="Q7" s="19" t="inlineStr">
-        <is>
-          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
-        </is>
-      </c>
-      <c r="R7" s="19" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S7" s="19" t="inlineStr">
-        <is>
-          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
-        </is>
-      </c>
-      <c r="T7" s="18" t="inlineStr">
-        <is>
-          <t>Jorge Bernal Peralta</t>
-        </is>
-      </c>
-      <c r="U7" s="18" t="inlineStr"/>
-      <c r="V7" s="21" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>Estado BUSCA inmueble</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>Realsa Brokers</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
-        </is>
-      </c>
-      <c r="I8" s="27" t="inlineStr">
-        <is>
-          <t>HOSPITAL BASE OSORNO</t>
-        </is>
-      </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>Región de los Lagos</t>
-        </is>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="inlineStr">
-        <is>
-          <t>no publicado</t>
-        </is>
-      </c>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="O8" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:00</t>
-        </is>
-      </c>
-      <c r="P8" s="26" t="inlineStr">
-        <is>
-          <t>1063538-206-I226</t>
-        </is>
-      </c>
-      <c r="Q8" s="27" t="inlineStr">
-        <is>
-          <t>UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R8" s="27" t="inlineStr">
-        <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
-        </is>
-      </c>
-      <c r="S8" s="27" t="inlineStr">
-        <is>
-          <t>El Hospital Base San José de Osorno, en adelante también “el Hospital”, llama a propuesta privada para generar un convenio de Arriendo de celdas de media tensión MT del Hospital Base San Jose Osorno. La forma de la presente licitación pública corresponde a aquella adquisición mayor o igual a 5.000 UTM y menor a 10.000 UTM.</t>
-        </is>
-      </c>
-      <c r="T8" s="26" t="inlineStr">
-        <is>
-          <t>Yasna Albarran</t>
-        </is>
-      </c>
-      <c r="U8" s="26" t="inlineStr"/>
-      <c r="V8" s="28" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Mandato de SERVICIO</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Contratan un servicio profesional inmobiliario: postulacion directa como oferente. Verificar requisitos de experiencia y garantia de seriedad.</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Realsa Brokers</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>CDP 91352 - CC 102 — TASACIÓN DE BIENES INMUEBLES</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>CLP 45,000,000</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="n">
-        <v>1101</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:00</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>867990-62-LE26</t>
-        </is>
-      </c>
-      <c r="Q9" s="13" t="inlineStr">
-        <is>
-          <t>nucleo/titulo: tasacion (+24) | objeto/titulo: inmueble (+14)</t>
-        </is>
-      </c>
-      <c r="R9" s="13" t="inlineStr">
-        <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
-        </is>
-      </c>
-      <c r="S9" s="13" t="inlineStr">
-        <is>
-          <t>El objeto de la presente licitación es la contratación del servicio de tasación de bienes inmuebles institucionales de la Universidad de Santiago de Chile, con el propósito de actualizar la información patrimonial de la Institución mediante la determinación del valor razonable de sus activos inmobiliarios, de conformidad con las Normas Internacionales de Información Financiera IFRS, las Normas Internacionales de Valoración IVS vigentes y demás normativa técnica aplicable, de acuerdo con las condiciones que se detallan en el Título II de las presentes bases de licitación.</t>
-        </is>
-      </c>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>meliza cabello</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="inlineStr"/>
-      <c r="V9" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V9"/>
+  <autoFilter ref="A1:V5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1887,7 +1433,7 @@
         </is>
       </c>
       <c r="J2" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1931,7 +1477,7 @@
         </is>
       </c>
       <c r="J3" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1975,7 +1521,7 @@
         </is>
       </c>
       <c r="J4" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2019,7 +1565,7 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2059,11 +1605,11 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2109,7 +1655,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2153,7 +1699,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2193,11 +1739,11 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2230,7 +1776,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122336</v>
+        <v>122320</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -2239,11 +1785,11 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2283,7 +1829,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -2333,7 +1879,7 @@
         </is>
       </c>
       <c r="J12" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2347,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2426,75 +1972,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIO DE ARRIENDO DE OFICINA CORPORATIVA EN MATO GROSSO DO SUL BRASIL PARA LA CORPORACIÓN REGIONAL DE DESARROLLO DE LA REGIÓN DE TARAPACÁ</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO DE LA REGION DE TARAPACA</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>Región de Tarapacá</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>CLP 26,000,000</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>636</v>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>obras 100-1.000 UTM</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01 15:00</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>bajo umbral de monto (Nacional, UF 636 (umbral UF 2.000))</t>
-        </is>
-      </c>
-      <c r="K2" s="11" t="inlineStr">
-        <is>
-          <t>1422259-9-CO26</t>
-        </is>
-      </c>
-      <c r="L2" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Estas licitaciones SI calzan con el servicio, pero quedan fuera por monto o plazo. Ojo: Mercado Publico publica el valor del CONTRATO (honorario), no el valor del activo — una tasacion de un edificio grande puede aparecer como UF 73. Revisar antes de descartar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2505,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2579,32 +2065,32 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1052836-6-LE26</t>
+          <t>1051173-11-LE26</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
+          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1057049-273-LR26</t>
+          <t>1052836-6-LE26</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
+          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
@@ -2619,12 +2105,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1057049-285-LR26</t>
+          <t>1057049-273-LR26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
@@ -2639,12 +2125,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1057049-296-LR26</t>
+          <t>1057049-285-LR26</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
@@ -2659,12 +2145,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1057049-321-LE26</t>
+          <t>1057049-296-LR26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
+          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
@@ -2679,12 +2165,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1057049-322-I226</t>
+          <t>1057049-321-LE26</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2699,12 +2185,12 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1057055-68-LP26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
@@ -2719,52 +2205,52 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057055-68-LP26</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057404-82-LE26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057417-183-LP26</t>
+          <t>1057404-82-LE26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -2779,12 +2265,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057417-51-LP26</t>
+          <t>1057417-183-LP26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
+          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
@@ -2799,52 +2285,52 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057420-37-LP26</t>
+          <t>1057417-51-LP26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
+          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057429-28-LP26</t>
+          <t>1057420-37-LP26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACTIVOS HORMONALES CON EQUIPO EN COMODATO </t>
+          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057429-53-LP26</t>
+          <t>1057472-92-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS GASES EN SANGRE CON EQUIPOS EN COMODATO</t>
+          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2859,12 +2345,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057472-92-LP26</t>
+          <t>1057480-46-LR26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
@@ -2879,52 +2365,52 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057489-255-LE26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>Funcionamiento y Habilitación de nueva Bodega</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057489-255-LE26</t>
+          <t>1057490-50-LR26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Funcionamiento y Habilitación de nueva Bodega</t>
+          <t>Arriendo Lavado y Administración de Ropa.</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057490-50-LR26</t>
+          <t>1057490-57-LP26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Lavado y Administración de Ropa.</t>
+          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -2939,12 +2425,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057490-57-LP26</t>
+          <t>1057490-65-LE26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
+          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2959,12 +2445,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057490-65-LE26</t>
+          <t>1057492-111-LP26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
+          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -2979,12 +2465,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057492-111-LP26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2999,12 +2485,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -3019,52 +2505,52 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057501-488-LE26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057501-488-LE26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057503-125-LE26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
@@ -3079,12 +2565,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057503-125-LE26</t>
+          <t>1057539-118-LP26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
+          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -3099,32 +2585,32 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057509-253-LE26</t>
+          <t>1057544-293-LE26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO COMPRA SERVICIOS PROFESIONALES DE TERAPEUTA OCUPACIONAL PARA PROYECTO DE NEUROREHABILITACIÓN PARA USUARIOS SECUELADOS DE ATAQUE CEREBROVASCULAR mjv</t>
+          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057539-118-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -3139,12 +2625,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057547-348-LE26</t>
+          <t>1057547-354-LP26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION BRONCOSCOPIOS DESECHABLES CON COMODATO DE MONITOR</t>
+          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
@@ -3159,12 +2645,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057736-6-L126</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -3179,12 +2665,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057547-354-LP26</t>
+          <t>1057922-22-LP26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -3199,12 +2685,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1057736-6-L126</t>
+          <t>1070620-86-LP26</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
+          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -3219,12 +2705,12 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1057922-22-LP26</t>
+          <t>1075963-309-LP26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
+          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
@@ -3239,32 +2725,32 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1057977-12-LE26</t>
+          <t>1075963-315-LP26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>cierro terreno futuro H. Rio Negro Hornopiren</t>
+          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1070620-86-LP26</t>
+          <t>1079650-57-LE26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
+          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
@@ -3279,96 +2765,96 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1071775-12-LE26</t>
+          <t>1079969-19-LP26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>TRASLADO DE ESTUDIANTES ULAGOS SEDE CHILOÉ -PIDPID</t>
+          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1075963-309-LP26</t>
+          <t>1099402-21-L126</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
+          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1075963-315-LP26</t>
+          <t>1109692-8-LE26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
+          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1078177-45-LE26</t>
+          <t>1116006-4-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE SERVICIO DE CAMBIO DE VENTANAS PARA LA ZONA DE CARABINEROS ARAUCANÍA.</t>
+          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1079969-19-LP26</t>
+          <t>1126922-33-LP26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
+          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
@@ -3379,16 +2865,16 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1080936-43-LE26</t>
+          <t>1165648-6-L126</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DEL SISTEMA DE DETECCIÓN ALARMA Y CONTROL DE INCENDIO DEL EDIFICIO DE LA ESCUELA DE INVESTIGACIONES POLICIALES</t>
+          <t>SERVICIO INTEGRAL DE MANTENIMIENTO PREVENTIVO, ASISTENCIA TÉCNICA, DIAGNÓSTICO, ATENCIÓN CORRECTIVA Y SOPORTE CONTINUO PARA SILLONES DENTALES Y COMPRESOR DEL DEPARTAMENTO DE SALUD MUNICIPAL DE LIMACHE</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
@@ -3399,36 +2885,36 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1099402-21-L126</t>
+          <t>1180730-37-LP26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
+          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1109692-8-LE26</t>
+          <t>1180830-16-LR26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
+          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
@@ -3439,172 +2925,172 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1110404-155-L126</t>
+          <t>1197-20-L126</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIO DE ARRIENDO DE CENTRO DE CONVENCIONES PARA LA REALIZACIÓN DEL ‘I CONVERSATORIO COMUNAL DE JÓVENES ESTUDIANTES TÉCNICO PROFESIONALES.</t>
+          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1110404-165-L126</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MATERIALES DE OFICINA Y APOYO PEDAGÓGICO PARA ESTABLECIMIENTOS EDUCACIONALES DEL SLEP CHINCHORRO</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1126922-33-LP26</t>
+          <t>1232565-33-LE26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1134432-67-LE26</t>
+          <t>1233615-56-LE26</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO VETERINARIO PARA LA OFICINA DE TENENCIA RESPONSABLE Y ZOONOSIS</t>
+          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1160-14-LE26</t>
+          <t>1261-19-LR26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>8305 Arriendo de Equinos Biobio-Queuco SAG Mulchén</t>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1160-15-LE26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>8101REPARACION Y MANTENCIÓN OFICINAS CONCEPCIÓN</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1165648-6-L126</t>
+          <t>1280-41-LE26</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO INTEGRAL DE MANTENIMIENTO PREVENTIVO, ASISTENCIA TÉCNICA, DIAGNÓSTICO, ATENCIÓN CORRECTIVA Y SOPORTE CONTINUO PARA SILLONES DENTALES Y COMPRESOR DEL DEPARTAMENTO DE SALUD MUNICIPAL DE LIMACHE</t>
+          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1180730-37-LP26</t>
+          <t>1280-42-LE26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
+          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1180830-16-LR26</t>
+          <t>1293138-13-LP26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
@@ -3619,12 +3105,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1305527-3-LP26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
@@ -3639,152 +3125,152 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1232565-33-LE26</t>
+          <t>1344190-12-LE26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
+          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1233615-56-LE26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1375746-17-LP26</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1280-41-LE26</t>
+          <t>1395865-16-LE26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
+          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1280-42-LE26</t>
+          <t>1415863-2-LE26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
+          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
@@ -3799,12 +3285,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1336-18-LP26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MOTONIVELADORA PARA OPERACIÓN DE REPERFILADO SIMPLE</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
@@ -3819,16 +3305,16 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1350-7-LE26</t>
+          <t>1443-1-LE26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN DE ÁREAS VERDES PARA OFICINAS</t>
+          <t>Servicio de bodegaje y almacenamiento</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
@@ -3839,52 +3325,52 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1395865-16-LE26</t>
+          <t>1448821-14-LP26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1415863-2-LE26</t>
+          <t>1469-189-L126</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1501468-17-LE26</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
@@ -3899,112 +3385,112 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1537592-17-LE26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1426098-12-LP26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CONTROL DE ACCESO IP IRC CORONEL</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1443-1-LE26</t>
+          <t>1554-55-LR26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje y almacenamiento</t>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1605-41-LP26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t>LP-4872 Servicios de mantención general edificios</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1460278-46-L126</t>
+          <t>1605-45-LP26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>Provisión de Kiosko metálico de medidas 2,4 x 6 mts, con puerta de acceso y ventana,  para el sector de Ruiz Tagle, Fac. Tecnológica.</t>
+          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1464-58-L126</t>
+          <t>162-26-LE26</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>TELE ELECTROCARDIOGRAFIA: ARRIENDO DE EQUIPO E INF</t>
+          <t>Servicio traslado de muestras a los Laboratorios</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
@@ -4019,32 +3505,32 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1469-166-L126</t>
+          <t>1624-21-L126</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REMODELACIÓN DE OFICINA DIRECCION DE INVESTIGACIÓN, UNIVERSIDAD DE TALCA”</t>
+          <t>Convenio de suministros de Oxígeno Médico, Recarga y Arriendo de cilindros para servicios Urgencias y Hospitalizados</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1641-219-LR26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
@@ -4059,12 +3545,12 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1655-23-LP26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
@@ -4079,16 +3565,16 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1658-189-LP26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
@@ -4099,52 +3585,52 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1605-45-LP26</t>
+          <t>1663-137-LE26</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>162-26-LE26</t>
+          <t>1671-30-LE26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>Servicio traslado de muestras a los Laboratorios</t>
+          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1624-21-L126</t>
+          <t>1696-11-LE26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>Convenio de suministros de Oxígeno Médico, Recarga y Arriendo de cilindros para servicios Urgencias y Hospitalizados</t>
+          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
@@ -4159,312 +3645,312 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1638-81-LE26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>Servicio de producción de eventos Carnaval del desierto departamento de cultura patrimonio e identidad DIDECO sm 001236</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1641-219-LR26</t>
+          <t>1973-96-LE26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1655-23-LP26</t>
+          <t>1978-100-L126</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1658-147-LE26</t>
+          <t>2069-155-LP26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>P.136-2026 PROVISIÓN DE NUEVO MONTACARGA EDIFICIO CONSISTORIAL CON MANTENCIÓN POR 12 MESES</t>
+          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>2098-115-LE26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1671-30-LE26</t>
+          <t>2098-124-LE26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
+          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1696-11-LE26</t>
+          <t>2098-127-LE26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
+          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>2098-133-LP26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1851-26-LE26</t>
+          <t>2098-134-LP26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MAQUINARA PARA COMPACTACION DPVC 2026</t>
+          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1905-2-LE26</t>
+          <t>2107-142-LE26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE SUBOFICINA</t>
+          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 4 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>1947-130-LP26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE SUMINISTRO DE ÓXIDO NÍTRICO Y ARRIENDO DE EQUIPO PARA TERAPIA DE OXIDO NITRICO Y TEST DE REACTIVIDAD DEL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1949-1-LP26</t>
+          <t>2109-10-LP26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO OBRAS MENORES INMUEBLES VALPARAÍSO.</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>1978-100-L126</t>
+          <t>2126-128-LE26</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
+          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>1979-182-LE26</t>
+          <t>2173-27-LE26</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>176.26 “ARRIENDO DE EQUIPOS PARA CIRUGÍA PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>2078-39-LE26</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS DE CONCEPCIÓN Y DE LA DELEGACIÓN BIOBIO DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO SC283 y SC377</t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>2080-261-LP26</t>
+          <t>2258-133-LR26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO GASES EN SANGRE CON EQUIPO EN COMODATO</t>
+          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
@@ -4479,92 +3965,92 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>2098-124-LE26</t>
+          <t>2258-168-LE26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
+          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>2098-127-LE26</t>
+          <t>2258-175-LR26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>2098-133-LP26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>2098-134-LP26</t>
+          <t>2258-72-LE26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
+          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>2107-130-LE26</t>
+          <t>2271-65-LE26</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS VPS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
@@ -4579,12 +4065,12 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>2107-136-LE26</t>
+          <t>2273-55-LE26</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE FUNCIONARIOS PARA HOSPITAL DE SANTA CRUZ</t>
+          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
@@ -4599,72 +4085,72 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>2109-10-LP26</t>
+          <t>2275-29-LE26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>2126-128-LE26</t>
+          <t>2279-58-LE26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
+          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>2173-27-LE26</t>
+          <t>2282-96-LE26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>2258-133-LR26</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
@@ -4679,12 +4165,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
@@ -4699,72 +4185,72 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>2258-72-LE26</t>
+          <t>2308-72-LE26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>2271-65-LE26</t>
+          <t>2332-101-L126</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>2273-55-LE26</t>
+          <t>2332-104-L126</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
+          <t>HABILITACIÓN BOX DENTAL Y SOME CENTRAL DE “POSTA LAS QUEMAS” DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2332-105-L126</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>ADQUISICIÓN DE TÓRULAS, SERVILLETAS, VASOS DESECHABLES Y EYECTORES ODONTOLÓGICOS PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
@@ -4779,12 +4265,12 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>2282-96-LE26</t>
+          <t>2366-54-LE26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
+          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
@@ -4799,132 +4285,132 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2308-72-LE26</t>
+          <t>2402-76-LE26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+          <t>SEGURIDAD RECINTO CELEBRACION FIESTAS PATRIAS 2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2320-26-LE26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO  SALÓN Y OTROS PARA JORNADA APS</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2322-72-LE26</t>
+          <t>2408-160-LP26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>Regularización del Activo Fijo  Inventario Munici</t>
+          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2324-107-L126</t>
+          <t>2408-210-L126</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 1032026 “SERVICIO DE ARRIENDO DE AMPLIFICACIÓN Y BAÑOS QUÍMICOS PARA ACTIVIDADES DEL MES DE LA PATRIA 2026 - DIRECCIÓN DE DESARROLLO COMUNITARIO - MUNICIPALIDAD DE PUERTO MONTT”</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS VARIOS PARA CABAÑAS RECINTO CHACAY.</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>2332-101-L126</t>
+          <t>2408-98-LE26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
+          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
@@ -4939,16 +4425,16 @@
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>2332-102-L126</t>
+          <t>2410-35-LP26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>MALLA MOSQUITERA E INSTALACIÓN DE ACRÍLICOS PARA SEGREGACIÓN ÁREA SUCIA SAPU Y CESFAM PADRE HURTADO Y CECOSF PUERTA SUR DEL DEPARTAMENTO DE SALUD DE PUERTO MONTT</t>
+          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
@@ -4959,12 +4445,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2366-54-LE26</t>
+          <t>2410-84-LE26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
@@ -4979,16 +4465,16 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2369-64-LP26</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>PP 69 Implementación bodegas resguardo de fichas</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
@@ -4999,12 +4485,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2426-44-LE26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
@@ -5019,96 +4505,96 @@
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2402-72-CO26</t>
+          <t>2430-71-LP26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>SERV.DE REP. Y REHABILITACION DE PILETA ORNAMENTAL</t>
+          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2402-74-L126</t>
+          <t>2445-110-LE26</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO A PROFESIONALES</t>
+          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2402-75-LE26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INST. TEMPORAL CAMARAS DE SEGURIDAD</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2402-76-LE26</t>
+          <t>2448-107-L126</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SEGURIDAD RECINTO CELEBRACION FIESTAS PATRIAS 2026</t>
+          <t>MEJORAMIENTO DE COMEDOR DE FUNCIONARIOS DROGUERIA  Y BODEGA DESAM</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -5119,56 +4605,56 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2448-110-L126</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>HABILITACION DE ESPACIO DE TRABAJO COLECTIVO CECOSF PUNTA MIRA</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2408-160-LP26</t>
+          <t>2450-90-LE26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2408-210-L126</t>
+          <t>2452-19-L126</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS VARIOS PARA CABAÑAS RECINTO CHACAY.</t>
+          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
@@ -5179,32 +4665,32 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2409-86-L126</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2409-91-L126</t>
+          <t>2460-112-LE26</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO ALUMNOS TALLER  EXTRAESCOLAR Y JORNADAS REFLEXION, ESCUELA D-870</t>
+          <t>Servicio de Arriendo de Graderías y Tribuna de Honor Desfile en Honor a Las Glorias del Ejército</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
@@ -5219,36 +4705,36 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2410-35-LP26</t>
+          <t>2460-113-LE26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
+          <t>Servicio de Arriendo de Vallas Desfile en Honor a las Glorias del Ejército</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2410-83-LE26</t>
+          <t>2460-99-LE26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de artículos hidráulicos para mantención de inmuebles DMI</t>
+          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
@@ -5259,36 +4745,36 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2410-84-LE26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2416-22-LE26</t>
+          <t>2546-49-LP26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PRODUCCIÓN DE EVENTOS PARA ACTIVIDADES DE LA OFICINA DE PERSONAS MAYORES 2026</t>
+          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
@@ -5299,152 +4785,152 @@
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2555-10-LP26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2430-69-LP26</t>
+          <t>2565-14-LP26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEDE SOCIAL COMITÉ DE ADELANTO Y DESARROLLO UNIÓN CIRCUNVALACIÓN NORTE CÓDIGO BIP N°40074315-0</t>
+          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2430-71-LP26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2445-110-LE26</t>
+          <t>2581-37-LP26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2452-19-L126</t>
+          <t>2585-87-LE26</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
+          <t>ADQ. VEH. ACUATICO Y TODOTERRENO ORD N°167-TURISMO</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2460-99-LE26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
@@ -5459,112 +4945,112 @@
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2483-231-LP26</t>
+          <t>2626-8-LE26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MONITOREO DE ALARMAS CON ACTUALIZACIÓN MANTENIMIENTO Y REPARACIÓN PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2664-38-L126</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2546-49-LP26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2548-71-LE26</t>
+          <t>2667-83-LE26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MOVILIZACIÓN TRASLADO PROGRAMA MASAMA</t>
+          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2548-73-LE26</t>
+          <t>2686-120-CO26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>FÁRMACOS PROGRAMA FOFAR - DSM PADRE LAS CASAS</t>
+          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2555-10-LP26</t>
+          <t>2697-23-LP26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
@@ -5579,32 +5065,32 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2565-14-LP26</t>
+          <t>2697-25-LR26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2699-32-LR26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>Servicio de Arriendo de Flota Vehicular</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
@@ -5619,52 +5105,52 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2702-62-LE26</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2702-63-LE26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2585-87-LE26</t>
+          <t>2703-175-L126</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VEH. ACUATICO Y TODOTERRENO ORD N°167-TURISMO</t>
+          <t>SC 12493 Servicio REAS retiro traslado y eliminación de Residuos</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
@@ -5679,36 +5165,36 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2709-77-LE26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>HABILITACION PARQUE RECREACIONAL LOS PEÑONES</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2600-23-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>Const. Accesibilidad Universal Edificio Municipal</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
@@ -5719,132 +5205,132 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2730-113-LE26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2626-8-LE26</t>
+          <t>2736-32-LE26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
+          <t>Materiales de Oficina</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2627-15-LE26</t>
+          <t>2744-30-LE26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>NORMALIZACIÓN ELÉCTRICA EDIFICIO CONSISTORIAL</t>
+          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2664-38-L126</t>
+          <t>2755-34-LE26</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2784-42-LP26</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2686-120-CO26</t>
+          <t>2784-44-LE26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
+          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2697-23-LP26</t>
+          <t>2788-43-LE26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
+          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
@@ -5859,212 +5345,212 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2793-91-LE26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2699-32-LR26</t>
+          <t>2905-40-LP26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Flota Vehicular</t>
+          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2702-62-LE26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2703-175-L126</t>
+          <t>2963-26-LR26</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>SC 12493 Servicio REAS retiro traslado y eliminación de Residuos</t>
+          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2730-113-LE26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2736-32-LE26</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>Materiales de Oficina</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2744-30-LE26</t>
+          <t>3017-68-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
+          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>3069-3-LE26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t>Traslado de Pasajeros</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>2770-109-LR26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DEPENDENCIAS DIRECCIÓN DE SALUD MUNICIPAL</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>3092-18-LE26</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>PROVISIÓN DE LOS SERVICIOS DE  LABORATORIO DE CANASTA DE BASICA Y GES APS   BÁSICA Y GES PARA LA DIRECCIÓN DE SALUD MUNICIPAL I.MUNICIPALIDAD DE CASABLANCA 2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
@@ -6079,12 +5565,12 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>2788-43-LE26</t>
+          <t>3159-18-LE26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
+          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
@@ -6099,32 +5585,32 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>2788-44-LE26</t>
+          <t>3172-46-LR26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE VALLAS PAPALES</t>
+          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>2793-100-CO26</t>
+          <t>3179-44-LE26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO SISTEMA CLIMATIZACIÓN DE DIFERENTES RECINTOS MUNICIPALES</t>
+          <t>ADQUISICIÓN DE CASACA OPERATIVA CON POLAR</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
@@ -6139,32 +5625,32 @@
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>2793-91-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>2793-97-LE26</t>
+          <t>3333-32-LE26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN SERVICIO DE TRASLADO DE DEUDOS MUNICIPALIDAD DE  HUECHURABA</t>
+          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
@@ -6179,12 +5665,12 @@
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>2825-49-L126</t>
+          <t>3384-20-LP26</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION E INSTALACION DE VENTANAS PARA POSTA PUTU</t>
+          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
@@ -6199,12 +5685,12 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>2905-40-LP26</t>
+          <t>3436-97-LE26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+          <t>Servicio mantenimiento de dependencias SIC 351978</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
@@ -6219,36 +5705,36 @@
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>3477-76-LE26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>2963-26-LR26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
@@ -6259,32 +5745,32 @@
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>3537-52-LE26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>Arriendo de una autohormigonera por 320 horas</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>3542-22-LE26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
@@ -6292,43 +5778,43 @@
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>3611-11-LE26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>Servicio de retiro traslado y eliminación de material cortopunzante residuos médicos y otros del Departamento de Salud Municipal Puerto Saavedra y su CSR de Dominguez</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>3017-68-LE26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
@@ -6339,56 +5825,56 @@
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>3069-3-LE26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Traslado de Pasajeros</t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>3656-148-LP26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>3092-16-L126</t>
+          <t>3668-14-LP26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE IMPRESION DE CARNET INTEGRAL  DE SALUD  ( ECICEP) PARA  PACIENTES DE LAS POSTAS DE SALUD RURALES  POR EL PROGRAMA MODELO DE ATENCION INTEGRAL DE SALUD FAMILIAR Y COMUNITARIA EN APS DE LA DIRECCION DE SALUD DE LA I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
@@ -6399,32 +5885,32 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>3159-18-LE26</t>
+          <t>3671-58-LE26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>3172-46-LR26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
@@ -6439,12 +5925,12 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>3172-63-LE26</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>MEJ.DEPENDENCIAS DIRECCIÓN EDUCACIÓNDOCT.E HIST.</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
@@ -6459,16 +5945,16 @@
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>3179-44-LE26</t>
+          <t>3710-84-L126</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CASACA OPERATIVA CON POLAR</t>
+          <t>ESCANER PARA BODEGA FARMACIA CESFAM VICTORIA</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
@@ -6479,52 +5965,52 @@
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>3210-7-L126</t>
+          <t>3775-28-LP26</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE AUTOCLAVE DEL DEPARTAMENTO DE SALUD DE SAN RAFAEL</t>
+          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>3798-13-LP26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>3290-7-LE26</t>
+          <t>3880-61-LE26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
@@ -6539,32 +6025,32 @@
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3333-32-LE26</t>
+          <t>3882-72-LP26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3384-20-LP26</t>
+          <t>3882-81-L126</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
+          <t>“SERVICIO DE ARRIENDO DE JUEGOS INFLABLES PARA ACTIVIDADES SECTORIALES DE LA ILUSTRE MUNICIPALIDAD DE LLAY LLAY”.</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
@@ -6579,16 +6065,16 @@
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3436-97-LE26</t>
+          <t>3882-85-LE26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>Servicio mantenimiento de dependencias SIC 351978</t>
+          <t>MEJORAMIENTO DE NUEVA OFICINA CONTROL I. MUNICIPALIDAD LLAY LLAY COMUNA LLAY LLAY</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
@@ -6599,16 +6085,16 @@
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>3477-76-LE26</t>
+          <t>3887-39-LP26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
+          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
@@ -6619,16 +6105,16 @@
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>3542-22-LE26</t>
+          <t>3889-41-LP26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
@@ -6639,92 +6125,92 @@
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>3565-58-LE26</t>
+          <t>3935-83-LP26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA EL EQUIPO PROFESIONALES</t>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>3595-25-LE26</t>
+          <t>3950-40-LE26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>Cambio de pavimento edificio consistorial</t>
+          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>3611-11-LE26</t>
+          <t>3997-59-B226</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>Servicio de retiro traslado y eliminación de material cortopunzante residuos médicos y otros del Departamento de Salud Municipal Puerto Saavedra y su CSR de Dominguez</t>
+          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>3656-148-LP26</t>
+          <t>4006-21-LE26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+          <t>Mejoramiento Area Deportiva Ventanas</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>3668-14-LP26</t>
+          <t>4031-14-LE26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
@@ -6739,176 +6225,176 @@
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>3671-58-LE26</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>3775-28-LP26</t>
+          <t>407-134-LE26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+          <t>RETIRO TORRE VENTADA HGGB</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>3798-13-LP26</t>
+          <t>4086-43-LE26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+          <t>SERVICIO ARRIENDO DE EXCAVADORA</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>3798-15-LP26</t>
+          <t>4099-22-LP26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PATIO MANIOBRAS CUERPO DE BOMBEROS EMPEDRADO - BP 40.057.848-0 - FRIL</t>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>3880-61-LE26</t>
+          <t>4121-23-LE26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
+          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>4152-28-LE26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>3887-39-LP26</t>
+          <t>418-51-LP26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>3889-41-LP26</t>
+          <t>4236-22-L126</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
+          <t>INSTALACIÓN DE VENTANA Y MAMPARA EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>3890-167-L126</t>
+          <t>4237-12-LR26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>ADQ. PREMIOS ACTIVIDADES OFICINA LOCAL DE LA NIÑEZ</t>
+          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
@@ -6919,56 +6405,56 @@
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>3890-171-L126</t>
+          <t>4238-66-B226</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MATERIALES DIDACTICOS Y OFICINA FIADI Y PMJH</t>
+          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>4295-41-LP26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>3938-25-LE26</t>
+          <t>4328-31-B226</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Cierre Perimetral Recinto Deportivo Catripulli</t>
+          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
@@ -6979,52 +6465,52 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>3997-59-B226</t>
+          <t>4342-2-LP26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
+          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>4006-21-LE26</t>
+          <t>4362-15-LP26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Area Deportiva Ventanas</t>
+          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>4031-14-LE26</t>
+          <t>4362-20-LE26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
+          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
@@ -7039,32 +6525,32 @@
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>438-49-LE26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>4086-43-LE26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO DE EXCAVADORA</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
@@ -7079,32 +6565,32 @@
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>4451-92-LE26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>4121-23-LE26</t>
+          <t>4457-70-L126</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+          <t>IMPLEMENTOS PRAPS MAS AMA, EQUIDAD RURAL, REHABILITACIÓN INTEGRAL Y ESPACIOS AMIGABLES.</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
@@ -7119,12 +6605,12 @@
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>4152-28-LE26</t>
+          <t>4591-20-LP26</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
+          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
@@ -7139,32 +6625,32 @@
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>4168-81-LE26</t>
+          <t>4623-4-L126</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE GRADERÍAS MECANO</t>
+          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>418-51-LP26</t>
+          <t>4629-26-LE26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
@@ -7179,56 +6665,56 @@
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>4202-39-LE26</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>Segundo llamado Arriendo recinto Pasamos Agosto</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>4236-22-L126</t>
+          <t>4642-93-LP26</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE VENTANA Y MAMPARA EDIFICIO CONSISTORIAL</t>
+          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>4237-12-LR26</t>
+          <t>4642-99-LE26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
@@ -7239,12 +6725,12 @@
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>4238-66-B226</t>
+          <t>4644-5-LP26</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
@@ -7259,12 +6745,12 @@
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>4295-41-LP26</t>
+          <t>4850-4-L126</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
@@ -7279,112 +6765,112 @@
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>4309-215-LP26</t>
+          <t>4920-12-LE26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONVENIO SUMINISTRO DE REACTIVOS PARA INMUNOANALISIS DE IGG -CHAGAS E IGRA DE TUBERCULOSIS ASOCIADO A EQUIPOS EN COMODATO 2026 </t>
+          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>4328-31-B226</t>
+          <t>4928-21-LP26</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
+          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>4342-2-LP26</t>
+          <t>4956-63-LP26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>4362-15-LP26</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>4362-20-LE26</t>
+          <t>4967-7-LR26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D243" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>438-49-LE26</t>
+          <t>5048-13-O126</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
+          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
@@ -7399,12 +6885,12 @@
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>439-26-LP26</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
@@ -7419,52 +6905,52 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>4414-61-LE26</t>
+          <t>5056-102-LP26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>1.500 CANASTAS DE ALIMENTOS PARA STOCK BODEGA ASISTENCIALIDAD - DIDECO</t>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>45-44-LE26</t>
+          <t>507428-94-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN ELÉCTRICA Y DE CORRIENTES DÉBILES PARA LAS DIFERENTES DEPENDENCIAS DE SENCE A NIVEL NACIONAL</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>4591-20-LP26</t>
+          <t>5194-4-LE26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
+          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
@@ -7479,32 +6965,32 @@
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>4594-25-LE26</t>
+          <t>520149-35-L126</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MEDICAMENTOS DEPARTAMENTO DE SALUD</t>
+          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO. </t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>4629-26-LE26</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
@@ -7519,32 +7005,32 @@
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>525512-33-LE26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>Diseño proyecto construcción sede social JJVV</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>4642-92-LP26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del Servicio de Obras de Habilitación de La Sala de Estimulación Temprana del Centro Médico Y Dental de Rancagua Perteneciente a la Red Salud de Carabineros. </t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
@@ -7559,12 +7045,12 @@
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>4642-93-LP26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
@@ -7579,16 +7065,16 @@
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>4642-99-LE26</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
@@ -7599,36 +7085,36 @@
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>4644-5-LP26</t>
+          <t>539119-81-LE26</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
+          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>4778-18-LE26</t>
+          <t>539119-85-LP26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANT.CORRECTIVO DEPENDENCIAS  DE U. CIRUGIA MENOR </t>
+          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
@@ -7639,52 +7125,52 @@
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>4829-43-L126</t>
+          <t>539119-86-LE26</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>SERV DE ACTUALIZACION ACTIVO FIJO E INVENTARIO.</t>
+          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>4850-3-LE26</t>
+          <t>5413-65-LE26</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>Servicio para reparación edificio</t>
+          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>4887-22-L126</t>
+          <t>5413-67-LE26</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>Obras menores de habilitación para el Centro de Creación Temuco</t>
+          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
@@ -7692,19 +7178,19 @@
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>4920-12-LE26</t>
+          <t>5420-20-LE26</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
+          <t>Diseño eléctrico para normalización de edificios</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
@@ -7719,112 +7205,112 @@
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>4928-21-LP26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>4956-63-LP26</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>5558-5-L126</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>4967-7-LR26</t>
+          <t>557639-74-LE26</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>5048-13-O126</t>
+          <t>5586-126-LE26</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
-          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D265" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
@@ -7839,12 +7325,12 @@
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>507428-94-LE26</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
@@ -7859,12 +7345,12 @@
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>5194-4-LE26</t>
+          <t>608-126-LR26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
@@ -7879,12 +7365,12 @@
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>622-55-LE26</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
@@ -7899,92 +7385,92 @@
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>5240-91-LE26</t>
+          <t>622847-13-LE26</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MANTENCIÓN REPARACIÓN Y MEJORAMIENTO DE LAS DEPENDENCIAS DEL GRUPO DE ESPECIALIDADES</t>
+          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 21 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>525512-33-LE26</t>
+          <t>627786-14-LE26</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>Diseño proyecto construcción sede social JJVV</t>
+          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>630-24-LE26</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>5300-50-LP26</t>
+          <t>633-48-LR26</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCION SEDE SOCIAL LO OVALLE </t>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>5300-54-LP26</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t>Construcción SS.HH. Estadio Municipal de Casablanca Código BIP 40077656-0</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
@@ -7999,36 +7485,36 @@
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>539119-80-LP26</t>
+          <t>649-8-LE26</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
@@ -8039,56 +7525,56 @@
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>539119-81-LE26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>539119-85-LP26</t>
+          <t>660-10-LE26</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>539119-86-LE26</t>
+          <t>673-3-LE26</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D279" s="13" t="inlineStr">
         <is>
@@ -8099,92 +7585,92 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>5413-65-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>5413-67-LE26</t>
+          <t>680-10-LE26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
+          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>5420-20-LE26</t>
+          <t>681016-3-L126</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>Diseño eléctrico para normalización de edificios</t>
+          <t>ADQUISICIÓN DE BIDONES DE AGUA PURIFICADA Y DISPENSADORES EN COMODATO</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>688-11-LP26</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>Arriendo Infraestructura de Respaldo</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>697057-30-LE26</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
@@ -8199,36 +7685,36 @@
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>5558-5-L126</t>
+          <t>697-29-LE26</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>Serv. habilitación electrica para equipo trifasico</t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D285" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>557639-74-LE26</t>
+          <t>707420-20-LE26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
@@ -8239,16 +7725,16 @@
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>712307-58-O126</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D287" s="13" t="inlineStr">
         <is>
@@ -8259,12 +7745,12 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>568658-43-LR26</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
@@ -8279,52 +7765,52 @@
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>575924-9-E226</t>
+          <t>742475-4-LE26</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>CAJTA-ARRIENDO DE SALONES PARA ENCUENTROS REGIONAL</t>
+          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>742-8-L126</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>608-126-LR26</t>
+          <t>748201-10-LE26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
@@ -8339,12 +7825,12 @@
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>748201-9-LP26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
@@ -8359,32 +7845,32 @@
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>627786-14-LE26</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>769-84-LP26</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
@@ -8399,92 +7885,92 @@
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>634-82-LE26</t>
+          <t>777304-55-LP26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
+          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>813685-9-LE26</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>649-8-LE26</t>
+          <t>824-3-LE26</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>673-3-LE26</t>
+          <t>837-88-LP26</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
@@ -8499,52 +7985,52 @@
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>838100-6-L126</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>680-10-LE26</t>
+          <t>845-17-LR26</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>681016-3-L126</t>
+          <t>854-28-LE26</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BIDONES DE AGUA PURIFICADA Y DISPENSADORES EN COMODATO</t>
+          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
@@ -8559,56 +8045,56 @@
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>682-3-LE26</t>
+          <t>867990-59-L126</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E INSTALACIÓN DE VENTANAS Y PUERTAS</t>
+          <t>cc 102 - sol 91975 servicio de mantenimiento del sistema de calefacción central con visita a terreno</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>697057-30-LE26</t>
+          <t>867990-81-L126</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+          <t>CC 102 SOL 92520 - Contrato servicio de mantención preventiva y puesta en marcha de sistema de presurización de las escaleras del edificio nuevo de la Facultad de Administración y Economía</t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>867990-84-L126</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
@@ -8619,32 +8105,32 @@
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>875646-67-LE26</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>731159-2-L126</t>
+          <t>886954-176-LP26</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>Servicio de traslado de personas para el 12° Juzgado de Garantía de Santiago</t>
+          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
@@ -8659,12 +8145,12 @@
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>886954-222-LR26</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
@@ -8679,116 +8165,116 @@
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>742475-4-LE26</t>
+          <t>886954-262-LP26</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>742-8-L126</t>
+          <t>886954-297-LP26</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>748201-10-LE26</t>
+          <t>929-23-L126</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+          <t>Mantenimiento de Instalaciones y Equipos Eléctricos, Oficinas DRM</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D311" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>931-23-LE26</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>750998-56-LE26</t>
+          <t>931-25-LE26</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALAS CINU</t>
+          <t>SERVICIOS DE REPARACIÓN DE TECHUMBRE Y SISTEMA DE AGUAS LLUVIAS – CASA DEL DEPORTISTA VICUÑA</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>931-26-LE26</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
@@ -8799,172 +8285,172 @@
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>769-84-LP26</t>
+          <t>931-27-LE26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>813685-9-LE26</t>
+          <t>935-22-LE26</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
+          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>948355-68-LP26</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>948806-117-LP26</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>956-57-L126</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>838100-6-L126</t>
+          <t>956-58-LE26</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>840405-12-LE26</t>
+          <t>957865-6-LE26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE MATERIALES PARA MEJORAMIENTO EDIFICIO ANEXO MUNICIPAL COMUNA DE RÍO CLARO </t>
+          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D321" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>975-12-O126</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>854-28-LE26</t>
+          <t>976-14-LP26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
@@ -8979,16 +8465,16 @@
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>867990-59-L126</t>
+          <t>979-49-L126</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t>cc 102 - sol 91975 servicio de mantenimiento del sistema de calefacción central con visita a terreno</t>
+          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
@@ -8999,16 +8485,16 @@
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>867990-84-L126</t>
+          <t>993-42-LE26</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
         <is>
-          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
+          <t>Servicio Reparación y Mantención Recinto Taltal</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D325" s="13" t="inlineStr">
         <is>
@@ -9019,358 +8505,58 @@
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>875646-67-LE26</t>
+          <t>993-47-LE26</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
+          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>996-35-LE26</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
         </is>
       </c>
       <c r="C327" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>886954-230-LP26</t>
+          <t>997-32-LP26</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual en consignación de dispositivo de asistencia ventricular izquierda de uso percutáneo para la Unidad de Hemodinamia del HGG con equipo en comodato</t>
+          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
         </is>
       </c>
       <c r="C328" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D328" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="11" t="inlineStr">
-        <is>
-          <t>886954-262-LP26</t>
-        </is>
-      </c>
-      <c r="B329" s="13" t="inlineStr">
-        <is>
-          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
-        </is>
-      </c>
-      <c r="C329" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D329" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="11" t="inlineStr">
-        <is>
-          <t>886954-297-LP26</t>
-        </is>
-      </c>
-      <c r="B330" s="13" t="inlineStr">
-        <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
-        </is>
-      </c>
-      <c r="C330" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D330" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="11" t="inlineStr">
-        <is>
-          <t>929-23-L126</t>
-        </is>
-      </c>
-      <c r="B331" s="13" t="inlineStr">
-        <is>
-          <t>Mantenimiento de Instalaciones y Equipos Eléctricos, Oficinas DRM</t>
-        </is>
-      </c>
-      <c r="C331" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D331" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="11" t="inlineStr">
-        <is>
-          <t>930-20-LE26</t>
-        </is>
-      </c>
-      <c r="B332" s="13" t="inlineStr">
-        <is>
-          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
-        </is>
-      </c>
-      <c r="C332" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D332" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="11" t="inlineStr">
-        <is>
-          <t>931-25-LE26</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIOS DE REPARACIÓN DE TECHUMBRE Y SISTEMA DE AGUAS LLUVIAS – CASA DEL DEPORTISTA VICUÑA</t>
-        </is>
-      </c>
-      <c r="C333" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D333" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="11" t="inlineStr">
-        <is>
-          <t>932-24-LE26</t>
-        </is>
-      </c>
-      <c r="B334" s="13" t="inlineStr">
-        <is>
-          <t>CONTRATACION CONVENIO DE SUMINISTRO 2026-2028 “SERVICIO DE MANTENCIÓN PREVENTIVA Y CORRECTIVA DE MAQUINAS DE EJERCICIOS CARDIOVASCULARES Y DE MUSCULACIÓN MULTIMARCAS” RECINTOS DEPORTIVOS HERMOGENES LIZANA DEL INSTITUTO NACIONAL DE DEPORTES DE CHILE REGIO</t>
-        </is>
-      </c>
-      <c r="C334" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D334" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="11" t="inlineStr">
-        <is>
-          <t>956-57-L126</t>
-        </is>
-      </c>
-      <c r="B335" s="13" t="inlineStr">
-        <is>
-          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
-        </is>
-      </c>
-      <c r="C335" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D335" s="13" t="inlineStr">
-        <is>
-          <t>score 11 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="11" t="inlineStr">
-        <is>
-          <t>956-58-LE26</t>
-        </is>
-      </c>
-      <c r="B336" s="13" t="inlineStr">
-        <is>
-          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
-        </is>
-      </c>
-      <c r="C336" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D336" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="11" t="inlineStr">
-        <is>
-          <t>957865-6-LE26</t>
-        </is>
-      </c>
-      <c r="B337" s="13" t="inlineStr">
-        <is>
-          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
-        </is>
-      </c>
-      <c r="C337" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D337" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="11" t="inlineStr">
-        <is>
-          <t>975-12-O126</t>
-        </is>
-      </c>
-      <c r="B338" s="13" t="inlineStr">
-        <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
-        </is>
-      </c>
-      <c r="C338" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D338" s="13" t="inlineStr">
-        <is>
-          <t>score 16 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="11" t="inlineStr">
-        <is>
-          <t>976-14-LP26</t>
-        </is>
-      </c>
-      <c r="B339" s="13" t="inlineStr">
-        <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
-        </is>
-      </c>
-      <c r="C339" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D339" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="11" t="inlineStr">
-        <is>
-          <t>979-49-L126</t>
-        </is>
-      </c>
-      <c r="B340" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
-        </is>
-      </c>
-      <c r="C340" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D340" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="11" t="inlineStr">
-        <is>
-          <t>986278-16-LE26</t>
-        </is>
-      </c>
-      <c r="B341" s="13" t="inlineStr">
-        <is>
-          <t>INSTALACIÓN Y CABLEADO DE ACCESS POINT EN CASA CENTRAL LAUTARO Y SEDE ANGOL CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
-        </is>
-      </c>
-      <c r="C341" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D341" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="11" t="inlineStr">
-        <is>
-          <t>993-42-LE26</t>
-        </is>
-      </c>
-      <c r="B342" s="13" t="inlineStr">
-        <is>
-          <t>Servicio Reparación y Mantención Recinto Taltal</t>
-        </is>
-      </c>
-      <c r="C342" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D342" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="11" t="inlineStr">
-        <is>
-          <t>997-32-LP26</t>
-        </is>
-      </c>
-      <c r="B343" s="13" t="inlineStr">
-        <is>
-          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
-        </is>
-      </c>
-      <c r="C343" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D343" s="13" t="inlineStr">
         <is>
           <t>score 0 &lt; 30</t>
         </is>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-09-02 19:32 · UF 40,876.41 · 4,526 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-06 18:41 · UF 40,881.68 · 4,767 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>CAMBIO: monto UF 122336.0-&gt;122320.0</t>
+          <t>CAMBIO: monto UF 122320.0-&gt;122304.0</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="M4" s="20" t="n">
-        <v>122320</v>
+        <v>122304</v>
       </c>
       <c r="N4" s="18" t="n">
         <v>53</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J6" s="11" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122320</v>
+        <v>122304</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
@@ -1829,11 +1829,11 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1991,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D328"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2045,72 +2045,72 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>1039-8-LP26</t>
+          <t>1036569-10-LP26</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE TRANSPORTE TERRESTRE</t>
+          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1051173-11-LE26</t>
+          <t>1039-8-LP26</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
+          <t>SERVICIO DE ARRIENDO DE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1052836-6-LE26</t>
+          <t>1051173-11-LE26</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
+          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1057049-273-LR26</t>
+          <t>1052836-6-LE26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
+          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
@@ -2125,12 +2125,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1057049-285-LR26</t>
+          <t>1057049-273-LR26</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
@@ -2145,12 +2145,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1057049-296-LR26</t>
+          <t>1057049-285-LR26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
@@ -2165,12 +2165,12 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1057049-321-LE26</t>
+          <t>1057049-296-LR26</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
+          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2185,12 +2185,12 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1057049-322-I226</t>
+          <t>1057049-321-LE26</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
@@ -2205,12 +2205,12 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1057055-68-LP26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -2225,32 +2225,32 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057049-328-LR26</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057404-82-LE26</t>
+          <t>1057055-68-LP26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2do Llamado ARRIENDO TORRE ENDOSCOPICA OTORRINO  </t>
+          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -2265,32 +2265,32 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057417-183-LP26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057417-51-LP26</t>
+          <t>1057417-183-LP26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
+          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -2305,32 +2305,32 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057420-37-LP26</t>
+          <t>1057417-186-LP26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
+          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057472-92-LP26</t>
+          <t>1057417-51-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
+          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2345,52 +2345,52 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057420-37-LP26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057489-255-LE26</t>
+          <t>1057472-92-LP26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Funcionamiento y Habilitación de nueva Bodega</t>
+          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057490-50-LR26</t>
+          <t>1057480-46-LR26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Lavado y Administración de Ropa.</t>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
@@ -2405,12 +2405,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057490-57-LP26</t>
+          <t>1057490-50-LR26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
+          <t>Arriendo Lavado y Administración de Ropa.</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -2425,12 +2425,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057490-65-LE26</t>
+          <t>1057490-57-LP26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE REACTIVOS PARA EL ANÁLISIS DE HORMONAS CON ARRIENDO DE EQUIPO PARA EL SERVICIO DE LABORATORIO</t>
+          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2465,12 +2465,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057492-121-LE26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2485,12 +2485,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057501-395-LR26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -2505,52 +2505,52 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057501-488-LE26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057501-473-LE26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t>Habilitación para Instalacion de Food Truck HSR</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057503-125-LE26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
@@ -2565,32 +2565,32 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057539-118-LP26</t>
+          <t>1057501-488-LE26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
+          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057544-293-LE26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
@@ -2605,12 +2605,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057503-125-LE26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -2625,12 +2625,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057547-354-LP26</t>
+          <t>1057508-112-LE26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
@@ -2645,12 +2645,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057736-6-L126</t>
+          <t>1057539-118-LP26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE BIENESTAR</t>
+          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -2665,12 +2665,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057922-22-LP26</t>
+          <t>1057539-129-LP26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
+          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -2685,12 +2685,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1070620-86-LP26</t>
+          <t>1057544-293-LE26</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
+          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -2705,12 +2705,12 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1075963-309-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
@@ -2725,12 +2725,12 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1075963-315-LP26</t>
+          <t>1057547-354-LP26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CINTAS REACTIVAS DE PROTROMBINA CON EQUIPO EN COMODATO POR 36 MESES</t>
+          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
@@ -2745,12 +2745,12 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1079650-57-LE26</t>
+          <t>1057922-22-LP26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
+          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
@@ -2765,12 +2765,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1079969-19-LP26</t>
+          <t>1057977-14-LE26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
+          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
@@ -2785,96 +2785,96 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1099402-21-L126</t>
+          <t>1070620-86-LP26</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
+          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1109692-8-LE26</t>
+          <t>1075963-309-LP26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO AUDIOVISUAL Y MULTIMEDIA SEDE PORVENIR</t>
+          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1116006-4-LE26</t>
+          <t>1079445-41-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
+          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1126922-33-LP26</t>
+          <t>1079650-57-LE26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1165648-6-L126</t>
+          <t>1079969-19-LP26</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO INTEGRAL DE MANTENIMIENTO PREVENTIVO, ASISTENCIA TÉCNICA, DIAGNÓSTICO, ATENCIÓN CORRECTIVA Y SOPORTE CONTINUO PARA SILLONES DENTALES Y COMPRESOR DEL DEPARTAMENTO DE SALUD MUNICIPAL DE LIMACHE</t>
+          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
@@ -2885,72 +2885,72 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1180730-37-LP26</t>
+          <t>1079969-20-LE26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
+          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1180830-16-LR26</t>
+          <t>1080303-8-LE26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+          <t>Serv. Armado Habilitación y Desarme de Pista Remo</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1197-20-L126</t>
+          <t>1099402-21-L126</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
+          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1107276-25-LE26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
@@ -2965,136 +2965,136 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1232565-33-LE26</t>
+          <t>1116006-4-LE26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
+          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1233615-56-LE26</t>
+          <t>1126922-33-LP26</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
+          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1175-71-LP26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1180730-37-LP26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1280-41-LE26</t>
+          <t>1180830-16-LR26</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
+          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1280-42-LE26</t>
+          <t>1197-20-L126</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
+          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1209403-8-L126</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
@@ -3105,12 +3105,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
@@ -3125,16 +3125,16 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1344190-12-LE26</t>
+          <t>1218393-40-L126</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
+          <t xml:space="preserve">APERTURA DE NUEVO VANO Y CIERRE DE VANO EXISTENTE BODEGA LAS ANIMAS </t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
@@ -3145,152 +3145,152 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1348-5-LP26</t>
+          <t>1232565-33-LE26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
+          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1351-6-LP26</t>
+          <t>1233615-56-LE26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
+          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1375746-17-LP26</t>
+          <t>1236-17-LE26</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
+          <t>REQ. 107_TRASLADOS TERRESTRES PARA DEPORTISTAS FINAL NACIONAL DE JUEGOS DEPORTIVOS ESCOLARES</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1395865-16-LE26</t>
+          <t>1237853-17-L126</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+          <t>SERVICIO DE ARRIENDO DE TÉCNICA PARA EVENTO DEPORTIVO, PARA LA CORPORACIÓN DEL DEPORTE DE LA FLORIDA</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1415863-2-LE26</t>
+          <t>1261-19-LR26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACIONES PSICOLABORALES PARA EL PROCESO DE RECLUTAMIENTO Y SELECCIÓN DEL DEPARTAMENTO DE GESTIÓN Y DESARROLLO DE LAS PERSONAS DEL INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1422824-25-LP26</t>
+          <t>1280-41-LE26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1280-42-LE26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
@@ -3305,12 +3305,12 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1443-1-LE26</t>
+          <t>1293138-13-LP26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje y almacenamiento</t>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
@@ -3325,12 +3325,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1305527-3-LP26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
@@ -3345,92 +3345,92 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1469-189-L126</t>
+          <t>1337-21-LE26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
+          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1501468-17-LE26</t>
+          <t>1344190-12-LE26</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
+          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1537592-17-LE26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1374899-36-LP26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
@@ -3445,72 +3445,72 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1375746-17-LP26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1605-45-LP26</t>
+          <t>1375753-31-LE26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+          <t>SERVICIO DE LEVANTAMIENTO DE INVENTARIO Y ARRIENDO</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>162-26-LE26</t>
+          <t>1395865-16-LE26</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>Servicio traslado de muestras a los Laboratorios</t>
+          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1624-21-L126</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>Convenio de suministros de Oxígeno Médico, Recarga y Arriendo de cilindros para servicios Urgencias y Hospitalizados</t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
@@ -3525,12 +3525,12 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1641-219-LR26</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
@@ -3545,12 +3545,12 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1655-23-LP26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
@@ -3565,56 +3565,56 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>1431841-56-LP26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1663-137-LE26</t>
+          <t>1431841-57-LE26</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
+          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1671-30-LE26</t>
+          <t>1443-1-LE26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>Reestructuración Oficina de Partes de la SEREMI de</t>
+          <t>Servicio de bodegaje y almacenamiento</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
@@ -3625,12 +3625,12 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1696-11-LE26</t>
+          <t>1448821-14-LP26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de sala de audiencia para el Juzgado de Familia de Arica</t>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
@@ -3645,176 +3645,176 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1469101-6-LP26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1973-96-LE26</t>
+          <t>1469-189-L126</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
+          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1978-100-L126</t>
+          <t>1501468-17-LE26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
+          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>2069-155-LP26</t>
+          <t>1537592-17-LE26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
+          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>2098-115-LE26</t>
+          <t>1540667-6-LR26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
+          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>2098-124-LE26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>2098-127-LE26</t>
+          <t>1554-55-LR26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>2098-133-LP26</t>
+          <t>1555-75-LP26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
+          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>2098-134-LP26</t>
+          <t>1605-41-LP26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
+          <t>LP-4872 Servicios de mantención general edificios</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
@@ -3825,52 +3825,52 @@
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>2107-142-LE26</t>
+          <t>1605-45-LP26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
+          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>2107-144-LP26</t>
+          <t>162-26-LE26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
+          <t>Servicio traslado de muestras a los Laboratorios</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>2109-10-LP26</t>
+          <t>1641-219-LR26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
+          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
@@ -3885,12 +3885,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>2126-128-LE26</t>
+          <t>1655-23-LP26</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
+          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
@@ -3905,16 +3905,16 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>2173-27-LE26</t>
+          <t>1658-189-LP26</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
@@ -3925,176 +3925,176 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>2179-14-LE26</t>
+          <t>1663-137-LE26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
+          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>2258-133-LR26</t>
+          <t>1696-15-LE26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>2258-168-LE26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>2258-175-LR26</t>
+          <t>1810-3-LE26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
+          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>1973-96-LE26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>2258-72-LE26</t>
+          <t>1973-97-LP26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>2271-65-LE26</t>
+          <t>1978-100-L126</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>2273-55-LE26</t>
+          <t>1978-112-L126</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
+          <t>CONVENIO MONITOREO SISTEMA DE ALARMA EN BODEGA REGIONAL SSMAULE</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2020-19-LE26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
@@ -4105,52 +4105,52 @@
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>2279-58-LE26</t>
+          <t>2069-155-LP26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
+          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>2282-96-LE26</t>
+          <t>2098-115-LE26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Memorial Victor Hugo Carreño Valdivi</t>
+          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2098-122-LP26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
@@ -4165,56 +4165,56 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2098-124-LE26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>2308-72-LE26</t>
+          <t>2098-127-LE26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>2332-101-L126</t>
+          <t>2098-133-LP26</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
+          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
@@ -4225,216 +4225,216 @@
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>2332-104-L126</t>
+          <t>2098-134-LP26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN BOX DENTAL Y SOME CENTRAL DE “POSTA LAS QUEMAS” DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>2332-105-L126</t>
+          <t>2107-142-LE26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TÓRULAS, SERVILLETAS, VASOS DESECHABLES Y EYECTORES ODONTOLÓGICOS PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>2366-54-LE26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2109-10-LP26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2123-22-CO26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>E1O2RT8 Traslado Pasajeros Provincia La Ligua</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2402-76-LE26</t>
+          <t>2126-128-LE26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>SEGURIDAD RECINTO CELEBRACION FIESTAS PATRIAS 2026</t>
+          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2173-27-LE26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2408-160-LP26</t>
+          <t>2176-55-LE26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2408-210-L126</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS VARIOS PARA CABAÑAS RECINTO CHACAY.</t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>2408-98-LE26</t>
+          <t>2258-133-LR26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
+          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>2410-35-LP26</t>
+          <t>2258-168-LE26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de artículos eléctricos para mantención de inmuebles</t>
+          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
@@ -4445,12 +4445,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2410-84-LE26</t>
+          <t>2258-175-LR26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
@@ -4465,52 +4465,52 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2426-44-LE26</t>
+          <t>2258-72-LE26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
+          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2430-59-LP26</t>
+          <t>2271-65-LE26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
+          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
@@ -4525,52 +4525,52 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2430-71-LP26</t>
+          <t>2273-55-LE26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2445-110-LE26</t>
+          <t>2274-43-L126</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
+          <t>HABILITACIÓN DE SALAS DE LACTANCIA MATERNA PARA LOS CESFAM SANTIAGO NUEVA EXTREMADURA Y SAN RAFAEL . EXP 13788</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>2275-29-LE26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
@@ -4585,16 +4585,16 @@
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2448-107-L126</t>
+          <t>2279-58-LE26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE COMEDOR DE FUNCIONARIOS DROGUERIA  Y BODEGA DESAM</t>
+          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -4605,12 +4605,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2448-110-L126</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE ESPACIO DE TRABAJO COLECTIVO CECOSF PUNTA MIRA</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
@@ -4625,52 +4625,52 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2450-90-LE26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2452-19-L126</t>
+          <t>2308-72-LE26</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE INFRAESTRUCTURA EN INMUEBLE</t>
+          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2332-104-L126</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>HABILITACIÓN BOX DENTAL Y SOME CENTRAL DE “POSTA LAS QUEMAS” DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
@@ -4685,92 +4685,92 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2460-112-LE26</t>
+          <t>2332-105-L126</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Graderías y Tribuna de Honor Desfile en Honor a Las Glorias del Ejército</t>
+          <t>ADQUISICIÓN DE TÓRULAS, SERVILLETAS, VASOS DESECHABLES Y EYECTORES ODONTOLÓGICOS PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2460-113-LE26</t>
+          <t>2332-52-LE26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Vallas Desfile en Honor a las Glorias del Ejército</t>
+          <t>ARRIENDO E INSTALACION CASILLEROS INTELIGENTES</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2460-99-LE26</t>
+          <t>2366-54-LE26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2546-49-LP26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>PROP PUBL N69 CONSTRUCCION SEDE SOCIAL V. PULMAHUE</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
@@ -4785,12 +4785,12 @@
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2555-10-LP26</t>
+          <t>2378-110-LP26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
@@ -4805,52 +4805,52 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2565-14-LP26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2408-152-LE26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2408-160-LP26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
@@ -4865,32 +4865,32 @@
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2408-98-LE26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2585-87-LE26</t>
+          <t>2410-84-LE26</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VEH. ACUATICO Y TODOTERRENO ORD N°167-TURISMO</t>
+          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
@@ -4905,12 +4905,12 @@
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
@@ -4925,16 +4925,16 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2426-44-LE26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
@@ -4945,76 +4945,76 @@
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2626-8-LE26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2664-38-L126</t>
+          <t>2430-68-LR26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>PUERTAS Y VENTANAS PARA AMPLIACION DE SALA ADRRI</t>
+          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2430-71-LP26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2667-83-LE26</t>
+          <t>2430-78-LP26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
+          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
@@ -5025,52 +5025,52 @@
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2686-120-CO26</t>
+          <t>2445-110-LE26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
+          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2697-23-LP26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION PLAZA DEPORTIVA EN COSTANERA SECTOR SAN SEBASTIAN</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2446-257-LE26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
@@ -5085,52 +5085,52 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2699-32-LR26</t>
+          <t>2446-260-LR26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Flota Vehicular</t>
+          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2702-62-LE26</t>
+          <t>2448-107-L126</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO BAÑOS QUÍMICOS FIESTA CHILEN</t>
+          <t>MEJORAMIENTO DE COMEDOR DE FUNCIONARIOS DROGUERIA  Y BODEGA DESAM</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2702-63-LE26</t>
+          <t>2448-110-L126</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
+          <t>HABILITACION DE ESPACIO DE TRABAJO COLECTIVO CECOSF PUNTA MIRA</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
@@ -5145,96 +5145,96 @@
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2703-175-L126</t>
+          <t>2450-90-LE26</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>SC 12493 Servicio REAS retiro traslado y eliminación de Residuos</t>
+          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2709-77-LE26</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION PARQUE RECREACIONAL LOS PEÑONES</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>2460-112-LE26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>Servicio de Arriendo de Graderías y Tribuna de Honor Desfile en Honor a Las Glorias del Ejército</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2730-113-LE26</t>
+          <t>2460-113-LE26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
+          <t>Servicio de Arriendo de Vallas Desfile en Honor a las Glorias del Ejército</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2736-32-LE26</t>
+          <t>2460-121-LE26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>Materiales de Oficina</t>
+          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
@@ -5245,92 +5245,92 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2744-30-LE26</t>
+          <t>2460-99-LE26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
+          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>2548-83-L126</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>SERVICIO HABILITACIÓN OFICINA CESFAM PLC</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2784-44-LE26</t>
+          <t>2555-10-LP26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
+          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2788-43-LE26</t>
+          <t>2565-14-LP26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BAÑOS FIESTAS PATRIAS</t>
+          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
@@ -5345,32 +5345,32 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2793-91-LE26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLATABANDA ACCESOS A EDIFICIO PDI COMUNA DE HUECHURABA</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2905-40-LP26</t>
+          <t>2581-37-LP26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
@@ -5385,36 +5385,36 @@
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2963-26-LR26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
@@ -5425,76 +5425,76 @@
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>2626-8-LE26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>3017-68-LE26</t>
+          <t>2667-83-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
+          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
@@ -5505,72 +5505,72 @@
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>3069-3-LE26</t>
+          <t>2667-90-LE26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>Traslado de Pasajeros</t>
+          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>2686-120-CO26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>3092-18-LE26</t>
+          <t>2697-25-LR26</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN DE LOS SERVICIOS DE  LABORATORIO DE CANASTA DE BASICA Y GES APS   BÁSICA Y GES PARA LA DIRECCIÓN DE SALUD MUNICIPAL I.MUNICIPALIDAD DE CASABLANCA 2026</t>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>3159-18-LE26</t>
+          <t>2699-32-LR26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
+          <t>Servicio de Arriendo de Flota Vehicular</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
@@ -5585,116 +5585,116 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>3172-46-LR26</t>
+          <t>2702-63-LE26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>3179-44-LE26</t>
+          <t>2702-65-LE26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CASACA OPERATIVA CON POLAR</t>
+          <t>ARRIENDO DE BAÑOS QUIMICOS ESTANDAR Y BAÑO TRAILER DOBLE VIP FIESTA DE LA CHILENIDAD 2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>2709-77-LE26</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>HABILITACION PARQUE RECREACIONAL LOS PEÑONES</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>3333-32-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>3384-20-LP26</t>
+          <t>2730-113-LE26</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
+          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>3436-97-LE26</t>
+          <t>2736-32-LE26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>Servicio mantenimiento de dependencias SIC 351978</t>
+          <t>Materiales de Oficina</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
@@ -5705,36 +5705,36 @@
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>3477-76-LE26</t>
+          <t>2744-30-LE26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>“MANTENCIÓN Y REPARACIÓN DE EDIFICIO MUNICIPAL”</t>
+          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>3525-8-LR26</t>
+          <t>2744-34-LE26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>Sum e instalación de taludes visita terreno volun</t>
+          <t xml:space="preserve">SERVICIO CONTROL DE PLAGAS INTEGRAL PARA ESTABLECIMIENTOS URBANOS Y RURALES DEL DEPARTAMENTO DE SALUD MUNICIPAL DE ANGOL </t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
@@ -5745,36 +5745,36 @@
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>3537-52-LE26</t>
+          <t>2755-34-LE26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de una autohormigonera por 320 horas</t>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>3542-22-LE26</t>
+          <t>2784-42-LP26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
@@ -5785,36 +5785,36 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>3611-11-LE26</t>
+          <t>2784-44-LE26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>Servicio de retiro traslado y eliminación de material cortopunzante residuos médicos y otros del Departamento de Salud Municipal Puerto Saavedra y su CSR de Dominguez</t>
+          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>3624-32-LP26</t>
+          <t>2794-22-LR26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
+          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
@@ -5825,16 +5825,16 @@
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>3624-33-LP26</t>
+          <t>2905-40-LP26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
+          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
@@ -5845,32 +5845,32 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>3656-148-LP26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>3668-14-LP26</t>
+          <t>2920-38-LP26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+          <t>Construcción Sede Juventud Robinsoniana.</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
@@ -5885,112 +5885,112 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>3671-58-LE26</t>
+          <t>2963-26-LR26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
+          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>3693-158-LP26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>3708-39-LE26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>3710-84-L126</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>ESCANER PARA BODEGA FARMACIA CESFAM VICTORIA</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>3775-28-LP26</t>
+          <t>3017-68-LE26</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>3798-13-LP26</t>
+          <t>3046-25-LE26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
@@ -6005,32 +6005,32 @@
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>3880-61-LE26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>3092-18-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>PROVISIÓN DE LOS SERVICIOS DE  LABORATORIO DE CANASTA DE BASICA Y GES APS   BÁSICA Y GES PARA LA DIRECCIÓN DE SALUD MUNICIPAL I.MUNICIPALIDAD DE CASABLANCA 2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
@@ -6045,12 +6045,12 @@
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3882-81-L126</t>
+          <t>3159-18-LE26</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE ARRIENDO DE JUEGOS INFLABLES PARA ACTIVIDADES SECTORIALES DE LA ILUSTRE MUNICIPALIDAD DE LLAY LLAY”.</t>
+          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
@@ -6065,16 +6065,16 @@
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3882-85-LE26</t>
+          <t>3172-46-LR26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE NUEVA OFICINA CONTROL I. MUNICIPALIDAD LLAY LLAY COMUNA LLAY LLAY</t>
+          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
@@ -6085,12 +6085,12 @@
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>3887-39-LP26</t>
+          <t>3179-49-LE26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+          <t>ADQUISICIÓN CASACA DE POLAR FRONTERA</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
@@ -6105,16 +6105,16 @@
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>3889-41-LP26</t>
+          <t>3179-50-LE26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
+          <t>ADQUISICIÓN DE CASACA DE CUERO MOTORISTAS</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
@@ -6125,72 +6125,72 @@
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>3179-51-LE26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>3950-40-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>3997-59-B226</t>
+          <t>3290-8-LE26</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>4006-21-LE26</t>
+          <t>3333-32-LE26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Area Deportiva Ventanas</t>
+          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
@@ -6205,32 +6205,32 @@
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>4031-14-LE26</t>
+          <t>3384-20-LP26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>REP. DEL 2 PISO DE LA SEDE SOCIAL DE CHAPIQUILTA</t>
+          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>3436-97-LE26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>Servicio mantenimiento de dependencias SIC 351978</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
@@ -6245,32 +6245,32 @@
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>407-134-LE26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>RETIRO TORRE VENTADA HGGB</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>4086-43-LE26</t>
+          <t>3537-52-LE26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO DE EXCAVADORA</t>
+          <t>Arriendo de una autohormigonera por 320 horas</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
@@ -6285,16 +6285,16 @@
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>3542-22-LE26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
@@ -6305,12 +6305,12 @@
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>4121-23-LE26</t>
+          <t>359-105-LE26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+          <t>ADQ. CLIP POLIMERO CON COMODATO DE APLICADORES</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
@@ -6325,76 +6325,76 @@
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>4152-28-LE26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>418-51-LP26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>4236-22-L126</t>
+          <t>3656-148-LP26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>INSTALACIÓN DE VENTANA Y MAMPARA EDIFICIO CONSISTORIAL</t>
+          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>4237-12-LR26</t>
+          <t>3668-14-LP26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
@@ -6405,32 +6405,32 @@
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>4238-66-B226</t>
+          <t>3671-58-LE26</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>4295-41-LP26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
@@ -6445,16 +6445,16 @@
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>4328-31-B226</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TERRENO SAN GREGORIO ÑIQUÉN</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
@@ -6465,152 +6465,152 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>4342-2-LP26</t>
+          <t>3710-84-L126</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
+          <t>ESCANER PARA BODEGA FARMACIA CESFAM VICTORIA</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>4362-15-LP26</t>
+          <t>3761-21-LE26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>4362-20-LE26</t>
+          <t>3775-28-LP26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>438-49-LE26</t>
+          <t>3789-33-LE26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION INTERIOR AGUAS LLUVIAS E INSTALACION ELECTRICA Y OTROS PARA LA DROGUERIA MUNICIPAL</t>
+          <t>ADQUISICION DE EQUIPOS DE REHABILITACION MOTORA</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>439-26-LP26</t>
+          <t>3798-13-LP26</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
+          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>4451-92-LE26</t>
+          <t>3880-61-LE26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
+          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>4457-70-L126</t>
+          <t>3882-72-LP26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTOS PRAPS MAS AMA, EQUIDAD RURAL, REHABILITACIÓN INTEGRAL Y ESPACIOS AMIGABLES.</t>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>4591-20-LP26</t>
+          <t>3882-81-L126</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
+          <t>“SERVICIO DE ARRIENDO DE JUEGOS INFLABLES PARA ACTIVIDADES SECTORIALES DE LA ILUSTRE MUNICIPALIDAD DE LLAY LLAY”.</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
@@ -6625,12 +6625,12 @@
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>4623-4-L126</t>
+          <t>3882-85-LE26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
+          <t>MEJORAMIENTO DE NUEVA OFICINA CONTROL I. MUNICIPALIDAD LLAY LLAY COMUNA LLAY LLAY</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
@@ -6645,116 +6645,116 @@
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>4629-26-LE26</t>
+          <t>3887-39-LP26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
+          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>3889-41-LP26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>4642-93-LP26</t>
+          <t>3912-19-LP26</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE OBRAS DE HABILITACIÓN DE LA SALA DE ESTIMULACIÓN TEMPRANA DEL CENTRO MÉDICO Y DENTAL DE VIÑA DEL MAR PERTENECIENTE A LA RED SALUD DE CARABINEROS.</t>
+          <t>Construccion sede social los acacios</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>4642-99-LE26</t>
+          <t>3935-83-LP26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>4644-5-LP26</t>
+          <t>3935-87-LE26</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>TRANSPORTE-CONTRATISTAS Y ARRIENDO MAQ FORESTAL</t>
+          <t>CONTRATACION SERVICIO DE ECOTOMOGRAFIA ABDOMINAL PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE 2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>4850-4-L126</t>
+          <t>3935-88-LE26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
+          <t>CONTRATACION SERVICIO DE MAMOGRAFIAS Y ECOTOMOGRAFIA MAMARIA PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
@@ -6765,52 +6765,52 @@
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>4920-12-LE26</t>
+          <t>3950-40-LE26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
+          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>4928-21-LP26</t>
+          <t>3963-16-LP26</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE MANTENCIÓN CORRECTIVA Y TRASLADO GG.EE. </t>
+          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>4956-63-LP26</t>
+          <t>3997-59-B226</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL LO BOZA</t>
+          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
@@ -6825,12 +6825,12 @@
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>4006-21-LE26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>Mejoramiento Area Deportiva Ventanas</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
@@ -6845,32 +6845,32 @@
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>4967-7-LR26</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D243" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>5048-13-O126</t>
+          <t>407-134-LE26</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>MEJ ESTERO CHAMIL - TRES VENTANAS, REGION DE LOS RIOS</t>
+          <t>RETIRO TORRE VENTADA HGGB</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
@@ -6885,32 +6885,32 @@
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>5048-51-O126</t>
+          <t>4099-22-LP26</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t>AIF TRES VENTANAS TRAMO 2</t>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D245" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>4121-23-LE26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
@@ -6925,12 +6925,12 @@
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>507428-94-LE26</t>
+          <t>4143-6-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
@@ -6945,12 +6945,12 @@
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>5194-4-LE26</t>
+          <t>4152-28-LE26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
@@ -6965,32 +6965,32 @@
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>520149-35-L126</t>
+          <t>418-51-LP26</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO. </t>
+          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>418-57-LP26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
@@ -7005,52 +7005,52 @@
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>525512-33-LE26</t>
+          <t>4189-38-LE26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t>Diseño proyecto construcción sede social JJVV</t>
+          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>4237-12-LR26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>4238-66-B226</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
@@ -7065,32 +7065,32 @@
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>539119-80-LP26</t>
+          <t>425-57-LR26</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>539119-81-LE26</t>
+          <t>4284-145-L126</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>Adquisición de 50 metros de leña nativa seca y trozada para calefacción dependencias municipales Según bases adjuntas Punto 2 productos requeridos</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
@@ -7105,16 +7105,16 @@
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>539119-85-LP26</t>
+          <t>4295-41-LP26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
@@ -7125,16 +7125,16 @@
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>539119-86-LE26</t>
+          <t>4295-67-LP26</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
@@ -7145,12 +7145,12 @@
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>5413-65-LE26</t>
+          <t>4309-233-LP26</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO DE ESTURIONES COYHAIQUE</t>
+          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
@@ -7165,16 +7165,16 @@
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>5413-67-LE26</t>
+          <t>4328-33-B226</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
+          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
@@ -7185,36 +7185,36 @@
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>5420-20-LE26</t>
+          <t>4342-2-LP26</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
-          <t>Diseño eléctrico para normalización de edificios</t>
+          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>4362-15-LP26</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
@@ -7225,92 +7225,92 @@
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>4362-20-LE26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>5558-5-L126</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>557639-74-LE26</t>
+          <t>4451-92-LE26</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
-          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
+          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>4454-27-LE26</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>SERVICIO DE TRASLADO - PROGRAMA SOCIAL</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D265" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>568658-43-LR26</t>
+          <t>4457-70-L126</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
+          <t>IMPLEMENTOS PRAPS MAS AMA, EQUIDAD RURAL, REHABILITACIÓN INTEGRAL Y ESPACIOS AMIGABLES.</t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
@@ -7325,12 +7325,12 @@
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>4494-61-LE26</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>HABILITACIÓN DE MÁSTILES URBANOS INSTITUCIONALES</t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
@@ -7345,32 +7345,32 @@
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>608-126-LR26</t>
+          <t>4584-13-LE26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>4591-20-LP26</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
@@ -7385,96 +7385,96 @@
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>622847-13-LE26</t>
+          <t>4623-4-L126</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
+          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>score 21 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>627786-14-LE26</t>
+          <t>4629-26-LE26</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO CAMBIO DE PUERTAS Y VENTANAS GRUPO OVALLE</t>
+          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>630-24-LE26</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>4642-99-LE26</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>634-82-LE26</t>
+          <t>483-47-L126</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
+          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
@@ -7485,12 +7485,12 @@
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>4850-4-L126</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
@@ -7505,12 +7505,12 @@
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>649-8-LE26</t>
+          <t>4920-12-LE26</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
+          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
@@ -7525,112 +7525,112 @@
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>660-10-LE26</t>
+          <t>4967-7-LR26</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
+          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>673-3-LE26</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MEJORAMIENTO RED SANITARIA EDIFICIO IN</t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D279" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>5056-102-LP26</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>680-10-LE26</t>
+          <t>507428-94-LE26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>681016-3-L126</t>
+          <t>5194-4-LE26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BIDONES DE AGUA PURIFICADA Y DISPENSADORES EN COMODATO</t>
+          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
@@ -7645,32 +7645,32 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>688-11-LP26</t>
+          <t>520149-35-L126</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Infraestructura de Respaldo</t>
+          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO. </t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>697057-30-LE26</t>
+          <t>5240-102-LR26</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
@@ -7685,36 +7685,36 @@
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>697-29-LE26</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>Serv. habilitación electrica para equipo trifasico</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D285" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>525512-33-LE26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>Diseño proyecto construcción sede social JJVV</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
@@ -7725,16 +7725,16 @@
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>527481-62-LE26</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>CONSTRUCCION SEDE EL MOLLAR</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D287" s="13" t="inlineStr">
         <is>
@@ -7745,12 +7745,12 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>527481-65-LE26</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>ARRIENDO DE EQUIPOS ELECTRICOS</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
@@ -7765,96 +7765,96 @@
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>742475-4-LE26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>742-8-L126</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>748201-10-LE26</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>539119-81-LE26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>539119-85-LP26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
@@ -7865,112 +7865,112 @@
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>769-84-LP26</t>
+          <t>539119-86-LE26</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>777304-55-LP26</t>
+          <t>5413-67-LE26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
+          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>813685-9-LE26</t>
+          <t>5420-20-LE26</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
+          <t>Diseño eléctrico para normalización de edificios</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>5558-5-L126</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
@@ -7985,32 +7985,32 @@
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>838100-6-L126</t>
+          <t>557639-74-LE26</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>5586-126-LE26</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
@@ -8025,12 +8025,12 @@
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>854-28-LE26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
@@ -8045,112 +8045,112 @@
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>867990-59-L126</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>cc 102 - sol 91975 servicio de mantenimiento del sistema de calefacción central con visita a terreno</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>867990-81-L126</t>
+          <t>608-126-LR26</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>CC 102 SOL 92520 - Contrato servicio de mantención preventiva y puesta en marcha de sistema de presurización de las escaleras del edificio nuevo de la Facultad de Administración y Economía</t>
+          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>867990-84-L126</t>
+          <t>622-55-LE26</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>875646-67-LE26</t>
+          <t>622847-13-LE26</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
+          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 21 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>886954-176-LP26</t>
+          <t>630-24-LE26</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
+          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>633-48-LR26</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
@@ -8165,76 +8165,76 @@
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>886954-262-LP26</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>886954-297-LP26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>929-23-L126</t>
+          <t>643-32-LE26</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>Mantenimiento de Instalaciones y Equipos Eléctricos, Oficinas DRM</t>
+          <t>TRASLADO FUNCIONARIOS OFICINA ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D311" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>931-23-LE26</t>
+          <t>649-8-LE26</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
+          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
@@ -8245,56 +8245,56 @@
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>931-25-LE26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE REPARACIÓN DE TECHUMBRE Y SISTEMA DE AGUAS LLUVIAS – CASA DEL DEPORTISTA VICUÑA</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>931-26-LE26</t>
+          <t>660-10-LE26</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
+          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>931-27-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
@@ -8305,52 +8305,52 @@
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>935-22-LE26</t>
+          <t>680-10-LE26</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
+          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>948355-68-LP26</t>
+          <t>680504-2-L126</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
+          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>948806-117-LP26</t>
+          <t>688-11-LP26</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
+          <t>Arriendo Infraestructura de Respaldo</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
@@ -8365,52 +8365,52 @@
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>956-57-L126</t>
+          <t>697057-30-LE26</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>956-58-LE26</t>
+          <t>697-29-LE26</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+          <t>Serv. habilitación electrica para equipo trifasico</t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>957865-6-LE26</t>
+          <t>699866-116-LP26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
@@ -8425,52 +8425,52 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>975-12-O126</t>
+          <t>707418-44-L126</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>976-14-LP26</t>
+          <t>707420-20-LE26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>979-49-L126</t>
+          <t>712307-58-O126</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
@@ -8485,56 +8485,56 @@
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>993-42-LE26</t>
+          <t>729-180-LE26</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
         <is>
-          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+          <t>SELLOS PRECINTOS EMBALAJE -CLS-2x20295</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D325" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>993-47-LE26</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
         <is>
-          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>996-35-LE26</t>
+          <t>742475-4-LE26</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
+          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
         </is>
       </c>
       <c r="C327" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
@@ -8545,18 +8545,838 @@
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
+          <t>742-8-L126</t>
+        </is>
+      </c>
+      <c r="B328" s="13" t="inlineStr">
+        <is>
+          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="11" t="inlineStr">
+        <is>
+          <t>748201-10-LE26</t>
+        </is>
+      </c>
+      <c r="B329" s="13" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+        </is>
+      </c>
+      <c r="C329" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="11" t="inlineStr">
+        <is>
+          <t>748201-9-LP26</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="inlineStr">
+        <is>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="11" t="inlineStr">
+        <is>
+          <t>763003-8-LE26</t>
+        </is>
+      </c>
+      <c r="B331" s="13" t="inlineStr">
+        <is>
+          <t>MATERIALES PARA ACONDICIONAMIENTO DE OFICINAS.</t>
+        </is>
+      </c>
+      <c r="C331" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D331" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="11" t="inlineStr">
+        <is>
+          <t>768-19-LR26</t>
+        </is>
+      </c>
+      <c r="B332" s="13" t="inlineStr">
+        <is>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+        </is>
+      </c>
+      <c r="C332" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D332" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="11" t="inlineStr">
+        <is>
+          <t>769-84-LP26</t>
+        </is>
+      </c>
+      <c r="B333" s="13" t="inlineStr">
+        <is>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+        </is>
+      </c>
+      <c r="C333" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="11" t="inlineStr">
+        <is>
+          <t>777304-55-LP26</t>
+        </is>
+      </c>
+      <c r="B334" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="11" t="inlineStr">
+        <is>
+          <t>780724-6-LE26</t>
+        </is>
+      </c>
+      <c r="B335" s="13" t="inlineStr">
+        <is>
+          <t>Remodelación dependencias TercerTribunal Ambiental</t>
+        </is>
+      </c>
+      <c r="C335" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D335" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="11" t="inlineStr">
+        <is>
+          <t>813685-9-LE26</t>
+        </is>
+      </c>
+      <c r="B336" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D336" s="13" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="11" t="inlineStr">
+        <is>
+          <t>813-87-LE26</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="inlineStr">
+        <is>
+          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
+        </is>
+      </c>
+      <c r="C337" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="11" t="inlineStr">
+        <is>
+          <t>824-3-LE26</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="inlineStr">
+        <is>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D338" s="13" t="inlineStr">
+        <is>
+          <t>score 19 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="11" t="inlineStr">
+        <is>
+          <t>829-2-O126</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="inlineStr">
+        <is>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+        </is>
+      </c>
+      <c r="C339" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D339" s="13" t="inlineStr">
+        <is>
+          <t>score 14 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="11" t="inlineStr">
+        <is>
+          <t>837-88-LP26</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="inlineStr">
+        <is>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D340" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>838100-6-L126</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+        </is>
+      </c>
+      <c r="C341" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="11" t="inlineStr">
+        <is>
+          <t>845-17-LR26</t>
+        </is>
+      </c>
+      <c r="B342" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+        </is>
+      </c>
+      <c r="C342" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D342" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="11" t="inlineStr">
+        <is>
+          <t>854-28-LE26</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="inlineStr">
+        <is>
+          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
+        </is>
+      </c>
+      <c r="C343" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="11" t="inlineStr">
+        <is>
+          <t>867990-81-L126</t>
+        </is>
+      </c>
+      <c r="B344" s="13" t="inlineStr">
+        <is>
+          <t>CC 102 SOL 92520 - Contrato servicio de mantención preventiva y puesta en marcha de sistema de presurización de las escaleras del edificio nuevo de la Facultad de Administración y Economía</t>
+        </is>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D344" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="11" t="inlineStr">
+        <is>
+          <t>867990-84-L126</t>
+        </is>
+      </c>
+      <c r="B345" s="13" t="inlineStr">
+        <is>
+          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
+        </is>
+      </c>
+      <c r="C345" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D345" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="11" t="inlineStr">
+        <is>
+          <t>867990-89-L126</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="inlineStr">
+        <is>
+          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
+        </is>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D346" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="11" t="inlineStr">
+        <is>
+          <t>875646-67-LE26</t>
+        </is>
+      </c>
+      <c r="B347" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
+        </is>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="11" t="inlineStr">
+        <is>
+          <t>885-80-LP26</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="inlineStr">
+        <is>
+          <t>Servicios de remodelación de oficinas de la Contraloría Regional de La Arauncanía</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D348" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="11" t="inlineStr">
+        <is>
+          <t>886954-176-LP26</t>
+        </is>
+      </c>
+      <c r="B349" s="13" t="inlineStr">
+        <is>
+          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
+        </is>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="11" t="inlineStr">
+        <is>
+          <t>886954-222-LR26</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="inlineStr">
+        <is>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+        </is>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="11" t="inlineStr">
+        <is>
+          <t>886954-262-LP26</t>
+        </is>
+      </c>
+      <c r="B351" s="13" t="inlineStr">
+        <is>
+          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+        </is>
+      </c>
+      <c r="C351" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="11" t="inlineStr">
+        <is>
+          <t>886954-297-LP26</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="inlineStr">
+        <is>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+        </is>
+      </c>
+      <c r="C352" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="11" t="inlineStr">
+        <is>
+          <t>931-23-LE26</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
+        </is>
+      </c>
+      <c r="C353" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D353" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="11" t="inlineStr">
+        <is>
+          <t>931-26-LE26</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
+        </is>
+      </c>
+      <c r="C354" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D354" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="11" t="inlineStr">
+        <is>
+          <t>931-27-LE26</t>
+        </is>
+      </c>
+      <c r="B355" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
+        </is>
+      </c>
+      <c r="C355" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D355" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="11" t="inlineStr">
+        <is>
+          <t>935-22-LE26</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="inlineStr">
+        <is>
+          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
+        </is>
+      </c>
+      <c r="C356" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D356" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="11" t="inlineStr">
+        <is>
+          <t>948355-68-LP26</t>
+        </is>
+      </c>
+      <c r="B357" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
+        </is>
+      </c>
+      <c r="C357" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="11" t="inlineStr">
+        <is>
+          <t>948806-117-LP26</t>
+        </is>
+      </c>
+      <c r="B358" s="13" t="inlineStr">
+        <is>
+          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
+        </is>
+      </c>
+      <c r="C358" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="11" t="inlineStr">
+        <is>
+          <t>956-57-L126</t>
+        </is>
+      </c>
+      <c r="B359" s="13" t="inlineStr">
+        <is>
+          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
+        </is>
+      </c>
+      <c r="C359" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D359" s="13" t="inlineStr">
+        <is>
+          <t>score 11 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="11" t="inlineStr">
+        <is>
+          <t>956-58-LE26</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="inlineStr">
+        <is>
+          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
+        </is>
+      </c>
+      <c r="C360" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D360" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="11" t="inlineStr">
+        <is>
+          <t>957865-6-LE26</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="inlineStr">
+        <is>
+          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
+        </is>
+      </c>
+      <c r="C361" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="11" t="inlineStr">
+        <is>
+          <t>975-12-O126</t>
+        </is>
+      </c>
+      <c r="B362" s="13" t="inlineStr">
+        <is>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+        </is>
+      </c>
+      <c r="C362" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D362" s="13" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="11" t="inlineStr">
+        <is>
+          <t>976-14-LP26</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
+        </is>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="11" t="inlineStr">
+        <is>
+          <t>979-49-L126</t>
+        </is>
+      </c>
+      <c r="B364" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D364" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="11" t="inlineStr">
+        <is>
+          <t>993-42-LE26</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="inlineStr">
+        <is>
+          <t>Servicio Reparación y Mantención Recinto Taltal</t>
+        </is>
+      </c>
+      <c r="C365" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D365" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="11" t="inlineStr">
+        <is>
+          <t>993-47-LE26</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="inlineStr">
+        <is>
+          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
+        </is>
+      </c>
+      <c r="C366" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D366" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="11" t="inlineStr">
+        <is>
+          <t>996-35-LE26</t>
+        </is>
+      </c>
+      <c r="B367" s="13" t="inlineStr">
+        <is>
+          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
+        </is>
+      </c>
+      <c r="C367" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D367" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="11" t="inlineStr">
+        <is>
           <t>997-32-LP26</t>
         </is>
       </c>
-      <c r="B328" s="13" t="inlineStr">
+      <c r="B368" s="13" t="inlineStr">
         <is>
           <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
         </is>
       </c>
-      <c r="C328" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D328" s="13" t="inlineStr">
+      <c r="C368" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D368" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="11" t="inlineStr">
+        <is>
+          <t>997-34-LE26</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arriendo de dos estanques móviles por 40 días </t>
+        </is>
+      </c>
+      <c r="C369" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" s="13" t="inlineStr">
         <is>
           <t>score 0 &lt; 30</t>
         </is>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Descartes (auditoria)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matches'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-09-06 18:41 · UF 40,881.68 · 4,767 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-10 04:54 · UF 40,893.78 · 4,711 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA(Matches!P2:P5)</f>
+        <f>COUNTA(Matches!P2:P4)</f>
         <v/>
       </c>
     </row>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Matches!A2:A5,"SI")</f>
+        <f>COUNTIF(Matches!A2:A4,"SI")</f>
         <v/>
       </c>
     </row>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Matches!B2:B5,"CAMBIO*")</f>
+        <f>COUNTIF(Matches!B2:B4,"CAMBIO*")</f>
         <v/>
       </c>
     </row>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Matches!C2:C5,"ALTA")</f>
+        <f>COUNTIF(Matches!C2:C4,"ALTA")</f>
         <v/>
       </c>
     </row>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Matches!E2:E5,"Mandato de SERVICIO")</f>
+        <f>COUNTIF(Matches!E2:E4,"Mandato de SERVICIO")</f>
         <v/>
       </c>
     </row>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Matches!E2:E5,"Estado BUSCA inmueble")</f>
+        <f>COUNTIF(Matches!E2:E4,"Estado BUSCA inmueble")</f>
         <v/>
       </c>
     </row>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Matches!E2:E5,"Estado OFRECE inmueble")</f>
+        <f>COUNTIF(Matches!E2:E4,"Estado OFRECE inmueble")</f>
         <v/>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Matches!G2:G5,"Gamma")</f>
+        <f>COUNTIF(Matches!G2:G4,"Gamma")</f>
         <v/>
       </c>
     </row>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Matches!G2:G5,"Realsa Brokers")</f>
+        <f>COUNTIF(Matches!G2:G4,"Realsa Brokers")</f>
         <v/>
       </c>
     </row>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS(Matches!N2:N5,"&lt;=7",Matches!N2:N5,"&gt;=0")</f>
+        <f>COUNTIFS(Matches!N2:N4,"&lt;=7",Matches!N2:N4,"&gt;=0")</f>
         <v/>
       </c>
     </row>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>SUM(Matches!M2:M5)</f>
+        <f>SUM(Matches!M2:M4)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Estado BUSCA inmueble</t>
+          <t>Estado OFRECE inmueble</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INMUEBLES 2026-2028</t>
+          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>Región del Biobío</t>
+          <t>Región de Coquimbo</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -966,21 +966,21 @@
       </c>
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>2026-09-08 15:30</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>2359-13-LP26</t>
+          <t>4295-54-LR26</t>
         </is>
       </c>
       <c r="Q2" s="13" t="inlineStr">
         <is>
-          <t>objeto/titulo: inmueble (+14) | transaccion: arriendo (+12) | UNSPSC 80131500 (+40)</t>
+          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
         </is>
       </c>
       <c r="R2" s="13" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="S2" s="13" t="inlineStr">
         <is>
-          <t>La Municipalidad de Talcahuano, llama a Propuesta Pública para el ARRIENDO DE INMUEBLES PARA LA MUNICIPALIDAD DE TALCAHUANO 2026-2028, por el sistema a suma alzada, exento de impuestos, sin intereses ni reajustes, financiada con Fondos Municipales.    La presente licitación se regirá por las presentes Bases Administrativas, Términos de Referencia y demás antecedentes que la componen.</t>
+          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
         </is>
       </c>
       <c r="T2" s="11" t="inlineStr">
         <is>
-          <t>Victor Sandoval Arias</t>
+          <t>Dirección de Administración y Finanzas</t>
         </is>
       </c>
       <c r="U2" s="11" t="inlineStr"/>
@@ -1006,314 +1006,213 @@
       </c>
     </row>
     <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: monto UF 122304.0-&gt;122268.0</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Estado OFRECE inmueble</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>Región de Tarapacá</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>CLP 5,000,000,000</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="n">
+        <v>122268</v>
+      </c>
+      <c r="N3" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
+          <t>5358-9-LR26</t>
+        </is>
+      </c>
+      <c r="Q3" s="19" t="inlineStr">
+        <is>
+          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
+        </is>
+      </c>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
+        </is>
+      </c>
+      <c r="S3" s="19" t="inlineStr">
+        <is>
+          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
+        </is>
+      </c>
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>Jorge Bernal Peralta</t>
+        </is>
+      </c>
+      <c r="U3" s="18" t="inlineStr"/>
+      <c r="V3" s="21" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>VIGENTE</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>VENTA DE TERRENOS DE PROPIEDAD MUNICIPAL LA SERENA</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Región de Coquimbo</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Estado BUSCA inmueble</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Realsa Brokers</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Región de los Lagos</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>no publicado</t>
         </is>
       </c>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-14 15:00</t>
-        </is>
-      </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>4295-54-LR26</t>
-        </is>
-      </c>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>objeto/titulo: terreno (+9) | transaccion: venta (+6) | UNSPSC 80131600 (+40)</t>
-        </is>
-      </c>
-      <c r="R3" s="13" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S3" s="13" t="inlineStr">
-        <is>
-          <t>El presente proceso tiene como objetivo, seleccionar mediante propuesta pública, al o a los compradores con quien se celebrará el contrato de compraventa de los inmuebles de propiedad municipal. Esta actuación se realiza conforme a lo establecido en el artículo 5, letra f), de la ley Nº 18.695, Orgánica Constitucional de Municipalidades, para el cumplimiento de sus funciones las municipalidades tendrán las siguientes atribuciones esenciales: “f) Adquirir y enajenar bienes muebles e inmuebles”.</t>
-        </is>
-      </c>
-      <c r="T3" s="11" t="inlineStr">
-        <is>
-          <t>Dirección de Administración y Finanzas</t>
-        </is>
-      </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="14" t="inlineStr">
+      <c r="M4" s="11" t="n"/>
+      <c r="N4" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>1063538-206-I226</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>UNSPSC 80131500 (+40)</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
+        </is>
+      </c>
+      <c r="S4" s="13" t="inlineStr">
+        <is>
+          <t>El Hospital Base San José de Osorno, en adelante también “el Hospital”, llama a propuesta privada para generar un convenio de Arriendo de celdas de media tensión MT del Hospital Base San Jose Osorno. La forma de la presente licitación pública corresponde a aquella adquisición mayor o igual a 5.000 UTM y menor a 10.000 UTM.</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>Yasna Albarran</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr"/>
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>Ver ficha</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>CAMBIO: monto UF 122320.0-&gt;122304.0</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>Estado OFRECE inmueble</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>El organismo vende o concesiona un activo: oportunidad de representar comprador/operador o de asesorar el proceso. Revisar bases y valor minimo.</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE TERRENO PARA PROYECTO EDUCACIONAL U</t>
-        </is>
-      </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>Región de Tarapacá</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t>CLP 5,000,000,000</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="n">
-        <v>122304</v>
-      </c>
-      <c r="N4" s="18" t="n">
-        <v>53</v>
-      </c>
-      <c r="O4" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:01</t>
-        </is>
-      </c>
-      <c r="P4" s="18" t="inlineStr">
-        <is>
-          <t>5358-9-LR26</t>
-        </is>
-      </c>
-      <c r="Q4" s="19" t="inlineStr">
-        <is>
-          <t>objeto/titulo: terreno (+9) | UNSPSC 80131600 (+40)</t>
-        </is>
-      </c>
-      <c r="R4" s="19" t="inlineStr">
-        <is>
-          <t>exige/pondera experiencia acreditable o es licitacion mayor</t>
-        </is>
-      </c>
-      <c r="S4" s="19" t="inlineStr">
-        <is>
-          <t>Lo indicado en Bases de la Licitación, aprobadas mediante Decreto N°21/2026 Adjunto.</t>
-        </is>
-      </c>
-      <c r="T4" s="18" t="inlineStr">
-        <is>
-          <t>Jorge Bernal Peralta</t>
-        </is>
-      </c>
-      <c r="U4" s="18" t="inlineStr"/>
-      <c r="V4" s="21" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>VIGENTE</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Estado BUSCA inmueble</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>El organismo demanda un inmueble en arriendo o compra: oportunidad de colocar una propiedad de cartera o de representar al propietario. Confirmar si las bases admiten a un corredor como oferente o exigen al titular del dominio.</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Realsa Brokers</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>“ARRIENDO DE CELDAS DE MEDIA TENSION MT”</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>HOSPITAL BASE OSORNO</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>Región de los Lagos</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>no publicado</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:00</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>1063538-206-I226</t>
-        </is>
-      </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>UNSPSC 80131500 (+40)</t>
-        </is>
-      </c>
-      <c r="R5" s="13" t="inlineStr">
-        <is>
-          <t>proceso menor o sin ponderacion fuerte de experiencia</t>
-        </is>
-      </c>
-      <c r="S5" s="13" t="inlineStr">
-        <is>
-          <t>El Hospital Base San José de Osorno, en adelante también “el Hospital”, llama a propuesta privada para generar un convenio de Arriendo de celdas de media tensión MT del Hospital Base San Jose Osorno. La forma de la presente licitación pública corresponde a aquella adquisición mayor o igual a 5.000 UTM y menor a 10.000 UTM.</t>
-        </is>
-      </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>Yasna Albarran</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="14" t="inlineStr">
-        <is>
-          <t>Ver ficha</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V5"/>
+  <autoFilter ref="A1:V4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1433,7 +1332,7 @@
         </is>
       </c>
       <c r="J2" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1477,7 +1376,7 @@
         </is>
       </c>
       <c r="J3" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1521,7 +1420,7 @@
         </is>
       </c>
       <c r="J4" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1565,7 +1464,7 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1609,7 +1508,7 @@
         </is>
       </c>
       <c r="J6" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1655,7 +1554,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1699,7 +1598,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1739,11 +1638,11 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1776,7 +1675,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122304</v>
+        <v>122268</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -1785,11 +1684,11 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1829,7 +1728,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1879,7 +1778,7 @@
         </is>
       </c>
       <c r="J12" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1972,15 +1871,75 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO TASACIÓN COMERCIAL INMUEBLE DAEM OLIVAR</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>CLP 2,000,000</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>&lt; 100 UTM (~&lt; UF 170)</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:00</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>bajo umbral de monto (Nacional, UF 49 (umbral UF 2.000))</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>923000-18-L126</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Estas licitaciones SI calzan con el servicio, pero quedan fuera por monto o plazo. Ojo: Mercado Publico publica el valor del CONTRATO (honorario), no el valor del activo — una tasacion de un edificio grande puede aparecer como UF 73. Revisar antes de descartar.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1991,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2045,12 +2004,12 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>1036569-10-LP26</t>
+          <t>1002772-96-LP26</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
+          <t>INSTRUMENTAL DE NEURO CON CRANEOTOMO EN COMODATO</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
@@ -2065,36 +2024,36 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1039-8-LP26</t>
+          <t>1026727-12-LE26</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE TRANSPORTE TERRESTRE</t>
+          <t>Arriendo de equipamiento prototipado para el CFT</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1051173-11-LE26</t>
+          <t>1035-22-L126</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
+          <t>Trabajos menores Casa Fiscal Conaf Pichilemu Region de O"Higgins</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
@@ -2105,32 +2064,32 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1052836-6-LE26</t>
+          <t>1035685-19-LE26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REHABILITACIÓN DE PUENTE EL DURAZNO</t>
+          <t>Ampliación de Espacio Académico Sede Panguipulli</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1057049-273-LR26</t>
+          <t>1036569-10-LP26</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE INMUNOHEMATOLOGIA CON EQUIPO EN COMODATO BANCO DE SANGRE</t>
+          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
@@ -2145,32 +2104,32 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1057049-285-LR26</t>
+          <t>1039-7-LR26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA EXAMEN DE ORINA CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>SERVICIO  DE ARRIENDO DE EQUIPO MECANIZADO</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1057049-296-LR26</t>
+          <t>1042-11-LE26</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
+          <t>Serv. traslado marítimo para faenas en Isla Mocha</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2185,32 +2144,32 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1057049-321-LE26</t>
+          <t>1051173-11-LE26</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>ICC. Servicio de Mantenimiento y Reparación de Aluminios del Hospital Clínico San Borja Arriarán y Sus Comodatos</t>
+          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1057049-322-I226</t>
+          <t>1057049-296-LR26</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -2225,12 +2184,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057049-328-LR26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -2245,12 +2204,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057055-68-LP26</t>
+          <t>1057049-328-LR26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -2265,32 +2224,32 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057049-329-LE26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057417-183-LP26</t>
+          <t>1057055-68-LP26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -2305,32 +2264,32 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057417-186-LP26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057417-51-LP26</t>
+          <t>1057417-183-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
+          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2345,32 +2304,32 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057420-37-LP26</t>
+          <t>1057417-186-LP26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
+          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057472-92-LP26</t>
+          <t>1057417-51-LP26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CASILLEROS INTELIGENTES PARA FARMACIA AMB</t>
+          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -2385,32 +2344,32 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057420-37-LP26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057490-50-LR26</t>
+          <t>1057480-46-LR26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Lavado y Administración de Ropa.</t>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -2425,12 +2384,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057490-57-LP26</t>
+          <t>1057492-121-LE26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE EQUIPO DE NEUROMONITOREO I</t>
+          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2445,12 +2404,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057492-111-LP26</t>
+          <t>1057501-395-LR26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CAJAS DE INSTRUMENTAL QX PARA UROLOGÍA</t>
+          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -2465,12 +2424,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057492-121-LE26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2485,12 +2444,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057501-395-LR26</t>
+          <t>1057501-462-LE26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
+          <t>HABILITACIÓN SALA PACIENTES MATERNIDAD HSR</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -2505,92 +2464,92 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057501-473-LE26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>Habilitación para Instalacion de Food Truck HSR</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057501-473-LE26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Habilitación para Instalacion de Food Truck HSR</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057501-488-LE26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057501-488-LE26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057503-125-LE26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
@@ -2605,12 +2564,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057503-125-LE26</t>
+          <t>1057508-112-LE26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
+          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -2625,12 +2584,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057508-112-LE26</t>
+          <t>1057539-129-LP26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
+          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
@@ -2645,12 +2604,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057539-118-LP26</t>
+          <t>1057544-293-LE26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS TORRES DE LAPAROSCOPIA</t>
+          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -2665,12 +2624,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057539-129-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -2685,12 +2644,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1057544-293-LE26</t>
+          <t>1057547-354-LP26</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
+          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -2705,32 +2664,32 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057552-19-LE26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>Convenio de Suministro Materiales de Oficina</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1057547-354-LP26</t>
+          <t>1057898-95-LE26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
@@ -2745,52 +2704,52 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1057922-22-LP26</t>
+          <t>1057977-14-LE26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPAMIENTO MÉDICO PARA HABILITACIÓN DE CESFAM CON SAR RAHUE ALTO</t>
+          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1057977-14-LE26</t>
+          <t>1058086-49-LP26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
+          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1070620-86-LP26</t>
+          <t>1070620-89-LP26</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM.RF PARA ARTROSCOPIA CON EQUIPO EN COMODATO</t>
+          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
@@ -2805,12 +2764,12 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1075963-309-LP26</t>
+          <t>1070620-93-LP26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE TIRAS REACTIVAS DE GLICEMIA CON EQUIPO EN COMODATO DE MONITOR DE GLICEMIA CAPILAR POR 36 MESES</t>
+          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
@@ -2825,32 +2784,32 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1079445-41-LE26</t>
+          <t>1070620-95-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
+          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1079650-57-LE26</t>
+          <t>1070620-96-LP26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
+          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
@@ -2865,52 +2824,52 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1079969-19-LP26</t>
+          <t>1079445-41-LE26</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
+          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1079969-20-LE26</t>
+          <t>1079445-42-LE26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
+          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1080303-8-LE26</t>
+          <t>1079650-57-LE26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Serv. Armado Habilitación y Desarme de Pista Remo</t>
+          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -2925,76 +2884,76 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1099402-21-L126</t>
+          <t>1079969-19-LP26</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ESPACIO PARA DISPOSICIÓN DE KIOSKO O CAFETERIA</t>
+          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1107276-25-LE26</t>
+          <t>1079969-20-LE26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
+          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1116006-4-LE26</t>
+          <t>1080303-8-LE26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
+          <t>Serv. Armado Habilitación y Desarme de Pista Remo</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1126922-33-LP26</t>
+          <t>1082957-29-LE26</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE SERVICIOS DE CONTROL DE PLAGAS PARA ESTABLECIMIENTOS EDUCACIONALES JARDINES INFANTILES Y OFICINAS DEL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LLANQUIHUE</t>
+          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
@@ -3005,76 +2964,76 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1175-71-LP26</t>
+          <t>1095-10-LE26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
+          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1180730-37-LP26</t>
+          <t>1095-11-LE26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION RECINTOS SERVICIO ONCOLÓGICO HCM</t>
+          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1180830-16-LR26</t>
+          <t>1107276-25-LE26</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>CONST. BODEGA FARMACIA CAN PP 77-2026</t>
+          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1197-20-L126</t>
+          <t>1116006-4-LE26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
+          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
@@ -3085,16 +3044,16 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1209403-8-L126</t>
+          <t>1175-71-LP26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
+          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
@@ -3105,12 +3064,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1175-74-LP26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
@@ -3125,16 +3084,16 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1218393-40-L126</t>
+          <t>1186229-28-LE26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">APERTURA DE NUEVO VANO Y CIERRE DE VANO EXISTENTE BODEGA LAS ANIMAS </t>
+          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
@@ -3145,72 +3104,72 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1232565-33-LE26</t>
+          <t>1197-20-L126</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUPO E INSFRAESTRUCTURA PROYECTO ULS2493</t>
+          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1233615-56-LE26</t>
+          <t>1198-33-LE26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CENTRO DE DISTRIBUCIÓN REGIONAL</t>
+          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1236-17-LE26</t>
+          <t>1209403-8-L126</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>REQ. 107_TRASLADOS TERRESTRES PARA DEPORTISTAS FINAL NACIONAL DE JUEGOS DEPORTIVOS ESCOLARES</t>
+          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1237853-17-L126</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE TÉCNICA PARA EVENTO DEPORTIVO, PARA LA CORPORACIÓN DEL DEPORTE DE LA FLORIDA</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
@@ -3225,72 +3184,72 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1218393-40-L126</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t xml:space="preserve">APERTURA DE NUEVO VANO Y CIERRE DE VANO EXISTENTE BODEGA LAS ANIMAS </t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1236-17-LE26</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t>REQ. 107_TRASLADOS TERRESTRES PARA DEPORTISTAS FINAL NACIONAL DE JUEGOS DEPORTIVOS ESCOLARES</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1280-41-LE26</t>
+          <t>1256505-28-LE26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO E INSTALACION DE SEÑALES</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1280-42-LE26</t>
+          <t>1261-19-LR26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DOS RODILLOS LISOS SIMPLES</t>
+          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
@@ -3305,232 +3264,232 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1261592-54-LE26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1337-21-LE26</t>
+          <t>1293138-13-LP26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
+          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1344190-12-LE26</t>
+          <t>1305527-3-LP26</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
+          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1348-5-LP26</t>
+          <t>1337-21-LE26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
+          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1351-6-LP26</t>
+          <t>1344190-12-LE26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
+          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1374899-36-LP26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1375746-17-LP26</t>
+          <t>1350296-80-LE26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
+          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1375753-31-LE26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE LEVANTAMIENTO DE INVENTARIO Y ARRIENDO</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1395865-16-LE26</t>
+          <t>1374899-36-LP26</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN PREVENTIVA ÁREA SANITARIA ARTEFACTOS SANITARIOS - TEATRO REGIONAL CERVANTES Y OFICINAS ADMINISTRATIVAS ASOCIACIÓN PATRIMONIAL CULTURAL REGIÓN DE LOS RÍOS</t>
+          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1375746-17-LP26</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1422824-25-LP26</t>
+          <t>1375753-31-LE26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE LEVANTAMIENTO DE INVENTARIO Y ARRIENDO</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
@@ -3545,152 +3504,152 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1391828-8-LE26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1431841-56-LP26</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1431841-57-LE26</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1443-1-LE26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje y almacenamiento</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1431841-56-LP26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1469101-6-LP26</t>
+          <t>1431841-57-LE26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
+          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1469-189-L126</t>
+          <t>1443-1-LE26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
+          <t>Servicio de bodegaje y almacenamiento</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1501468-17-LE26</t>
+          <t>1448821-14-LP26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
+          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
@@ -3705,72 +3664,72 @@
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1537592-17-LE26</t>
+          <t>1469101-6-LP26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
+          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1540667-6-LR26</t>
+          <t>1469-189-L126</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
+          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1469-205-L126</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1501468-17-LE26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
@@ -3785,72 +3744,72 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1555-75-LP26</t>
+          <t>1537592-17-LE26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
+          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1540667-6-LR26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1605-45-LP26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>LP-5125 SERVICIO DE DISPENSADORES Y PURIFICADORES DE AGUA PARA LAS OFICINAS DEL SII</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>162-26-LE26</t>
+          <t>1549-85-LE26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Servicio traslado de muestras a los Laboratorios</t>
+          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
@@ -3865,12 +3824,12 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1641-219-LR26</t>
+          <t>1554-55-LR26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>FMM - SERVICIO DE ARRIENDO DE EQUIPOS DE CLIMATIZACIÓN</t>
+          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
@@ -3885,12 +3844,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>1655-23-LP26</t>
+          <t>1555-75-LP26</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CONTEINER PARA ATENCIÓN OFTALMOLÓGICA</t>
+          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
@@ -3905,12 +3864,12 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>1562-57-L126</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
@@ -3925,156 +3884,156 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>1663-137-LE26</t>
+          <t>1562-59-L126</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
+          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>1696-15-LE26</t>
+          <t>1562-60-LR26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
+          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1574-33-LP26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>1810-3-LE26</t>
+          <t>1575-14-LE26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
+          <t>MANTENCION DE OFICINAS</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>1973-96-LE26</t>
+          <t>1605-41-LP26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
+          <t>LP-4872 Servicios de mantención general edificios</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>1973-97-LP26</t>
+          <t>1643-75-LE26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
+          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>1978-100-L126</t>
+          <t>1657-17-L126</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN VENTANA, PUERTA Y TRASLADO DE HIGROMETRO SSMAULE</t>
+          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>1978-112-L126</t>
+          <t>1658-189-LP26</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO MONITOREO SISTEMA DE ALARMA EN BODEGA REGIONAL SSMAULE</t>
+          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
@@ -4085,252 +4044,252 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>2020-19-LE26</t>
+          <t>1663-137-LE26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
+          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>2069-155-LP26</t>
+          <t>1696-15-LE26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
+          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>2098-115-LE26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>2098-122-LP26</t>
+          <t>1810-3-LE26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
+          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>2098-124-LE26</t>
+          <t>1894-25-LP26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO TERMOCICLADOR MULTINACAL PARA EL SERVICIO DE LABORATORIO CLINICO HRV</t>
+          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>2098-127-LE26</t>
+          <t>1947-157-LE26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE TIRAS REACTIVAS PARA HEMOGLOBINA CON EQUIPAMIENTO EN COMODATO</t>
+          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>2098-133-LP26</t>
+          <t>1947-168-LE26</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>2098-134-LP26</t>
+          <t>1969-18-LE26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
+          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>2107-142-LE26</t>
+          <t>1973-96-LE26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>2107-144-LP26</t>
+          <t>1973-97-LP26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
+          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>2109-10-LP26</t>
+          <t>1978-112-L126</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
+          <t>CONVENIO MONITOREO SISTEMA DE ALARMA EN BODEGA REGIONAL SSMAULE</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2123-22-CO26</t>
+          <t>2020-19-LE26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>E1O2RT8 Traslado Pasajeros Provincia La Ligua</t>
+          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2126-128-LE26</t>
+          <t>2069-155-LP26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE HABILITACIÓN DE DISPOSITIVO EXTERNO HOSPITAL DIA DEL HOSPITAL SAN PABLO DE COQUIMBO</t>
+          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
@@ -4345,32 +4304,32 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2173-27-LE26</t>
+          <t>2098-115-LE26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PUNTUAL DE MANTENCION PREVENTIVA Y CORRECTIVA A EQUIPOS Y SISTEMAS DE CLIMATIZACION EN EDIFICIOS DE LA JURISDICCION ZONAL SANTIAGO</t>
+          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2176-55-LE26</t>
+          <t>2098-122-LP26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
+          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
@@ -4385,72 +4344,72 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2179-14-LE26</t>
+          <t>2098-133-LP26</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
+          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>2258-133-LR26</t>
+          <t>2098-134-LP26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AEROAMBULANCIA PARA EL TRASLADO DE PACIENTES CRÍTICOS BENEFICIARIOS DEL HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>2258-168-LE26</t>
+          <t>2102-31-LE26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
+          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2258-175-LR26</t>
+          <t>2107-142-LE26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
+          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
@@ -4465,32 +4424,32 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2258-72-LE26</t>
+          <t>2109-10-LP26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE RETIRO TRASLADO Y DISPOSICIÓN FINAL DE RESIDUOS SÓLIDOS ASIMILABLES A DOMICILIARIOS PARA HOSPITAL REGIONAL DE ANTOFAGASTA</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
@@ -4505,12 +4464,12 @@
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2271-65-LE26</t>
+          <t>2123-22-CO26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>Instalación y habilitación del Sistema de Ayudas Visuales  Faro del Aeródromo Santo Domingo de acuerdo a bases técnicas adjuntas</t>
+          <t>E1O2RT8 Traslado Pasajeros Provincia La Ligua</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
@@ -4525,12 +4484,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2273-55-LE26</t>
+          <t>2176-55-LE26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
+          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
@@ -4545,56 +4504,56 @@
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2274-43-L126</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE SALAS DE LACTANCIA MATERNA PARA LOS CESFAM SANTIAGO NUEVA EXTREMADURA Y SAN RAFAEL . EXP 13788</t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2205-14-LE26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2279-58-LE26</t>
+          <t>2258-168-LE26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
+          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -4605,12 +4564,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2258-175-LR26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
@@ -4625,12 +4584,12 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
@@ -4645,52 +4604,52 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2308-72-LE26</t>
+          <t>2273-55-LE26</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>ADQ. HABILITACIÓN Y PUESTA EN MARCHA BÁSCULA</t>
+          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2332-104-L126</t>
+          <t>2274-43-L126</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN BOX DENTAL Y SOME CENTRAL DE “POSTA LAS QUEMAS” DEL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>HABILITACIÓN DE SALAS DE LACTANCIA MATERNA PARA LOS CESFAM SANTIAGO NUEVA EXTREMADURA Y SAN RAFAEL . EXP 13788</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2332-105-L126</t>
+          <t>2275-29-LE26</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TÓRULAS, SERVILLETAS, VASOS DESECHABLES Y EYECTORES ODONTOLÓGICOS PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
@@ -4705,92 +4664,92 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2332-52-LE26</t>
+          <t>2279-56-LE26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INSTALACION CASILLEROS INTELIGENTES</t>
+          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2366-54-LE26</t>
+          <t>2279-58-LE26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SAPU CORTO EN CESFAM RVZ</t>
+          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2378-110-LP26</t>
+          <t>2292-57-L126</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
+          <t>Contratación del Servicio Integral de Habilitación, Soporte Técnico y Monitoreo de Sistemas de Alarmas por 24 meses en Centros de Salud de Talca</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
@@ -4805,36 +4764,36 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2313-5-LE26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>Servicios de Conservación de Edificio Terminal</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2408-152-LE26</t>
+          <t>2322-82-LE26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
+          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
@@ -4845,32 +4804,32 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2408-160-LP26</t>
+          <t>2324-112-LE26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2408-98-LE26</t>
+          <t>2332-106-L126</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO PARA LAVADORA DEL CESFAM ANTONIO VARAS PERTENECIENTE AL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
@@ -4885,52 +4844,52 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2410-84-LE26</t>
+          <t>2332-109-L126</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARTÍCULOS PARA SALA  DE REHABILITACIÓN</t>
+          <t>ADQUISICIÓN DE INSTRUMENTAL DENTAL PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2332-52-LE26</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>ARRIENDO E INSTALACION CASILLEROS INTELIGENTES</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2426-44-LE26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
@@ -4945,76 +4904,76 @@
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2430-59-LP26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2430-68-LR26</t>
+          <t>2378-110-LP26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
+          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2430-71-LP26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL VILLA EL SALAR ANTOFAGASTA. CÓDIGO BIP N°40058997-0</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2430-78-LP26</t>
+          <t>2408-152-LE26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
+          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
@@ -5025,32 +4984,32 @@
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2445-110-LE26</t>
+          <t>2408-160-LP26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
+          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>2408-98-LE26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
@@ -5065,36 +5024,36 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2446-257-LE26</t>
+          <t>2410-41-LE26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
+          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2446-260-LR26</t>
+          <t>2411-14-L126</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
+          <t>ADQUISICION MATERIALES VARIOS DE USO O CONSUMO PARA DEPARTAMENTO CEMENTERIO</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
@@ -5105,16 +5064,16 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2448-107-L126</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE COMEDOR DE FUNCIONARIOS DROGUERIA  Y BODEGA DESAM</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
@@ -5125,132 +5084,132 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2448-110-L126</t>
+          <t>2426-44-LE26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE ESPACIO DE TRABAJO COLECTIVO CECOSF PUNTA MIRA</t>
+          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2450-90-LE26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2430-68-LR26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2460-112-LE26</t>
+          <t>2430-78-LP26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Graderías y Tribuna de Honor Desfile en Honor a Las Glorias del Ejército</t>
+          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2460-113-LE26</t>
+          <t>2445-110-LE26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Vallas Desfile en Honor a las Glorias del Ejército</t>
+          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2460-121-LE26</t>
+          <t>2445-115-LE26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
+          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2460-99-LE26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras varias para el Departamento de Rentas </t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
@@ -5265,112 +5224,112 @@
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2446-257-LE26</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2548-83-L126</t>
+          <t>2446-260-LR26</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN OFICINA CESFAM PLC</t>
+          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2555-10-LP26</t>
+          <t>2446-266-LP26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO DE PERSONAL DE BRIGADAS SIC 629</t>
+          <t>MANTENCIÓN CASA MAC AULIFFE</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2565-14-LP26</t>
+          <t>2450-90-LE26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS CON EQUIPOS EN COMODATO</t>
+          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2460-108-LE26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
@@ -5385,36 +5344,36 @@
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2460-121-LE26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2483-242-CO26</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
@@ -5425,32 +5384,32 @@
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2626-8-LE26</t>
+          <t>2548-83-L126</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO LIMPIA FOSAS Y ARRIENDO BAÑOS QUÍMICOS</t>
+          <t>SERVICIO HABILITACIÓN OFICINA CESFAM PLC</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
@@ -5465,32 +5424,32 @@
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2667-83-LE26</t>
+          <t>2581-36-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
+          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
@@ -5505,16 +5464,16 @@
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2667-90-LE26</t>
+          <t>2581-37-LP26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
+          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
@@ -5525,232 +5484,232 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>2686-120-CO26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INSTALACION DE MODULOS DE OFICINAS</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>2699-32-LR26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Flota Vehicular</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>2702-63-LE26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>2702-65-LE26</t>
+          <t>2667-83-LE26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE BAÑOS QUIMICOS ESTANDAR Y BAÑO TRAILER DOBLE VIP FIESTA DE LA CHILENIDAD 2026</t>
+          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>2709-77-LE26</t>
+          <t>2667-90-LE26</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION PARQUE RECREACIONAL LOS PEÑONES</t>
+          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>2697-25-LR26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>HABILITACIÓN CASA DE OFICIOS</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>2730-113-LE26</t>
+          <t>2702-63-LE26</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Traslado y Movilización Para Distintos  Programas de Dideco</t>
+          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>2736-32-LE26</t>
+          <t>2710-55-LE26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>Materiales de Oficina</t>
+          <t>SERVICIO DE ARRIENDO TOTEM</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>2744-30-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>2744-34-LE26</t>
+          <t>2744-30-LE26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO CONTROL DE PLAGAS INTEGRAL PARA ESTABLECIMIENTOS URBANOS Y RURALES DEL DEPARTAMENTO DE SALUD MUNICIPAL DE ANGOL </t>
+          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>2744-34-LE26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t xml:space="preserve">SERVICIO CONTROL DE PLAGAS INTEGRAL PARA ESTABLECIMIENTOS URBANOS Y RURALES DEL DEPARTAMENTO DE SALUD MUNICIPAL DE ANGOL </t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
@@ -5765,12 +5724,12 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>2755-34-LE26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
@@ -5785,56 +5744,56 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>2784-44-LE26</t>
+          <t>2784-42-LP26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
+          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>2794-22-LR26</t>
+          <t>2784-44-LE26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
+          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>2905-40-LP26</t>
+          <t>2794-22-LR26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento y Ampliación Sede Social Plazoleta</t>
+          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
@@ -5845,192 +5804,192 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>2817-63-LE26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>2920-38-LP26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Juventud Robinsoniana.</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>2963-26-LR26</t>
+          <t>2906-18-LE26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMAGENOLOGÍA PARA LOS CENTROS DE SALUD FAMILIAR Y LAS UNIDADES DEPENDIENTES DEL DEPARTAMENTO DE ADMINISTRACIÓN DE SALUD DE LA I. MUNICIPALIDAD DE LA GRANJA”</t>
+          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2920-38-LP26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>Construcción Sede Juventud Robinsoniana.</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>2950-44-LP26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>3017-68-LE26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPAMIENTO PARA PATRULLAJE PREVENTIVO Y AMPLIACION DE LAS DEPENDENCIAS DE LA DIRECCION DE SEGURIDAD PUBLICA</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>3046-25-LE26</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>3046-25-LE26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3092-18-LE26</t>
+          <t>3047-54-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN DE LOS SERVICIOS DE  LABORATORIO DE CANASTA DE BASICA Y GES APS   BÁSICA Y GES PARA LA DIRECCIÓN DE SALUD MUNICIPAL I.MUNICIPALIDAD DE CASABLANCA 2026</t>
+          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
@@ -6045,40 +6004,40 @@
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3159-18-LE26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE VENTANAS EN VIVIENDAS FISCALES</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3172-46-LR26</t>
+          <t>3172-68-LE26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO AMPLACIÓN ESFOCAR SEDE PUERTO MONTT</t>
+          <t>ADQ. MAT. DEPENDENCIAS 2DO. NIVEL ASESORÍA DIGCAR</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6164,12 @@
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>3384-20-LP26</t>
+          <t>3333-38-LE26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
+          <t>SERV TRASLADO ESCOLAR JARDIN RETOÑOS DE AMOR OLMUE</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
@@ -6225,52 +6184,52 @@
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>3436-97-LE26</t>
+          <t>3333-41-LE26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>Servicio mantenimiento de dependencias SIC 351978</t>
+          <t>SERVICIO DE TRASLADO PARA EQUIPO RED LOCAL 2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>3525-8-LR26</t>
+          <t>3355-9-LP26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>Sum e instalación de taludes visita terreno volun</t>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPAMIENTO HIDROELÉCTRICO Y SERVICIO DE RECUPERACIÓN HABILITACIÓN Y PUESTA EN MARCHA DE LA MICRO CENTRAL ELÉCTRICA DEL REFUGIO MILITAR LOS BARROS </t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>3537-52-LE26</t>
+          <t>3384-20-LP26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de una autohormigonera por 320 horas</t>
+          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
@@ -6285,16 +6244,16 @@
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>3542-22-LE26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
@@ -6305,12 +6264,12 @@
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>359-105-LE26</t>
+          <t>3537-52-LE26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>ADQ. CLIP POLIMERO CON COMODATO DE APLICADORES</t>
+          <t>Arriendo de una autohormigonera por 320 horas</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
@@ -6325,12 +6284,12 @@
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>3624-32-LP26</t>
+          <t>3587-20-LE26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
+          <t>SERVICIO DE REPARACIÓN MANTENIMIENTO PREVENTIVO CORRECTIVO Y SOPORTES PARA EQUIPOS RADIOCOMUNICACIONES DEPARTAMENTO DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
@@ -6345,56 +6304,56 @@
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>3624-33-LP26</t>
+          <t>359-105-LE26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
+          <t>ADQ. CLIP POLIMERO CON COMODATO DE APLICADORES</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>3656-148-LP26</t>
+          <t>359-106-LE26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SECTOR PIMPINELA COMUNA DE REQUÍNOA</t>
+          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>3668-14-LP26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CAMARIN Y SEDE ESTADIO LOS BAJOS DE SAN AGUSTÍN CALERA DE TANGO - CÓDIGO BIP N°40069327-0</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
@@ -6405,52 +6364,52 @@
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>3671-58-LE26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>3693-158-LP26</t>
+          <t>3671-58-LE26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>3708-39-LE26</t>
+          <t>3671-61-LE26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
+          <t xml:space="preserve">“SUMINISTRO DE OXÍGENO” PARA DEPENDENCIAS DE SALUD DE LA COMUNA DE CHILLÁN VIEJO. </t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
@@ -6465,16 +6424,16 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>3710-84-L126</t>
+          <t>3678-22-LE26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>ESCANER PARA BODEGA FARMACIA CESFAM VICTORIA</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
@@ -6485,72 +6444,72 @@
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>3761-21-LE26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>3775-28-LP26</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SSHH OFICINA Y AU MUN. DE HIJUELAS</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>3789-33-LE26</t>
+          <t>3761-21-LE26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS DE REHABILITACION MOTORA</t>
+          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>3798-13-LP26</t>
+          <t>3789-33-LE26</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO CONSISTORIAL EMPEDRADO - BIP 40.068.326-0 - FRIL</t>
+          <t>ADQUISICION DE EQUIPOS DE REHABILITACION MOTORA</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
@@ -6558,67 +6517,67 @@
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>3880-61-LE26</t>
+          <t>3847-41-LE26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
+          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>3880-61-LE26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>3882-81-L126</t>
+          <t>3882-72-LP26</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>“SERVICIO DE ARRIENDO DE JUEGOS INFLABLES PARA ACTIVIDADES SECTORIALES DE LA ILUSTRE MUNICIPALIDAD DE LLAY LLAY”.</t>
+          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
@@ -6645,16 +6604,16 @@
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>3887-39-LP26</t>
+          <t>3885-51-LP26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>Concesion Explotacion Estacionamiento C Villarrica</t>
+          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
@@ -6685,72 +6644,72 @@
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>3912-19-LP26</t>
+          <t>3908-42-L126</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>Construccion sede social los acacios</t>
+          <t>SERVICIO DE TRASLADO Y ALOJAMIENTO PARA BARRIO COPAHUE COMUNA DE RENAICO</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>3912-19-LP26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t>Construccion sede social los acacios</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>3935-87-LE26</t>
+          <t>3935-83-LP26</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACION SERVICIO DE ECOTOMOGRAFIA ABDOMINAL PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE 2026</t>
+          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>3935-88-LE26</t>
+          <t>3935-87-LE26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACION SERVICIO DE MAMOGRAFIAS Y ECOTOMOGRAFIA MAMARIA PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE</t>
+          <t>CONTRATACION SERVICIO DE ECOTOMOGRAFIA ABDOMINAL PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE 2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
@@ -6765,52 +6724,52 @@
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>3950-40-LE26</t>
+          <t>3935-88-LE26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
+          <t>CONTRATACION SERVICIO DE MAMOGRAFIAS Y ECOTOMOGRAFIA MAMARIA PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>3963-16-LP26</t>
+          <t>3950-40-LE26</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
+          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>3997-59-B226</t>
+          <t>3963-16-LP26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
+          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
@@ -6825,72 +6784,72 @@
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>4006-21-LE26</t>
+          <t>3997-59-B226</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Area Deportiva Ventanas</t>
+          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>4006-21-LE26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>Mejoramiento Area Deportiva Ventanas</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D243" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>407-134-LE26</t>
+          <t>4063-1-LP26</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>RETIRO TORRE VENTADA HGGB</t>
+          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
@@ -6905,32 +6864,32 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>4121-23-LE26</t>
+          <t>4099-22-LP26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SEÑALÉTICA Y REDUCTORES DE VELOCIDAD</t>
+          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>4143-6-LE26</t>
+          <t>4099-25-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
+          <t>Servicio de Arriendo de Gestor Documental</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
@@ -6945,32 +6904,32 @@
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>4152-28-LE26</t>
+          <t>4127-41-LE26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACION Y HABILITACION DE VIVIENDAS</t>
+          <t>[DIVAP] Estudio del bodegaje de ajuares</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>418-51-LP26</t>
+          <t>4127-47-LE26</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CON COMODATO MICROBIOLOGÍA</t>
+          <t>[DIGEDEP] Curso Rehabilitación Oral</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
@@ -6985,12 +6944,12 @@
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>418-57-LP26</t>
+          <t>4143-6-LE26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
+          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
@@ -7005,12 +6964,12 @@
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>4189-38-LE26</t>
+          <t>418-57-LP26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
+          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
@@ -7025,32 +6984,32 @@
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>4237-12-LR26</t>
+          <t>4189-38-LE26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>CONCESION DEL SISTEMA DE CONTROL DE ESTACIONAMIENTOS EN LAS VIAS PUBLOICAS EN LA COMUNA DE CONCEPCION II LLAMADO</t>
+          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>4238-66-B226</t>
+          <t>425-57-LR26</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE HABILITACION CENTRO DE RESOLUTIVIDAD</t>
+          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
@@ -7065,56 +7024,56 @@
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>425-57-LR26</t>
+          <t>4284-145-L126</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
+          <t>Adquisición de 50 metros de leña nativa seca y trozada para calefacción dependencias municipales Según bases adjuntas Punto 2 productos requeridos</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>4284-145-L126</t>
+          <t>4290-60-LE26</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de 50 metros de leña nativa seca y trozada para calefacción dependencias municipales Según bases adjuntas Punto 2 productos requeridos</t>
+          <t>Serv. arriendo vallas de seguridad Fiestas Patrias</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>4295-41-LP26</t>
+          <t>4295-67-LP26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>Reposición Sede Comunitaria Francisco de Aguirre</t>
+          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
@@ -7125,16 +7084,16 @@
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>4295-67-LP26</t>
+          <t>4306-32-LE26</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
+          <t>ADQUISICION EQUIPAMIENTO CASA PROG. HABITABILIDAD</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
@@ -7225,40 +7184,40 @@
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>4362-20-LE26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>Extensión Redes AP-AS Sede Las Pozas II</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>439-26-LP26</t>
+          <t>4451-102-LE26</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
+          <t>Reparación de cubiertas de edificio Polideportivo</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
@@ -7325,36 +7284,36 @@
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>4494-61-LE26</t>
+          <t>45-45-LR26</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE MÁSTILES URBANOS INSTITUCIONALES</t>
+          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>4584-13-LE26</t>
+          <t>45-48-LE26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
+          <t>SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
@@ -7365,132 +7324,132 @@
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>4591-20-LP26</t>
+          <t>4584-13-LE26</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
+          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D269" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>4623-4-L126</t>
+          <t>4591-20-LP26</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
+          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>4629-26-LE26</t>
+          <t>4623-4-L126</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
+          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>4623-5-L126</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>SUMINISTRO DE MANTENCIÓN DE OBRAS MENORES PARA LAS OFICINAS DEPENDIENTES DE LA DIRECCIÓN REGIONAL DEL TRABAJO DE BIOBÍO</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>4642-99-LE26</t>
+          <t>4629-26-LE26</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
+          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>483-47-L126</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>4850-4-L126</t>
+          <t>4642-99-LE26</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
+          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
@@ -7505,16 +7464,16 @@
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>4920-12-LE26</t>
+          <t>483-47-L126</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA EDIFICIO DEPARTAMENTO DE SALUD COMUNA DE ROMERAL</t>
+          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
@@ -7525,52 +7484,52 @@
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>4850-4-L126</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>4967-7-LR26</t>
+          <t>4887-28-E226</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE SUTURAS ENERGIZADAS + CONSOLAS EN COMODATO</t>
+          <t>Obras de habilitación Centro de Creación Temuco</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>5048-51-O126</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>AIF TRES VENTANAS TRAMO 2</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
@@ -7585,12 +7544,12 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
@@ -7605,12 +7564,12 @@
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>507428-94-LE26</t>
+          <t>5056-102-LP26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO DE TERAPIA FÍSICA PARA REHABILITACIÓN NHA</t>
+          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
@@ -7625,12 +7584,12 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>5194-4-LE26</t>
+          <t>5056-108-LP26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>Mejora y Habilitación Cancha Futbolito Colina I</t>
+          <t>ARRIENDO DE REENVASADORA AUTOMÁTICA DE MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
@@ -7645,32 +7604,32 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>520149-35-L126</t>
+          <t>5240-102-LR26</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO. </t>
+          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>5240-102-LR26</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
@@ -7685,136 +7644,136 @@
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>527481-62-LE26</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t>CONSTRUCCION SEDE EL MOLLAR</t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D285" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>525512-33-LE26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>Diseño proyecto construcción sede social JJVV</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>527481-62-LE26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE EL MOLLAR</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D287" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>527481-65-LE26</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS ELECTRICOS</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>539119-81-LE26</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>539119-90-LE26</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>539119-80-LP26</t>
+          <t>5418-13-LE26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>Digitalización Documentos Almacenados Bodega</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
@@ -7825,16 +7784,16 @@
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>539119-81-LE26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
@@ -7845,36 +7804,36 @@
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>539119-85-LP26</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO POR LÍNEA DE ARTÍCULOS DE ESCRITORIO Y MATERIALES PEDAGÓGICOS PARA JARDINES INFANTILES ADMINISTRADOS POR EL DEPARTAMENTO DE PLANIFICACIÓN Y DESARROLLO SOCIAL B.6 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS POR UN PERIODO 12 MESES.</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>539119-86-LE26</t>
+          <t>5558-5-L126</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE AMENIDADES PARA EL HOTEL TRIZANO UBICADO EN LA COMUNA DE ÑUÑOA ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1 DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
@@ -7885,12 +7844,12 @@
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>5413-67-LE26</t>
+          <t>5586-126-LE26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DE FACHADAS EDIFICIOS CAMPUS CHUYACA</t>
+          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
@@ -7905,152 +7864,152 @@
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>5420-20-LE26</t>
+          <t>564953-71-LP26</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>Diseño eléctrico para normalización de edificios</t>
+          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>584264-46-LE26</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>HABILITACIÓN POSTA URBANA SARA GAJARDO</t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>5558-5-L126</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D299" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>557639-74-LE26</t>
+          <t>622-55-LE26</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t>PODA PARA TRES RECINTOS EDUCACIONALES CORMUN</t>
+          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>622847-13-LE26</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 21 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>568658-43-LR26</t>
+          <t>630-24-LE26</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
+          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>633-48-LR26</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
@@ -8065,116 +8024,116 @@
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>608-126-LR26</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MÁQUINAS DE HEMODIÁLISIS Y MÁQUINAS DE HEMODIAFILTRACIÓN</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>622847-13-LE26</t>
+          <t>643-32-LE26</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
+          <t>TRASLADO FUNCIONARIOS OFICINA ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>score 21 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>630-24-LE26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>660-10-LE26</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>634-82-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
@@ -8185,12 +8144,12 @@
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>680504-2-L126</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
@@ -8205,136 +8164,136 @@
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>643-32-LE26</t>
+          <t>688-11-LP26</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>TRASLADO FUNCIONARIOS OFICINA ISLA DE PASCUA</t>
+          <t>Arriendo Infraestructura de Respaldo</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D311" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>649-8-LE26</t>
+          <t>696217-4-LE26</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION Y REPARACION EDIFICIO MINVU ANTOFAGASTA</t>
+          <t>Serv de Mantencion de inmueble Oficina Colchane</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>696961-4-LP26</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>HABILITACIÓN DE OFICINAS PROYECTO CENTRALIZADO</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>660-10-LE26</t>
+          <t>697-29-LE26</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
+          <t>Serv. habilitación electrica para equipo trifasico</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>699866-116-LP26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>680-10-LE26</t>
+          <t>707418-44-L126</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>Suministro e Instalación de Ventanas PVC Europeo</t>
+          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>680504-2-L126</t>
+          <t>707420-20-LE26</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
+          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
@@ -8345,32 +8304,32 @@
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>688-11-LP26</t>
+          <t>712307-58-O126</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Infraestructura de Respaldo</t>
+          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>697057-30-LE26</t>
+          <t>729-180-LE26</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA EIVG FL SANTA CRUZ</t>
+          <t>SELLOS PRECINTOS EMBALAJE -CLS-2x20295</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
@@ -8385,32 +8344,32 @@
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>697-29-LE26</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t>Serv. habilitación electrica para equipo trifasico</t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>699866-116-LP26</t>
+          <t>748201-9-LP26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
@@ -8425,12 +8384,12 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>707418-44-L126</t>
+          <t>763003-8-LE26</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
+          <t>MATERIALES PARA ACONDICIONAMIENTO DE OFICINAS.</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
@@ -8445,16 +8404,16 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
@@ -8465,32 +8424,32 @@
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>769-84-LP26</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>729-180-LE26</t>
+          <t>777304-55-LP26</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
         <is>
-          <t>SELLOS PRECINTOS EMBALAJE -CLS-2x20295</t>
+          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
@@ -8505,116 +8464,116 @@
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>780724-6-LE26</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>Remodelación dependencias TercerTribunal Ambiental</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>742475-4-LE26</t>
+          <t>813-87-LE26</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
         </is>
       </c>
       <c r="C327" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>742-8-L126</t>
+          <t>820-3-O126</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
         <is>
-          <t>Mantención Oficina de INDAP Coyhaique, región de Aysén</t>
+          <t>RESTAURACIÓN Y HABILITACIÓN BIBLIOTECA MUNICIPAL EX ESCUELA 3, HUASCO</t>
         </is>
       </c>
       <c r="C328" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>748201-10-LE26</t>
+          <t>824-3-LE26</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ESPONJA DESECHABLE  JABONOSA PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y  REHABILITACIÓN CAPREDENA</t>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
         </is>
       </c>
       <c r="C329" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D329" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C330" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>763003-8-LE26</t>
+          <t>837-88-LP26</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
         <is>
-          <t>MATERIALES PARA ACONDICIONAMIENTO DE OFICINAS.</t>
+          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
         </is>
       </c>
       <c r="C331" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
@@ -8625,72 +8584,72 @@
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>839186-11-LP26</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>2 LLAMADO HABILITACIÓN CANCHA DE FÚTBOL Y CIERRE</t>
         </is>
       </c>
       <c r="C332" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>769-84-LP26</t>
+          <t>845-17-LR26</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
         <is>
-          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
         </is>
       </c>
       <c r="C333" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D333" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>777304-55-LP26</t>
+          <t>867990-85-L126</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
+          <t>cc 102 sol. 92417- Mantención y reparación de sala con visita a terreno</t>
         </is>
       </c>
       <c r="C334" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>780724-6-LE26</t>
+          <t>867990-89-L126</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
         <is>
-          <t>Remodelación dependencias TercerTribunal Ambiental</t>
+          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
         </is>
       </c>
       <c r="C335" s="11" t="n">
@@ -8705,32 +8664,32 @@
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>813685-9-LE26</t>
+          <t>885-80-LP26</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN PREVENTIVA A LOS EQUIPOS DE CLIMATIZACIÓN Y REFRIGERACIÓN DE LOS EDIFICIOS DEPENDIENTES DE LA DIRECCIÓN GENERAL DEL TERRITORIO MARITIMO Y DE MARINA MERCANTE</t>
+          <t>Servicios de remodelación de oficinas de la Contraloría Regional de La Arauncanía</t>
         </is>
       </c>
       <c r="C336" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>813-87-LE26</t>
+          <t>886954-176-LP26</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
         <is>
-          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
+          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
         </is>
       </c>
       <c r="C337" s="11" t="n">
@@ -8745,96 +8704,96 @@
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>886954-222-LR26</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
         </is>
       </c>
       <c r="C338" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>886954-297-LP26</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
         </is>
       </c>
       <c r="C339" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D339" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>898-181-LP26</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>Servicios de Laboratorio Dental con Equipo en Comodato</t>
         </is>
       </c>
       <c r="C340" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>838100-6-L126</t>
+          <t>899-39-LE26</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro y traslado a requerimiento de agua potable </t>
+          <t>“Servicio de Mantención Preventiva y Correctiva de PEAS y Limpieza de Estanque de Aguas Servidas para Hospital San José de Casablanca</t>
         </is>
       </c>
       <c r="C341" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D341" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>899-40-LE26</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t>“Convenio de Suministro de Medicamentos para el Hospital San José de Casablanca”</t>
         </is>
       </c>
       <c r="C342" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
@@ -8845,56 +8804,56 @@
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>854-28-LE26</t>
+          <t>905-30-LE26</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO ESPACIO RADIAL JARDIN DISTANCIA JUNJI XI.</t>
+          <t>Cambio de Red Eléctrica de las dependencias de Oficina Sectorial San Fernando Región de O´Higgins.</t>
         </is>
       </c>
       <c r="C343" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D343" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>867990-81-L126</t>
+          <t>924-27-LP26</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
         <is>
-          <t>CC 102 SOL 92520 - Contrato servicio de mantención preventiva y puesta en marcha de sistema de presurización de las escaleras del edificio nuevo de la Facultad de Administración y Economía</t>
+          <t>Servicio de bodegaje para la Seremi de Salud R.M.</t>
         </is>
       </c>
       <c r="C344" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>867990-84-L126</t>
+          <t>931-23-LE26</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
         <is>
-          <t>CDP 92718 CC102 Ejecución del “26-TE-OF-SELLOS BAJO CANALETAS DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”</t>
+          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
         </is>
       </c>
       <c r="C345" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D345" s="13" t="inlineStr">
         <is>
@@ -8905,16 +8864,16 @@
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>867990-89-L126</t>
+          <t>931-26-LE26</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
         <is>
-          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
+          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
         </is>
       </c>
       <c r="C346" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
@@ -8925,36 +8884,36 @@
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>875646-67-LE26</t>
+          <t>931-27-LE26</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE BRONCOSCOPIO RIGIDO POR 3 MESES</t>
+          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
         </is>
       </c>
       <c r="C347" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D347" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>885-80-LP26</t>
+          <t>935-22-LE26</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
         <is>
-          <t>Servicios de remodelación de oficinas de la Contraloría Regional de La Arauncanía</t>
+          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
         </is>
       </c>
       <c r="C348" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
@@ -8965,12 +8924,12 @@
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>886954-176-LP26</t>
+          <t>948354-135-LP26</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
         <is>
-          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C349" s="11" t="n">
@@ -8985,12 +8944,12 @@
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>948355-68-LP26</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
         </is>
       </c>
       <c r="C350" s="11" t="n">
@@ -9005,12 +8964,12 @@
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>886954-262-LP26</t>
+          <t>948806-117-LP26</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
         <is>
-          <t>Convenio suministro anual de Dispositivo de embolización intrasacular con equipo en comodato para la Unidad de Neurovascular del HGGB</t>
+          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
         </is>
       </c>
       <c r="C351" s="11" t="n">
@@ -9025,72 +8984,72 @@
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>886954-297-LP26</t>
+          <t>963423-10-LE26</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+          <t>serv. reparacion conservacion y pintura inmueble</t>
         </is>
       </c>
       <c r="C352" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>931-23-LE26</t>
+          <t>975-12-O126</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
         </is>
       </c>
       <c r="C353" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D353" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>931-26-LE26</t>
+          <t>976-14-LP26</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
+          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
         </is>
       </c>
       <c r="C354" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t>931-27-LE26</t>
+          <t>993-47-LE26</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
+          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
         </is>
       </c>
       <c r="C355" s="11" t="n">
@@ -9105,12 +9064,12 @@
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
-          <t>935-22-LE26</t>
+          <t>996-35-LE26</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
         <is>
-          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
+          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
         </is>
       </c>
       <c r="C356" s="11" t="n">
@@ -9125,12 +9084,12 @@
     <row r="357">
       <c r="A357" s="11" t="inlineStr">
         <is>
-          <t>948355-68-LP26</t>
+          <t>997-32-LP26</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
+          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
         </is>
       </c>
       <c r="C357" s="11" t="n">
@@ -9145,238 +9104,18 @@
     <row r="358">
       <c r="A358" s="11" t="inlineStr">
         <is>
-          <t>948806-117-LP26</t>
+          <t>997-34-LE26</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
+          <t xml:space="preserve">Arriendo de dos estanques móviles por 40 días </t>
         </is>
       </c>
       <c r="C358" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D358" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="11" t="inlineStr">
-        <is>
-          <t>956-57-L126</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="inlineStr">
-        <is>
-          <t>servicio para atención de niños, niñas y adolescentes con trastorno del espectro autista (Casablanca)</t>
-        </is>
-      </c>
-      <c r="C359" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D359" s="13" t="inlineStr">
-        <is>
-          <t>score 11 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="11" t="inlineStr">
-        <is>
-          <t>956-58-LE26</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="inlineStr">
-        <is>
-          <t>Adquisición Canalización Configuración Instalación y Puesta en Marcha de 16 Access Point en dependencias del nuevo Hospital Claudio Vicuña de San Antonio</t>
-        </is>
-      </c>
-      <c r="C360" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D360" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="11" t="inlineStr">
-        <is>
-          <t>957865-6-LE26</t>
-        </is>
-      </c>
-      <c r="B361" s="13" t="inlineStr">
-        <is>
-          <t>SERV.DE ALMACENAJE TRASLADO Y CUSTODIA DE CAJAS</t>
-        </is>
-      </c>
-      <c r="C361" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D361" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="11" t="inlineStr">
-        <is>
-          <t>975-12-O126</t>
-        </is>
-      </c>
-      <c r="B362" s="13" t="inlineStr">
-        <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
-        </is>
-      </c>
-      <c r="C362" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D362" s="13" t="inlineStr">
-        <is>
-          <t>score 16 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="11" t="inlineStr">
-        <is>
-          <t>976-14-LP26</t>
-        </is>
-      </c>
-      <c r="B363" s="13" t="inlineStr">
-        <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
-        </is>
-      </c>
-      <c r="C363" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D363" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="11" t="inlineStr">
-        <is>
-          <t>979-49-L126</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Levantamiento y diseño del proyecto de normalización de la red húmeda para el recinto de Maestranza Central </t>
-        </is>
-      </c>
-      <c r="C364" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D364" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="11" t="inlineStr">
-        <is>
-          <t>993-42-LE26</t>
-        </is>
-      </c>
-      <c r="B365" s="13" t="inlineStr">
-        <is>
-          <t>Servicio Reparación y Mantención Recinto Taltal</t>
-        </is>
-      </c>
-      <c r="C365" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D365" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="11" t="inlineStr">
-        <is>
-          <t>993-47-LE26</t>
-        </is>
-      </c>
-      <c r="B366" s="13" t="inlineStr">
-        <is>
-          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
-        </is>
-      </c>
-      <c r="C366" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D366" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="11" t="inlineStr">
-        <is>
-          <t>996-35-LE26</t>
-        </is>
-      </c>
-      <c r="B367" s="13" t="inlineStr">
-        <is>
-          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
-        </is>
-      </c>
-      <c r="C367" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D367" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="11" t="inlineStr">
-        <is>
-          <t>997-32-LP26</t>
-        </is>
-      </c>
-      <c r="B368" s="13" t="inlineStr">
-        <is>
-          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
-        </is>
-      </c>
-      <c r="C368" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D368" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="11" t="inlineStr">
-        <is>
-          <t>997-34-LE26</t>
-        </is>
-      </c>
-      <c r="B369" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Arriendo de dos estanques móviles por 40 días </t>
-        </is>
-      </c>
-      <c r="C369" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D369" s="13" t="inlineStr">
         <is>
           <t>score 0 &lt; 30</t>
         </is>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-09-10 04:54 · UF 40,893.78 · 4,711 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-14 19:30 · UF 40,926.41 · 4,546 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>CAMBIO: monto UF 122304.0-&gt;122268.0</t>
+          <t>CAMBIO: monto UF 122268.0-&gt;122171.0</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M3" s="20" t="n">
-        <v>122268</v>
+        <v>122171</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>53</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122268</v>
+        <v>122171</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1950,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2024,12 +2024,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>1026727-12-LE26</t>
+          <t>1002772-97-LP26</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de equipamiento prototipado para el CFT</t>
+          <t>SUMINISTROS ODONTOLOGICOS PARA REHABILITACION ORAL</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
@@ -2044,92 +2044,92 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1035-22-L126</t>
+          <t>1026727-12-LE26</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Trabajos menores Casa Fiscal Conaf Pichilemu Region de O"Higgins</t>
+          <t>Arriendo de equipamiento prototipado para el CFT</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1035685-19-LE26</t>
+          <t>1027-15-LP26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Ampliación de Espacio Académico Sede Panguipulli</t>
+          <t>Servicio de Mantención Reparación y Habilitación de Campamentos Móviles Talleres y Bodegas de la Administración Directa en la Provincia de Huasco Región de Atacama.</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1036569-10-LP26</t>
+          <t>1035-22-L126</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
+          <t>Trabajos menores Casa Fiscal Conaf Pichilemu Region de O"Higgins</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1039-7-LR26</t>
+          <t>1035685-19-LE26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO  DE ARRIENDO DE EQUIPO MECANIZADO</t>
+          <t>Ampliación de Espacio Académico Sede Panguipulli</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1042-11-LE26</t>
+          <t>1036569-10-LP26</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Serv. traslado marítimo para faenas en Isla Mocha</t>
+          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2144,32 +2144,32 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1051173-11-LE26</t>
+          <t>1039-7-LR26</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
+          <t>SERVICIO  DE ARRIENDO DE EQUIPO MECANIZADO</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1057049-296-LR26</t>
+          <t>1040538-15-L126</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>JCD VALVULA BIOLOGICA CON COMODATO</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MONTAJE, HABILITACIÓN Y APOYO LOGÍSTICO PARA ACTIVIDAD EN NEVADOS DE CHILLÁN</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -2184,12 +2184,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057049-322-I226</t>
+          <t>1040538-16-L126</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>Servicio integral para la obtención, coordinación y habilitación del derecho de   participación de la Región de Ñuble dentro del stand de Chile en FIT Buenos   Aires 2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -2204,12 +2204,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057049-328-LR26</t>
+          <t>1042-11-LE26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
+          <t>Serv. traslado marítimo para faenas en Isla Mocha</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -2224,32 +2224,32 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057049-329-LE26</t>
+          <t>1051173-11-LE26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
+          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057055-68-LP26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>GSP SUMINISTRO DE MEDICAMENTOS PROPOFOL CON EQUIPOS EN COMODATO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -2264,32 +2264,32 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057049-328-LR26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057417-183-LP26</t>
+          <t>1057049-329-LE26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>pmt CONVENIO DE TRASLADO DE FÁRMACOS</t>
+          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2304,32 +2304,32 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057417-186-LP26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057417-51-LP26</t>
+          <t>1057417-186-LP26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FRESAS UN SOLO USO CON MOTOR DE NEURO  OTOLOGICO EN COMODATO</t>
+          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -2364,32 +2364,32 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057429-85-LE26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>EJECUCIÓN DE RADIER PARA BODEGA DE FARMACIA</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057492-121-LE26</t>
+          <t>1057429-86-LE26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
+          <t>ARRIENDO DE SETS DE MOTORES QUIRÚRGICOS</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2404,12 +2404,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057501-395-LR26</t>
+          <t>1057480-46-LR26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
+          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -2424,12 +2424,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057486-21-LE26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>Servicio de rehabilitación psicosocial tipo I y II</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2444,12 +2444,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057501-462-LE26</t>
+          <t>1057489-285-LP26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA PACIENTES MATERNIDAD HSR</t>
+          <t>Arriendo de Huelleros digitales y Pistola Escáner</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -2464,32 +2464,32 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057501-473-LE26</t>
+          <t>1057492-121-LE26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Habilitación para Instalacion de Food Truck HSR</t>
+          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057492-123-LE26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>SUMINISTRO DE BAJADAS PARA BOMBA PCA CON ENTREGA DE EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
@@ -2504,32 +2504,32 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057501-488-LE26</t>
+          <t>1057492-128-LP26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
+          <t>SERVICIO ARRIENDO DE LAVADORA TERMODESINFECTADORA</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057494-60-LE26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t>SUMINISTRO DE DRENAJES DE HERIDAS CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -2544,12 +2544,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057503-125-LE26</t>
+          <t>1057501-395-LR26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de Arriendo de Litotriptor y Nefroscopio para el Hospital Padre Alberto Hurtado</t>
+          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
@@ -2564,12 +2564,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057508-112-LE26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -2584,12 +2584,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057539-129-LP26</t>
+          <t>1057501-462-LE26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
+          <t>HABILITACIÓN SALA PACIENTES MATERNIDAD HSR</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
@@ -2604,32 +2604,32 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057544-293-LE26</t>
+          <t>1057501-473-LE26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Dosímetros Análisis y Emisión de Informes Trimestrales</t>
+          <t>Habilitación para Instalacion de Food Truck HSR</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
@@ -2644,12 +2644,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1057547-354-LP26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO 1 TORRE LAPAROSCOPIA CON OPTICA DE 0 Y 30</t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -2664,56 +2664,56 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1057552-19-LE26</t>
+          <t>1057508-112-LE26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Convenio de Suministro Materiales de Oficina</t>
+          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1057898-95-LE26</t>
+          <t>1057509-269-LP26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
+          <t>CONVENIO CONTRATACIÓN DE SERVICIOS DE APOYO PROFESIONALY TÉCNICO PARA EL DEPARTAMENTO DE EQUIPAMIENTO CLÍNICO DEL HOSPITAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1057977-14-LE26</t>
+          <t>1057509-292-LE26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
+          <t>“CONVENIO COMPRA SERVICIOS DE PROFESIONAL APOYO AL PROCESO DE GESTIÓN AL SISTEMA DE GESTIÓN DE COSTOS PARA EL DEPARTAMENTO DE FINANZAS” brd</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
@@ -2724,12 +2724,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1058086-49-LP26</t>
+          <t>1057511-28-LE26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
+          <t xml:space="preserve">COMPRA DE SERVICIOS DE TRASLADO HODOM POR CAMPAÑA </t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
@@ -2744,12 +2744,12 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1070620-89-LP26</t>
+          <t>1057539-129-LP26</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
+          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
@@ -2764,12 +2764,12 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1070620-93-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
@@ -2784,32 +2784,32 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1070620-95-LE26</t>
+          <t>1057552-19-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
+          <t>Convenio de Suministro Materiales de Oficina</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1070620-96-LP26</t>
+          <t>1057898-95-LE26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
+          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
@@ -2824,52 +2824,52 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1079445-41-LE26</t>
+          <t>1057962-9-LE26</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
+          <t>CAMBIOS DE VENTANAS PARA EDIFICIO PRINCIPAL Y OTROS ESTABLECIMIENTOS SSC</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1079445-42-LE26</t>
+          <t>1057977-14-LE26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
+          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1079650-57-LE26</t>
+          <t>1058012-28-LE26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS REHABILITACION COLDAS UDEC HTC</t>
+          <t>MEDICAMENTO SEVOFLURANO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -2884,52 +2884,52 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1079969-19-LP26</t>
+          <t>1058086-49-LP26</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
+          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1079969-20-LE26</t>
+          <t>1070620-89-LP26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
+          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1080303-8-LE26</t>
+          <t>1070620-93-LP26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Serv. Armado Habilitación y Desarme de Pista Remo</t>
+          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
@@ -2944,32 +2944,32 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1082957-29-LE26</t>
+          <t>1070620-95-LE26</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
+          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1095-10-LE26</t>
+          <t>1070620-96-LP26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
+          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
@@ -2984,12 +2984,12 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1095-11-LE26</t>
+          <t>1075963-370-LE26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
+          <t>ARRIENDO CON OPCION DE COMPRA SECADOR KAESER REFRIGERATIVO KYOSEC POR 3 MESES</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
@@ -3004,96 +3004,96 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1107276-25-LE26</t>
+          <t>1075963-403-L126</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
+          <t>ARRIENDO SISTEMA MONITOREO EN LINEA PARA REFRIGERADORES DE FARMACOS ONCOLOGICOS</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1116006-4-LE26</t>
+          <t>1079445-41-LE26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
+          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1175-71-LP26</t>
+          <t>1079445-42-LE26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
+          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1175-74-LP26</t>
+          <t>1079969-19-LP26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
+          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1186229-28-LE26</t>
+          <t>1079969-20-LE26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
+          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1197-20-L126</t>
+          <t>1082957-29-LE26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
+          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
@@ -3124,52 +3124,52 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1198-33-LE26</t>
+          <t>1095-10-LE26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
+          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1209403-8-L126</t>
+          <t>1095-11-LE26</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
+          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1107276-25-LE26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
@@ -3184,16 +3184,16 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1218393-40-L126</t>
+          <t>1116006-4-LE26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">APERTURA DE NUEVO VANO Y CIERRE DE VANO EXISTENTE BODEGA LAS ANIMAS </t>
+          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
@@ -3204,52 +3204,52 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1236-17-LE26</t>
+          <t>1171317-10-LP26</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>REQ. 107_TRASLADOS TERRESTRES PARA DEPORTISTAS FINAL NACIONAL DE JUEGOS DEPORTIVOS ESCOLARES</t>
+          <t xml:space="preserve">CONSTRUCCIÓN SEDE SOCIAL AGRUPACIÓN DE MOTOQUEROS CHILLÁN </t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1256505-28-LE26</t>
+          <t>1175-71-LP26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
+          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1261-19-LR26</t>
+          <t>1175-74-LP26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Habilitación paseo urbanofluvial lecho río Mapocho</t>
+          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
@@ -3264,56 +3264,56 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1261592-54-LE26</t>
+          <t>1186229-28-LE26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
+          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1197594-17-LE26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t>CONSULTORIA PLAN MAESTRO AREAS VERDES Y PAISAJISMO</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1293138-13-LP26</t>
+          <t>1198-33-LE26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>BODEGA ABAST SOMBREADERO JARDIN INFANTIL Y OTROS</t>
+          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
@@ -3324,32 +3324,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1305527-3-LP26</t>
+          <t>1209403-8-L126</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>CONTRAT. ARRIENDO DEL SIST. DE CONTROL DE ASIS</t>
+          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1337-21-LE26</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
@@ -3364,52 +3364,52 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1344190-12-LE26</t>
+          <t>1224953-26-LE26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE AYUDAS TÉCNICAS PARA LA ESTABILIZACIÓN Y POSICIONAMIENTO DEL CUERPO EN SEDENTEGRUPO G-4</t>
+          <t>Rehabilitación oral mediante prótesis removibles</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1348-5-LP26</t>
+          <t>1239966-10-LE26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
+          <t>HABILITACION DE CENTRO AIDIA DE PUERTO NATALES</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1350296-80-LE26</t>
+          <t>1256505-28-LE26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
@@ -3424,152 +3424,152 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1351-6-LP26</t>
+          <t>1261592-54-LE26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
+          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1374899-36-LP26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1375746-17-LP26</t>
+          <t>1337-21-LE26</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
+          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1375753-31-LE26</t>
+          <t>1340-51-LE26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE LEVANTAMIENTO DE INVENTARIO Y ARRIENDO</t>
+          <t>SERVICIO DE MANTENCION Y REPARACION DE INSTALACIONES Cierre Perimetral Con pilar metálico y brazo soldado de 60x60 Malla Urbana Acmafor con 3 portones 6 metros Recinto PAC 001 Valdivia – Dirección de Vialidad Región de Los Ríos.</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1391828-8-LE26</t>
+          <t>1346284-10-LE26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1346284-11-LE26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1422824-25-LP26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1350296-80-LE26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
@@ -3584,56 +3584,56 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1431841-56-LP26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1431841-57-LE26</t>
+          <t>1374899-36-LP26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
+          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1443-1-LE26</t>
+          <t>1375158-7-LP26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje y almacenamiento</t>
+          <t>ADQUISICIÓN DE VEINTICUATRO 24 SIERRAS DE AUTOPSIA Y UN 01 PACK EQUIPOS DE REFRIGERACIÓNCONGELACIÓN PARA DEPARTAMENTO DE TANATOLOGÍA DEL NUEVO EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL DE SANTIAGO</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
@@ -3644,92 +3644,92 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1448821-14-LP26</t>
+          <t>1375746-17-LP26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POZO PROFUNDO HUEQUI NORTE CHAITÉN</t>
+          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1469101-6-LP26</t>
+          <t>1391828-8-LE26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
+          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1469-189-L126</t>
+          <t>1417913-122-LE26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Habilitación de Laboratorio Central – Facultad de Odontología, Universidad de Talca</t>
+          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL EPP PARA FUNCIONARIOS Y ESTABLECIMIENTOS DEPENDIENTES DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1469-205-L126</t>
+          <t>1422824-1-LR26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
+          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1501468-17-LE26</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO RELOJ CONTROL E.E</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
@@ -3744,196 +3744,196 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1537592-17-LE26</t>
+          <t>1422832-9-LR26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
+          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1540667-6-LR26</t>
+          <t>1431841-56-LP26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
+          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1431841-57-LE26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>1549-85-LE26</t>
+          <t>1443-1-LE26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
+          <t>Servicio de bodegaje y almacenamiento</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1554-55-LR26</t>
+          <t>1469101-6-LP26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>contratación de Servicios de Transporte de pasajeros zona Norte y Sur del país apoyo traslado de pacientes del Hospital Regional Copiapó.</t>
+          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>1555-75-LP26</t>
+          <t>1469-205-L126</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
+          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>1562-57-L126</t>
+          <t>1469-211-L126</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
+          <t>MATERIAL GRÁFICO, TRASLADO, MONTAJE, INSTALACION, SUPERVISIÓN, DESMONTAJE Y RETIRO PARA UTALCA ABRE PUERTAS 2026, UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>1562-59-L126</t>
+          <t>1499887-19-CO26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
+          <t>SERVICIOS TÉCNICOS DE HABILITACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>1562-60-LR26</t>
+          <t>1533460-6-LP26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
+          <t>SERVICIO DE ARRIENDO DE SISTEMA INFORMÁTICO FINANCIERO CONTABLE Y RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>1574-33-LP26</t>
+          <t>1537592-17-LE26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
+          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
@@ -3944,52 +3944,52 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>1575-14-LE26</t>
+          <t>1540667-6-LR26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>MANTENCION DE OFICINAS</t>
+          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>1605-41-LP26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>LP-4872 Servicios de mantención general edificios</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>1643-75-LE26</t>
+          <t>1549-85-LE26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
+          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
@@ -4004,32 +4004,32 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>1657-17-L126</t>
+          <t>1555-75-LP26</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
+          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>1658-189-LP26</t>
+          <t>1562-57-L126</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>P.230-2026 REPARACIÓN CUBIERTA DE LONA SUPERIOR CASA DE MÁQUINAS MUSEO FERROVIARIO</t>
+          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
@@ -4044,92 +4044,92 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>1663-137-LE26</t>
+          <t>1562-59-L126</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SISTEMA MOVIL PARA SEDACION</t>
+          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>1696-15-LE26</t>
+          <t>1562-60-LR26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
+          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1574-33-LP26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>1810-3-LE26</t>
+          <t>1575-14-LE26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
+          <t>MANTENCION DE OFICINAS</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>1894-25-LP26</t>
+          <t>1643-75-LE26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
+          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
@@ -4144,152 +4144,152 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>1947-157-LE26</t>
+          <t>1657-17-L126</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
+          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>1947-168-LE26</t>
+          <t>1696-15-LE26</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>1969-18-LE26</t>
+          <t>1697-40-LR26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
+          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>1973-96-LE26</t>
+          <t>1735-50-LE26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE VIDEOCOLONOSCOPIO </t>
+          <t>HABILITACION CEFAM DE CONTINGENCIA 3ra. ETAPA TUB</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>1973-97-LP26</t>
+          <t>1743-69-LP26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
+          <t>Construcción Sede Social Manquehua</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>1978-112-L126</t>
+          <t>1810-3-LE26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO MONITOREO SISTEMA DE ALARMA EN BODEGA REGIONAL SSMAULE</t>
+          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2020-19-LE26</t>
+          <t>1894-25-LP26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
+          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2069-155-LP26</t>
+          <t>1947-113-LR26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>CGM ARRIENDO DE RESECTOSCOPIOS BIPOLARES Y NEFROSC</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE NUTRICIONES PARENTERALES DE DIFERENTES VOLÚMENES CON BAJADAS DE BOMBA DE INFUSIÓN Y EQUIPOS EN COMODATO PARA EL HOSPITAL ROBERTO DEL RÍO CFO</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
@@ -4304,32 +4304,32 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2098-115-LE26</t>
+          <t>1947-157-LE26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO FÁRMACO PROPOFOL CON SET DE ADMINISTRACIÓN KIT TIVA MÁS 6 BOMBAS DE JERINGA EN COMODATO POR UN PERIODO DE 24 MESES HRAV PAC N°163</t>
+          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2098-122-LP26</t>
+          <t>1947-168-LE26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
@@ -4344,112 +4344,112 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2098-133-LP26</t>
+          <t>1969-18-LE26</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
+          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>2098-134-LP26</t>
+          <t>1973-97-LP26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
+          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>2102-31-LE26</t>
+          <t>1979-192-LE26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
+          <t>175.26 “ARRIENDO DE EQUIPOS PARA PABELLÓN GINECOLOGICO PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2107-142-LE26</t>
+          <t>2020-19-LE26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
+          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2107-144-LP26</t>
+          <t>2062-5-L126</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
+          <t>Servicio de Coffe Break , almuerzo, arriendo de salón y Equipamiento  para "Jornada de Reconocimiento a Maestros de Maestros de la Provincia de Cachapoal"</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2109-10-LP26</t>
+          <t>2098-122-LP26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
+          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
@@ -4464,96 +4464,96 @@
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2123-22-CO26</t>
+          <t>2098-133-LP26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>E1O2RT8 Traslado Pasajeros Provincia La Ligua</t>
+          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2176-55-LE26</t>
+          <t>2098-134-LP26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
+          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2179-14-LE26</t>
+          <t>2098-139-LE26</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
+          <t>CONVENIO SUMINISTRO BOLSAS DE ASPIRACIÓN PARA REPOSICIÓN BODEGA FOLIO PAC 200 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2205-14-LE26</t>
+          <t>2102-31-LE26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
+          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2258-168-LE26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
@@ -4564,12 +4564,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2258-175-LR26</t>
+          <t>2109-10-LP26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
@@ -4584,12 +4584,12 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2176-55-LE26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
@@ -4604,32 +4604,32 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2273-55-LE26</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPAMIENTO PARA DESARROLLO DE EVENTOS MUNICIPALES LA PINTANA</t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2274-43-L126</t>
+          <t>2205-14-LE26</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE SALAS DE LACTANCIA MATERNA PARA LOS CESFAM SANTIAGO NUEVA EXTREMADURA Y SAN RAFAEL . EXP 13788</t>
+          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
@@ -4644,16 +4644,16 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2275-29-LE26</t>
+          <t>2258-168-LE26</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y REMODELACIÓN DEPARTAMENTOS DE USO VACACIONAL BIENESTAR MUNICIPAL</t>
+          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
@@ -4664,92 +4664,92 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2279-56-LE26</t>
+          <t>2258-175-LR26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2279-58-LE26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>SP 592 ADQUISICION DE MATERIALES DE OFICINA CORPORATIVOS</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2279-56-LE26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2279-66-LE26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>SP 754 Servicio de Arriendo de Bodegas</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2292-57-L126</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>Contratación del Servicio Integral de Habilitación, Soporte Técnico y Monitoreo de Sistemas de Alarmas por 24 meses en Centros de Salud de Talca</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
@@ -4764,32 +4764,32 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2313-5-LE26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>Servicios de Conservación de Edificio Terminal</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2322-82-LE26</t>
+          <t>2313-5-LE26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
+          <t>Servicios de Conservación de Edificio Terminal</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
@@ -4804,52 +4804,52 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2324-112-LE26</t>
+          <t>2322-82-LE26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
+          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2332-106-L126</t>
+          <t>2324-112-LE26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO PARA LAVADORA DEL CESFAM ANTONIO VARAS PERTENECIENTE AL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2332-109-L126</t>
+          <t>2332-106-L126</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE INSTRUMENTAL DENTAL PARA EL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO PARA LAVADORA DEL CESFAM ANTONIO VARAS PERTENECIENTE AL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
@@ -4864,52 +4864,52 @@
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2332-52-LE26</t>
+          <t>2332-112-L126</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO E INSTALACION CASILLEROS INTELIGENTES</t>
+          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2332-70-LE26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>CS DE ARRIENDO DE APLICACION DE AGENDA VIRTUAL</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
@@ -4924,96 +4924,96 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2378-110-LP26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2378-110-LP26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2408-152-LE26</t>
+          <t>2385-53-LE26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
+          <t>SERVICIO DE ARRIENDO DE CARGADOR FRONTAL CON OPERADOR</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2408-160-LP26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2408-98-LE26</t>
+          <t>2408-152-LE26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
+          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
@@ -5024,16 +5024,16 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2410-41-LE26</t>
+          <t>2408-160-LP26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
+          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
@@ -5044,12 +5044,12 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2411-14-L126</t>
+          <t>2408-98-LE26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION MATERIALES VARIOS DE USO O CONSUMO PARA DEPARTAMENTO CEMENTERIO</t>
+          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
@@ -5064,36 +5064,36 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2409-96-L126</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>SERVICIO DE TRASLADO PARA ALUMNAS TALLER DE EXTRAESCOLAR Y JORNADAS DE REFLEXION PARA ESCUELA D-953</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2426-44-LE26</t>
+          <t>2410-41-LE26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
+          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
@@ -5104,36 +5104,36 @@
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2430-59-LP26</t>
+          <t>2411-14-L126</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
+          <t>ADQUISICION MATERIALES VARIOS DE USO O CONSUMO PARA DEPARTAMENTO CEMENTERIO</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2430-68-LR26</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
@@ -5144,12 +5144,12 @@
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2430-78-LP26</t>
+          <t>2426-44-LE26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
+          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
@@ -5164,92 +5164,92 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2445-110-LE26</t>
+          <t>2428-70-LP26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CASETAS E INST ESTANQUES DE AGUA</t>
+          <t>SERVICIO DE ARRIENDO DE OFICINA MOVIL -SOCIAL</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2445-115-LE26</t>
+          <t>2429-8-LP26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
+          <t>RENOVACIÓN DE INFRAESTRUCTURA DE RED INFORMÁTICA Y NORMALIZACIÓN DE CABLEADO ESTRUCTURADO DE LAS DEPENDENCIAS DE LA IMA</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2446-257-LE26</t>
+          <t>2430-68-LR26</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
+          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2446-260-LR26</t>
+          <t>2430-77-LP26</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
+          <t>MEJORAMIENTO SEDE SOCIAL EL ANCLA ANTOFAGASTA CÓDIGO BIP N°40073719-0</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
@@ -5264,16 +5264,16 @@
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2446-266-LP26</t>
+          <t>2430-78-LP26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN CASA MAC AULIFFE</t>
+          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
@@ -5284,76 +5284,76 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2450-90-LE26</t>
+          <t>2445-115-LE26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de cubre suelos Tiki Tiki y sistema de riego para rehabilitación de espacio público</t>
+          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2460-108-LE26</t>
+          <t>2446-257-LE26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
+          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2460-121-LE26</t>
+          <t>2446-260-LR26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
+          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
@@ -5364,12 +5364,12 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2483-242-CO26</t>
+          <t>2446-266-LP26</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+          <t>MANTENCIÓN CASA MAC AULIFFE</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
@@ -5384,72 +5384,72 @@
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2448-133-LE26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>HABILITACION OFICINA MODULAR CECOSF PUNTA MIRA</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2548-83-L126</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN OFICINA CESFAM PLC</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2460-108-LE26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2581-36-LE26</t>
+          <t>2460-121-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
+          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
@@ -5464,16 +5464,16 @@
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2581-37-LP26</t>
+          <t>2483-242-CO26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO EDIFICIO SEGURIDAD PUBLICA COMUNA CONCHALÍ</t>
+          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
@@ -5484,52 +5484,52 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2581-36-LE26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
@@ -5544,36 +5544,36 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>2667-83-LE26</t>
+          <t>2591-106-LR26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
+          <t>REPOSICION OFICINA SRCEI POZO ALMONTE</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
@@ -5584,16 +5584,16 @@
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>2667-90-LE26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
@@ -5604,72 +5604,72 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>2697-25-LR26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA DE OFICIOS</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>2702-63-LE26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN Y HABILITACIÓN CABALLERIZAS CENTRO DE</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>2710-55-LE26</t>
+          <t>2667-83-LE26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO TOTEM</t>
+          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>2667-90-LE26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
@@ -5684,52 +5684,52 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>2744-30-LE26</t>
+          <t>2687-16-CO26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Estructural de Sala AIDA CESFAM Alemania</t>
+          <t>REPOSICIÓN DE VENTANAS TERMOPANEL ESCUELA BÁSICA RURAL EL YECO</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>2744-34-LE26</t>
+          <t>2710-55-LE26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO CONTROL DE PLAGAS INTEGRAL PARA ESTABLECIMIENTOS URBANOS Y RURALES DEL DEPARTAMENTO DE SALUD MUNICIPAL DE ANGOL </t>
+          <t>SERVICIO DE ARRIENDO TOTEM</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>2755-34-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MOVIL PARA DEPARTAMENTO OPERACIONES</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
@@ -5744,56 +5744,56 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>2784-42-LP26</t>
+          <t>2784-44-LE26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN RECINTO COMUNITARIO LA HIGUERA comuna de La Ligua Cod.40067467-0</t>
+          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>2784-44-LE26</t>
+          <t>2794-22-LR26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
+          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>2794-22-LR26</t>
+          <t>2817-63-LE26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
+          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
@@ -5804,72 +5804,72 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>2817-63-LE26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>2906-18-LE26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>2906-18-LE26</t>
+          <t>2920-38-LP26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
+          <t>Construcción Sede Juventud Robinsoniana.</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>2920-38-LP26</t>
+          <t>2950-44-LP26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Juventud Robinsoniana.</t>
+          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
@@ -5884,40 +5884,40 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>2950-44-LP26</t>
+          <t>29-64-LP26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
+          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2974-71-L126</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>SERVICIO DE TALA DE ÁRBOL EN CASA DE HUESPEDES TANTAUCO (512/2026)</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
@@ -5964,16 +5964,16 @@
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>3046-25-LE26</t>
+          <t>299-17-LP26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
+          <t>E102RT9BRANDING Y ORNAMENTACION RECINTOS LOS RIOS</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
@@ -5984,72 +5984,72 @@
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3047-54-LE26</t>
+          <t>3015-52-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
+          <t>HABILITACIÓN DE DESAGÜES EN SECTORES DE LA CRUZ</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>3016-52-LE26</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>Servicio de Suministro Trofeos Galvanos Placas y Otros para Actividades Municipales del Área de Gestión Municipal Departamento de Salud y Departamento de Educación</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3172-68-LE26</t>
+          <t>3046-25-LE26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MAT. DEPENDENCIAS 2DO. NIVEL ASESORÍA DIGCAR</t>
+          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>3179-49-LE26</t>
+          <t>3047-54-LE26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CASACA DE POLAR FRONTERA</t>
+          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
@@ -6064,36 +6064,36 @@
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>3179-50-LE26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE CASACA DE CUERO MOTORISTAS</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>3179-51-LE26</t>
+          <t>3117-88-LE26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ZAPATILLA DE CICLISTA PARA EL STOCK DEL DEPARTAMENTO L.2</t>
+          <t>OFICINA Y BODEGA MODULAR C.R. LAS SALINAS</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
@@ -6104,72 +6104,72 @@
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>3172-68-LE26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>ADQ. MAT. DEPENDENCIAS 2DO. NIVEL ASESORÍA DIGCAR</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>3290-8-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>3333-32-LE26</t>
+          <t>3290-8-LE26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>SERV. LEVANTAMIENTO REGISTRO DE INVENTARIO I.M.O</t>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>3333-38-LE26</t>
+          <t>3328-100-L126</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>SERV TRASLADO ESCOLAR JARDIN RETOÑOS DE AMOR OLMUE</t>
+          <t>ASB/PROVISIÒN E INSTALACIÒN DE VENTANAS TIPO TERMOPANEL CRT</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
@@ -6244,40 +6244,40 @@
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>3525-8-LR26</t>
+          <t>3474-53-LE26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>Sum e instalación de taludes visita terreno volun</t>
+          <t>SERVICIO DE ARRIENDO Y MANT. MAQUINAS FOTOCOPIADO</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>3537-52-LE26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de una autohormigonera por 320 horas</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
@@ -6304,12 +6304,12 @@
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>359-105-LE26</t>
+          <t>359-106-LE26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>ADQ. CLIP POLIMERO CON COMODATO DE APLICADORES</t>
+          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
@@ -6324,32 +6324,32 @@
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>359-106-LE26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>3624-32-LP26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
@@ -6364,16 +6364,16 @@
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>3624-33-LP26</t>
+          <t>3671-61-LE26</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
+          <t xml:space="preserve">“SUMINISTRO DE OXÍGENO” PARA DEPENDENCIAS DE SALUD DE LA COMUNA DE CHILLÁN VIEJO. </t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
@@ -6384,32 +6384,32 @@
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>3671-58-LE26</t>
+          <t>3678-22-LE26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO” </t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>3671-61-LE26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“SUMINISTRO DE OXÍGENO” PARA DEPENDENCIAS DE SALUD DE LA COMUNA DE CHILLÁN VIEJO. </t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
@@ -6424,12 +6424,12 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>3678-22-LE26</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
@@ -6444,152 +6444,152 @@
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>3693-158-LP26</t>
+          <t>3708-40-LE26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
+          <t>HABILITACION OFICINAS TRANSITO OBRAS Y OTRAS</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>3708-39-LE26</t>
+          <t>3761-21-LE26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
+          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>3761-21-LE26</t>
+          <t>3775-33-LE26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
+          <t>SERV. ARRIENDO EXCAVADORA Y 2 MOTOBOMBAS HIJUELAS</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>3789-33-LE26</t>
+          <t>3798-19-LR26</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS DE REHABILITACION MOTORA</t>
+          <t>ADQUISICIÓN DE TERRENO DE INFRAESTRUCTURA PÚBLICA</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>3847-41-LE26</t>
+          <t>3836-37-LE26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
+          <t>OFICINA MODULAR JUZGADO POLICIA LOCAL DE TOLTEN</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>3880-61-LE26</t>
+          <t>3847-41-LE26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CAMARINES ESCUELA DE COLIN SECPLAN</t>
+          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>3882-72-LP26</t>
+          <t>3880-65-LE26</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CANCHA CLUB DEPORTIVO LAS PALMAS COMUNA DE LLAY LLAY</t>
+          <t>SEDE SOCIAL CLUB ADULTO MAYOR SECTOR EL PARRON</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>3882-85-LE26</t>
+          <t>3885-51-LP26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE NUEVA OFICINA CONTROL I. MUNICIPALIDAD LLAY LLAY COMUNA LLAY LLAY</t>
+          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
@@ -6604,16 +6604,16 @@
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>3885-51-LP26</t>
+          <t>3889-41-LP26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
+          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
@@ -6624,12 +6624,12 @@
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>3889-41-LP26</t>
+          <t>3912-19-LP26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
+          <t>Construccion sede social los acacios</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
@@ -6644,32 +6644,32 @@
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>3908-42-L126</t>
+          <t>3950-40-LE26</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO Y ALOJAMIENTO PARA BARRIO COPAHUE COMUNA DE RENAICO</t>
+          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>3912-19-LP26</t>
+          <t>3963-16-LP26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>Construccion sede social los acacios</t>
+          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
@@ -6684,92 +6684,92 @@
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>3935-83-LP26</t>
+          <t>3997-59-B226</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN DE PATIO TECHADO Y HABILITACIÓN DE COCINERÍAS DE GALERÍA MUNICIPAL COMUNA DE FREIRE</t>
+          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>3935-87-LE26</t>
+          <t>4006-21-LE26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACION SERVICIO DE ECOTOMOGRAFIA ABDOMINAL PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE 2026</t>
+          <t>Mejoramiento Area Deportiva Ventanas</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>3935-88-LE26</t>
+          <t>4037-64-LE26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACION SERVICIO DE MAMOGRAFIAS Y ECOTOMOGRAFIA MAMARIA PARA DEPARTAMENTO DE SALUD MUNICIPAL DE FREIRE</t>
+          <t>SERVICIO REGULARIZACION Y HABILITACION SALA APICOLA</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>3950-40-LE26</t>
+          <t>4055-69-L126</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
+          <t>ADQUISICION DE SERVICIO DE FORMACIÓN EN TERRENO PA</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>3963-16-LP26</t>
+          <t>4063-1-LP26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
+          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
@@ -6784,12 +6784,12 @@
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>3997-59-B226</t>
+          <t>407-113-LP26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
+          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
@@ -6804,12 +6804,12 @@
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>4006-21-LE26</t>
+          <t>4099-25-LE26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Area Deportiva Ventanas</t>
+          <t>Servicio de Arriendo de Gestor Documental</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
@@ -6824,16 +6824,16 @@
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>4063-1-LP26</t>
+          <t>411-43-CO26</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
+          <t>CONSTRUCCIÓN BODEGA MUNICIPAL SECTOR LA HUERTA</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
@@ -6844,16 +6844,16 @@
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>4127-41-LE26</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>[DIVAP] Estudio del bodegaje de ajuares</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D245" s="13" t="inlineStr">
         <is>
@@ -6864,32 +6864,32 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>4099-22-LP26</t>
+          <t>4127-47-LE26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción Sede Las Mercedes Comuna de María Pinto </t>
+          <t>[DIGEDEP] Curso Rehabilitación Oral</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>4099-25-LE26</t>
+          <t>4143-6-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Gestor Documental</t>
+          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
@@ -6904,52 +6904,52 @@
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>4127-41-LE26</t>
+          <t>418-57-LP26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>[DIVAP] Estudio del bodegaje de ajuares</t>
+          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>4127-47-LE26</t>
+          <t>418-60-LE26</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t>[DIGEDEP] Curso Rehabilitación Oral</t>
+          <t>CONTRATACIÓN DE SERVICIO AUXILIAR DE BODEGA</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>4143-6-LE26</t>
+          <t>4189-38-LE26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
+          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
@@ -6964,12 +6964,12 @@
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>418-57-LP26</t>
+          <t>425-57-LR26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
+          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
@@ -6984,232 +6984,232 @@
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>4189-38-LE26</t>
+          <t>4295-67-LP26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
+          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>425-57-LR26</t>
+          <t>4306-32-LE26</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
+          <t>ADQUISICION EQUIPAMIENTO CASA PROG. HABITABILIDAD</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D253" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>4284-145-L126</t>
+          <t>4309-233-LP26</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de 50 metros de leña nativa seca y trozada para calefacción dependencias municipales Según bases adjuntas Punto 2 productos requeridos</t>
+          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>4290-60-LE26</t>
+          <t>4328-33-B226</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>Serv. arriendo vallas de seguridad Fiestas Patrias</t>
+          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>4295-67-LP26</t>
+          <t>4342-2-LP26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
+          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>4306-32-LE26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION EQUIPAMIENTO CASA PROG. HABITABILIDAD</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>4309-233-LP26</t>
+          <t>4451-102-LE26</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
+          <t>Reparación de cubiertas de edificio Polideportivo</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>4328-33-B226</t>
+          <t>4451-92-LE26</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
+          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>4342-2-LP26</t>
+          <t>4494-64-LP26</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES LIRQUEN</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>4362-15-LP26</t>
+          <t>4494-65-LP26</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Las Pozas II Nacimiento</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES PENCO</t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>439-26-LP26</t>
+          <t>45-45-LR26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
+          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>4451-102-LE26</t>
+          <t>45-48-LE26</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>Reparación de cubiertas de edificio Polideportivo</t>
+          <t>SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
@@ -7224,32 +7224,32 @@
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>4451-92-LE26</t>
+          <t>4584-13-LE26</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
+          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>4454-27-LE26</t>
+          <t>4591-20-LP26</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO - PROGRAMA SOCIAL</t>
+          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
@@ -7264,76 +7264,76 @@
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>4457-70-L126</t>
+          <t>4623-5-L126</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
-          <t>IMPLEMENTOS PRAPS MAS AMA, EQUIDAD RURAL, REHABILITACIÓN INTEGRAL Y ESPACIOS AMIGABLES.</t>
+          <t>SUMINISTRO DE MANTENCIÓN DE OBRAS MENORES PARA LAS OFICINAS DEPENDIENTES DE LA DIRECCIÓN REGIONAL DEL TRABAJO DE BIOBÍO</t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>45-45-LR26</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>45-48-LE26</t>
+          <t>4686-30-LE26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
+          <t>Servicio de arrendamiento de bodegas</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>4584-13-LE26</t>
+          <t>483-47-L126</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
+          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D269" s="13" t="inlineStr">
         <is>
@@ -7344,72 +7344,72 @@
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>4591-20-LP26</t>
+          <t>4887-28-E226</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
+          <t>Obras de habilitación Centro de Creación Temuco</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>4623-4-L126</t>
+          <t>4956-68-LP26</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN DE ESTRUCTURA Y PISO DE LA OFICINA DE FISCALIZADORES DE LA INSPECCIÓN COMUNAL DEL TRABAJO TOMÉ</t>
+          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>4623-5-L126</t>
+          <t>4967-35-LP26</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MANTENCIÓN DE OBRAS MENORES PARA LAS OFICINAS DEPENDIENTES DE LA DIRECCIÓN REGIONAL DEL TRABAJO DE BIOBÍO</t>
+          <t>CONVENIO DE SUMINISTRO DE CÁNULAS DE ALTO FLUJO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>4629-26-LE26</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PUESTOS DE TRABAJO DT</t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
@@ -7424,12 +7424,12 @@
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>5056-108-LP26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>ARRIENDO DE REENVASADORA AUTOMÁTICA DE MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
@@ -7444,52 +7444,52 @@
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>4642-99-LE26</t>
+          <t>5240-102-LR26</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t>PROVISIÓN E INSTALACIÓN DE PUERTAS ABATIBLES EN LAS DEPENDENCIAS DEL HOSPITAL DE CARABINEROS.</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>483-47-L126</t>
+          <t>5240-90-LR26</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
+          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>4850-4-L126</t>
+          <t>527481-62-LE26</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PREVENCIÓN Y CONTROL DE PLAGAS PARA LAS DEPENDENCIAS DEL MUSEO GABRIELA MISTRAL DE VICUÑA </t>
+          <t>CONSTRUCCION SEDE EL MOLLAR</t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
@@ -7504,32 +7504,32 @@
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>4887-28-E226</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>Obras de habilitación Centro de Creación Temuco</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
@@ -7544,152 +7544,152 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>5048-51-O126</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>AIF TRES VENTANAS TRAMO 2</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>5056-102-LP26</t>
+          <t>539119-81-LE26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS NO INVASIVOS PARA CARDIOLOGÍA AMBULATORIA</t>
+          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>5056-108-LP26</t>
+          <t>539119-90-LE26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE REENVASADORA AUTOMÁTICA DE MEDICAMENTOS</t>
+          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>5240-102-LR26</t>
+          <t>5418-13-LE26</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
+          <t>Digitalización Documentos Almacenados Bodega</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>547640-16-L126</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t xml:space="preserve">MEJORAMIENTO Y HABILITACIÓN CASA DE SALUD MENTAL </t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>527481-62-LE26</t>
+          <t>5482-102-LE26</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE EL MOLLAR</t>
+          <t>ARRIENDO Y MANTENCIÓN DE 2 ESCANERES PARA DOM</t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D285" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>5520-75-LP26</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>Traslado Pasajeros Minera Collahuasi</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
@@ -7704,16 +7704,16 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>539119-80-LP26</t>
+          <t>5558-5-L126</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
@@ -7724,136 +7724,136 @@
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>539119-81-LE26</t>
+          <t>564953-71-LP26</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>539119-90-LE26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>5418-13-LE26</t>
+          <t>584264-46-LE26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>Digitalización Documentos Almacenados Bodega</t>
+          <t>HABILITACIÓN POSTA URBANA SARA GAJARDO</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>607-67-O126</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>622847-13-LE26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 21 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>5558-5-L126</t>
+          <t>633-54-LP26</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>CONVENIO DE SUMINISTRO SERVICIO DE ARRIENDO DE MOD</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>5586-126-LE26</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>JG REMODELACIÓN DEPARTAMENTO DE CIRUGÍA 4º PISO EDIFICIO S</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
@@ -7864,276 +7864,276 @@
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>564953-71-LP26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>568658-43-LR26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>584264-46-LE26</t>
+          <t>657-7-LE26</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POSTA URBANA SARA GAJARDO</t>
+          <t>FTO DS49 CS Nuevos terrenos Chile Chico Serviu</t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>660-10-LE26</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D299" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>622-55-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t>CONFECCIÓN E IMPRESIÓN SOBRES 10X23 CON VENTANILLA</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>622847-13-LE26</t>
+          <t>680504-2-L126</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
+          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>score 21 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>630-24-LE26</t>
+          <t>688-11-LP26</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DISPENSADORES NUEVOS DE AGUA PURIFICADA</t>
+          <t>Arriendo Infraestructura de Respaldo</t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>633-48-LR26</t>
+          <t>696217-4-LE26</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS PARA ÁREAS PROTEGIDAS AP ADMINISTRADAS POR LA CORPORACIÓN NACIONAL FORESTAL CONAF</t>
+          <t>Serv de Mantencion de inmueble Oficina Colchane</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>634-82-LE26</t>
+          <t>696961-4-LP26</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
+          <t>HABILITACIÓN DE OFICINAS PROYECTO CENTRALIZADO</t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>697-29-LE26</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>Serv. habilitación electrica para equipo trifasico</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>643-32-LE26</t>
+          <t>699866-116-LP26</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t>TRASLADO FUNCIONARIOS OFICINA ISLA DE PASCUA</t>
+          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>707418-44-L126</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>660-10-LE26</t>
+          <t>711841-14-L126</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
+          <t>MANTENCION SISTEMA CONTROL DE INCENDIO EDIFICIO MDSYF</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>732515-1-L126</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t>CONVENIO DE SUMINISTRO EN ADQUISICION DE PRODUCTOS DE DIFUSION Y PUBLICIDAD PARA GOBIERNO EN TERRENO</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
@@ -8144,32 +8144,32 @@
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>680504-2-L126</t>
+          <t>732868-3-L126</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
+          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>688-11-LP26</t>
+          <t>748201-9-LP26</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Infraestructura de Respaldo</t>
+          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
@@ -8184,192 +8184,192 @@
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>696217-4-LE26</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>Serv de Mantencion de inmueble Oficina Colchane</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>696961-4-LP26</t>
+          <t>769-84-LP26</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE OFICINAS PROYECTO CENTRALIZADO</t>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>697-29-LE26</t>
+          <t>777304-55-LP26</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>Serv. habilitación electrica para equipo trifasico</t>
+          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>699866-116-LP26</t>
+          <t>780724-6-LE26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
+          <t>Remodelación dependencias TercerTribunal Ambiental</t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>707418-44-L126</t>
+          <t>813-87-LE26</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
+          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>707420-20-LE26</t>
+          <t>820-3-O126</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MANTENCIÓN DE ÁREAS VERDES PARA JARDINES INFANTILES SALAS CUNA Y OFICINAS TERRITORIALES DE FUNDACIÓN INTEGRA REGIÓN DEL MAULE.</t>
+          <t>RESTAURACIÓN Y HABILITACIÓN BIBLIOTECA MUNICIPAL EX ESCUELA 3, HUASCO</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>712307-58-O126</t>
+          <t>824-3-LE26</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>Pavimentos Participativos 35 proceso, Grupo 6, Temuco y Padre Las Casas</t>
+          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>729-180-LE26</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>SELLOS PRECINTOS EMBALAJE -CLS-2x20295</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>838794-10-LE26</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>SERV DE CIERRE DE TABIQUERÍA EN PAREDES DE OFICINA PALIATIVO DEL CENTRO DE ATENCIÓN PRIMARIA DE SALU DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>839186-11-LP26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>2 LLAMADO HABILITACIÓN CANCHA DE FÚTBOL Y CIERRE</t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
@@ -8384,16 +8384,16 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>763003-8-LE26</t>
+          <t>840405-14-CO26</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>MATERIALES PARA ACONDICIONAMIENTO DE OFICINAS.</t>
+          <t>ADQUISICION DE MATERIALES PARA MEJORAMIENTO EDIFICIO ANEXO MUNICIPAL COMUNA DE RÍO CLARO PRIVADA</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
@@ -8404,16 +8404,16 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>867990-85-L126</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>cc 102 sol. 92417- Mantención y reparación de sala con visita a terreno</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
@@ -8424,32 +8424,32 @@
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>769-84-LP26</t>
+          <t>867990-89-L126</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>777304-55-LP26</t>
+          <t>875646-69-LP26</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
+          <t>JCB. Servicio de arriendo de sistema RISPACS</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
@@ -8464,32 +8464,32 @@
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>780724-6-LE26</t>
+          <t>886954-176-LP26</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
         <is>
-          <t>Remodelación dependencias TercerTribunal Ambiental</t>
+          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>813-87-LE26</t>
+          <t>886954-294-LP26</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
         <is>
-          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
+          <t>Conv. Suministro Prótesis Para U. Medicina Fisica y Rehabilitación del HGGB</t>
         </is>
       </c>
       <c r="C327" s="11" t="n">
@@ -8504,12 +8504,12 @@
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>820-3-O126</t>
+          <t>886954-298-LP26</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
         <is>
-          <t>RESTAURACIÓN Y HABILITACIÓN BIBLIOTECA MUNICIPAL EX ESCUELA 3, HUASCO</t>
+          <t>Convenio Suministro de Cataratas con Equipos en Comodatos</t>
         </is>
       </c>
       <c r="C328" s="11" t="n">
@@ -8524,56 +8524,56 @@
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>898-181-LP26</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>Servicios de Laboratorio Dental con Equipo en Comodato</t>
         </is>
       </c>
       <c r="C329" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D329" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>899-39-LE26</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>“Servicio de Mantención Preventiva y Correctiva de PEAS y Limpieza de Estanque de Aguas Servidas para Hospital San José de Casablanca</t>
         </is>
       </c>
       <c r="C330" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>837-88-LP26</t>
+          <t>899-40-LE26</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
         <is>
-          <t>CDP422 Serv. Mantención de sistemas de renovación de Aérea y Climatización de las sedes del Servicio Médico Legal de Rancagua San Fernando Santa Cruz Puerto Montt Valdivia La Unión y Osorno de la Zona Sur.</t>
+          <t>“Convenio de Suministro de Medicamentos para el Hospital San José de Casablanca”</t>
         </is>
       </c>
       <c r="C331" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
@@ -8584,36 +8584,36 @@
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>839186-11-LP26</t>
+          <t>900-45-LP26</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
         <is>
-          <t>2 LLAMADO HABILITACIÓN CANCHA DE FÚTBOL Y CIERRE</t>
+          <t xml:space="preserve">Servicio de Habilitación sala UHCIP </t>
         </is>
       </c>
       <c r="C332" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>845-17-LR26</t>
+          <t>905-30-LE26</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE EDIFICACIONES JUNJI</t>
+          <t>Cambio de Red Eléctrica de las dependencias de Oficina Sectorial San Fernando Región de O´Higgins.</t>
         </is>
       </c>
       <c r="C333" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D333" s="13" t="inlineStr">
         <is>
@@ -8624,56 +8624,56 @@
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>867990-85-L126</t>
+          <t>924-27-LP26</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
         <is>
-          <t>cc 102 sol. 92417- Mantención y reparación de sala con visita a terreno</t>
+          <t>Servicio de bodegaje para la Seremi de Salud R.M.</t>
         </is>
       </c>
       <c r="C334" s="11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>867990-89-L126</t>
+          <t>928-27-LR26</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
         <is>
-          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
+          <t>SERVICIO DE ARRENDAMIENTO DE PERIMETROS FREESTANDING</t>
         </is>
       </c>
       <c r="C335" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D335" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>885-80-LP26</t>
+          <t>931-23-LE26</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
         <is>
-          <t>Servicios de remodelación de oficinas de la Contraloría Regional de La Arauncanía</t>
+          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
         </is>
       </c>
       <c r="C336" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
@@ -8684,12 +8684,12 @@
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>886954-176-LP26</t>
+          <t>937232-85-LE26</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
         <is>
-          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
+          <t>SERVICIO DE ARRIENDO DE CAMILLAS DE TRANSPORTE HIDRAULICAS POR 24 MESES</t>
         </is>
       </c>
       <c r="C337" s="11" t="n">
@@ -8704,12 +8704,12 @@
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>886954-222-LR26</t>
+          <t>948354-135-LP26</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CIRCUITOS Y CANULAS DE ALTO FLUJO NASAL CON EQUIPOS EN COMODATO PARA HGGB</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C338" s="11" t="n">
@@ -8724,12 +8724,12 @@
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>886954-297-LP26</t>
+          <t>948806-117-LP26</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>Convenio anual Maleta en tránsito de Set de Ablación con equipo en comodato para la Unidad de Electrofisiología del HGGB</t>
+          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
         </is>
       </c>
       <c r="C339" s="11" t="n">
@@ -8744,56 +8744,56 @@
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>898-181-LP26</t>
+          <t>963423-10-LE26</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>Servicios de Laboratorio Dental con Equipo en Comodato</t>
+          <t>serv. reparacion conservacion y pintura inmueble</t>
         </is>
       </c>
       <c r="C340" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>899-39-LE26</t>
+          <t>975-12-O126</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Mantención Preventiva y Correctiva de PEAS y Limpieza de Estanque de Aguas Servidas para Hospital San José de Casablanca</t>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
         </is>
       </c>
       <c r="C341" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D341" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>899-40-LE26</t>
+          <t>986278-21-LE26</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>“Convenio de Suministro de Medicamentos para el Hospital San José de Casablanca”</t>
+          <t>EQUIPAMIENTO FUNGIBLES Y OTROS PARA ESCUELA INDUSTRIA Y ENERGÍAS PARA CASA CENTRAL LAUTARO Y SEDE ANGOL DEL CFT REGIÓN DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="C342" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
@@ -8804,320 +8804,20 @@
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>905-30-LE26</t>
+          <t>993-47-LE26</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
         <is>
-          <t>Cambio de Red Eléctrica de las dependencias de Oficina Sectorial San Fernando Región de O´Higgins.</t>
+          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
         </is>
       </c>
       <c r="C343" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D343" s="13" t="inlineStr">
         <is>
           <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="11" t="inlineStr">
-        <is>
-          <t>924-27-LP26</t>
-        </is>
-      </c>
-      <c r="B344" s="13" t="inlineStr">
-        <is>
-          <t>Servicio de bodegaje para la Seremi de Salud R.M.</t>
-        </is>
-      </c>
-      <c r="C344" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="D344" s="13" t="inlineStr">
-        <is>
-          <t>score 13 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="11" t="inlineStr">
-        <is>
-          <t>931-23-LE26</t>
-        </is>
-      </c>
-      <c r="B345" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
-        </is>
-      </c>
-      <c r="C345" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D345" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="11" t="inlineStr">
-        <is>
-          <t>931-26-LE26</t>
-        </is>
-      </c>
-      <c r="B346" s="13" t="inlineStr">
-        <is>
-          <t>SERVICIOS DE REPARACIÓN DE RED AGUA POTABLE Y SERVICIOS HIGIÉNICOS RECINTO CENDYR LA SERENA</t>
-        </is>
-      </c>
-      <c r="C346" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D346" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="11" t="inlineStr">
-        <is>
-          <t>931-27-LE26</t>
-        </is>
-      </c>
-      <c r="B347" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIOS DE REPARACIÓN DE CALZADA VEREDA CONSTRUCCIÓN DE CONTENCIÓN Y DRENAJES RECINTO CENDYR LA SERENA </t>
-        </is>
-      </c>
-      <c r="C347" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D347" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="11" t="inlineStr">
-        <is>
-          <t>935-22-LE26</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="inlineStr">
-        <is>
-          <t>MANT. REP.  MAQ. Y EQUIP. RECINTOS IND XII REGION</t>
-        </is>
-      </c>
-      <c r="C348" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D348" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="11" t="inlineStr">
-        <is>
-          <t>948354-135-LP26</t>
-        </is>
-      </c>
-      <c r="B349" s="13" t="inlineStr">
-        <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
-        </is>
-      </c>
-      <c r="C349" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D349" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="11" t="inlineStr">
-        <is>
-          <t>948355-68-LP26</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE TRANSDUCTORES SIMPLES Y DOBLES CON CABLES INTERFASE CON EQUIPO EN COMODATO POR SISTEMA DE SUMINISTRO PARA EL HOSPITAL DIPRECA </t>
-        </is>
-      </c>
-      <c r="C350" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D350" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="11" t="inlineStr">
-        <is>
-          <t>948806-117-LP26</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="inlineStr">
-        <is>
-          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
-        </is>
-      </c>
-      <c r="C351" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D351" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="11" t="inlineStr">
-        <is>
-          <t>963423-10-LE26</t>
-        </is>
-      </c>
-      <c r="B352" s="13" t="inlineStr">
-        <is>
-          <t>serv. reparacion conservacion y pintura inmueble</t>
-        </is>
-      </c>
-      <c r="C352" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="D352" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="11" t="inlineStr">
-        <is>
-          <t>975-12-O126</t>
-        </is>
-      </c>
-      <c r="B353" s="13" t="inlineStr">
-        <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
-        </is>
-      </c>
-      <c r="C353" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D353" s="13" t="inlineStr">
-        <is>
-          <t>score 16 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="11" t="inlineStr">
-        <is>
-          <t>976-14-LP26</t>
-        </is>
-      </c>
-      <c r="B354" s="13" t="inlineStr">
-        <is>
-          <t>“SERVICIO DE REFORESTACION POR HABILITACIÓN INGRESO A CUARTEL SSEI DEL AEROPUERTO DE PUNTA ARENAS”</t>
-        </is>
-      </c>
-      <c r="C354" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D354" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="11" t="inlineStr">
-        <is>
-          <t>993-47-LE26</t>
-        </is>
-      </c>
-      <c r="B355" s="13" t="inlineStr">
-        <is>
-          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
-        </is>
-      </c>
-      <c r="C355" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D355" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="11" t="inlineStr">
-        <is>
-          <t>996-35-LE26</t>
-        </is>
-      </c>
-      <c r="B356" s="13" t="inlineStr">
-        <is>
-          <t>CIERRE PERIMETRAL Y PORTON VEHICULAR RECINTO PEÑUELAS</t>
-        </is>
-      </c>
-      <c r="C356" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D356" s="13" t="inlineStr">
-        <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="11" t="inlineStr">
-        <is>
-          <t>997-32-LP26</t>
-        </is>
-      </c>
-      <c r="B357" s="13" t="inlineStr">
-        <is>
-          <t>13 días de arriendo  Terminadora de  Asfalto Finisher para apoyo de los trabajos de mezcla asfáltica en  caliente que se realizarán en distintos caminos de la Provincia de Cachapoal y Colchagua perteneciente a la Dirección de Vialidad Región del Lib</t>
-        </is>
-      </c>
-      <c r="C357" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D357" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="11" t="inlineStr">
-        <is>
-          <t>997-34-LE26</t>
-        </is>
-      </c>
-      <c r="B358" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Arriendo de dos estanques móviles por 40 días </t>
-        </is>
-      </c>
-      <c r="C358" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D358" s="13" t="inlineStr">
-        <is>
-          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-09-14 19:30 · UF 40,926.41 · 4,546 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-18 19:14 · UF 40,959.07 · 4,540 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>CAMBIO: monto UF 122268.0-&gt;122171.0</t>
+          <t>CAMBIO: monto UF 122171.0-&gt;122073.0</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M3" s="20" t="n">
-        <v>122171</v>
+        <v>122073</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>53</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="J2" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="J3" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J4" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="J6" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122171</v>
+        <v>122073</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -1684,11 +1684,11 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="J12" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1792,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1873,21 +1873,21 @@
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="11" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TASACIÓN COMERCIAL INMUEBLE DAEM OLIVAR</t>
+          <t>SERVICIO DE TASACIÓN DE BIEN INMUEBLE</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Región del Biobío</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>CLP 2,000,000</t>
+          <t>CLP 400,000</t>
         </is>
       </c>
       <c r="G2" s="11" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
@@ -1910,17 +1910,17 @@
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>2026-09-15 12:00</t>
+          <t>2026-09-25 09:00</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
-          <t>bajo umbral de monto (Nacional, UF 49 (umbral UF 2.000))</t>
+          <t>bajo umbral de monto (Nacional, UF 10 (umbral UF 2.000))</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
-          <t>923000-18-L126</t>
+          <t>4055-74-L126</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
@@ -1929,8 +1929,66 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>ARRIENDO DE INMUEBLE PARA GABINETE PSICOTECNICO</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ERCILLA</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Región de la Araucanía</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>CLP 14,400,000</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>352</v>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>100-1.000 UTM (~UF 170-1.700)</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>bajo umbral de monto (Nacional, UF 352 (umbral UF 2.000))</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>4306-34-LE26</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>Ver ficha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Estas licitaciones SI calzan con el servicio, pero quedan fuera por monto o plazo. Ojo: Mercado Publico publica el valor del CONTRATO (honorario), no el valor del activo — una tasacion de un edificio grande puede aparecer como UF 73. Revisar antes de descartar.</t>
         </is>
@@ -1939,6 +1997,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1950,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2044,92 +2103,92 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>1026727-12-LE26</t>
+          <t>1027-15-LP26</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de equipamiento prototipado para el CFT</t>
+          <t>Servicio de Mantención Reparación y Habilitación de Campamentos Móviles Talleres y Bodegas de la Administración Directa en la Provincia de Huasco Región de Atacama.</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>1027-15-LP26</t>
+          <t>1035685-19-LE26</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Mantención Reparación y Habilitación de Campamentos Móviles Talleres y Bodegas de la Administración Directa en la Provincia de Huasco Región de Atacama.</t>
+          <t>Ampliación de Espacio Académico Sede Panguipulli</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>1035-22-L126</t>
+          <t>1036569-10-LP26</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Trabajos menores Casa Fiscal Conaf Pichilemu Region de O"Higgins</t>
+          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1035685-19-LE26</t>
+          <t>1039-7-LR26</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Ampliación de Espacio Académico Sede Panguipulli</t>
+          <t>SERVICIO  DE ARRIENDO DE EQUIPO MECANIZADO</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1036569-10-LP26</t>
+          <t>1040538-15-L126</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO: EQUIPAMIENTO REHABILITACIÓN TELETÓN</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE MONTAJE, HABILITACIÓN Y APOYO LOGÍSTICO PARA ACTIVIDAD EN NEVADOS DE CHILLÁN</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
@@ -2144,32 +2203,32 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1039-7-LR26</t>
+          <t>1057049-322-I226</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO  DE ARRIENDO DE EQUIPO MECANIZADO</t>
+          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1040538-15-L126</t>
+          <t>1057049-328-LR26</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE MONTAJE, HABILITACIÓN Y APOYO LOGÍSTICO PARA ACTIVIDAD EN NEVADOS DE CHILLÁN</t>
+          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -2184,12 +2243,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1040538-16-L126</t>
+          <t>1057049-329-LE26</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Servicio integral para la obtención, coordinación y habilitación del derecho de   participación de la Región de Ñuble dentro del stand de Chile en FIT Buenos   Aires 2026</t>
+          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -2204,72 +2263,72 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1042-11-LE26</t>
+          <t>1057402-144-LP26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Serv. traslado marítimo para faenas en Isla Mocha</t>
+          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1051173-11-LE26</t>
+          <t>1057417-186-LP26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE DEPENDENCIAS</t>
+          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057049-322-I226</t>
+          <t>1057429-85-LE26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS PARA BIOLOGIA MOLECULAR CON COMODATO DE EQUIPOS LABORATORIO CENTRAL</t>
+          <t>EJECUCIÓN DE RADIER PARA BODEGA DE FARMACIA</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057049-328-LR26</t>
+          <t>1057429-86-LE26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>SHV SUMINISTRO DE REACTIVOS DE AUTOINMUNIDAD CON EQUIPOS EN COMODATO LABORATORIO CENTRAL</t>
+          <t>ARRIENDO DE SETS DE MOTORES QUIRÚRGICOS</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
@@ -2284,12 +2343,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057049-329-LE26</t>
+          <t>1057472-101-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
+          <t>ARRIENDO DE ENDOSCOPIOS</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2304,32 +2363,32 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057486-21-LE26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>Servicio de rehabilitación psicosocial tipo I y II</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057417-186-LP26</t>
+          <t>1057489-285-LP26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
+          <t>Arriendo de Huelleros digitales y Pistola Escáner</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -2344,52 +2403,52 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057420-37-LP26</t>
+          <t>1057491-177-LP26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO PARA EL SERVICIO DE TRASLADO DE FUNCIONARIOS EN ACTIVIDADES DOMICILIARIAS Y TERRENO DEL HOSPITAL DE LA FAMILIA Y LA COMUNIDAD DE HUÉPIL POR EL PERIODO DE 24 MESES 3ER LLAMADO</t>
+          <t>ARRIENDO DE INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057429-85-LE26</t>
+          <t>1057491-178-LP26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>EJECUCIÓN DE RADIER PARA BODEGA DE FARMACIA</t>
+          <t>EXAMENES POR CITOMETRIA DE FLUJO CON COMODATO</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057429-86-LE26</t>
+          <t>1057492-121-LE26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SETS DE MOTORES QUIRÚRGICOS</t>
+          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2404,12 +2463,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057480-46-LR26</t>
+          <t>1057492-123-LE26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Servicio externo de traslado de pacientes para El Hospital San José de Melipilla </t>
+          <t>SUMINISTRO DE BAJADAS PARA BOMBA PCA CON ENTREGA DE EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -2424,12 +2483,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057486-21-LE26</t>
+          <t>1057492-128-LP26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Servicio de rehabilitación psicosocial tipo I y II</t>
+          <t>SERVICIO ARRIENDO DE LAVADORA TERMODESINFECTADORA</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2444,12 +2503,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057489-285-LP26</t>
+          <t>1057494-60-LE26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de Huelleros digitales y Pistola Escáner</t>
+          <t>SUMINISTRO DE DRENAJES DE HERIDAS CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -2464,12 +2523,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057492-121-LE26</t>
+          <t>1057501-395-LR26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
+          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
@@ -2484,12 +2543,12 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057492-123-LE26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE BAJADAS PARA BOMBA PCA CON ENTREGA DE EQUIPOS EN COMODATO</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
@@ -2504,32 +2563,32 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057492-128-LP26</t>
+          <t>1057501-473-LE26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO DE LAVADORA TERMODESINFECTADORA</t>
+          <t>Habilitación para Instalacion de Food Truck HSR</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057494-60-LE26</t>
+          <t>1057501-477-LP26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE DRENAJES DE HERIDAS CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
+          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -2544,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057501-395-LR26</t>
+          <t>1057501-493-LP26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
+          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
@@ -2564,12 +2623,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057503-137-LR26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>Adquisición de Test Reportado de Orina Completa y Sedimentos Urinarios Automatizados con Equipamiento en Comodato para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -2584,72 +2643,72 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057501-462-LE26</t>
+          <t>1057509-269-LP26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SALA PACIENTES MATERNIDAD HSR</t>
+          <t>CONVENIO CONTRATACIÓN DE SERVICIOS DE APOYO PROFESIONALY TÉCNICO PARA EL DEPARTAMENTO DE EQUIPAMIENTO CLÍNICO DEL HOSPITAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057501-473-LE26</t>
+          <t>1057509-275-LP26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Habilitación para Instalacion de Food Truck HSR</t>
+          <t>CONVENIO COMPRA DE SERVICIOS PARA TÉCNICOS DE BODEGA DE GASES CLÍNICOS</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057509-292-LE26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>“CONVENIO COMPRA SERVICIOS DE PROFESIONAL APOYO AL PROCESO DE GESTIÓN AL SISTEMA DE GESTIÓN DE COSTOS PARA EL DEPARTAMENTO DE FINANZAS” brd</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057511-28-LE26</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t xml:space="preserve">COMPRA DE SERVICIOS DE TRASLADO HODOM POR CAMPAÑA </t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -2664,12 +2723,12 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1057508-112-LE26</t>
+          <t>1057539-129-LP26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIPOS PARA EL SERVICIO  DE ATENCIÓN MÉDICA DE URGENCIA DEL SERVICIO  DE SALUD ÑUBLE</t>
+          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
@@ -2684,36 +2743,36 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1057509-269-LP26</t>
+          <t>1057547-350-LR26</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO CONTRATACIÓN DE SERVICIOS DE APOYO PROFESIONALY TÉCNICO PARA EL DEPARTAMENTO DE EQUIPAMIENTO CLÍNICO DEL HOSPITAL REGIONAL DE ÑUBLE</t>
+          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1057509-292-LE26</t>
+          <t>1057552-19-LE26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>“CONVENIO COMPRA SERVICIOS DE PROFESIONAL APOYO AL PROCESO DE GESTIÓN AL SISTEMA DE GESTIÓN DE COSTOS PARA EL DEPARTAMENTO DE FINANZAS” brd</t>
+          <t>Convenio de Suministro Materiales de Oficina</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
@@ -2724,12 +2783,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1057511-28-LE26</t>
+          <t>1057898-95-LE26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPRA DE SERVICIOS DE TRASLADO HODOM POR CAMPAÑA </t>
+          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
@@ -2744,72 +2803,72 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1057539-129-LP26</t>
+          <t>1057962-9-LE26</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
+          <t>CAMBIOS DE VENTANAS PARA EDIFICIO PRINCIPAL Y OTROS ESTABLECIMIENTOS SSC</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1057977-14-LE26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1057552-19-LE26</t>
+          <t>1058012-28-LE26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Convenio de Suministro Materiales de Oficina</t>
+          <t>MEDICAMENTO SEVOFLURANO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1057898-95-LE26</t>
+          <t>1058086-49-LP26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
+          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
@@ -2824,52 +2883,52 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1057962-9-LE26</t>
+          <t>1063538-222-LE26</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>CAMBIOS DE VENTANAS PARA EDIFICIO PRINCIPAL Y OTROS ESTABLECIMIENTOS SSC</t>
+          <t>SERVICIO DE ARRIENDO LÁMPARAS QUIRÚRGICAS DOBLE</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1057977-14-LE26</t>
+          <t>1070620-89-LP26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
+          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1058012-28-LE26</t>
+          <t>1070620-93-LP26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>MEDICAMENTO SEVOFLURANO CON EQUIPO EN COMODATO</t>
+          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -2884,12 +2943,12 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1058086-49-LP26</t>
+          <t>1070620-95-LE26</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
+          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
@@ -2904,12 +2963,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1070620-89-LP26</t>
+          <t>1070620-96-LP26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
+          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
@@ -2924,12 +2983,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1070620-93-LP26</t>
+          <t>1075963-370-LE26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
+          <t>ARRIENDO CON OPCION DE COMPRA SECADOR KAESER REFRIGERATIVO KYOSEC POR 3 MESES</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
@@ -2944,136 +3003,136 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1070620-95-LE26</t>
+          <t>1075963-403-L126</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
+          <t>ARRIENDO SISTEMA MONITOREO EN LINEA PARA REFRIGERADORES DE FARMACOS ONCOLOGICOS</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1070620-96-LP26</t>
+          <t>1076710-10-LP26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
+          <t xml:space="preserve">SUMINISTRO OFICINALES Y MAGISTRALES POR 12 MESES </t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1075963-370-LE26</t>
+          <t>1079445-41-LE26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CON OPCION DE COMPRA SECADOR KAESER REFRIGERATIVO KYOSEC POR 3 MESES</t>
+          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1075963-403-L126</t>
+          <t>1079445-42-LE26</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO SISTEMA MONITOREO EN LINEA PARA REFRIGERADORES DE FARMACOS ONCOLOGICOS</t>
+          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1079445-41-LE26</t>
+          <t>1079969-20-LE26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
+          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1079445-42-LE26</t>
+          <t>1082957-29-LE26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
+          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1079969-19-LP26</t>
+          <t>1085111-23-O126</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>CAMBIO DE CUBIERTA Y MEJORAMIENTO GALPÓN O.S.11.</t>
+          <t>CONSERVACIÓN TECHUMBRE EDIFICIO SERVIU ÑUBLE</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
@@ -3084,52 +3143,52 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1079969-20-LE26</t>
+          <t>1095-10-LE26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
+          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1082957-29-LE26</t>
+          <t>1095-11-LE26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
+          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1095-10-LE26</t>
+          <t>1096-15-O126</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
+          <t>ATIF HABILITACIÓN CALLE DE RODAJE ALFA Y OBRAS ANEXAS AEROPUERTO PUNTA AREN</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
@@ -3144,12 +3203,12 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1095-11-LE26</t>
+          <t>1106-22-LP26</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
+          <t>Serv Arriendo Eq para faenas de Colocacion asfalto</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
@@ -3164,36 +3223,36 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1107276-25-LE26</t>
+          <t>1116006-4-LE26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN TRASLADO E INSTALACIÓN DE SISTEMA MOD</t>
+          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1116006-4-LE26</t>
+          <t>1126922-36-LP26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
+          <t>CONTRATO SUMINISTRO MAT PEDAGOGICOS Y OFICINA</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
@@ -3204,36 +3263,36 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1171317-10-LP26</t>
+          <t>1129-7-L126</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCIÓN SEDE SOCIAL AGRUPACIÓN DE MOTOQUEROS CHILLÁN </t>
+          <t>SERVICIO DE ARRIENDO Y MANTENCIÓN DE 2 (DOS) DISPENSADORES DE AGUA PURIFICADA CONECTADOS A LA RED DE AGUA POTABLE CON INSTALACION INCLUIDA POR UN PERÍODO DE 36 MESES.</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1175-71-LP26</t>
+          <t>1171317-10-LP26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
+          <t xml:space="preserve">CONSTRUCCIÓN SEDE SOCIAL AGRUPACIÓN DE MOTOQUEROS CHILLÁN </t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
@@ -3244,76 +3303,76 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1175-74-LP26</t>
+          <t>1175-71-LP26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
+          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1186229-28-LE26</t>
+          <t>1175-74-LP26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
+          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1197594-17-LE26</t>
+          <t>1180730-38-LE26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORIA PLAN MAESTRO AREAS VERDES Y PAISAJISMO</t>
+          <t>BOLSOS DE TERRENO ESPECIALIDAD CESFAM 18</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1198-33-LE26</t>
+          <t>1186229-28-LE26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
+          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
@@ -3324,16 +3383,16 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1209403-8-L126</t>
+          <t>1197-21-L126</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SERVICIO DE DISEÑO, CONSTRUCCIÓN Y CERTIFICACIÓN DE RED DE GAS EN DEPENDENCIAS RESIDENCIA FAMILIAR 18 DE SEPTIEMBRE</t>
+          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
@@ -3344,52 +3403,52 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1197594-17-LE26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>CONSULTORIA PLAN MAESTRO AREAS VERDES Y PAISAJISMO</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1224953-26-LE26</t>
+          <t>1198-33-LE26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>Rehabilitación oral mediante prótesis removibles</t>
+          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1239966-10-LE26</t>
+          <t>1208100-8-LP26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CENTRO AIDIA DE PUERTO NATALES</t>
+          <t xml:space="preserve">SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE EVALUACIÓN FORMATIVA PARA LA ADOPCIÓN Y EL ACOGIMIENTO UEFAA Y RESIDENCIA FAMILIAR DE ADOLESCENTES DE MACHALÍ </t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
@@ -3404,12 +3463,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1256505-28-LE26</t>
+          <t>1216085-59-LP26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
+          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
@@ -3424,12 +3483,12 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1261592-54-LE26</t>
+          <t>1224953-26-LE26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
+          <t>Rehabilitación oral mediante prótesis removibles</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
@@ -3444,32 +3503,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1224957-60-LE26</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t>CONSERVACION DE RECINTOS EDUCACIONALE</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1337-21-LE26</t>
+          <t>1239966-10-LE26</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO COSTERO DE PERSONAL DE ADMINISTRACIÓN DIRECTA</t>
+          <t>HABILITACION DE CENTRO AIDIA DE PUERTO NATALES</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
@@ -3484,16 +3543,16 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1340-51-LE26</t>
+          <t>1247197-66-LP26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION Y REPARACION DE INSTALACIONES Cierre Perimetral Con pilar metálico y brazo soldado de 60x60 Malla Urbana Acmafor con 3 portones 6 metros Recinto PAC 001 Valdivia – Dirección de Vialidad Región de Los Ríos.</t>
+          <t>SUMINISTRO DE PRODUCTOS DE OFICINA PARA LA CORESAM</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
@@ -3504,72 +3563,72 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1346284-10-LE26</t>
+          <t>1256505-28-LE26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1346284-11-LE26</t>
+          <t>1261592-54-LE26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
+          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1348-5-LP26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1350296-80-LE26</t>
+          <t>1298354-27-LE26</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
+          <t>Conservación y Habilitación Salas y Muros</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
@@ -3584,132 +3643,132 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1351-6-LP26</t>
+          <t>1340-51-LE26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
+          <t>SERVICIO DE MANTENCION Y REPARACION DE INSTALACIONES Cierre Perimetral Con pilar metálico y brazo soldado de 60x60 Malla Urbana Acmafor con 3 portones 6 metros Recinto PAC 001 Valdivia – Dirección de Vialidad Región de Los Ríos.</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1374899-36-LP26</t>
+          <t>1346284-10-LE26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1375158-7-LP26</t>
+          <t>1346284-11-LE26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VEINTICUATRO 24 SIERRAS DE AUTOPSIA Y UN 01 PACK EQUIPOS DE REFRIGERACIÓNCONGELACIÓN PARA DEPARTAMENTO DE TANATOLOGÍA DEL NUEVO EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL DE SANTIAGO</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1375746-17-LP26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1391828-8-LE26</t>
+          <t>1350296-80-LE26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
+          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1417913-122-LE26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL EPP PARA FUNCIONARIOS Y ESTABLECIMIENTOS DEPENDIENTES DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1422824-1-LR26</t>
+          <t>1374899-36-LP26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE REACTIVOS PARA EXÁMENES BIOQUÍMICOS INMUNOENDOCRINOLÓGICOS Y SEROLOGICOS CON EQUIPAMIENTO Y SISTEMA INFORMÁTICO DE LABORATORIO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
@@ -3724,96 +3783,96 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1422824-25-LP26</t>
+          <t>1375158-7-LP26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>ADQUISICIÓN DE VEINTICUATRO 24 SIERRAS DE AUTOPSIA Y UN 01 PACK EQUIPOS DE REFRIGERACIÓNCONGELACIÓN PARA DEPARTAMENTO DE TANATOLOGÍA DEL NUEVO EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL DE SANTIAGO</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1422832-9-LR26</t>
+          <t>1375746-17-LP26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERVICIOS DE ARRENDAMIENTO DE NEUROMONITOREO INTRAOPERATORIO ASPIRADOR ULTRASÓNICO KIT PARA NEUROTOMIA LUMBAR POR RADIOFRECUENCIA PARA EL SERVICIO DE NEUROCIRUGIA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1431841-56-LP26</t>
+          <t>1391828-8-LE26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
+          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1431841-57-LE26</t>
+          <t>1417913-116-LE26</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
+          <t>ADQUISICIÓN DE EQUIPOS TECNOLÓGICOS PARA DEPENDENCIAS DE CORMUDESI</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>1443-1-LE26</t>
+          <t>1417913-119-LE26</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje y almacenamiento</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO PARA LA EJECUCIÓN Y FORTALECIMIENTO DE PROGRAMAS DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
@@ -3824,52 +3883,52 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1469101-6-LP26</t>
+          <t>1417913-122-LE26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
+          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL EPP PARA FUNCIONARIOS Y ESTABLECIMIENTOS DEPENDIENTES DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>1469-205-L126</t>
+          <t>1422824-10-LE26</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
+          <t>CONTRATO DE SUMINISTRO DE CINTAS PARA PRUEBA DEL BIOSENSOR DE CREATININA CON EQUIPO EN COMODATO PARA LA UNIDAD DE IMAGENOLOGÍA COMPLEJA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>1469-211-L126</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>MATERIAL GRÁFICO, TRASLADO, MONTAJE, INSTALACION, SUPERVISIÓN, DESMONTAJE Y RETIRO PARA UTALCA ABRE PUERTAS 2026, UNIVERSIDAD DE TALCA</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
@@ -3884,92 +3943,92 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>1499887-19-CO26</t>
+          <t>1431841-56-LP26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS TÉCNICOS DE HABILITACIÓN DIGITAL</t>
+          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>1533460-6-LP26</t>
+          <t>1431841-57-LE26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE SISTEMA INFORMÁTICO FINANCIERO CONTABLE Y RECURSOS HUMANOS</t>
+          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>1537592-17-LE26</t>
+          <t>1469101-6-LP26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Elementos de Seguridad Protección Personal y Equipamiento para Trabajos en Terreno</t>
+          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>1540667-6-LR26</t>
+          <t>1469-205-L126</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
+          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1469-211-L126</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>MATERIAL GRÁFICO, TRASLADO, MONTAJE, INSTALACION, SUPERVISIÓN, DESMONTAJE Y RETIRO PARA UTALCA ABRE PUERTAS 2026, UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
@@ -3984,12 +4043,12 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>1549-85-LE26</t>
+          <t>1483330-1-LP26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
+          <t>SERVICIO DE ARRIENDO IMPLEMENTACIÓN Y MANTENCIÓN</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
@@ -4004,12 +4063,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>1555-75-LP26</t>
+          <t>1499887-19-CO26</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
+          <t>SERVICIOS TÉCNICOS DE HABILITACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
@@ -4024,112 +4083,112 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>1562-57-L126</t>
+          <t>1523-123-LE26</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
+          <t>PPTA 127-26 SERVICIO DE TRASLADO PARA PACIENTES DE</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>1562-59-L126</t>
+          <t>1533460-6-LP26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
+          <t>SERVICIO DE ARRIENDO DE SISTEMA INFORMÁTICO FINANCIERO CONTABLE Y RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>1562-60-LR26</t>
+          <t>1540667-6-LR26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
+          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>1574-33-LP26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>1575-14-LE26</t>
+          <t>1549-85-LE26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>MANTENCION DE OFICINAS</t>
+          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>1643-75-LE26</t>
+          <t>1549-90-LP26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
+          <t>ARRIENDO DE 14 SILLONES DE HEMODIÁLISIS</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
@@ -4144,36 +4203,36 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>1657-17-L126</t>
+          <t>1555-75-LP26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
+          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>1696-15-LE26</t>
+          <t>1562-57-L126</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
+          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
@@ -4184,56 +4243,56 @@
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>1697-40-LR26</t>
+          <t>1562-59-L126</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO TRASLADO DE PERSONAS PARA EL CINJ</t>
+          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>1735-50-LE26</t>
+          <t>1562-60-LR26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CEFAM DE CONTINGENCIA 3ra. ETAPA TUB</t>
+          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>1743-69-LP26</t>
+          <t>1574-33-LP26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Manquehua</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
@@ -4244,92 +4303,92 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>1810-3-LE26</t>
+          <t>1574-34-LE26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
+          <t>CHEE MANT. EMERGENCIA ELQUI REG. COQUIMBO J.I. Y OFICINAS - SC 61183</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>1894-25-LP26</t>
+          <t>1574-35-LP26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 2</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>1947-113-LR26</t>
+          <t>1575-14-LE26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE NUTRICIONES PARENTERALES DE DIFERENTES VOLÚMENES CON BAJADAS DE BOMBA DE INFUSIÓN Y EQUIPOS EN COMODATO PARA EL HOSPITAL ROBERTO DEL RÍO CFO</t>
+          <t>MANTENCION DE OFICINAS</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>1947-157-LE26</t>
+          <t>1596-50-LP26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
+          <t>PANTALLA LED PARA EL EDIFICIO DEL GORE MAULE</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>1947-168-LE26</t>
+          <t>1643-75-LE26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
@@ -4344,52 +4403,52 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>1969-18-LE26</t>
+          <t>1657-17-L126</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
+          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>1973-97-LP26</t>
+          <t>1696-15-LE26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
+          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>1979-192-LE26</t>
+          <t>1735-50-LE26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>175.26 “ARRIENDO DE EQUIPOS PARA PABELLÓN GINECOLOGICO PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+          <t>HABILITACION CEFAM DE CONTINGENCIA 3ra. ETAPA TUB</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
@@ -4404,16 +4463,16 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>2020-19-LE26</t>
+          <t>1743-69-LP26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
+          <t>Construcción Sede Social Manquehua</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
@@ -4424,172 +4483,172 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>2062-5-L126</t>
+          <t>1754-45-LE26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Coffe Break , almuerzo, arriendo de salón y Equipamiento  para "Jornada de Reconocimiento a Maestros de Maestros de la Provincia de Cachapoal"</t>
+          <t>OFICINA TIMBRES DIDÁCTICO MENAJE Y PILAS</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>2098-122-LP26</t>
+          <t>1810-3-LE26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
+          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>2098-133-LP26</t>
+          <t>1894-25-LP26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PAQUETES DE PARTO Y PAQUETES DE CIRUGÍA UNIVERSAL PARA REPOSICIÓN BODEGA FOLIO PAC 156 – PARA UN PERIODO DE 18 MESES</t>
+          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>2098-134-LP26</t>
+          <t>1947-113-LR26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO CLORHEXIDINAS ALCOHOL AL 70% POVIDONAS Y VASELINA LÍQUIDA PARA REPOSICIÓN BODEGA FOLIO PAC 159 – PARA UN PERIODO DE 24 MESES</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE NUTRICIONES PARENTERALES DE DIFERENTES VOLÚMENES CON BAJADAS DE BOMBA DE INFUSIÓN Y EQUIPOS EN COMODATO PARA EL HOSPITAL ROBERTO DEL RÍO CFO</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>2098-139-LE26</t>
+          <t>1947-157-LE26</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO BOLSAS DE ASPIRACIÓN PARA REPOSICIÓN BODEGA FOLIO PAC 200 – PARA UN PERIODO DE 18 MESES</t>
+          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>2102-31-LE26</t>
+          <t>1947-168-LE26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>2107-144-LP26</t>
+          <t>1969-18-LE26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
+          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>2109-10-LP26</t>
+          <t>1973-97-LP26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE FOTOCOPIADO IMPRESIÓN Y ESCANEO CON EQUIPOS EN COMODATO</t>
+          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>2176-55-LE26</t>
+          <t>1979-192-LE26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>PASAJES Y SERV. TRASLADO STGO-ISLA JUAN FERNANDEZ-STGO</t>
+          <t>175.26 “ARRIENDO DE EQUIPOS PARA PABELLÓN GINECOLOGICO PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
@@ -4604,72 +4663,72 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>2179-14-LE26</t>
+          <t>1987-5-LE26</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
+          <t>LP ARRIENDO UNID. MODULARES CONTAO RES EX LAGOS 805-2026 17.09.26 I. 22.09.001</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2205-14-LE26</t>
+          <t>2020-19-LE26</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
+          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2258-168-LE26</t>
+          <t>2048-73-LP26</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MAPEO TERMICO DE BODEGAS DEL HRA.</t>
+          <t>Servicio de traslado para pacientes H.A.</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2258-175-LR26</t>
+          <t>2078-45-LE26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
+          <t>APRUEBA Y PUBLICA BASES ADMINISTRATIVAS PARA “SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS CONCEPCIÓN Y DELEGACIÓN BIOBIO AMBAS DEPENDIENTE DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO”. SC 283-2026 y 377-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
@@ -4684,12 +4743,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2098-122-LP26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
@@ -4704,16 +4763,16 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2279-56-LE26</t>
+          <t>2098-139-LE26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
+          <t>CONVENIO SUMINISTRO BOLSAS DE ASPIRACIÓN PARA REPOSICIÓN BODEGA FOLIO PAC 200 – PARA UN PERIODO DE 18 MESES</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
@@ -4724,52 +4783,52 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2279-66-LE26</t>
+          <t>2102-31-LE26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>SP 754 Servicio de Arriendo de Bodegas</t>
+          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2111-231-LE26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>ARRIENDO DE EQUIPOS DE MONITORIZACION PARA UTI</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
@@ -4784,156 +4843,156 @@
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2313-5-LE26</t>
+          <t>2111-270-LP26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>Servicios de Conservación de Edificio Terminal</t>
+          <t>MANTAS TÉRMICAS CON EQUIPO EN COMODATO III</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2322-82-LE26</t>
+          <t>2111-282-LP26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
+          <t>FRESAS NEUROCIRUGÍA Y COLUMNA EQUIPO COMODATO III</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2324-112-LE26</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2332-106-L126</t>
+          <t>2205-14-LE26</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO PREVENTIVO PARA LAVADORA DEL CESFAM ANTONIO VARAS PERTENECIENTE AL DEPARTAMENTO DE SALUD MUNICIPAL DE PUERTO MONTT</t>
+          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2332-112-L126</t>
+          <t>2258-175-LR26</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE HERRAMIENTAS PARA UNIDAD DE OPERACIONES DEL DEPARTAMENTO DE SALUD MUNICIPAL</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2332-70-LE26</t>
+          <t>2258-37-LR26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>CS DE ARRIENDO DE APLICACION DE AGENDA VIRTUAL</t>
+          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2273-58-LE26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>REHABILITACIÓN SKATE PARK LO MARTÍNEZ</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2279-56-LE26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
@@ -4944,76 +5003,76 @@
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2378-110-LP26</t>
+          <t>2279-66-LE26</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
+          <t>SP 754 Servicio de Arriendo de Bodegas</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2385-53-LE26</t>
+          <t>2282-97-LR26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE CARGADOR FRONTAL CON OPERADOR</t>
+          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2408-152-LE26</t>
+          <t>2313-5-LE26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL PARA TRABAJOS EN TERRENO</t>
+          <t>Servicios de Conservación de Edificio Terminal</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
@@ -5024,12 +5083,12 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2408-160-LP26</t>
+          <t>2322-82-LE26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
@@ -5044,76 +5103,76 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2408-98-LE26</t>
+          <t>2324-112-LE26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>Contrato de Suministro para el Servicio de Mantención de Carpetas de Pasto Sintético Departamento de Desarrollo Deportivo – Municipalidad de Los Ángeles</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2409-96-L126</t>
+          <t>2332-70-LE26</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA ALUMNAS TALLER DE EXTRAESCOLAR Y JORNADAS DE REFLEXION PARA ESCUELA D-953</t>
+          <t>CS DE ARRIENDO DE APLICACION DE AGENDA VIRTUAL</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2410-41-LE26</t>
+          <t>2345-117-LP26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
+          <t>ARRIENDO Y MANTENCIÓN DE EQUIPOS PSICOTÉCNICOS Y SENSOMÉTRICOS PARA LA MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2411-14-L126</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION MATERIALES VARIOS DE USO O CONSUMO PARA DEPARTAMENTO CEMENTERIO</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
@@ -5124,12 +5183,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
@@ -5144,72 +5203,72 @@
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2426-44-LE26</t>
+          <t>2378-110-LP26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
+          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2428-70-LP26</t>
+          <t>2385-53-LE26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE OFICINA MOVIL -SOCIAL</t>
+          <t>SERVICIO DE ARRIENDO DE CARGADOR FRONTAL CON OPERADOR</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2429-8-LP26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN DE INFRAESTRUCTURA DE RED INFORMÁTICA Y NORMALIZACIÓN DE CABLEADO ESTRUCTURADO DE LAS DEPENDENCIAS DE LA IMA</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2430-59-LP26</t>
+          <t>2409-96-L126</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
+          <t>SERVICIO DE TRASLADO PARA ALUMNAS TALLER DE EXTRAESCOLAR Y JORNADAS DE REFLEXION PARA ESCUELA D-953</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
@@ -5224,56 +5283,56 @@
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2430-68-LR26</t>
+          <t>2409-97-L126</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
+          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2430-77-LP26</t>
+          <t>2409-98-L126</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL EL ANCLA ANTOFAGASTA CÓDIGO BIP N°40073719-0</t>
+          <t>SERVICIO TRASLADO ALUMNAS A JORNADAS REFLEXION, ESCUELA D-926</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2430-78-LP26</t>
+          <t>2410-41-LE26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
+          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
@@ -5284,36 +5343,36 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2445-115-LE26</t>
+          <t>2426-41-LE26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
+          <t>Obras de reforzamiento edificio Nasro Maluk</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>2426-44-LE26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
@@ -5324,32 +5383,32 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2446-257-LE26</t>
+          <t>2428-70-LP26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
+          <t>SERVICIO DE ARRIENDO DE OFICINA MOVIL -SOCIAL</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 22 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2446-260-LR26</t>
+          <t>2429-8-LP26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
+          <t>RENOVACIÓN DE INFRAESTRUCTURA DE RED INFORMÁTICA Y NORMALIZACIÓN DE CABLEADO ESTRUCTURADO DE LAS DEPENDENCIAS DE LA IMA</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
@@ -5364,72 +5423,72 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2446-266-LP26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN CASA MAC AULIFFE</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2448-133-LE26</t>
+          <t>2430-68-LR26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINA MODULAR CECOSF PUNTA MIRA</t>
+          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>2430-77-LP26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>MEJORAMIENTO SEDE SOCIAL EL ANCLA ANTOFAGASTA CÓDIGO BIP N°40073719-0</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2460-108-LE26</t>
+          <t>2430-78-LP26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
+          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
@@ -5444,32 +5503,32 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2460-121-LE26</t>
+          <t>2445-115-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
+          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2483-242-CO26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
@@ -5484,52 +5543,52 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>2446-257-LE26</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>2446-260-LR26</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>2581-36-LE26</t>
+          <t>2446-266-LP26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
+          <t>MANTENCIÓN CASA MAC AULIFFE</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
@@ -5544,76 +5603,76 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>2446-271-LR26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>REHABILITACION CASA DE LA CULTURA</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>2591-106-LR26</t>
+          <t>2448-133-LE26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>REPOSICION OFICINA SRCEI POZO ALMONTE</t>
+          <t>HABILITACION OFICINA MODULAR CECOSF PUNTA MIRA</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>2460-108-LE26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
@@ -5624,36 +5683,36 @@
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>2460-121-LE26</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>2667-83-LE26</t>
+          <t>2467-100-L126</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
+          <t>NUEVO LLAMADO ADQUISICIÓN CON INSTALACION DE CORTINAS ROLLER DOBLE BLACKOUT  SCREEN PARA TERCER PISO EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
@@ -5664,12 +5723,12 @@
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>2667-90-LE26</t>
+          <t>2483-242-CO26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
+          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
@@ -5684,32 +5743,32 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>2687-16-CO26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE VENTANAS TERMOPANEL ESCUELA BÁSICA RURAL EL YECO</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>2710-55-LE26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO TOTEM</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
@@ -5724,12 +5783,12 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>2581-36-LE26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
@@ -5744,52 +5803,52 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>2784-44-LE26</t>
+          <t>2582-53-LR26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO DE  ESPECIALIDADES EDIFICIO CONSISTORIAL</t>
+          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>2794-22-LR26</t>
+          <t>2585-119-LE26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
+          <t>ADQ. SERV TRASLADO TERRESTRE NAC DIDECO ORD N°3042 IMA CRC</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>2817-63-LE26</t>
+          <t>2591-106-LR26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
+          <t>REPOSICION OFICINA SRCEI POZO ALMONTE</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
@@ -5804,52 +5863,52 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>2591-156-B226</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>2906-18-LE26</t>
+          <t>2600-26-LR26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
+          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>2920-38-LP26</t>
+          <t>2600-29-LE26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Juventud Robinsoniana.</t>
+          <t>Const. accesibilidad universal Edificio Municipal</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
@@ -5864,16 +5923,16 @@
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>2950-44-LP26</t>
+          <t>2627-18-LR26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
+          <t>MEJORAMIENTO RECINTO CLUB DEPORTIVO INTERSPORTING</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
@@ -5884,132 +5943,132 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>29-64-LP26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>GTM 54-2026 SERVICIO DE REPOSICIÓN DE VENTANAS</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>2974-71-L126</t>
+          <t>2667-71-LR26</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TALA DE ÁRBOL EN CASA DE HUESPEDES TANTAUCO (512/2026)</t>
+          <t>ARRIENDO SOPORTE Y MANTENCIÓN DE CENTRAL TELEFONICA IP TELEFONOS IP Y PLATAFORMA DE CONTACT CENTER</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>2667-83-LE26</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>2667-90-LE26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>299-17-LP26</t>
+          <t>2687-16-CO26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>E102RT9BRANDING Y ORNAMENTACION RECINTOS LOS RIOS</t>
+          <t>REPOSICIÓN DE VENTANAS TERMOPANEL ESCUELA BÁSICA RURAL EL YECO</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>3015-52-LE26</t>
+          <t>2710-55-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE DESAGÜES EN SECTORES DE LA CRUZ</t>
+          <t>SERVICIO DE ARRIENDO TOTEM</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>3016-52-LE26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Suministro Trofeos Galvanos Placas y Otros para Actividades Municipales del Área de Gestión Municipal Departamento de Salud y Departamento de Educación</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
@@ -6024,76 +6083,76 @@
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>3046-25-LE26</t>
+          <t>2732-34-LP26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>DL-34 SERVICIO DE MEJORAMIENTO DEL SISTEMA DE CALEFACCION DE EDIFICIO ADMINISTRATIVO</t>
+          <t>Serv. Arriendo de Baños Químicos Ferias Libres</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>3047-54-LE26</t>
+          <t>2733-18-LE26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
+          <t>Serv.habilitación Sala Sensorial-Liceo Peñaflor</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>2760-113-LE26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PMU 2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>3117-88-LE26</t>
+          <t>2760-115-LE26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>OFICINA Y BODEGA MODULAR C.R. LAS SALINAS</t>
+          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PRO EMPLEO</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
@@ -6104,92 +6163,92 @@
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>3172-68-LE26</t>
+          <t>2794-22-LR26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MAT. DEPENDENCIAS 2DO. NIVEL ASESORÍA DIGCAR</t>
+          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>2817-63-LE26</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>3290-8-LE26</t>
+          <t>2831-37-LE26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS EXPO QTA</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>3328-100-L126</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>ASB/PROVISIÒN E INSTALACIÒN DE VENTANAS TIPO TERMOPANEL CRT</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>3333-41-LE26</t>
+          <t>2906-18-LE26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA EQUIPO RED LOCAL 2026</t>
+          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
@@ -6204,76 +6263,76 @@
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>3355-9-LP26</t>
+          <t>2920-38-LP26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE EQUIPAMIENTO HIDROELÉCTRICO Y SERVICIO DE RECUPERACIÓN HABILITACIÓN Y PUESTA EN MARCHA DE LA MICRO CENTRAL ELÉCTRICA DEL REFUGIO MILITAR LOS BARROS </t>
+          <t>Construcción Sede Juventud Robinsoniana.</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>3384-20-LP26</t>
+          <t>2950-44-LP26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
+          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>3474-53-LE26</t>
+          <t>2974-71-L126</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO Y MANT. MAQUINAS FOTOCOPIADO</t>
+          <t>SERVICIO DE TALA DE ÁRBOL EN CASA DE HUESPEDES TANTAUCO (512/2026)</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>3525-8-LR26</t>
+          <t>2974-73-L126</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>Sum e instalación de taludes visita terreno volun</t>
+          <t>(DIS) PROVISIÓN E INSTALACIÓN DE CHAPA Y PERILLÓNES PARA EL INMUEBLE DE CAMINO LA VIÑA N° 12.130(535/2026)</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
@@ -6284,32 +6343,32 @@
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>3587-20-LE26</t>
+          <t>2981-235-LP26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN MANTENIMIENTO PREVENTIVO CORRECTIVO Y SOPORTES PARA EQUIPOS RADIOCOMUNICACIONES DEPARTAMENTO DE SALUD MUNICIPAL</t>
+          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>359-106-LE26</t>
+          <t>2981-236-LR26</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
+          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
@@ -6324,12 +6383,12 @@
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>3624-32-LP26</t>
+          <t>299-17-LP26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
+          <t>E102RT9BRANDING Y ORNAMENTACION RECINTOS LOS RIOS</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
@@ -6344,52 +6403,52 @@
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>3624-33-LP26</t>
+          <t>2992-49-LE26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
+          <t>habilitación sombra retractil en patio escuela</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>3671-61-LE26</t>
+          <t>3015-52-LE26</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">“SUMINISTRO DE OXÍGENO” PARA DEPENDENCIAS DE SALUD DE LA COMUNA DE CHILLÁN VIEJO. </t>
+          <t>HABILITACIÓN DE DESAGÜES EN SECTORES DE LA CRUZ</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>3678-22-LE26</t>
+          <t>3015-56-LP26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
+          <t>MEJ ACCESIBILIDAD Y ENTORNO SEDE SOCIAL TERRAVIDA</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
@@ -6404,16 +6463,16 @@
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>3693-158-LP26</t>
+          <t>3016-52-LE26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
+          <t>Servicio de Suministro Trofeos Galvanos Placas y Otros para Actividades Municipales del Área de Gestión Municipal Departamento de Salud y Departamento de Educación</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
@@ -6424,16 +6483,16 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>3708-39-LE26</t>
+          <t>3047-54-LE26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
+          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
@@ -6444,12 +6503,12 @@
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>3708-40-LE26</t>
+          <t>3084-31-LE26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS TRANSITO OBRAS Y OTRAS</t>
+          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
@@ -6464,56 +6523,56 @@
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>3761-21-LE26</t>
+          <t>3117-88-LE26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
+          <t>OFICINA Y BODEGA MODULAR C.R. LAS SALINAS</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>3775-33-LE26</t>
+          <t>3160-3-LE26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>SERV. ARRIENDO EXCAVADORA Y 2 MOTOBOMBAS HIJUELAS</t>
+          <t>SERVICIO DE CAMBIO DE TECHUMBRE DEL EDIFICIO COMMILDIRUNO</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>3798-19-LR26</t>
+          <t>3210-11-L126</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE TERRENO DE INFRAESTRUCTURA PÚBLICA</t>
+          <t>SERVICIO DE EXÁMENES DE FONDO DE OJO PARA USUARIOS DEL DEPARTAMENTO DE SALUD SAN RAFAEL</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
@@ -6524,176 +6583,176 @@
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>3836-37-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t>OFICINA MODULAR JUZGADO POLICIA LOCAL DE TOLTEN</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>3847-41-LE26</t>
+          <t>3290-8-LE26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
+          <t>HABILITACIÓN CTER PDI TEMUCO</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>3880-65-LE26</t>
+          <t>3328-100-L126</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>SEDE SOCIAL CLUB ADULTO MAYOR SECTOR EL PARRON</t>
+          <t>ASB/PROVISIÒN E INSTALACIÒN DE VENTANAS TIPO TERMOPANEL CRT</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>3885-51-LP26</t>
+          <t>3355-9-LP26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPAMIENTO HIDROELÉCTRICO Y SERVICIO DE RECUPERACIÓN HABILITACIÓN Y PUESTA EN MARCHA DE LA MICRO CENTRAL ELÉCTRICA DEL REFUGIO MILITAR LOS BARROS </t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>3889-41-LP26</t>
+          <t>3384-20-LP26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
+          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>3912-19-LP26</t>
+          <t>3474-53-LE26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>Construccion sede social los acacios</t>
+          <t>SERVICIO DE ARRIENDO Y MANT. MAQUINAS FOTOCOPIADO</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>3950-40-LE26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>3963-16-LP26</t>
+          <t>3542-23-LE26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
+          <t xml:space="preserve">ARRIENDO DE EXCAVADORA 20 TON SIN OPERADOR </t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>3997-59-B226</t>
+          <t>3542-26-LE26</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>ADECUACIÓN DEPARTAMENTO DE FINANZAS Y JUZGADO DE POLICÍA LOCAL EN EDIFICIO CONSISTORIAL DE LA MUNICIPALIDAD DE COLTAUCO</t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
@@ -6704,32 +6763,32 @@
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>4006-21-LE26</t>
+          <t>3587-20-LE26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>Mejoramiento Area Deportiva Ventanas</t>
+          <t>SERVICIO DE REPARACIÓN MANTENIMIENTO PREVENTIVO CORRECTIVO Y SOPORTES PARA EQUIPOS RADIOCOMUNICACIONES DEPARTAMENTO DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>4037-64-LE26</t>
+          <t>359-106-LE26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REGULARIZACION Y HABILITACION SALA APICOLA</t>
+          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
@@ -6744,36 +6803,36 @@
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>4055-69-L126</t>
+          <t>359-107-LE26</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE SERVICIO DE FORMACIÓN EN TERRENO PA</t>
+          <t>ROCURONIO BROMURO CON COMODATO DE EQUIPO</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>4063-1-LP26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
@@ -6784,16 +6843,16 @@
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>407-113-LP26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO Y CORRECTIVO DE GRUPOS ELECTRÓGENO EDIFICIO CAA Y PSIQUIATRÍA</t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
@@ -6804,36 +6863,36 @@
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>4099-25-LE26</t>
+          <t>3678-22-LE26</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Arriendo de Gestor Documental</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D243" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>411-43-CO26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN BODEGA MUNICIPAL SECTOR LA HUERTA</t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
@@ -6844,16 +6903,16 @@
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>4127-41-LE26</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t>[DIVAP] Estudio del bodegaje de ajuares</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D245" s="13" t="inlineStr">
         <is>
@@ -6864,52 +6923,52 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>4127-47-LE26</t>
+          <t>3708-40-LE26</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>[DIGEDEP] Curso Rehabilitación Oral</t>
+          <t>HABILITACION OFICINAS TRANSITO OBRAS Y OTRAS</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>4143-6-LE26</t>
+          <t>3761-21-LE26</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
+          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>418-57-LP26</t>
+          <t>3775-33-LE26</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
+          <t>SERV. ARRIENDO EXCAVADORA Y 2 MOTOBOMBAS HIJUELAS</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
@@ -6924,96 +6983,96 @@
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>418-60-LE26</t>
+          <t>3798-19-LR26</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIO AUXILIAR DE BODEGA</t>
+          <t>ADQUISICIÓN DE TERRENO DE INFRAESTRUCTURA PÚBLICA</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>4189-38-LE26</t>
+          <t>3836-37-LE26</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Ficha Técnica Fiesta de la Nalca 2026</t>
+          <t>OFICINA MODULAR JUZGADO POLICIA LOCAL DE TOLTEN</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>425-57-LR26</t>
+          <t>3847-41-LE26</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
+          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>4295-67-LP26</t>
+          <t>3880-65-LE26</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
+          <t>SEDE SOCIAL CLUB ADULTO MAYOR SECTOR EL PARRON</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>4306-32-LE26</t>
+          <t>3885-51-LP26</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION EQUIPAMIENTO CASA PROG. HABITABILIDAD</t>
+          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D253" s="13" t="inlineStr">
         <is>
@@ -7024,92 +7083,92 @@
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>4309-233-LP26</t>
+          <t>3889-41-LP26</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
+          <t>MEJORAMIENTO AREA VERDE Y SEDE VILLA CARRANZA</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>4328-33-B226</t>
+          <t>3908-44-LE26</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
+          <t>HABILITACIÓN Y SEÑALIZACIÓN PLAZOLETA RENÉ PINEDA Y MEJORAMIENTO PLAZA POBLACIÓN NUEVO VIVIR COMUNA DE RENAICO</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>4342-2-LP26</t>
+          <t>3912-19-LP26</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
+          <t>Construccion sede social los acacios</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>439-26-LP26</t>
+          <t>3950-40-LE26</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
+          <t>MEJORAMIENTO INTERNO EXTERNO Y LIMPIEZA DE TERRENO EN POSTA DE SALUD RURAL EN LOCALIDAD DE PUERTO AGUIRRE</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>4451-102-LE26</t>
+          <t>3963-16-LP26</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>Reparación de cubiertas de edificio Polideportivo</t>
+          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
@@ -7124,32 +7183,32 @@
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>4451-92-LE26</t>
+          <t>3994-29-LR26</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPO ELECTROGENO PARA ANIVERSARIO</t>
+          <t>CONST. SEDE Y ESPACIO COMUNITARIO GULTRO ORIENTE</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>4494-64-LP26</t>
+          <t>4037-64-LE26</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACION VIAL INCENDIOS FORESTALES LIRQUEN</t>
+          <t>SERVICIO REGULARIZACION Y HABILITACION SALA APICOLA</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
@@ -7164,32 +7223,32 @@
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>4494-65-LP26</t>
+          <t>4055-69-L126</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACION VIAL INCENDIOS FORESTALES PENCO</t>
+          <t>ADQUISICION DE SERVICIO DE FORMACIÓN EN TERRENO PA</t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>45-45-LR26</t>
+          <t>4063-1-LP26</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
+          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
@@ -7204,36 +7263,36 @@
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>45-48-LE26</t>
+          <t>4099-25-LE26</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
+          <t>Servicio de Arriendo de Gestor Documental</t>
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>4584-13-LE26</t>
+          <t>411-43-CO26</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
         <is>
-          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
+          <t>CONSTRUCCIÓN BODEGA MUNICIPAL SECTOR LA HUERTA</t>
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
@@ -7244,52 +7303,52 @@
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>4591-20-LP26</t>
+          <t>4127-41-LE26</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
         <is>
-          <t>arriendo tractor desbrozador Vialidad Prov. Colchagua.</t>
+          <t>[DIVAP] Estudio del bodegaje de ajuares</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D265" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>4623-5-L126</t>
+          <t>4127-47-LE26</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MANTENCIÓN DE OBRAS MENORES PARA LAS OFICINAS DEPENDIENTES DE LA DIRECCIÓN REGIONAL DEL TRABAJO DE BIOBÍO</t>
+          <t>[DIGEDEP] Curso Rehabilitación Oral</t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>4642-91-LP26</t>
+          <t>4143-6-LE26</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
+          <t>ADQ. MATERIAL Y ARRIENDO MAQUINA BACHEO PALMILLA</t>
         </is>
       </c>
       <c r="C267" s="11" t="n">
@@ -7304,92 +7363,92 @@
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>4686-30-LE26</t>
+          <t>418-57-LP26</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
         <is>
-          <t>Servicio de arrendamiento de bodegas</t>
+          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>483-47-L126</t>
+          <t>418-60-LE26</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
         <is>
-          <t>PROFESIONAL DE APOYO PARA LA OFICINA DE CALIDAD Y SEGURIDAD DEL PACIENTE REQUERIDOS POR EL HOSPITAL DR. HANS GRONEMANN GLAND (Hospital de Contulmo).</t>
+          <t>CONTRATACIÓN DE SERVICIO AUXILIAR DE BODEGA</t>
         </is>
       </c>
       <c r="C269" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D269" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>4887-28-E226</t>
+          <t>425-57-LR26</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
         <is>
-          <t>Obras de habilitación Centro de Creación Temuco</t>
+          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>4956-68-LP26</t>
+          <t>4295-67-LP26</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN LADERA SUR PONIENTE DEL CERRO COLOR</t>
+          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>4967-35-LP26</t>
+          <t>4295-82-LP26</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE CÁNULAS DE ALTO FLUJO CON EQUIPO EN COMODATO</t>
+          <t>ARRIENDO INSTALACIÓN Y MANTENCIÓN DE GABINETES PSICOTÉCNICOS 2026-2029</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
@@ -7404,32 +7463,32 @@
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>5048-51-O126</t>
+          <t>4306-32-LE26</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
         <is>
-          <t>AIF TRES VENTANAS TRAMO 2</t>
+          <t>ADQUISICION EQUIPAMIENTO CASA PROG. HABITABILIDAD</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>5056-108-LP26</t>
+          <t>4309-233-LP26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE REENVASADORA AUTOMÁTICA DE MEDICAMENTOS</t>
+          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
@@ -7444,92 +7503,92 @@
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>5240-102-LR26</t>
+          <t>4328-33-B226</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
+          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>5240-90-LR26</t>
+          <t>4342-2-LP26</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EMBALAJE MUDANZA Y TRANSPORTE</t>
+          <t>SERVICIOS PARA LAS DEPENDENCIAS DE LA DRMN</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>527481-62-LE26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE EL MOLLAR</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>528208-35-LP26</t>
+          <t>4451-102-LE26</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
+          <t>Reparación de cubiertas de edificio Polideportivo</t>
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>5349-90-LR26</t>
+          <t>4494-64-LP26</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES LIRQUEN</t>
         </is>
       </c>
       <c r="C279" s="11" t="n">
@@ -7544,32 +7603,32 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>539119-80-LP26</t>
+          <t>4494-65-LP26</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES PENCO</t>
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>539119-81-LE26</t>
+          <t>45-45-LR26</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN E IMPERMEABILIZACIÓN DE CUBIERTA DEL EDIFICIO NORAMBUENA ADMINISTRADO POR LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
         </is>
       </c>
       <c r="C281" s="11" t="n">
@@ -7584,16 +7643,16 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>539119-90-LE26</t>
+          <t>45-48-LE26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
         <is>
-          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
+          <t>SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
@@ -7604,16 +7663,16 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>5418-13-LE26</t>
+          <t>4584-13-LE26</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
         <is>
-          <t>Digitalización Documentos Almacenados Bodega</t>
+          <t>SEGUNDO LLAMADO MEJORAMIENTO RECINTO EX INTERNADO MUNICIPAL MARCHIGUE</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
@@ -7624,32 +7683,32 @@
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>547640-16-L126</t>
+          <t>4631-19-LP26</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEJORAMIENTO Y HABILITACIÓN CASA DE SALUD MENTAL </t>
+          <t>CONSULTORÍA PLAN MAESTRO VIDEOVIGILANCIA L12-26</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 28 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>5482-102-LE26</t>
+          <t>4642-91-LP26</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO Y MANTENCIÓN DE 2 ESCANERES PARA DOM</t>
+          <t xml:space="preserve">PROVISIÓN E INSTALACIÓN DE UN 1 DENSITÓMETRO ÓSEO CON OBRAS DE HABILITACIÓN DESTINADO AL SERVICIO DE IMAGENOLOGÍA DEL HOSPITAL DE CARABINEROS. </t>
         </is>
       </c>
       <c r="C285" s="11" t="n">
@@ -7664,32 +7723,32 @@
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>548874-70-LR26</t>
+          <t>4686-30-LE26</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
         <is>
-          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
+          <t>Servicio de arrendamiento de bodegas</t>
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>5520-75-LP26</t>
+          <t>4803-29-LP26</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
         <is>
-          <t>Traslado Pasajeros Minera Collahuasi</t>
+          <t>SERVICIOS PROFESIONALES Y ARRIENDO DE EQUIPAMIENTO</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
@@ -7704,12 +7763,12 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>5558-5-L126</t>
+          <t>4887-28-E226</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPLEMENTACIÓN PUNTO VERDE Y SERVICIO DE RECICLAJE PARA DEPENDENCIAS DEL INSTITUTO DE SEGURIDAD LABORAL EN LA REGIÓN DE LA ARAUCANÍA</t>
+          <t>Obras de habilitación Centro de Creación Temuco</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
@@ -7717,19 +7776,19 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>564953-71-LP26</t>
+          <t>4967-35-LP26</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
+          <t>CONVENIO DE SUMINISTRO DE CÁNULAS DE ALTO FLUJO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
@@ -7744,12 +7803,12 @@
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>568658-43-LR26</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
@@ -7764,32 +7823,32 @@
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>584264-46-LE26</t>
+          <t>5056-108-LP26</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN POSTA URBANA SARA GAJARDO</t>
+          <t>ARRIENDO DE REENVASADORA AUTOMÁTICA DE MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>607-67-O126</t>
+          <t>5240-102-LR26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN ESTACIÓN FUNICULAR Y CENTRO DE EXPERIENCIA</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="C292" s="11" t="n">
@@ -7804,32 +7863,32 @@
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>622847-13-LE26</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
         <is>
-          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>score 21 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>633-54-LP26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO SERVICIO DE ARRIENDO DE MOD</t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
@@ -7844,16 +7903,16 @@
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>634-82-LE26</t>
+          <t>539119-80-LP26</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
         <is>
-          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
+          <t>CONTRATACIÓN DE SERVICIOS DE EMERGENCIAS SANITARIAS REPARACIÓN YO REPOSICIÓN DE REDES DE ALCANTARILLADO AGUA POTABLE Y REDES DE GAS EN INMUEBLES UBICADOS EN LA REGIÓN METROPOLITANA DEPENDIENTE DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
@@ -7864,16 +7923,16 @@
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>638-14-O126</t>
+          <t>539119-90-LE26</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
+          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
@@ -7884,76 +7943,76 @@
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>653-15-O126</t>
+          <t>5418-13-LE26</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
         <is>
-          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
+          <t>Digitalización Documentos Almacenados Bodega</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>657-7-LE26</t>
+          <t>547640-16-L126</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
         <is>
-          <t>FTO DS49 CS Nuevos terrenos Chile Chico Serviu</t>
+          <t xml:space="preserve">MEJORAMIENTO Y HABILITACIÓN CASA DE SALUD MENTAL </t>
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>660-10-LE26</t>
+          <t>5482-102-LE26</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
         <is>
-          <t>DIAGNÓSTICO Y ELABORACIÓN DEL PLAN MAESTRO</t>
+          <t>ARRIENDO Y MANTENCIÓN DE 2 ESCANERES PARA DOM</t>
         </is>
       </c>
       <c r="C299" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D299" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>673663-20-LP26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
@@ -7964,92 +8023,92 @@
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>680504-2-L126</t>
+          <t>5510-7-LR26</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
         <is>
-          <t>Mantención Anual Tableros Eléctricos del Edificio RPP Curicó</t>
+          <t>HABILITACIÓN CAFETERÍA ZÓCALO TORRE JEA - FCFM</t>
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>688-11-LP26</t>
+          <t>5596-5-LP26</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
         <is>
-          <t>Arriendo Infraestructura de Respaldo</t>
+          <t>INVENTARIO PATRIMONIO CULTURAL INMUEBLE AYP.</t>
         </is>
       </c>
       <c r="C302" s="11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 26 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>696217-4-LE26</t>
+          <t>564953-71-LP26</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
         <is>
-          <t>Serv de Mantencion de inmueble Oficina Colchane</t>
+          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>696961-4-LP26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE OFICINAS PROYECTO CENTRALIZADO</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>697-29-LE26</t>
+          <t>584264-46-LE26</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
         <is>
-          <t>Serv. habilitación electrica para equipo trifasico</t>
+          <t>HABILITACIÓN POSTA URBANA SARA GAJARDO</t>
         </is>
       </c>
       <c r="C305" s="11" t="n">
@@ -8064,36 +8123,36 @@
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>699866-116-LP26</t>
+          <t>5858-6-LP26</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
+          <t>MEJORAMIENTO SEDE SOCIAL LOCALIDAD CERRO BLANCO-O</t>
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>707418-44-L126</t>
+          <t>608897-57-LE26</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE PODA, TALA Y RETIRO DE ÁRBOLES ALTOS PARA JARDINES INFANTILES, SALAS CUNA Y OFICINAS REGIONALES DE FUNDACIÓN INTEGRA, REGIÓN DE COQUIMBO</t>
+          <t>REPRESENTACIÓN EN PROCESO DE MANTENCIÓN DE LA ACREDITACIÓN ENAC ISOIEC17025:2017 DEL SISTEMA DE GESTIÓN DE CALIDAD DEL DEPARTAMENTO REDES DE MONITOREO</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
@@ -8104,52 +8163,52 @@
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>711841-14-L126</t>
+          <t>614795-7-LE26</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
         <is>
-          <t>MANTENCION SISTEMA CONTROL DE INCENDIO EDIFICIO MDSYF</t>
+          <t>Inventario de Emisiones art 73 DS 18-23</t>
         </is>
       </c>
       <c r="C308" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>732515-1-L126</t>
+          <t>622847-13-LE26</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO EN ADQUISICION DE PRODUCTOS DE DIFUSION Y PUBLICIDAD PARA GOBIERNO EN TERRENO</t>
+          <t>AIFO REPOSICIÓN CERCO PERIMETRAL TERRENO VAITEA RN</t>
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 21 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>732868-3-L126</t>
+          <t>633-54-LP26</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Adquisición y Distribución de Bidones de Agua purificada, entrega de dispensadores en comodato para el Juzgado de Letras del Trabajo de San Bernardo”</t>
+          <t>CONVENIO DE SUMINISTRO SERVICIO DE ARRIENDO DE MOD</t>
         </is>
       </c>
       <c r="C310" s="11" t="n">
@@ -8164,32 +8223,32 @@
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>748201-9-LP26</t>
+          <t>634-82-LE26</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE MATRACES E INYECTABLES PARA LAS FARMACIAS DE LOS CENTROS DE SALUD Y REHABILITACIÓN CAPREDENA</t>
+          <t>REACTIVOS QUÍMICOS PARA EL DEPARTAMENTO DE SEGURI</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D311" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>768-19-LR26</t>
+          <t>638-14-O126</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
+          <t>CONSTRUCCIÓN EDIFICIO INSTITUCIONAL MINVU MAGALLANES Y ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
@@ -8204,56 +8263,56 @@
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>769-84-LP26</t>
+          <t>652-49-LE26</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
         <is>
-          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
+          <t>Arriendo de Móviles Traslado Funcionarios Usuarios</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>777304-55-LP26</t>
+          <t>653-15-O126</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
+          <t>Habilitación de Terrenos Etapa V Lote D y E, Las Americas, Talca</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>780724-6-LE26</t>
+          <t>657-7-LE26</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
         <is>
-          <t>Remodelación dependencias TercerTribunal Ambiental</t>
+          <t>FTO DS49 CS Nuevos terrenos Chile Chico Serviu</t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
@@ -8264,32 +8323,32 @@
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>813-87-LE26</t>
+          <t>673663-20-LP26</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
         <is>
-          <t>Arriendo dispositivo almacenamiento E1O2RT9</t>
+          <t>CONSTRUCCION SEDE SOCIAL EL BOSQUE COMUNA DE ANDA</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>820-3-O126</t>
+          <t>688-11-LP26</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
         <is>
-          <t>RESTAURACIÓN Y HABILITACIÓN BIBLIOTECA MUNICIPAL EX ESCUELA 3, HUASCO</t>
+          <t>Arriendo Infraestructura de Respaldo</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
@@ -8304,72 +8363,72 @@
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>824-3-LE26</t>
+          <t>696217-4-LE26</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
         <is>
-          <t>ASES. A LA CONTRAPARTE TÉCN. INVENTARIO MAULE</t>
+          <t>Serv de Mantencion de inmueble Oficina Colchane</t>
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>829-2-O126</t>
+          <t>696961-4-LP26</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
+          <t>HABILITACIÓN DE OFICINAS PROYECTO CENTRALIZADO</t>
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>838794-10-LE26</t>
+          <t>697055-7-LE26</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
         <is>
-          <t>SERV DE CIERRE DE TABIQUERÍA EN PAREDES DE OFICINA PALIATIVO DEL CENTRO DE ATENCIÓN PRIMARIA DE SALU DE VILLA ALEMANA</t>
+          <t xml:space="preserve">HABILITACION SALA ENTREVISTA VIDEO GRABADA </t>
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>839186-11-LP26</t>
+          <t>699866-116-LP26</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
         <is>
-          <t>2 LLAMADO HABILITACIÓN CANCHA DE FÚTBOL Y CIERRE</t>
+          <t xml:space="preserve">Bolsa de  aspiración  3lts con equipo en comodato </t>
         </is>
       </c>
       <c r="C321" s="11" t="n">
@@ -8384,12 +8443,12 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>840405-14-CO26</t>
+          <t>711841-14-L126</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MATERIALES PARA MEJORAMIENTO EDIFICIO ANEXO MUNICIPAL COMUNA DE RÍO CLARO PRIVADA</t>
+          <t>MANTENCION SISTEMA CONTROL DE INCENDIO EDIFICIO MDSYF</t>
         </is>
       </c>
       <c r="C322" s="11" t="n">
@@ -8404,32 +8463,32 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>867990-85-L126</t>
+          <t>761391-137-LE26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>cc 102 sol. 92417- Mantención y reparación de sala con visita a terreno</t>
+          <t>83 EA GUB ECG HABILITACIÓN Y REMODELACIÓN DE BAÑOS DEL PABELLÓN DE DORMITORIOS ESCUELA DE AVIACIÓN.</t>
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>867990-89-L126</t>
+          <t>768-19-LR26</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
         <is>
-          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
+          <t>REPOSICIÓN SEDE CLUB CULTURAL Y SOCIAL JORGE V</t>
         </is>
       </c>
       <c r="C324" s="11" t="n">
@@ -8444,12 +8503,12 @@
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>875646-69-LP26</t>
+          <t>769-84-LP26</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
         <is>
-          <t>JCB. Servicio de arriendo de sistema RISPACS</t>
+          <t>KIT DETECCIÓN VPH POR PCR Y EQUIP. COMODATO PP-88</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
@@ -8464,12 +8523,12 @@
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>886954-176-LP26</t>
+          <t>777304-55-LP26</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
         <is>
-          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
+          <t>SERVICIO DE ARRIENDO DE MESA TRAUMATOLÓGICA</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
@@ -8484,32 +8543,32 @@
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>886954-294-LP26</t>
+          <t>780724-6-LE26</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
         <is>
-          <t>Conv. Suministro Prótesis Para U. Medicina Fisica y Rehabilitación del HGGB</t>
+          <t>Remodelación dependencias TercerTribunal Ambiental</t>
         </is>
       </c>
       <c r="C327" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>886954-298-LP26</t>
+          <t>820-3-O126</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
         <is>
-          <t>Convenio Suministro de Cataratas con Equipos en Comodatos</t>
+          <t>RESTAURACIÓN Y HABILITACIÓN BIBLIOTECA MUNICIPAL EX ESCUELA 3, HUASCO</t>
         </is>
       </c>
       <c r="C328" s="11" t="n">
@@ -8524,36 +8583,36 @@
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>898-181-LP26</t>
+          <t>829-2-O126</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
         <is>
-          <t>Servicios de Laboratorio Dental con Equipo en Comodato</t>
+          <t>HABILITACION Y AMPLIACION EDIFICIO GORE MAGALLANES-2DO LLAMADO</t>
         </is>
       </c>
       <c r="C329" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D329" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>899-39-LE26</t>
+          <t>838794-10-LE26</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
         <is>
-          <t>“Servicio de Mantención Preventiva y Correctiva de PEAS y Limpieza de Estanque de Aguas Servidas para Hospital San José de Casablanca</t>
+          <t>SERV DE CIERRE DE TABIQUERÍA EN PAREDES DE OFICINA PALIATIVO DEL CENTRO DE ATENCIÓN PRIMARIA DE SALU DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="C330" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
@@ -8564,92 +8623,92 @@
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>899-40-LE26</t>
+          <t>839186-11-LP26</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
         <is>
-          <t>“Convenio de Suministro de Medicamentos para el Hospital San José de Casablanca”</t>
+          <t>2 LLAMADO HABILITACIÓN CANCHA DE FÚTBOL Y CIERRE</t>
         </is>
       </c>
       <c r="C331" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>900-45-LP26</t>
+          <t>867990-89-L126</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Habilitación sala UHCIP </t>
+          <t>CDP 92973 CC 102 - “26-TE-BA-FORROS METÁLICOS TECHUMBRE BAÑOS 1ER PISO DIMEC, EDIFICIO 710, FACULTAD DE INGENIERÍA”.</t>
         </is>
       </c>
       <c r="C332" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>905-30-LE26</t>
+          <t>875646-69-LP26</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
         <is>
-          <t>Cambio de Red Eléctrica de las dependencias de Oficina Sectorial San Fernando Región de O´Higgins.</t>
+          <t>JCB. Servicio de arriendo de sistema RISPACS</t>
         </is>
       </c>
       <c r="C333" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D333" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>924-27-LP26</t>
+          <t>886954-176-LP26</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
         <is>
-          <t>Servicio de bodegaje para la Seremi de Salud R.M.</t>
+          <t>Convenio De Suministro por Tubos con Sensor y Sonda Estimuladora con equipo en Comodato</t>
         </is>
       </c>
       <c r="C334" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>928-27-LR26</t>
+          <t>886954-294-LP26</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRENDAMIENTO DE PERIMETROS FREESTANDING</t>
+          <t>Conv. Suministro Prótesis Para U. Medicina Fisica y Rehabilitación del HGGB</t>
         </is>
       </c>
       <c r="C335" s="11" t="n">
@@ -8664,32 +8723,32 @@
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>931-23-LE26</t>
+          <t>886954-298-LP26</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO MANTENCIÓN CANCHA FUTBOL DE PASTO NATURAL RECINTO DEPORTIVO CENDYR LA SERENA</t>
+          <t>Convenio Suministro de Cataratas con Equipos en Comodatos</t>
         </is>
       </c>
       <c r="C336" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>937232-85-LE26</t>
+          <t>898-181-LP26</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE CAMILLAS DE TRANSPORTE HIDRAULICAS POR 24 MESES</t>
+          <t>Servicios de Laboratorio Dental con Equipo en Comodato</t>
         </is>
       </c>
       <c r="C337" s="11" t="n">
@@ -8704,56 +8763,56 @@
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>948354-135-LP26</t>
+          <t>899-39-LE26</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
+          <t>“Servicio de Mantención Preventiva y Correctiva de PEAS y Limpieza de Estanque de Aguas Servidas para Hospital San José de Casablanca</t>
         </is>
       </c>
       <c r="C338" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>948806-117-LP26</t>
+          <t>900-45-LP26</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
+          <t xml:space="preserve">Servicio de Habilitación sala UHCIP </t>
         </is>
       </c>
       <c r="C339" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D339" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>963423-10-LE26</t>
+          <t>900-60-L126</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>serv. reparacion conservacion y pintura inmueble</t>
+          <t>HDS - COMPRA DE BOLSAS PLASTICAS PARA BODEGA</t>
         </is>
       </c>
       <c r="C340" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
@@ -8764,52 +8823,52 @@
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>975-12-O126</t>
+          <t>924-27-LP26</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+          <t>Servicio de bodegaje para la Seremi de Salud R.M.</t>
         </is>
       </c>
       <c r="C341" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D341" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>986278-21-LE26</t>
+          <t>928-27-LR26</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO FUNGIBLES Y OTROS PARA ESCUELA INDUSTRIA Y ENERGÍAS PARA CASA CENTRAL LAUTARO Y SEDE ANGOL DEL CFT REGIÓN DE LA ARAUCANIA</t>
+          <t>SERVICIO DE ARRENDAMIENTO DE PERIMETROS FREESTANDING</t>
         </is>
       </c>
       <c r="C342" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>993-47-LE26</t>
+          <t>930-23-LE26</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
         <is>
-          <t>CONTROL PLAGAS RECINTOS  FISCALES</t>
+          <t>MANTENCIÓN GENERAL RECINTOS DEPORTIVOS IND AFTA.</t>
         </is>
       </c>
       <c r="C343" s="11" t="n">
@@ -8818,6 +8877,146 @@
       <c r="D343" s="13" t="inlineStr">
         <is>
           <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="11" t="inlineStr">
+        <is>
+          <t>937232-85-LE26</t>
+        </is>
+      </c>
+      <c r="B344" s="13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ARRIENDO DE CAMILLAS DE TRANSPORTE HIDRAULICAS POR 24 MESES</t>
+        </is>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="11" t="inlineStr">
+        <is>
+          <t>948354-135-LP26</t>
+        </is>
+      </c>
+      <c r="B345" s="13" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
+        </is>
+      </c>
+      <c r="C345" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="11" t="inlineStr">
+        <is>
+          <t>948806-117-LP26</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="inlineStr">
+        <is>
+          <t>Adquisición de Catéteres para Electrofisiología con Equipo en Comodato en Modalidad de Consignación</t>
+        </is>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="11" t="inlineStr">
+        <is>
+          <t>963423-10-LE26</t>
+        </is>
+      </c>
+      <c r="B347" s="13" t="inlineStr">
+        <is>
+          <t>serv. reparacion conservacion y pintura inmueble</t>
+        </is>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D347" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="11" t="inlineStr">
+        <is>
+          <t>975-12-O126</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="inlineStr">
+        <is>
+          <t>Plan Maestro de Evacuación y Drenaje de Aguas Lluvias de Buin y Paine, RM.</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D348" s="13" t="inlineStr">
+        <is>
+          <t>score 16 &lt; 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="11" t="inlineStr">
+        <is>
+          <t>986278-21-LE26</t>
+        </is>
+      </c>
+      <c r="B349" s="13" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO FUNGIBLES Y OTROS PARA ESCUELA INDUSTRIA Y ENERGÍAS PARA CASA CENTRAL LAUTARO Y SEDE ANGOL DEL CFT REGIÓN DE LA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D349" s="13" t="inlineStr">
+        <is>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="11" t="inlineStr">
+        <is>
+          <t>993-48-LP26</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="inlineStr">
+        <is>
+          <t>Servicio de arriendo de 800 horas máquina de 2 excavadoras para la construcción de zanja sector Vallecito Provincia de El Loa Región de Antofagasta.</t>
+        </is>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" s="13" t="inlineStr">
+        <is>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>

--- a/docs/licitaciones-ultima.xlsx
+++ b/docs/licitaciones-ultima.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corrida 2026-09-18 19:14 · UF 40,959.07 · 4,540 licitaciones activas barridas</t>
+          <t>Corrida 2026-09-22 19:54 · UF 40,991.75 · 3,941 licitaciones activas barridas</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>CAMBIO: monto UF 122171.0-&gt;122073.0</t>
+          <t>CAMBIO: monto UF 122073.0-&gt;121976.0</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M3" s="20" t="n">
-        <v>122073</v>
+        <v>121976</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>53</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="J2" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="J3" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J4" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="J6" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>122073</v>
+        <v>121976</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
@@ -1684,11 +1684,11 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="J12" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="G3" s="11" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>bajo umbral de monto (Nacional, UF 352 (umbral UF 2.000))</t>
+          <t>bajo umbral de monto (Nacional, UF 351 (umbral UF 2.000))</t>
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
@@ -2009,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D350"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2243,12 +2243,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>1057049-329-LE26</t>
+          <t>1057384-143-LE26</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>JAC ADQ. DE MANTAS TÉRMICAS CON COMODATO DE EQUIPO</t>
+          <t>Equipo en Comodato Convenio de suministro reactiv</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
@@ -2263,32 +2263,32 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1057402-144-LP26</t>
+          <t>1057417-186-LP26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Arriendo de Bodegaje Externo para el Hospital Clínico de Magallanes</t>
+          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1057417-186-LP26</t>
+          <t>1057472-101-LP26</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 2 CAMAS DE PARTO</t>
+          <t>ARRIENDO DE ENDOSCOPIOS</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
@@ -2303,32 +2303,32 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1057429-85-LE26</t>
+          <t>1057486-21-LE26</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>EJECUCIÓN DE RADIER PARA BODEGA DE FARMACIA</t>
+          <t>Servicio de rehabilitación psicosocial tipo I y II</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>1057429-86-LE26</t>
+          <t>1057489-285-LP26</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE SETS DE MOTORES QUIRÚRGICOS</t>
+          <t>Arriendo de Huelleros digitales y Pistola Escáner</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
@@ -2343,12 +2343,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>1057472-101-LP26</t>
+          <t>1057491-177-LP26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ENDOSCOPIOS</t>
+          <t>ARRIENDO DE INSTRUMENTAL QUIRURGICO</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -2363,12 +2363,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>1057486-21-LE26</t>
+          <t>1057491-178-LP26</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Servicio de rehabilitación psicosocial tipo I y II</t>
+          <t>EXAMENES POR CITOMETRIA DE FLUJO CON COMODATO</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
@@ -2383,12 +2383,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>1057489-285-LP26</t>
+          <t>1057492-123-LE26</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de Huelleros digitales y Pistola Escáner</t>
+          <t>SUMINISTRO DE BAJADAS PARA BOMBA PCA CON ENTREGA DE EQUIPOS EN COMODATO</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -2403,12 +2403,12 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1057491-177-LP26</t>
+          <t>1057492-128-LP26</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE INSTRUMENTAL QUIRURGICO</t>
+          <t>SERVICIO ARRIENDO DE LAVADORA TERMODESINFECTADORA</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
@@ -2423,12 +2423,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>1057491-178-LP26</t>
+          <t>1057501-395-LR26</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>EXAMENES POR CITOMETRIA DE FLUJO CON COMODATO</t>
+          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -2443,12 +2443,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>1057492-121-LE26</t>
+          <t>1057501-435-LR26</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SS ARRIENDO CAJAS INSTRUMENTAL QX CX DIGESTIVA ALT</t>
+          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
@@ -2463,12 +2463,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1057492-123-LE26</t>
+          <t>1057501-606-LR26</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE BAJADAS PARA BOMBA PCA CON ENTREGA DE EQUIPOS EN COMODATO</t>
+          <t>CONVENIO BAJADAS BOMBA DE INFUSION CON COMODATO</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -2483,12 +2483,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1057492-128-LP26</t>
+          <t>1057503-137-LR26</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO ARRIENDO DE LAVADORA TERMODESINFECTADORA</t>
+          <t>Adquisición de Test Reportado de Orina Completa y Sedimentos Urinarios Automatizados con Equipamiento en Comodato para el Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -2503,32 +2503,32 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>1057494-60-LE26</t>
+          <t>1057509-275-LP26</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE DRENAJES DE HERIDAS CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
+          <t>CONVENIO COMPRA DE SERVICIOS PARA TÉCNICOS DE BODEGA DE GASES CLÍNICOS</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>1057501-395-LR26</t>
+          <t>1057511-28-LE26</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Inmunohematología Unidad de Medicina Transfusional con equipos en comodato por 24 meses </t>
+          <t xml:space="preserve">COMPRA DE SERVICIOS DE TRASLADO HODOM POR CAMPAÑA </t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
@@ -2543,12 +2543,12 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>1057501-435-LR26</t>
+          <t>1057532-77-LE26</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE ARCO C Y EQUIPO RAYO PORTÁTIL</t>
+          <t>“ADQUISICION DE CINTAS DE GLICEMIA CON GLUCOMETROS EN COMODATO PARA RED ASISTENCIAL APS EN CUMPLIMIENTO DE PROGRAMAS MINISTERIALES DE APS”</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
@@ -2563,72 +2563,72 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>1057501-473-LE26</t>
+          <t>1057539-129-LP26</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Habilitación para Instalacion de Food Truck HSR</t>
+          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>1057501-477-LP26</t>
+          <t>1057962-9-LE26</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Convenio reactivos para exámenes de inmunología serología infecciona y Autoinmunidad con equipos en comodato por 24 meses</t>
+          <t>CAMBIOS DE VENTANAS PARA EDIFICIO PRINCIPAL Y OTROS ESTABLECIMIENTOS SSC</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>1057501-493-LP26</t>
+          <t>1057977-14-LE26</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE MÁQUINA DE ANESTESIA HSR</t>
+          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>1057503-137-LR26</t>
+          <t>1058012-28-LE26</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Test Reportado de Orina Completa y Sedimentos Urinarios Automatizados con Equipamiento en Comodato para el Hospital Padre Alberto Hurtado</t>
+          <t>MEDICAMENTO SEVOFLURANO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
@@ -2643,152 +2643,152 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1057509-269-LP26</t>
+          <t>1058086-49-LP26</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO CONTRATACIÓN DE SERVICIOS DE APOYO PROFESIONALY TÉCNICO PARA EL DEPARTAMENTO DE EQUIPAMIENTO CLÍNICO DEL HOSPITAL REGIONAL DE ÑUBLE</t>
+          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>1057509-275-LP26</t>
+          <t>1063538-222-LE26</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO COMPRA DE SERVICIOS PARA TÉCNICOS DE BODEGA DE GASES CLÍNICOS</t>
+          <t>SERVICIO DE ARRIENDO LÁMPARAS QUIRÚRGICAS DOBLE</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>1057509-292-LE26</t>
+          <t>1075963-370-LE26</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>“CONVENIO COMPRA SERVICIOS DE PROFESIONAL APOYO AL PROCESO DE GESTIÓN AL SISTEMA DE GESTIÓN DE COSTOS PARA EL DEPARTAMENTO DE FINANZAS” brd</t>
+          <t>ARRIENDO CON OPCION DE COMPRA SECADOR KAESER REFRIGERATIVO KYOSEC POR 3 MESES</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>1057511-28-LE26</t>
+          <t>1075963-403-L126</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPRA DE SERVICIOS DE TRASLADO HODOM POR CAMPAÑA </t>
+          <t>ARRIENDO SISTEMA MONITOREO EN LINEA PARA REFRIGERADORES DE FARMACOS ONCOLOGICOS</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>1057539-129-LP26</t>
+          <t>1076710-10-LP26</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO OXIGENO Y ARRIENDO ESTANQUE.</t>
+          <t xml:space="preserve">SUMINISTRO OFICINALES Y MAGISTRALES POR 12 MESES </t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>1057547-350-LR26</t>
+          <t>1085111-23-O126</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION PROTESIS CADERAS CON COMODATO INSTRUMENTAL QUIRURGICO</t>
+          <t>CONSERVACIÓN TECHUMBRE EDIFICIO SERVIU ÑUBLE</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1057552-19-LE26</t>
+          <t>1095-10-LE26</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Convenio de Suministro Materiales de Oficina</t>
+          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1057898-95-LE26</t>
+          <t>1095-11-LE26</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN EQUIPOS Y EQUIPAMIENTO DE REHABILITACIÓN PARA EL CENTRO DE SALUD FAMILIAR Y SAR DURAN TRUJILLO SAN CARLOS SERVICIO DE SALUD ÑUBLE</t>
+          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
@@ -2803,152 +2803,152 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1057962-9-LE26</t>
+          <t>1096-15-O126</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>CAMBIOS DE VENTANAS PARA EDIFICIO PRINCIPAL Y OTROS ESTABLECIMIENTOS SSC</t>
+          <t>ATIF HABILITACIÓN CALLE DE RODAJE ALFA Y OBRAS ANEXAS AEROPUERTO PUNTA AREN</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>1057977-14-LE26</t>
+          <t>1106-22-LP26</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Ampliacion RX dental box medicos y bodegas H.Futa</t>
+          <t>Serv Arriendo Eq para faenas de Colocacion asfalto</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1058012-28-LE26</t>
+          <t>1110404-205-LP26</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>MEDICAMENTO SEVOFLURANO CON EQUIPO EN COMODATO</t>
+          <t>MANTENCIÓN SS.HH. Y COCINAS DE CASAS DE PROFESORES Y REPOSICION DE CUBICULOS SEPARADORES EN SS.HH. DEL ESTABLECIMIENTO LICEO GRANADEROS DE PUTRE PERTENECIENTE A SLEP DE CHINCHORRO</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>1058086-49-LP26</t>
+          <t>1126922-36-LP26</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO PROPOFOL ASOCIADO AL COMODATO DE BOMBAS DE INFUSIÓN CON MODELOS FARMACOCINÉTICOS </t>
+          <t>CONTRATO SUMINISTRO MAT PEDAGOGICOS Y OFICINA</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>1063538-222-LE26</t>
+          <t>1129-7-L126</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO LÁMPARAS QUIRÚRGICAS DOBLE</t>
+          <t>SERVICIO DE ARRIENDO Y MANTENCIÓN DE 2 (DOS) DISPENSADORES DE AGUA PURIFICADA CONECTADOS A LA RED DE AGUA POTABLE CON INSTALACION INCLUIDA POR UN PERÍODO DE 36 MESES.</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>1070620-89-LP26</t>
+          <t>1171317-10-LP26</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>PZM-SUM ENVOLTURAS ESTERILIZACION +EQUIPO COMODATO</t>
+          <t xml:space="preserve">CONSTRUCCIÓN SEDE SOCIAL AGRUPACIÓN DE MOTOQUEROS CHILLÁN </t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>1070620-93-LP26</t>
+          <t>1175-71-LP26</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>PVE TOALLAS DE PAPEL CON DISPENSADORES EN COMODATO</t>
+          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1070620-95-LE26</t>
+          <t>1175-74-LP26</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>PVE TRASLADO DE PACIENTES RADIOYODADOS DESDE AFTA</t>
+          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
@@ -2963,136 +2963,136 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1070620-96-LP26</t>
+          <t>1180730-38-LE26</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>PVE FRESAS NEUROQUIRURGICAS CON EQUIPO EN COMODATO</t>
+          <t>BOLSOS DE TERRENO ESPECIALIDAD CESFAM 18</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1075963-370-LE26</t>
+          <t>1186229-28-LE26</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO CON OPCION DE COMPRA SECADOR KAESER REFRIGERATIVO KYOSEC POR 3 MESES</t>
+          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1075963-403-L126</t>
+          <t>1197-21-L126</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO SISTEMA MONITOREO EN LINEA PARA REFRIGERADORES DE FARMACOS ONCOLOGICOS</t>
+          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>score 15 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1076710-10-LP26</t>
+          <t>1197594-17-LE26</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO OFICINALES Y MAGISTRALES POR 12 MESES </t>
+          <t>CONSULTORIA PLAN MAESTRO AREAS VERDES Y PAISAJISMO</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1079445-41-LE26</t>
+          <t>1208100-8-LP26</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS Y PUERTAS CASAS VILLA LAS NACIONES</t>
+          <t xml:space="preserve">SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE EVALUACIÓN FORMATIVA PARA LA ADOPCIÓN Y EL ACOGIMIENTO UEFAA Y RESIDENCIA FAMILIAR DE ADOLESCENTES DE MACHALÍ </t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1079445-42-LE26</t>
+          <t>1224953-26-LE26</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>ADQ. VENTANAS CASAS ANEXAS RETEN PAMPA GUANACO</t>
+          <t>Rehabilitación oral mediante prótesis removibles</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1079969-20-LE26</t>
+          <t>1224957-60-LE26</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN Y REMODELACIÓN 1ER SUBTERRÁNEO EDIFICIO</t>
+          <t>CONSERVACION DE RECINTOS EDUCACIONALE</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
@@ -3103,12 +3103,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1082957-29-LE26</t>
+          <t>1237328-66-LE26</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Servicios de provisión e instalación de cortinas duo roller para las dependencias de ProChile ubicadas en la Región Metropolitana comuna de Santiago.</t>
+          <t>MEJORAMIENTO Y HABILITACIÓN CESFAM CARLOS IBAÑEZ</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
@@ -3116,59 +3116,59 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1085111-23-O126</t>
+          <t>1239966-10-LE26</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN TECHUMBRE EDIFICIO SERVIU ÑUBLE</t>
+          <t>HABILITACION DE CENTRO AIDIA DE PUERTO NATALES</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1095-10-LE26</t>
+          <t>1247197-66-LP26</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE DOS EXCAVADORAS ORUGAS 250 HORAS</t>
+          <t>SUMINISTRO DE PRODUCTOS DE OFICINA PARA LA CORESAM</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1095-11-LE26</t>
+          <t>1256505-28-LE26</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE TRES EXCAVADORAS ORUGAS 420 HORAS</t>
+          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
@@ -3183,12 +3183,12 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1096-15-O126</t>
+          <t>1261592-54-LE26</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>ATIF HABILITACIÓN CALLE DE RODAJE ALFA Y OBRAS ANEXAS AEROPUERTO PUNTA AREN</t>
+          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
@@ -3203,156 +3203,156 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1106-22-LP26</t>
+          <t>1271359-120-B226</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>Serv Arriendo Eq para faenas de Colocacion asfalto</t>
+          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1116006-4-LE26</t>
+          <t>1298354-27-LE26</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Corte de Árboles dependencias Aeródromo Tte. Vidal</t>
+          <t>Conservación y Habilitación Salas y Muros</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1126922-36-LP26</t>
+          <t>1346284-10-LE26</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO SUMINISTRO MAT PEDAGOGICOS Y OFICINA</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1129-7-L126</t>
+          <t>1346284-11-LE26</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO Y MANTENCIÓN DE 2 (DOS) DISPENSADORES DE AGUA PURIFICADA CONECTADOS A LA RED DE AGUA POTABLE CON INSTALACION INCLUIDA POR UN PERÍODO DE 36 MESES.</t>
+          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1171317-10-LP26</t>
+          <t>1348-5-LP26</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCIÓN SEDE SOCIAL AGRUPACIÓN DE MOTOQUEROS CHILLÁN </t>
+          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1175-71-LP26</t>
+          <t>1350296-80-LE26</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>8426 “ADQUISICIÓN DE ECOBIÓMETRO PARA COMPLEJO ASISTENCIAL PADRE LAS CASAS”</t>
+          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1175-74-LP26</t>
+          <t>1351-6-LP26</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>6026: “ARRIENDO DE EQUIPOS CRITICOS PARA EL SAMU SSAS”</t>
+          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1180730-38-LE26</t>
+          <t>1360-10-LE26</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>BOLSOS DE TERRENO ESPECIALIDAD CESFAM 18</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE CONSTRUCCIÓN DE CIERRE PERIMETRAL CON ILUMINACIÓN LED DE INSTALACIÓN DE FAENAS PARA OFICINA DE PUENTE ALTO DE LA DIRECCIÓN REGIÓN METROPOLITANA</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
@@ -3363,36 +3363,36 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1186229-28-LE26</t>
+          <t>1374899-36-LP26</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>Ropa técnica de trabajo Unidad Atención en terreno</t>
+          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1197-21-L126</t>
+          <t>1375158-7-LP26</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIONES Y REPARACIONES MENORES OFICINA DR DE ATACAMA</t>
+          <t>ADQUISICIÓN DE VEINTICUATRO 24 SIERRAS DE AUTOPSIA Y UN 01 PACK EQUIPOS DE REFRIGERACIÓNCONGELACIÓN PARA DEPARTAMENTO DE TANATOLOGÍA DEL NUEVO EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL DE SANTIAGO</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
@@ -3403,36 +3403,36 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1197594-17-LE26</t>
+          <t>1375746-15-LE26</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORIA PLAN MAESTRO AREAS VERDES Y PAISAJISMO</t>
+          <t>SERVICIO DE HABILITACIÓN KITCHENETTE Y RECEPCIÓN CASONA DEL SLEP DEL ACONCAGUA</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1198-33-LE26</t>
+          <t>1391828-8-LE26</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO Y REPARACION DE LAS DEPENDENCIAS IND</t>
+          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
@@ -3443,92 +3443,92 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1208100-8-LP26</t>
+          <t>1417913-116-LE26</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE TRANSPORTE Y TRASLADO DE PASAJEROS PARA LA UNIDAD DE EVALUACIÓN FORMATIVA PARA LA ADOPCIÓN Y EL ACOGIMIENTO UEFAA Y RESIDENCIA FAMILIAR DE ADOLESCENTES DE MACHALÍ </t>
+          <t>ADQUISICIÓN DE EQUIPOS TECNOLÓGICOS PARA DEPENDENCIAS DE CORMUDESI</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1216085-59-LP26</t>
+          <t>1417913-119-LE26</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO EN COMODATO HEMOGLOBINA GLICOSILADA</t>
+          <t>ADQUISICIÓN DE EQUIPAMIENTO PARA LA EJECUCIÓN Y FORTALECIMIENTO DE PROGRAMAS DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1224953-26-LE26</t>
+          <t>1417913-129-LP26</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>Rehabilitación oral mediante prótesis removibles</t>
+          <t>CONVENIO DE SUMINISTRO PARA LA PROVISIÓN INSTALACIÓN MANTENCIÓN Y REPARACIÓN DE AIRES ACONDICIONADOS PARA DEPENDENCIAS DE CORMUDESI POR 24 MESES</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1224957-60-LE26</t>
+          <t>1422824-10-LE26</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACION DE RECINTOS EDUCACIONALE</t>
+          <t>CONTRATO DE SUMINISTRO DE CINTAS PARA PRUEBA DEL BIOSENSOR DE CREATININA CON EQUIPO EN COMODATO PARA LA UNIDAD DE IMAGENOLOGÍA COMPLEJA DEL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1239966-10-LE26</t>
+          <t>1422824-25-LP26</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION DE CENTRO AIDIA DE PUERTO NATALES</t>
+          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
@@ -3543,92 +3543,92 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1247197-66-LP26</t>
+          <t>1431841-56-LP26</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE PRODUCTOS DE OFICINA PARA LA CORESAM</t>
+          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1256505-28-LE26</t>
+          <t>1431841-57-LE26</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN Y HABILITACIÓN SALA SENSORIAL EZN</t>
+          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1261592-54-LE26</t>
+          <t>1469101-6-LP26</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSTALACIÓN Y HABILITACIÓN DE HUERTO COMUNITARIO </t>
+          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1271359-120-B226</t>
+          <t>1469-205-L126</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO MODULOS Y PASILLOS DE CIRCULACIÓN - C.BAUZA</t>
+          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>1298354-27-LE26</t>
+          <t>1469-211-L126</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>Conservación y Habilitación Salas y Muros</t>
+          <t>MATERIAL GRÁFICO, TRASLADO, MONTAJE, INSTALACION, SUPERVISIÓN, DESMONTAJE Y RETIRO PARA UTALCA ABRE PUERTAS 2026, UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
@@ -3643,92 +3643,92 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>1340-51-LE26</t>
+          <t>1483330-1-LP26</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION Y REPARACION DE INSTALACIONES Cierre Perimetral Con pilar metálico y brazo soldado de 60x60 Malla Urbana Acmafor con 3 portones 6 metros Recinto PAC 001 Valdivia – Dirección de Vialidad Región de Los Ríos.</t>
+          <t>SERVICIO DE ARRIENDO IMPLEMENTACIÓN Y MANTENCIÓN</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>1346284-10-LE26</t>
+          <t>1499887-19-CO26</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
+          <t>SERVICIOS TÉCNICOS DE HABILITACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>1346284-11-LE26</t>
+          <t>1523-123-LE26</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CONTEINER PLEGABLE TRASLADO Y MONTAJE</t>
+          <t>PPTA 127-26 SERVICIO DE TRASLADO PARA PACIENTES DE</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>1348-5-LP26</t>
+          <t>1533460-6-LP26</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN OFICINA REGISTRO CIVIL PURRANQUE</t>
+          <t>SERVICIO DE ARRIENDO DE SISTEMA INFORMÁTICO FINANCIERO CONTABLE Y RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1350296-80-LE26</t>
+          <t>1540667-6-LR26</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE DISPENSADORES DE AGUA PURIFICADA CALIENTE Y FRÍA CON CONEXIÓN A LA RED DE AGUA POTABLE PARA EL HOSPITAL DE ALTO HOSPICIO POR UN PERÍODO DE 24 MESES</t>
+          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
@@ -3743,32 +3743,32 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>1351-6-LP26</t>
+          <t>1549-70-LR26</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO HABILITACIÓN DE OFICINA QUILPUÉ</t>
+          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>1374899-36-LP26</t>
+          <t>1549-85-LE26</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO DE SUMINISTRO DE FÁRMACO PROPOFOL CON BOMBAS DE INFUSIÓN TIVATCI EN COMODATO</t>
+          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
@@ -3783,92 +3783,92 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>1375158-7-LP26</t>
+          <t>1549-90-LP26</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VEINTICUATRO 24 SIERRAS DE AUTOPSIA Y UN 01 PACK EQUIPOS DE REFRIGERACIÓNCONGELACIÓN PARA DEPARTAMENTO DE TANATOLOGÍA DEL NUEVO EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL DE SANTIAGO</t>
+          <t>ARRIENDO DE 14 SILLONES DE HEMODIÁLISIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>1375746-17-LP26</t>
+          <t>1549-92-LP26</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV LEVANTAMIENTO DE INVENTARIO ACTIVO FIJO SLEP </t>
+          <t>HABILITACIÓN UNIDAD DE HOSPITALIZACIÓN DOMICILIARI</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>1391828-8-LE26</t>
+          <t>1555-75-LP26</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Informes Técnicos Destinación Inmuebles y DAA</t>
+          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>1417913-116-LE26</t>
+          <t>1562-57-L126</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPOS TECNOLÓGICOS PARA DEPENDENCIAS DE CORMUDESI</t>
+          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>1417913-119-LE26</t>
+          <t>1562-59-L126</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPAMIENTO PARA LA EJECUCIÓN Y FORTALECIMIENTO DE PROGRAMAS DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
+          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
@@ -3883,92 +3883,92 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>1417913-122-LE26</t>
+          <t>1562-60-LR26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ELEMENTOS DE PROTECCIÓN PERSONAL EPP PARA FUNCIONARIOS Y ESTABLECIMIENTOS DEPENDIENTES DEL DEPARTAMENTO DE SALUD DE CORMUDESI</t>
+          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 12 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>1422824-10-LE26</t>
+          <t>1574-33-LP26</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE CINTAS PARA PRUEBA DEL BIOSENSOR DE CREATININA CON EQUIPO EN COMODATO PARA LA UNIDAD DE IMAGENOLOGÍA COMPLEJA DEL HOSPITAL CARLOS VAN BUREN</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>1422824-25-LP26</t>
+          <t>1574-34-LE26</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>CONTRATO DE SUMINISTRO DE ASAS DE CORTE PARA HISTERO-RESECTOSCOPIA CON EQUIPAMIENTO EN COMODATO PARA EL HOSPITAL CARLOS VAN BUREN</t>
+          <t>CHEE MANT. EMERGENCIA ELQUI REG. COQUIMBO J.I. Y OFICINAS - SC 61183</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>1431841-56-LP26</t>
+          <t>1574-35-LP26</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Sala de Monitoreo y Punto de Cámaras</t>
+          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 2</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>1431841-57-LE26</t>
+          <t>1596-50-LP26</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DEPENDENCIAS OLN COMUNA DE RECOLETA</t>
+          <t>PANTALLA LED PARA EL EDIFICIO DEL GORE MAULE</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
@@ -3983,72 +3983,72 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>1469101-6-LP26</t>
+          <t>1638-91-LE26</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS DE OBRAS DE HABILITACIÓN RFA MACHALI</t>
+          <t>MEJORAMIENTO ACCESO SEDE CENTRO ESTACION DIEGO DE ALMAGRO SM 1245</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>1469-205-L126</t>
+          <t>1643-75-LE26</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO PROVISIÓN E INSTALACIÓN EQUIPOS DE CLIMATIZACIÓN PARA OFICINAS VDE DE LA UNIVERSIDAD DE TALCA</t>
+          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>1469-211-L126</t>
+          <t>1696-15-LE26</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>MATERIAL GRÁFICO, TRASLADO, MONTAJE, INSTALACION, SUPERVISIÓN, DESMONTAJE Y RETIRO PARA UTALCA ABRE PUERTAS 2026, UNIVERSIDAD DE TALCA</t>
+          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>1483330-1-LP26</t>
+          <t>1735-50-LE26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO IMPLEMENTACIÓN Y MANTENCIÓN</t>
+          <t>HABILITACION CEFAM DE CONTINGENCIA 3ra. ETAPA TUB</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
@@ -4063,52 +4063,52 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>1499887-19-CO26</t>
+          <t>1743-69-LP26</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS TÉCNICOS DE HABILITACIÓN DIGITAL</t>
+          <t>Construcción Sede Social Manquehua</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>1523-123-LE26</t>
+          <t>1754-45-LE26</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>PPTA 127-26 SERVICIO DE TRASLADO PARA PACIENTES DE</t>
+          <t>OFICINA TIMBRES DIDÁCTICO MENAJE Y PILAS</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>1533460-6-LP26</t>
+          <t>1947-113-LR26</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE SISTEMA INFORMÁTICO FINANCIERO CONTABLE Y RECURSOS HUMANOS</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE NUTRICIONES PARENTERALES DE DIFERENTES VOLÚMENES CON BAJADAS DE BOMBA DE INFUSIÓN Y EQUIPOS EN COMODATO PARA EL HOSPITAL ROBERTO DEL RÍO CFO</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
@@ -4123,52 +4123,52 @@
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>1540667-6-LR26</t>
+          <t>1969-18-LE26</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>OBRA REMODELACIÓN SERV MED FÍSICA Y REHABILITACIÓN</t>
+          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>1549-70-LR26</t>
+          <t>1973-97-LP26</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 07 MAQUINAS DE ANESTESIA</t>
+          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>1549-85-LE26</t>
+          <t>1979-192-LE26</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE BICICLETERO MEL DEL HSJ</t>
+          <t>175.26 “ARRIENDO DE EQUIPOS PARA PABELLÓN GINECOLOGICO PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
@@ -4183,32 +4183,32 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>1549-90-LP26</t>
+          <t>1987-5-LE26</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE 14 SILLONES DE HEMODIÁLISIS</t>
+          <t>LP ARRIENDO UNID. MODULARES CONTAO RES EX LAGOS 805-2026 17.09.26 I. 22.09.001</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>1555-75-LP26</t>
+          <t>2048-73-LP26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>CORTADOR QUIRURGICO DE VELLO Y COMODATO DE RASURAD</t>
+          <t>Servicio de traslado para pacientes H.A.</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
@@ -4223,72 +4223,72 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>1562-57-L126</t>
+          <t>2078-45-LE26</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN DEL EQUIPO DE FUSIÓN PERL X-3, DEL DEPARTAMENTO LABORATORIOS</t>
+          <t>APRUEBA Y PUBLICA BASES ADMINISTRATIVAS PARA “SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS CONCEPCIÓN Y DELEGACIÓN BIOBIO AMBAS DEPENDIENTE DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO”. SC 283-2026 y 377-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>1562-59-L126</t>
+          <t>2098-122-LP26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN CON COMPRA DE COMPONENTES ESPECIFICOS, PARA EQUIPO ICP-MS 8800, SERIE: JP13150178, DEL DEPARTAMENTO DE LABORATORIOS</t>
+          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>1562-60-LR26</t>
+          <t>2098-147-LE26</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO INFRAESTRUCTURA DE PROCESAMIENTO Y ALMACE</t>
+          <t>MODIFICACION REPARACION Y HABILITACION DE ESPACIOS SERVICIO DE KINESIOLOGIA</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>score 12 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>1574-33-LP26</t>
+          <t>2102-31-LE26</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 1</t>
+          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
@@ -4296,23 +4296,23 @@
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 10 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>1574-34-LE26</t>
+          <t>2107-144-LP26</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>CHEE MANT. EMERGENCIA ELQUI REG. COQUIMBO J.I. Y OFICINAS - SC 61183</t>
+          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
@@ -4323,72 +4323,72 @@
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>1574-35-LP26</t>
+          <t>2111-231-LE26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>SCHEE - CONTRATO SUMINISTRO MANTENCION J.I. Y OFICINAS PROVINCIA DE ELQUI ZONA 2</t>
+          <t>ARRIENDO DE EQUIPOS DE MONITORIZACION PARA UTI</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>1575-14-LE26</t>
+          <t>2111-270-LP26</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>MANTENCION DE OFICINAS</t>
+          <t>MANTAS TÉRMICAS CON EQUIPO EN COMODATO III</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>1596-50-LP26</t>
+          <t>2111-282-LP26</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>PANTALLA LED PARA EL EDIFICIO DEL GORE MAULE</t>
+          <t>FRESAS NEUROCIRUGÍA Y COLUMNA EQUIPO COMODATO III</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>1643-75-LE26</t>
+          <t>2126-139-LR26</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO EQUIP. PARA ATENCION DE DONANTES CON DONA</t>
+          <t>Convenio de Suministro de Hemodiálisis con Arriendo de Equipamiento para el Hospital San Pablo de Coquimbo</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
@@ -4403,52 +4403,52 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>1657-17-L126</t>
+          <t>2179-14-LE26</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>EVALUACIÓN Y SUPERVISIÓN DE CENTROS DE TRATAMIENTO Y REHABILITACIÓN EN CONSUMO PROBLEMÁTICO DE SUSTANCIAS DE LA REGIÓN DE COQUIMBO, CONVENIO SENDA-MINSAL</t>
+          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 9 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>1696-15-LE26</t>
+          <t>2258-210-LR26</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>Servicio de mantención del sistema de alarmas de incendio en edificios de Blanco Encalada N° 945 y General Lagos N° 766 Arica</t>
+          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>1735-50-LE26</t>
+          <t>2273-58-LE26</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION CEFAM DE CONTINGENCIA 3ra. ETAPA TUB</t>
+          <t>REHABILITACIÓN SKATE PARK LO MARTÍNEZ</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
@@ -4463,16 +4463,16 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>1743-69-LP26</t>
+          <t>2279-56-LE26</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Social Manquehua</t>
+          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
@@ -4483,172 +4483,172 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>1754-45-LE26</t>
+          <t>2279-66-LE26</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>OFICINA TIMBRES DIDÁCTICO MENAJE Y PILAS</t>
+          <t>SP 754 Servicio de Arriendo de Bodegas</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>1810-3-LE26</t>
+          <t>2287-25-LP26</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN MEJORAMIENTO MANTENCIÓN COD. E1O2RT9</t>
+          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>1894-25-LP26</t>
+          <t>2324-115-LE26</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>DVO-ARRIENDO MOTONIVELADORAS VARIOS CAMINOS</t>
+          <t>LICITACIÓN PÚBLICA N° 96 2026 SERVICIO PLAN DE MANTENCIÓN SISTEMA DE CALEFACCIÓN Y SISTEMA DE RED DE INCENDIO CASA PAULY – DIRECCIÓN DE OPERACIONES</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>1947-113-LR26</t>
+          <t>2343-31-LE26</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE NUTRICIONES PARENTERALES DE DIFERENTES VOLÚMENES CON BAJADAS DE BOMBA DE INFUSIÓN Y EQUIPOS EN COMODATO PARA EL HOSPITAL ROBERTO DEL RÍO CFO</t>
+          <t>REMODELACION DE OFICINAS EN PARQUE O´HIGGINS</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>1947-157-LE26</t>
+          <t>2345-117-LP26</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>244 ADQUISICIÓN DE REACTIVOS DE TINCIÓN DE GRAM CON EQUIPO EN COMODATO PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RIO CFO</t>
+          <t>ARRIENDO Y MANTENCIÓN DE EQUIPOS PSICOTÉCNICOS Y SENSOMÉTRICOS PARA LA MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 14 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>1947-168-LE26</t>
+          <t>2345-139-LR26</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE MONITORES DE SIGNOS VITALES PARA EL HOSPITAL DE NIÑOS DR. ROBERTO DEL RÍO GRS</t>
+          <t>Mantención Preventiva y Correctiva Reparaciones Mejoras y Urgencias de los Sistemas Eléctricos en los Inmuebles</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>1969-18-LE26</t>
+          <t>2369-69-LP26</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SALA DE VENTAS MODULAR PARA CET YUMBEL</t>
+          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>1973-97-LP26</t>
+          <t>2369-72-LP26</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE CASILLEROS AUTOATENCIÓN MEDICAMENTOS</t>
+          <t>PP 45 Construcc. sede social Chile III</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>1979-192-LE26</t>
+          <t>2378-110-LP26</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>175.26 “ARRIENDO DE EQUIPOS PARA PABELLÓN GINECOLOGICO PARA NODO COSTERO: HOSPITAL NVA IMPERIAL.”</t>
+          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
@@ -4663,52 +4663,52 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>1987-5-LE26</t>
+          <t>2402-85-L126</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>LP ARRIENDO UNID. MODULARES CONTAO RES EX LAGOS 805-2026 17.09.26 I. 22.09.001</t>
+          <t>SERVICIO DE TRASLADO RANCAGUA - VIÑA DEL MAR - RANCAGUA</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>score 17 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>2020-19-LE26</t>
+          <t>2405-108-LR26</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>SERVICIOS MULTITÉCNICOS DE MANTENCIÓN DE OFICINAS</t>
+          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>2048-73-LP26</t>
+          <t>2409-98-L126</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>Servicio de traslado para pacientes H.A.</t>
+          <t>SERVICIO TRASLADO ALUMNAS A JORNADAS REFLEXION, ESCUELA D-926</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
@@ -4723,32 +4723,32 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>2078-45-LE26</t>
+          <t>2429-8-LP26</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>APRUEBA Y PUBLICA BASES ADMINISTRATIVAS PARA “SERVICIOS DE TRANSPORTE PARA TRASLADO DE FUNCIONARIOS DE LA UNIDAD DE ZOONOSIS CONCEPCIÓN Y DELEGACIÓN BIOBIO AMBAS DEPENDIENTE DE LA SEREMI DE SALUD REGIÓN DEL BIOBIO”. SC 283-2026 y 377-2026</t>
+          <t>RENOVACIÓN DE INFRAESTRUCTURA DE RED INFORMÁTICA Y NORMALIZACIÓN DE CABLEADO ESTRUCTURADO DE LAS DEPENDENCIAS DE LA IMA</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>2098-122-LP26</t>
+          <t>2430-59-LP26</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO ARRIENDO UPS DE 200 KVA</t>
+          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
@@ -4763,16 +4763,16 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>2098-139-LE26</t>
+          <t>2430-68-LR26</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>CONVENIO SUMINISTRO BOLSAS DE ASPIRACIÓN PARA REPOSICIÓN BODEGA FOLIO PAC 200 – PARA UN PERIODO DE 18 MESES</t>
+          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
@@ -4783,36 +4783,36 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>2102-31-LE26</t>
+          <t>2430-77-LP26</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>NORMALIZACION BODEGAS DE FARMACIA Y ECONOMATO</t>
+          <t>MEJORAMIENTO SEDE SOCIAL EL ANCLA ANTOFAGASTA CÓDIGO BIP N°40073719-0</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>2107-144-LP26</t>
+          <t>2430-78-LP26</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>SUMINISTRO DE IMPLANTES QUIRURGICOS Y ADITAMENTOS PROTESICOS IMPLANTOLOGICOS PARA DEPARTAMENTO ODONTOESTOMATOLOGIA</t>
+          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
@@ -4823,176 +4823,176 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>2111-231-LE26</t>
+          <t>2445-115-LE26</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO DE EQUIPOS DE MONITORIZACION PARA UTI</t>
+          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 6 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>2111-270-LP26</t>
+          <t>2446-243-LP26</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>MANTAS TÉRMICAS CON EQUIPO EN COMODATO III</t>
+          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>2111-282-LP26</t>
+          <t>2446-257-LE26</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>FRESAS NEUROCIRUGÍA Y COLUMNA EQUIPO COMODATO III</t>
+          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>2179-14-LE26</t>
+          <t>2446-260-LR26</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>CONV. DE PRECIOS SERV. DE TRASLADO PERSONAL TEMUCO</t>
+          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>score 9 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>2205-14-LE26</t>
+          <t>2446-266-LP26</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>GAS MEDICINAL Y ARRIENDO DE CILINDROS</t>
+          <t>MANTENCIÓN CASA MAC AULIFFE</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>2258-175-LR26</t>
+          <t>2446-271-LR26</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>TEST MOLECULARES CON ENTREGA DE EQUIPOS EN COMODATO PARA LA UNIDAD DE LABORATORIO CLÍNICO</t>
+          <t>REHABILITACION CASA DE LA CULTURA</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>2258-37-LR26</t>
+          <t>2448-133-LE26</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>TEST REPORTADO QUIMICA INMUNOLOGIA SEROLOGIA HORMONAS HEMATOLOGIA GASOMETRIA EN EQUIPOS EN COMODATO</t>
+          <t>HABILITACION OFICINA MODULAR CECOSF PUNTA MIRA</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>2273-58-LE26</t>
+          <t>2455-46-LP26</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACIÓN SKATE PARK LO MARTÍNEZ</t>
+          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>2279-56-LE26</t>
+          <t>2460-108-LE26</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>SP 567 ADQUISICION E INSTALACION DE MODULOS DE OFICINA</t>
+          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
@@ -5003,52 +5003,52 @@
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>2279-66-LE26</t>
+          <t>2467-100-L126</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>SP 754 Servicio de Arriendo de Bodegas</t>
+          <t>NUEVO LLAMADO ADQUISICIÓN CON INSTALACION DE CORTINAS ROLLER DOBLE BLACKOUT  SCREEN PARA TERCER PISO EDIFICIO CONSISTORIAL</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>score 19 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>2282-97-LR26</t>
+          <t>2494-79-LP26</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>PP 192-2025 ARRIENDO DE SISTEMA PARA LA GESTIÓN DE</t>
+          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 13 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>2287-25-LP26</t>
+          <t>2565-15-LR26</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN PLAZAS 1 Y 3 PASAJE 9 BARRIO CAUPOLI</t>
+          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
@@ -5063,16 +5063,16 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>2313-5-LE26</t>
+          <t>2581-36-LE26</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Servicios de Conservación de Edificio Terminal</t>
+          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
@@ -5083,192 +5083,192 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>2322-82-LE26</t>
+          <t>2585-119-LE26</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de teléfonos IP para dependencias Municipales</t>
+          <t>ADQ. SERV TRASLADO TERRESTRE NAC DIDECO ORD N°3042 IMA CRC</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>2324-112-LE26</t>
+          <t>2591-106-LR26</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 107 2026 SERVICIO ARRIENDO DE 3 EQUIPOS STARLINK MINI O EQUIVALENTE PLAN ITINERANTE ADAPTADOR USB-C Y BATERÍA EXTERNA POR 36 MESES.-   </t>
+          <t>REPOSICION OFICINA SRCEI POZO ALMONTE</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>2332-70-LE26</t>
+          <t>2600-29-LE26</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>CS DE ARRIENDO DE APLICACION DE AGENDA VIRTUAL</t>
+          <t>Const. accesibilidad universal Edificio Municipal</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>2345-117-LP26</t>
+          <t>2627-18-LR26</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO Y MANTENCIÓN DE EQUIPOS PSICOTÉCNICOS Y SENSOMÉTRICOS PARA LA MUNICIPALIDAD DE LAS CONDES</t>
+          <t>MEJORAMIENTO RECINTO CLUB DEPORTIVO INTERSPORTING</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>2369-69-LP26</t>
+          <t>2667-39-LR26</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>PP 44 Construcc. sede social Villa Santa Maria</t>
+          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 11 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>2369-72-LP26</t>
+          <t>2667-71-LR26</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>PP 45 Construcc. sede social Chile III</t>
+          <t>ARRIENDO SOPORTE Y MANTENCIÓN DE CENTRAL TELEFONICA IP TELEFONOS IP Y PLATAFORMA DE CONTACT CENTER</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>2378-110-LP26</t>
+          <t>2667-90-LE26</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO YO  MANTENCIÓN DE BAÑOS QUIMICOS</t>
+          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>2385-53-LE26</t>
+          <t>2687-16-CO26</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE CARGADOR FRONTAL CON OPERADOR</t>
+          <t>REPOSICIÓN DE VENTANAS TERMOPANEL ESCUELA BÁSICA RURAL EL YECO</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>score 14 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>2405-108-LR26</t>
+          <t>2723-61-LR26</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION Y URBANIZACION LOTEO ALTOS</t>
+          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>2409-96-L126</t>
+          <t>2732-34-LP26</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADO PARA ALUMNAS TALLER DE EXTRAESCOLAR Y JORNADAS DE REFLEXION PARA ESCUELA D-953</t>
+          <t>Serv. Arriendo de Baños Químicos Ferias Libres</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
@@ -5283,56 +5283,56 @@
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>2409-97-L126</t>
+          <t>2733-18-LE26</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TRASLADOS INTERNOS PARA ESCUELA D-934</t>
+          <t>Serv.habilitación Sala Sensorial-Liceo Peñaflor</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>2409-98-L126</t>
+          <t>2760-112-LE26</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO TRASLADO ALUMNAS A JORNADAS REFLEXION, ESCUELA D-926</t>
+          <t>REPARACION DE CUBIERTA Y HABILITACIÓN DE OFICINAS DE LA DIRECCIÓN DE SEGURIDAD PÚBLICA</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>2410-41-LE26</t>
+          <t>2760-113-LE26</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de máquinas de oficina </t>
+          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PMU 2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
@@ -5343,16 +5343,16 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>2426-41-LE26</t>
+          <t>2760-115-LE26</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>Obras de reforzamiento edificio Nasro Maluk</t>
+          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PRO EMPLEO</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
@@ -5363,16 +5363,16 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>2426-44-LE26</t>
+          <t>2794-22-LR26</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>CIERRE PERIMETRAL Y MEJ ACERA PARA SEDE SOCIAL</t>
+          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
@@ -5383,76 +5383,76 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>2428-70-LP26</t>
+          <t>2817-63-LE26</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO DE OFICINA MOVIL -SOCIAL</t>
+          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>score 22 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>2429-8-LP26</t>
+          <t>2831-37-LE26</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN DE INFRAESTRUCTURA DE RED INFORMÁTICA Y NORMALIZACIÓN DE CABLEADO ESTRUCTURADO DE LAS DEPENDENCIAS DE LA IMA</t>
+          <t>SERVICIO DE VENTA DE ENTRADAS EXPO QTA</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>2430-59-LP26</t>
+          <t>2905-42-LP26</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>P.M.U. “HABILITACIÓN ZONA DE JUEGOS PARQUE NICOLÁS TIRADO ANTOFAGASTA”</t>
+          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>2430-68-LR26</t>
+          <t>2920-38-LP26</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO INTEGRAL PLAZA SOTOMAYOR Y LOCALES COMERCIALES COMUNA DE ANTOFAGASTA</t>
+          <t>Construcción Sede Juventud Robinsoniana.</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
@@ -5463,12 +5463,12 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>2430-77-LP26</t>
+          <t>2950-44-LP26</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL EL ANCLA ANTOFAGASTA CÓDIGO BIP N°40073719-0</t>
+          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
@@ -5483,16 +5483,16 @@
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>2430-78-LP26</t>
+          <t>299-17-LP26</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>CONSERVACIÓN SEDE SOCIAL RUBÉN INFANTA ANTOFAGASTA CÓDIGO BIP N°40073072-0</t>
+          <t>E102RT9BRANDING Y ORNAMENTACION RECINTOS LOS RIOS</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
@@ -5503,36 +5503,36 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>2445-115-LE26</t>
+          <t>2997-58-LE26</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIONES VARIAS PARA CESFFAM COLON SP 842</t>
+          <t>Habilitación Espacio Deportivo Chañaral alto</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 8 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>2446-243-LP26</t>
+          <t>3015-56-LP26</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>CONSULTORÍA DISEÑO MUSEO COQUIMBO CASA GALLEGUILLO</t>
+          <t>MEJ ACCESIBILIDAD Y ENTORNO SEDE SOCIAL TERRAVIDA</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
@@ -5543,56 +5543,56 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>2446-257-LE26</t>
+          <t>3085-64-L126</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CASA GALLEGUILLOS</t>
+          <t>REPARACIÓN DE TECHUMBRE, INSTALACIÓN DE PUERTA Y VENTANA A LOGIA EN VIVIENDA FISCAL</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>2446-260-LR26</t>
+          <t>3085-65-L126</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licitación Pública N°4102026 “MEJORAMIENTO EDIFICIO CONSISTORIAL BILBAO”.                                                                                                                                                                                     </t>
+          <t>SERVICIO DE PROVISIÓN E INSTALACIÓN DE VENTANAS TERMOPANEL 04 VIVIENDAS FISCALES</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>2446-266-LP26</t>
+          <t>3117-88-LE26</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>MANTENCIÓN CASA MAC AULIFFE</t>
+          <t>OFICINA Y BODEGA MODULAR C.R. LAS SALINAS</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
@@ -5603,172 +5603,172 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>2446-271-LR26</t>
+          <t>3160-3-LE26</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>REHABILITACION CASA DE LA CULTURA</t>
+          <t>SERVICIO DE CAMBIO DE TECHUMBRE DEL EDIFICIO COMMILDIRUNO</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>2448-133-LE26</t>
+          <t>3160-4-LE26</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINA MODULAR CECOSF PUNTA MIRA</t>
+          <t>SERVICIO DE INSTALACIÓN DE TERMOPANEL EDIFICIO DIRECCIONES UNO</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>2455-46-LP26</t>
+          <t>3210-11-L126</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN SISTEMA DE TELEVIGILANCIA</t>
+          <t>SERVICIO DE EXÁMENES DE FONDO DE OJO PARA USUARIOS DEL DEPARTAMENTO DE SALUD SAN RAFAEL</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>2460-108-LE26</t>
+          <t>324-48-LP26</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>Adquisición de Material Bibliográfico para Sedes del Departamento Bibliotecas - SBC N° 1.061</t>
+          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>2460-121-LE26</t>
+          <t>3328-100-L126</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoras de pisos en Recintos Municipales </t>
+          <t>ASB/PROVISIÒN E INSTALACIÒN DE VENTANAS TIPO TERMOPANEL CRT</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>2467-100-L126</t>
+          <t>3355-9-LP26</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>NUEVO LLAMADO ADQUISICIÓN CON INSTALACION DE CORTINAS ROLLER DOBLE BLACKOUT  SCREEN PARA TERCER PISO EDIFICIO CONSISTORIAL</t>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPAMIENTO HIDROELÉCTRICO Y SERVICIO DE RECUPERACIÓN HABILITACIÓN Y PUESTA EN MARCHA DE LA MICRO CENTRAL ELÉCTRICA DEL REFUGIO MILITAR LOS BARROS </t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>2483-242-CO26</t>
+          <t>3480-20-LE26</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+          <t>Revestimiento exterior con metal siding y ventana</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>2494-79-LP26</t>
+          <t>3525-8-LR26</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO OFICINA LOCAL DE LA NIÑEZ COYHAIQUE</t>
+          <t>Sum e instalación de taludes visita terreno volun</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>score 13 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>2565-15-LR26</t>
+          <t>3542-23-LE26</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REACTIVOS DE QUIMICA Y HORMONAS CON EQUIPO EN COMODATO PARA LABORATORIO DEL CESFAM DE CHEPICA</t>
+          <t xml:space="preserve">ARRIENDO DE EXCAVADORA 20 TON SIN OPERADOR </t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
@@ -5783,16 +5783,16 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>2581-36-LE26</t>
+          <t>3542-26-LE26</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN MÁQUINA TRITURADORA MULTIPROPÓSITO PARA EL DEPARTAMENTO DE MEDIOAMBIENTE</t>
+          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
@@ -5803,56 +5803,56 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>2582-53-LR26</t>
+          <t>359-107-LE26</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>CONCESIÓN ESPACIOS VENTA DE SOAP 2027-2029</t>
+          <t>ROCURONIO BROMURO CON COMODATO DE EQUIPO</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>2585-119-LE26</t>
+          <t>3624-32-LP26</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>ADQ. SERV TRASLADO TERRESTRE NAC DIDECO ORD N°3042 IMA CRC</t>
+          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>2591-106-LR26</t>
+          <t>3624-33-LP26</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>REPOSICION OFICINA SRCEI POZO ALMONTE</t>
+          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
@@ -5863,12 +5863,12 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>2591-156-B226</t>
+          <t>3678-22-LE26</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO SEDE SOCIAL J.V.  N 1 P.ALMONTE</t>
+          <t>CONSTRUCCIÓN SEDE SOCIAL SECTOR MEDIA LUNA LAS PALMAS COMUNA DE PETORCA</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
@@ -5883,16 +5883,16 @@
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>2600-26-LR26</t>
+          <t>3693-158-LP26</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>Concesión Servicio de Estacionamiento Regulados en la vía Pública de Parral</t>
+          <t>CONSTRUCCIÓN SEDE JUNTA DE VECINOS VILLA ALTOS DE ZAÑARTU COMUNA DE EL QUISCO CÓDIGO BIP 40076595-0</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
@@ -5903,12 +5903,12 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>2600-29-LE26</t>
+          <t>3708-39-LE26</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>Const. accesibilidad universal Edificio Municipal</t>
+          <t>SUMINISTRO DE ALARMAS PARA DEPENDENCIAS</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
@@ -5923,76 +5923,76 @@
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>2627-18-LR26</t>
+          <t>3708-40-LE26</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO RECINTO CLUB DEPORTIVO INTERSPORTING</t>
+          <t>HABILITACION OFICINAS TRANSITO OBRAS Y OTRAS</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>2667-39-LR26</t>
+          <t>3761-21-LE26</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN NUEVO EDIFICIO 37° COMISARIA DE VITACURA</t>
+          <t>Desarme Limpieza e Inhabilitación de Terreno Campamento Los Leones Comuna de Coelemu</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>score 11 &lt; 30</t>
+          <t>score 15 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>2667-71-LR26</t>
+          <t>3775-33-LE26</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>ARRIENDO SOPORTE Y MANTENCIÓN DE CENTRAL TELEFONICA IP TELEFONOS IP Y PLATAFORMA DE CONTACT CENTER</t>
+          <t>SERV. ARRIENDO EXCAVADORA Y 2 MOTOBOMBAS HIJUELAS</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>2667-83-LE26</t>
+          <t>3798-19-LR26</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Banquetearía y Producción con Recinto Incluido para Ceremonia Día del Profesor y Asistentes de la Educación de los Colegios Municipales de Vitacura Año 2026</t>
+          <t>ADQUISICIÓN DE TERRENO DE INFRAESTRUCTURA PÚBLICA</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
@@ -6003,52 +6003,52 @@
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>2667-90-LE26</t>
+          <t>3847-41-LE26</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE PUNTOS DE CÁMARAS EN RECINTOS MUNICIPALES DE LA COMUNA DE VITACURA</t>
+          <t>DISEÑO PLAN MAESTRO PARQUE URBANO BAQUEDANO</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>2687-16-CO26</t>
+          <t>3885-51-LP26</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>REPOSICIÓN DE VENTANAS TERMOPANEL ESCUELA BÁSICA RURAL EL YECO</t>
+          <t xml:space="preserve">AMPLIACION OFICINA DE FINANZAS ILUSTRE MUNICIPALIDAD DE PICA </t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>2710-55-LE26</t>
+          <t>3908-44-LE26</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO TOTEM</t>
+          <t>HABILITACIÓN Y SEÑALIZACIÓN PLAZOLETA RENÉ PINEDA Y MEJORAMIENTO PLAZA POBLACIÓN NUEVO VIVIR COMUNA DE RENAICO</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
@@ -6063,52 +6063,52 @@
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>2723-61-LR26</t>
+          <t>3938-39-L126</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>Concesión Estacionamientos Calles Comuna de Buin</t>
+          <t>CONTRATACION DE SERVICIO DE TRASLADO DE AGRICULTORES PARA 11 ACCIONES FORMATIVAS - PDTI CURARREHUE</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>2732-34-LP26</t>
+          <t>3963-16-LP26</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>Serv. Arriendo de Baños Químicos Ferias Libres</t>
+          <t>Mej. Sede y Multicancha Pobl.Juan Gonzalez Peumo</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>2733-18-LE26</t>
+          <t>3994-29-LR26</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>Serv.habilitación Sala Sensorial-Liceo Peñaflor</t>
+          <t>CONST. SEDE Y ESPACIO COMUNITARIO GULTRO ORIENTE</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
@@ -6116,39 +6116,39 @@
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>score 8 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>2760-113-LE26</t>
+          <t>4037-64-LE26</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PMU 2026</t>
+          <t>SERVICIO REGULARIZACION Y HABILITACION SALA APICOLA</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>2760-115-LE26</t>
+          <t>4037-66-LE26</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN CASACAS DE TRABAJO PERSONAL PRO EMPLEO</t>
+          <t xml:space="preserve">SERV. LIMPIEZA PROGRAMA CANONES LIMPIOS CASAS </t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
@@ -6163,16 +6163,16 @@
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>2794-22-LR26</t>
+          <t>4063-1-LP26</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>Adquisicion de Terreno para Medio Ambiente L.A.</t>
+          <t>CONSTRUCCIÓN SEDE CLUB COLO COLO DE CUYÁN MARIQUINA</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
@@ -6183,72 +6183,72 @@
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>2817-63-LE26</t>
+          <t>4099-25-LE26</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>MEJ. OFICINA SEC. MUNICIPAL Y SALA DE CONCEJO</t>
+          <t>Servicio de Arriendo de Gestor Documental</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>2831-37-LE26</t>
+          <t>411-43-CO26</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VENTA DE ENTRADAS EXPO QTA</t>
+          <t>CONSTRUCCIÓN BODEGA MUNICIPAL SECTOR LA HUERTA</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>2905-42-LP26</t>
+          <t>4160-14-LP26</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>Habilitación Oficinas Municipales Calle Alberto C</t>
+          <t>CONSTRUCCION SEDE SOCIAL JJVV LOS NOTROS HUALPEN</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>2906-18-LE26</t>
+          <t>418-57-LP26</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO ESPACIO RADIAL 2026-2027</t>
+          <t>SERV. ARRIENDO DE ENDOSCOPIOS Y COLONOSCOPIOS HPA</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
@@ -6263,56 +6263,56 @@
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>2920-38-LP26</t>
+          <t>425-57-LR26</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>Construcción Sede Juventud Robinsoniana.</t>
+          <t>SERVICIO DE INSPECCIÓN TÉCNICA PARA LA HABILITACIÓN DEL CENTRO DE JUSTICIA DE TEMUCO - TRIBUNAL DE FAMILIA CIVILES 1° 2° Y 3° JUZGADO DE LETRAS Y DE FAMILIA Y JUZGADO DE LETRAS DEL TRABAJO</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>2950-44-LP26</t>
+          <t>425-66-LP26</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>REPARACIÓN TECHUMBRE Y AZOTEAS DEL EDIFICIO HABITABILIDAD ESCUELA NAVAL ARTURO PRAT</t>
+          <t>Servicio de Habilitación Fiscalía Judicial</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>2974-71-L126</t>
+          <t>4295-67-LP26</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE TALA DE ÁRBOL EN CASA DE HUESPEDES TANTAUCO (512/2026)</t>
+          <t>Servicio de enlace de datos voz IP y CCTV para oficinas remotas</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
@@ -6323,156 +6323,156 @@
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>2974-73-L126</t>
+          <t>4295-82-LP26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
         <is>
-          <t>(DIS) PROVISIÓN E INSTALACIÓN DE CHAPA Y PERILLÓNES PARA EL INMUEBLE DE CAMINO LA VIÑA N° 12.130(535/2026)</t>
+          <t>ARRIENDO INSTALACIÓN Y MANTENCIÓN DE GABINETES PSICOTÉCNICOS 2026-2029</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>2981-235-LP26</t>
+          <t>4309-233-LP26</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN MODULARES CECAPRO 2027</t>
+          <t>CONVENIO SUMINISTRO PARA EXÁMENES DE COAGULACIÓN CON EQUIPAMIENTO EN COMODATO 2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>2981-236-LR26</t>
+          <t>4328-33-B226</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>DEINFRA - HABILITACIÓN CECAPRO 2027 COD. BIP 40081088-0</t>
+          <t>ADQUISICIÓN TERRENO TIUQUILEMU</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>299-17-LP26</t>
+          <t>439-26-LP26</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>E102RT9BRANDING Y ORNAMENTACION RECINTOS LOS RIOS</t>
+          <t>HABILITACIÓN DE PATIOS RECREATIVOS ESCUELA MEC</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>2992-49-LE26</t>
+          <t>4451-102-LE26</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
         <is>
-          <t>habilitación sombra retractil en patio escuela</t>
+          <t>Reparación de cubiertas de edificio Polideportivo</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>3015-52-LE26</t>
+          <t>4494-64-LP26</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN DE DESAGÜES EN SECTORES DE LA CRUZ</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES LIRQUEN</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>score 10 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>3015-56-LP26</t>
+          <t>4494-65-LP26</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
         <is>
-          <t>MEJ ACCESIBILIDAD Y ENTORNO SEDE SOCIAL TERRAVIDA</t>
+          <t>REHABILITACION VIAL INCENDIOS FORESTALES PENCO</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>3016-52-LE26</t>
+          <t>45-45-LR26</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
         <is>
-          <t>Servicio de Suministro Trofeos Galvanos Placas y Otros para Actividades Municipales del Área de Gestión Municipal Departamento de Salud y Departamento de Educación</t>
+          <t>SERVICIO DE SEGURIDAD FISICA PARA DEPENDENCIAS DEL SENCE NIVEL CENTRAL Y DIRECCION REGIONAL METROPOLITANA</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
@@ -6483,152 +6483,152 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>3047-54-LE26</t>
+          <t>4631-19-LP26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS DE RED Y ACCESORIOS PARA DEPARTAMENTO INFORMATICA</t>
+          <t>CONSULTORÍA PLAN MAESTRO VIDEOVIGILANCIA L12-26</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 28 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>3084-31-LE26</t>
+          <t>4686-30-LE26</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t>Servicio de arrendamiento de bodegas</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 19 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>3117-88-LE26</t>
+          <t>4803-29-LP26</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
         <is>
-          <t>OFICINA Y BODEGA MODULAR C.R. LAS SALINAS</t>
+          <t>SERVICIOS PROFESIONALES Y ARRIENDO DE EQUIPAMIENTO</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>3160-3-LE26</t>
+          <t>4967-35-LP26</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE CAMBIO DE TECHUMBRE DEL EDIFICIO COMMILDIRUNO</t>
+          <t>CONVENIO DE SUMINISTRO DE CÁNULAS DE ALTO FLUJO CON EQUIPO EN COMODATO</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>3210-11-L126</t>
+          <t>5048-51-O126</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE EXÁMENES DE FONDO DE OJO PARA USUARIOS DEL DEPARTAMENTO DE SALUD SAN RAFAEL</t>
+          <t>AIF TRES VENTANAS TRAMO 2</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>324-48-LP26</t>
+          <t>507428-115-LP26</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
         <is>
-          <t>HABILITACION OFICINAS DIRECCION DE TRÁNSITO</t>
+          <t>ADQUISICIÓN DE EQUIPOS DE REHABILITACIÓN NHA</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>score 16 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>3290-8-LE26</t>
+          <t>5240-102-LR26</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
         <is>
-          <t>HABILITACIÓN CTER PDI TEMUCO</t>
+          <t>CONTRATACIÓN DEL SERVICIO DE TRASLADO Y APOYO LOGÍSTICO DEL SEMINARIO INTERNACIONAL AÑO 2026 DE LA ESCUELA DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>score 6 &lt; 30</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>3328-100-L126</t>
+          <t>528208-35-LP26</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
         <is>
-          <t>ASB/PROVISIÒN E INSTALACIÒN DE VENTANAS TIPO TERMOPANEL CRT</t>
+          <t>HABILITACIÓN DE CRUCE SEMAFORIZADO EN CALLES SALVADOR GUTIÉRREZ - RESBALÓN - FANALOZA</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
@@ -6643,12 +6643,12 @@
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>3355-9-LP26</t>
+          <t>5349-90-LR26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE EQUIPAMIENTO HIDROELÉCTRICO Y SERVICIO DE RECUPERACIÓN HABILITACIÓN Y PUESTA EN MARCHA DE LA MICRO CENTRAL ELÉCTRICA DEL REFUGIO MILITAR LOS BARROS </t>
+          <t>SERVICIOS DE TRANSPORTE INTERURBANO DE LOCOMOCIÓN COLECTIVA PARA TRASLADO DE PACIENTES Y FUNCIONARIOS DEL HOSPITAL</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
@@ -6663,152 +6663,152 @@
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>3384-20-LP26</t>
+          <t>539119-90-LE26</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
         <is>
-          <t>Arriendo de 28 estaciones de trabajo para el IGM</t>
+          <t>PROYECTO DE ADQUISICIÓN INSTALACIÓN Y PUESTA EN MARCHA DE TOBOGÁN PARA PISCINAS DE LA COMISIÓN ADMINISTRATIVA CLUB DE CAMPO CUMBRES ADMINISTRADO POR EL DEPARTAMENTO RECREACIONAL Y GASTRONÓMICO B.1. DE LA DIRECCIÓN DE BIENESTAR DE CARABINEROS</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>3474-53-LE26</t>
+          <t>5420-22-LP26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE ARRIENDO Y MANT. MAQUINAS FOTOCOPIADO</t>
+          <t>Arriendo de enlace de voz y datos</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 16 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>3525-8-LR26</t>
+          <t>547640-16-L126</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
         <is>
-          <t>Sum e instalación de taludes visita terreno volun</t>
+          <t xml:space="preserve">MEJORAMIENTO Y HABILITACIÓN CASA DE SALUD MENTAL </t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 17 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>3542-23-LE26</t>
+          <t>548874-70-LR26</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO DE EXCAVADORA 20 TON SIN OPERADOR </t>
+          <t>SERV MULTIBAM SUCURSALES Y GOBIERNOS EN TERRENO</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>3542-26-LE26</t>
+          <t>5510-7-LR26</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REMODELACIÓN DE OFICINAS DEL TALLER DE MANTENIMIENTO</t>
+          <t>HABILITACIÓN CAFETERÍA ZÓCALO TORRE JEA - FCFM</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>3587-20-LE26</t>
+          <t>5590-2-LE26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN MANTENIMIENTO PREVENTIVO CORRECTIVO Y SOPORTES PARA EQUIPOS RADIOCOMUNICACIONES DEPARTAMENTO DE SALUD MUNICIPAL</t>
+          <t>Habilitación de Laboratorio FIRC</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>359-106-LE26</t>
+          <t>5596-5-LP26</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
         <is>
-          <t>CISTOSCOPIOS FLEXIBLES CON EQUIPOS EN COMODATO.</t>
+          <t>INVENTARIO PATRIMONIO CULTURAL INMUEBLE AYP.</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>score 0 &lt; 30</t>
+          <t>score 26 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>359-107-LE26</t>
+          <t>564953-71-LP26</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
         <is>
-          <t>ROCURONIO BROMURO CON COMODATO DE EQUIPO</t>
+          <t>HABILITACIÓN FARMACIA COMUNAL COLON</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
@@ -6823,96 +6823,96 @@
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>3624-32-LP26</t>
+          <t>568658-43-LR26</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN CASA DE LA CULTURA NOGALES</t>
+          <t xml:space="preserve">COMODATO DE EQUIPAMIENTO MICROBIOLOGIA </t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
+          <t>score 0 &lt; 30</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>3624-33-LP26</t>
+          <t>5839-6-LR26</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO CASA DE LA CULTURA EL MELÓN</t>
+          <t>Suministro Test reportado y Eq. comodato B. Sangre</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>solo mencion de inmueble, sin servicio inmobiliario</t>
